--- a/Översikt BORGHOLM.xlsx
+++ b/Översikt BORGHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45029</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>44704</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45433</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>44903</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45903</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>46254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44809</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>44523</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>45107</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44781</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>45161</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>45146</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45918</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>45930</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45918</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>45736</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>46220</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>44638</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45175</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>45926</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>46188</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>45027</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>46224</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>44704</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45478</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>46188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>46224</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>44482</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>44459</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>46169</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>46169</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>45736</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44973</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>46188</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>44953</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>45442</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>44704</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>44704</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44783</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45887</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>45911</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>44781</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>44837</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>46188</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>46185</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>46105</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>46223</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>45796</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>46105</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>46188</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         <v>46223</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>44623</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>44711</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>45994</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>45994</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>46169</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>44840</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>46070</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>46203</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>45758</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>46203</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>44725</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44865</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>44649</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>46203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>46203</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>44772</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>44781</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45084</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>45273</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>45084</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>45902</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>44984</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>44776</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>46041</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>45433</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>46059</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>46069</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>46073</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>46185</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>46196</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>46197</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>45385</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>46246</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>45439</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>45820</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>45820</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>45111</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>45903</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>46185</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>46196</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12121,7 +12121,7 @@
         <v>46197</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>46246</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>44783</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>44747</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>44840</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>44783</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>44501</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>44477</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>44742</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>44503</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>44951</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>44642</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>45280</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>45621</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>45323</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>45125</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>44776</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>45670</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>45903</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>45713</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13680,7 +13680,7 @@
         <v>45671</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>45923</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>45928</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>45713</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45569</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>45812</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         <v>45348</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
         <v>46169</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>46169</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>45125</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>45330</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>44796</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>45005</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>46070</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>45264</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45385</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>44467</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>44953</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15019,7 +15019,7 @@
         <v>46196</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>46196</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>46105</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>46105</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>46105</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>46197</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>44795</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>46203</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>46203</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>46203</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>46203</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>45774</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45468</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45273</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>45789</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>45169</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45805</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>45867</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>44756</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>45713</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>45812</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>45812</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>45754</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>46105</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>46105</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>46169</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>46196</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>46196</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>46197</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>46203</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>46203</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>46203</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>46203</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>

--- a/Översikt BORGHOLM.xlsx
+++ b/Översikt BORGHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45029</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>44704</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45433</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>44903</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45903</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>46254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44809</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>44523</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>45107</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44781</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>45161</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>45146</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45918</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>45930</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45918</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44638</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>45736</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>46220</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45175</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>45926</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>45027</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>46188</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>46224</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>44704</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45478</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>46188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>46224</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>44482</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>46169</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>46169</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45736</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>46188</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45442</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>44953</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>44973</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>44704</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44704</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44783</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>45796</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45887</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>45911</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>46105</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>44781</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>46185</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>46188</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>46223</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>44837</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>46105</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>46188</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>46223</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>44623</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44725</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>46070</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>45994</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>45994</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>44840</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>46169</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>45758</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>46203</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>44711</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>46203</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>44649</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>44865</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>46203</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>46203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44772</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44781</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>44984</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45439</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>46041</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45902</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>46059</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>46069</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>46073</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>44776</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>45820</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>45820</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45084</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>45084</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>46185</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>46197</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>46196</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>45433</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>46246</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>45273</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>45385</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>45111</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>45903</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>46185</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>46197</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>46196</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         <v>46246</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44783</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>44747</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>44840</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>44783</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>44501</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>44477</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>44742</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44503</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>44776</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>45468</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>45169</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>45903</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>45323</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>46070</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>45923</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>45928</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>45805</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>44467</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>46105</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>46105</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>46105</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>44953</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45125</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>45280</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45812</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>45348</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>45569</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>45273</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>46169</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>46169</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>45867</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>45671</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44795</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>45621</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>46196</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>46196</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>45774</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>46197</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>46203</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>46203</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>46203</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>45713</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>46203</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>45125</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>44796</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>45330</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>44951</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>45005</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>44642</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>45264</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>45385</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>45670</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>45713</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>45789</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>44756</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16381,7 +16381,7 @@
         <v>45713</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>45812</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>45812</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>45754</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>46105</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>46105</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>46169</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>46197</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>46196</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>46196</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>46203</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>46203</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>46203</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>46203</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>

--- a/Översikt BORGHOLM.xlsx
+++ b/Översikt BORGHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45029</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>44704</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45433</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>44903</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45903</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>46254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44809</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>44523</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>45107</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44781</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>45161</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>45146</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45918</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>45930</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45918</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44638</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>45736</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>46220</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45175</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>45926</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>45027</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>46188</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>46224</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>44704</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45478</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>46188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>46224</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>44482</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>46169</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>46169</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45736</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>46188</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45442</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>44953</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>44973</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>44704</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44704</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44783</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>45796</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45887</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>45911</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>46105</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>44781</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>46185</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>46188</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>46223</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>44837</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>46105</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>46188</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>46223</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>44623</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44725</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>46070</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>45994</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>45994</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>44840</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>46169</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>45758</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>46203</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>44711</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>46203</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>44649</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>44865</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>46203</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>46203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44772</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44781</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>44984</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45439</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>46041</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45902</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>46059</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>46069</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>46073</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>44776</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>45820</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>45820</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45084</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>45084</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>46185</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>46197</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>46196</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>45433</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>46246</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>45273</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>45385</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>45111</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>45903</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>46185</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>46197</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>46196</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         <v>46246</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44783</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>44747</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>44840</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>44783</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>44501</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>44477</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>44742</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44503</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>44776</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>45468</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>45169</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>45903</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>45323</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>46070</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>45923</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>45928</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>45805</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>44467</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>46105</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>46105</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>46105</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>44953</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45125</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>45280</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45812</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>45348</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>45569</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>45273</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>46169</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>46169</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>45867</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>45671</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44795</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>45621</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>46196</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>46196</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>45774</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>46197</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>46203</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>46203</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>46203</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>45713</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>46203</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>45125</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>44796</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>45330</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>44951</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>45005</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>44642</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>45264</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>45385</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>45670</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>45713</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>45789</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>44756</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16381,7 +16381,7 @@
         <v>45713</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>45812</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>45812</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>45754</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>46105</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>46105</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>46169</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>46197</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>46196</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>46196</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>46203</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>46203</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>46203</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>46203</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>

--- a/Översikt BORGHOLM.xlsx
+++ b/Översikt BORGHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45029</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>44704</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45433</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>44903</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45903</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>46254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44809</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>44523</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>45107</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44781</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>45161</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>45146</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45918</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>45930</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45918</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13558-2025</t>
+          <t>A 12534-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45736</v>
+        <v>44638</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3233,19 +3233,19 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>8.6</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3260,18 +3260,130 @@
         <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
       </c>
       <c r="T23" t="n">
+        <v>9</v>
+      </c>
+      <c r="U23" t="n">
+        <v>9</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Backklöver
+Backtimjan
+Jordtistel
+Sårläka
+Vårstarr
+Krutbrännare
+Nattviol
+Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 12534-2022 artfynd.xlsx", "A 12534-2022")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 12534-2022 karta.png", "A 12534-2022")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 12534-2022 georefererad karta.tif", "A 12534-2022")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 12534-2022 FSC-klagomål.docx", "A 12534-2022")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 12534-2022 FSC-klagomål mail.docx", "A 12534-2022")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 12534-2022 tillsynsbegäran.docx", "A 12534-2022")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 12534-2022 tillsynsbegäran mail.docx", "A 12534-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 13558-2025</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>45736</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>4</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
         <v>8</v>
       </c>
-      <c r="U23" t="n">
+      <c r="T24" t="n">
         <v>8</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="U24" t="n">
+        <v>8</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Honungsblomster
 Backruta
@@ -3283,151 +3395,39 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 13558-2025 artfynd.xlsx", "A 13558-2025")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 13558-2025 karta.png", "A 13558-2025")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 13558-2025 georefererad karta.tif", "A 13558-2025")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 13558-2025 FSC-klagomål.docx", "A 13558-2025")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 13558-2025 FSC-klagomål mail.docx", "A 13558-2025")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 13558-2025 tillsynsbegäran.docx", "A 13558-2025")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 13558-2025 tillsynsbegäran mail.docx", "A 13558-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 12534-2022</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>44638</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>5</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>8</v>
-      </c>
-      <c r="T24" t="n">
-        <v>9</v>
-      </c>
-      <c r="U24" t="n">
-        <v>9</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Backklöver
-Backtimjan
-Jordtistel
-Sårläka
-Vårstarr
-Krutbrännare
-Nattviol
-Sankt pers nycklar</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 12534-2022 artfynd.xlsx", "A 12534-2022")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 12534-2022 karta.png", "A 12534-2022")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 12534-2022 georefererad karta.tif", "A 12534-2022")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 12534-2022 FSC-klagomål.docx", "A 12534-2022")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 12534-2022 FSC-klagomål mail.docx", "A 12534-2022")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 12534-2022 tillsynsbegäran.docx", "A 12534-2022")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 12534-2022 tillsynsbegäran mail.docx", "A 12534-2022")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31399-2026</t>
+          <t>A 31515-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3456,14 +3456,19 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L25" t="n">
         <v>3</v>
@@ -3490,12 +3495,241 @@
         <v>8</v>
       </c>
       <c r="T25" t="n">
+        <v>10</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Blå slemspindling
+Sårläka
+Vårärt
+Anisspindling
+Skogsknipprot
+Strävlosta
+Blåsippa
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31515-2026 artfynd.xlsx", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31515-2026 karta.png", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31515-2026 georefererad karta.tif", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31515-2026 FSC-klagomål.docx", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31515-2026 FSC-klagomål mail.docx", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31515-2026 tillsynsbegäran.docx", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31515-2026 tillsynsbegäran mail.docx", "A 31515-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 31516-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3</v>
+      </c>
+      <c r="L26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>8</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="T26" t="n">
+        <v>10</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Blå slemspindling
+Sårläka
+Vårärt
+Anisspindling
+Skogsknipprot
+Strävlosta
+Blåsippa
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31516-2026 artfynd.xlsx", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31516-2026 karta.png", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31516-2026 georefererad karta.tif", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31516-2026 FSC-klagomål.docx", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31516-2026 FSC-klagomål mail.docx", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31516-2026 tillsynsbegäran.docx", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31516-2026 tillsynsbegäran mail.docx", "A 31516-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 31399-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>8</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Backklöver
 Jordtistel
@@ -3507,112 +3741,224 @@
 Vanliga ängsnycklar</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31399-2026 artfynd.xlsx", "A 31399-2026")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31399-2026 karta.png", "A 31399-2026")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31399-2026 georefererad karta.tif", "A 31399-2026")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31399-2026 FSC-klagomål.docx", "A 31399-2026")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31399-2026 FSC-klagomål mail.docx", "A 31399-2026")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31399-2026 tillsynsbegäran.docx", "A 31399-2026")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31399-2026 tillsynsbegäran mail.docx", "A 31399-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 31515-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>S 2741-2022</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>44704</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>55</v>
+      </c>
+      <c r="U28" t="n">
+        <v>49</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Almlav
+Ask
+Korskovall
+Ekoxe
+Slät lönnlav
+Stor häxört
+Underviol
+Vitskivlav</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2741-2022 artfynd.xlsx", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 2741-2022 karta.png", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 2741-2022 georefererad karta.tif", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 2741-2022 FSC-klagomål.docx", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 2741-2022 FSC-klagomål mail.docx", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 2741-2022 tillsynsbegäran.docx", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 2741-2022 tillsynsbegäran mail.docx", "S 2741-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S 2057-2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="E29" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="I29" t="n">
         <v>0.8</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J29" t="n">
         <v>3</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K29" t="n">
         <v>3</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L29" t="n">
         <v>3</v>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
         <v>3</v>
       </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>8</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Blå slemspindling
 Sårläka
@@ -3624,112 +3970,112 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31515-2026 artfynd.xlsx", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31515-2026 karta.png", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31515-2026 georefererad karta.tif", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31515-2026 FSC-klagomål.docx", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31515-2026 FSC-klagomål mail.docx", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31515-2026 tillsynsbegäran.docx", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31515-2026 tillsynsbegäran mail.docx", "A 31515-2026")</f>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2057-2026 artfynd.xlsx", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 2057-2026 karta.png", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 2057-2026 georefererad karta.tif", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 2057-2026 FSC-klagomål.docx", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 2057-2026 FSC-klagomål mail.docx", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 2057-2026 tillsynsbegäran.docx", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 2057-2026 tillsynsbegäran mail.docx", "S 2057-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 31516-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>S 2058-2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E27" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="E30" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I27" t="n">
+      <c r="I30" t="n">
         <v>0.8</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J30" t="n">
         <v>3</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K30" t="n">
         <v>3</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L30" t="n">
         <v>3</v>
       </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>3</v>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>8</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T30" t="n">
         <v>10</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Blå slemspindling
 Sårläka
@@ -3741,352 +4087,6 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31516-2026 artfynd.xlsx", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31516-2026 karta.png", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31516-2026 georefererad karta.tif", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31516-2026 FSC-klagomål.docx", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31516-2026 FSC-klagomål mail.docx", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31516-2026 tillsynsbegäran.docx", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31516-2026 tillsynsbegäran mail.docx", "A 31516-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>S 2741-2022</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>44704</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>5</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3</v>
-      </c>
-      <c r="R28" t="n">
-        <v>2</v>
-      </c>
-      <c r="S28" t="n">
-        <v>8</v>
-      </c>
-      <c r="T28" t="n">
-        <v>55</v>
-      </c>
-      <c r="U28" t="n">
-        <v>49</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Almlav
-Ask
-Korskovall
-Ekoxe
-Slät lönnlav
-Stor häxört
-Underviol
-Vitskivlav</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2741-2022 artfynd.xlsx", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 2741-2022 karta.png", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 2741-2022 georefererad karta.tif", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 2741-2022 FSC-klagomål.docx", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 2741-2022 FSC-klagomål mail.docx", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 2741-2022 tillsynsbegäran.docx", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 2741-2022 tillsynsbegäran mail.docx", "S 2741-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>S 2057-2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3</v>
-      </c>
-      <c r="L29" t="n">
-        <v>3</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>8</v>
-      </c>
-      <c r="T29" t="n">
-        <v>10</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Blå slemspindling
-Sårläka
-Vårärt
-Anisspindling
-Skogsknipprot
-Strävlosta
-Blåsippa
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2057-2026 artfynd.xlsx", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 2057-2026 karta.png", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 2057-2026 georefererad karta.tif", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 2057-2026 FSC-klagomål.docx", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 2057-2026 FSC-klagomål mail.docx", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 2057-2026 tillsynsbegäran.docx", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 2057-2026 tillsynsbegäran mail.docx", "S 2057-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>S 2058-2026</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3</v>
-      </c>
-      <c r="L30" t="n">
-        <v>3</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>10</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Blå slemspindling
-Sårläka
-Vårärt
-Anisspindling
-Skogsknipprot
-Strävlosta
-Blåsippa
-Grönvit nattviol</t>
-        </is>
-      </c>
       <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2058-2026 artfynd.xlsx", "S 2058-2026")</f>
         <v/>
@@ -4136,7 +4136,7 @@
         <v>45175</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 46794-2025</t>
+          <t>A 16171-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4240,14 +4240,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45926</v>
+        <v>45027</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4260,13 +4260,13 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>12.2</v>
       </c>
       <c r="J32" t="n">
         <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>2</v>
@@ -4293,12 +4293,122 @@
         <v>6</v>
       </c>
       <c r="T32" t="n">
+        <v>7</v>
+      </c>
+      <c r="U32" t="n">
+        <v>6</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Sårläka
+Älg
+Murgröna
+Blåsippa
+Rostticka
+Bredarun</t>
+        </is>
+      </c>
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 16171-2023 artfynd.xlsx", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 16171-2023 karta.png", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 16171-2023 georefererad karta.tif", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 16171-2023 FSC-klagomål.docx", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 16171-2023 FSC-klagomål mail.docx", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 16171-2023 tillsynsbegäran.docx", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 16171-2023 tillsynsbegäran mail.docx", "A 16171-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 46794-2025</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>45926</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>6</v>
+      </c>
+      <c r="T33" t="n">
         <v>10</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U33" t="n">
         <v>9</v>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Mindre ekbock
 Sårläka
@@ -4308,112 +4418,112 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 46794-2025 artfynd.xlsx", "A 46794-2025")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 46794-2025 karta.png", "A 46794-2025")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 46794-2025 georefererad karta.tif", "A 46794-2025")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 46794-2025 FSC-klagomål.docx", "A 46794-2025")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 46794-2025 FSC-klagomål mail.docx", "A 46794-2025")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 46794-2025 tillsynsbegäran.docx", "A 46794-2025")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 46794-2025 tillsynsbegäran mail.docx", "A 46794-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A 27298-2026</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D33" s="1" t="n">
+      <c r="D34" s="1" t="n">
         <v>46188</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="E34" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="I34" t="n">
         <v>3.3</v>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="n">
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
         <v>5</v>
       </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>5</v>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>6</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T34" t="n">
         <v>6</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Grenplattnos
 Jungfrulin
@@ -4423,112 +4533,112 @@
 Murgröna</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27298-2026 artfynd.xlsx", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27298-2026 karta.png", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27298-2026 georefererad karta.tif", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27298-2026 FSC-klagomål.docx", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27298-2026 FSC-klagomål mail.docx", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27298-2026 tillsynsbegäran.docx", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27298-2026 tillsynsbegäran mail.docx", "A 27298-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>A 31558-2026</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D34" s="1" t="n">
+      <c r="D35" s="1" t="n">
         <v>46224</v>
       </c>
-      <c r="E34" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="E35" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" t="n">
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K35" t="n">
         <v>2</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L35" t="n">
         <v>3</v>
       </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
         <v>3</v>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>6</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T35" t="n">
         <v>7</v>
       </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Blå slemspindling
 Sårläka
@@ -4538,142 +4648,32 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W34">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31558-2026 artfynd.xlsx", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="X34">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31558-2026 karta.png", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="Y34">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31558-2026 georefererad karta.tif", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="AA34">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31558-2026 FSC-klagomål.docx", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="AB34">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31558-2026 FSC-klagomål mail.docx", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="AC34">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31558-2026 tillsynsbegäran.docx", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="AD34">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31558-2026 tillsynsbegäran mail.docx", "A 31558-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 16171-2023</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>45027</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>2</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>6</v>
-      </c>
-      <c r="T35" t="n">
-        <v>7</v>
-      </c>
-      <c r="U35" t="n">
-        <v>6</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka
-Älg
-Murgröna
-Blåsippa
-Rostticka
-Bredarun</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 16171-2023 artfynd.xlsx", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 16171-2023 karta.png", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 16171-2023 georefererad karta.tif", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 16171-2023 FSC-klagomål.docx", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 16171-2023 FSC-klagomål mail.docx", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 16171-2023 tillsynsbegäran.docx", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 16171-2023 tillsynsbegäran mail.docx", "A 16171-2023")</f>
         <v/>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
         <v>44704</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45478</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>46188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>46224</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>44482</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>46169</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>46169</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45736</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7960-2023</t>
+          <t>A 21797-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44973</v>
+        <v>45442</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5609,16 +5609,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5627,27 +5627,360 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
       </c>
       <c r="T44" t="n">
+        <v>11</v>
+      </c>
+      <c r="U44" t="n">
+        <v>6</v>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Sydlig kantmusseron
+Murgröna
+Skogsknipprot
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21797-2024 artfynd.xlsx", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="X44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21797-2024 karta.png", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="Y44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21797-2024 georefererad karta.tif", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="AA44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21797-2024 FSC-klagomål.docx", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="AB44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21797-2024 FSC-klagomål mail.docx", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="AC44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21797-2024 tillsynsbegäran.docx", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="AD44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21797-2024 tillsynsbegäran mail.docx", "A 21797-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A 27290-2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>2</v>
+      </c>
+      <c r="S45" t="n">
         <v>4</v>
       </c>
-      <c r="U44" t="n">
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Gotlandsmåra
+Skogsknipprot
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27290-2026 artfynd.xlsx", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="X45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27290-2026 karta.png", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="Y45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27290-2026 georefererad karta.tif", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="AA45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27290-2026 FSC-klagomål.docx", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="AB45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27290-2026 FSC-klagomål mail.docx", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="AC45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27290-2026 tillsynsbegäran.docx", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="AD45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27290-2026 tillsynsbegäran mail.docx", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="AE45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 27290-2026 prioriterade fågelarter.docx", "A 27290-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A 4164-2023</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>44953</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>2</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>4</v>
+      </c>
+      <c r="T46" t="n">
+        <v>5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Crepis tectorum subsp. tectorum
+Kösa
+Murgröna
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 4164-2023 artfynd.xlsx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="X46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 4164-2023 karta.png", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="Y46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 4164-2023 georefererad karta.tif", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AA46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 4164-2023 FSC-klagomål.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AB46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 4164-2023 FSC-klagomål mail.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AC46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 4164-2023 tillsynsbegäran.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AD46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 4164-2023 tillsynsbegäran mail.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>A 7960-2023</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>44973</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
         <v>3</v>
       </c>
-      <c r="V44" s="2" t="inlineStr">
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>4</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
         <is>
           <t>Vresalm
 Pilfotsspindling
@@ -5655,365 +5988,32 @@
 Strävlosta</t>
         </is>
       </c>
-      <c r="W44">
+      <c r="W47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 7960-2023 artfynd.xlsx", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="X44">
+      <c r="X47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 7960-2023 karta.png", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="Y44">
+      <c r="Y47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 7960-2023 georefererad karta.tif", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="AA44">
+      <c r="AA47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 7960-2023 FSC-klagomål.docx", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="AB44">
+      <c r="AB47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 7960-2023 FSC-klagomål mail.docx", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="AC44">
+      <c r="AC47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 7960-2023 tillsynsbegäran.docx", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="AD44">
+      <c r="AD47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 7960-2023 tillsynsbegäran mail.docx", "A 7960-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>A 27290-2026</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E45" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>1</v>
-      </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>2</v>
-      </c>
-      <c r="R45" t="n">
-        <v>2</v>
-      </c>
-      <c r="S45" t="n">
-        <v>4</v>
-      </c>
-      <c r="T45" t="n">
-        <v>4</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Gotlandsmåra
-Skogsknipprot
-Havsörn</t>
-        </is>
-      </c>
-      <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27290-2026 artfynd.xlsx", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27290-2026 karta.png", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27290-2026 georefererad karta.tif", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27290-2026 FSC-klagomål.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27290-2026 FSC-klagomål mail.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27290-2026 tillsynsbegäran.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27290-2026 tillsynsbegäran mail.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="AE45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 27290-2026 prioriterade fågelarter.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>A 4164-2023</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>44953</v>
-      </c>
-      <c r="E46" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" t="n">
-        <v>2</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>2</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>4</v>
-      </c>
-      <c r="T46" t="n">
-        <v>5</v>
-      </c>
-      <c r="U46" t="n">
-        <v>4</v>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>Crepis tectorum subsp. tectorum
-Kösa
-Murgröna
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 4164-2023 artfynd.xlsx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 4164-2023 karta.png", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 4164-2023 georefererad karta.tif", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 4164-2023 FSC-klagomål.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 4164-2023 FSC-klagomål mail.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 4164-2023 tillsynsbegäran.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 4164-2023 tillsynsbegäran mail.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>A 21797-2024</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>45442</v>
-      </c>
-      <c r="E47" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2</v>
-      </c>
-      <c r="L47" t="n">
-        <v>1</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>4</v>
-      </c>
-      <c r="T47" t="n">
-        <v>11</v>
-      </c>
-      <c r="U47" t="n">
-        <v>6</v>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>Sydlig kantmusseron
-Murgröna
-Skogsknipprot
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21797-2024 artfynd.xlsx", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21797-2024 karta.png", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21797-2024 georefererad karta.tif", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21797-2024 FSC-klagomål.docx", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21797-2024 FSC-klagomål mail.docx", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21797-2024 tillsynsbegäran.docx", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21797-2024 tillsynsbegäran mail.docx", "A 21797-2024")</f>
         <v/>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
         <v>44704</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44704</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44783</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38860-2025</t>
+          <t>A 24048-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6362,10 +6362,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45887</v>
+        <v>45796</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6378,22 +6378,22 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
         <v>2</v>
       </c>
-      <c r="K51" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6402,160 +6402,160 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
       </c>
       <c r="T51" t="n">
+        <v>5</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>Loppstarr
+Ängsstarr
+Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="W51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24048-2025 artfynd.xlsx", "A 24048-2025")</f>
+        <v/>
+      </c>
+      <c r="X51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24048-2025 karta.png", "A 24048-2025")</f>
+        <v/>
+      </c>
+      <c r="Y51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24048-2025 georefererad karta.tif", "A 24048-2025")</f>
+        <v/>
+      </c>
+      <c r="AA51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24048-2025 FSC-klagomål.docx", "A 24048-2025")</f>
+        <v/>
+      </c>
+      <c r="AB51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24048-2025 FSC-klagomål mail.docx", "A 24048-2025")</f>
+        <v/>
+      </c>
+      <c r="AC51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24048-2025 tillsynsbegäran.docx", "A 24048-2025")</f>
+        <v/>
+      </c>
+      <c r="AD51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24048-2025 tillsynsbegäran mail.docx", "A 24048-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>A 38860-2025</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>45887</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="n">
         <v>3</v>
       </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsknipprot
 Revlummer</t>
         </is>
       </c>
-      <c r="W51">
+      <c r="W52">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 38860-2025 artfynd.xlsx", "A 38860-2025")</f>
         <v/>
       </c>
-      <c r="X51">
+      <c r="X52">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 38860-2025 karta.png", "A 38860-2025")</f>
         <v/>
       </c>
-      <c r="Y51">
+      <c r="Y52">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 38860-2025 georefererad karta.tif", "A 38860-2025")</f>
         <v/>
       </c>
-      <c r="AA51">
+      <c r="AA52">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 38860-2025 FSC-klagomål.docx", "A 38860-2025")</f>
         <v/>
       </c>
-      <c r="AB51">
+      <c r="AB52">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 38860-2025 FSC-klagomål mail.docx", "A 38860-2025")</f>
         <v/>
       </c>
-      <c r="AC51">
+      <c r="AC52">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 38860-2025 tillsynsbegäran.docx", "A 38860-2025")</f>
         <v/>
       </c>
-      <c r="AD51">
+      <c r="AD52">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 38860-2025 tillsynsbegäran mail.docx", "A 38860-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>A 24048-2025</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="n">
-        <v>45796</v>
-      </c>
-      <c r="E52" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>2</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>2</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>2</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>3</v>
-      </c>
-      <c r="T52" t="n">
-        <v>5</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
-        <is>
-          <t>Loppstarr
-Ängsstarr
-Kärrknipprot</t>
-        </is>
-      </c>
-      <c r="W52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24048-2025 artfynd.xlsx", "A 24048-2025")</f>
-        <v/>
-      </c>
-      <c r="X52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24048-2025 karta.png", "A 24048-2025")</f>
-        <v/>
-      </c>
-      <c r="Y52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24048-2025 georefererad karta.tif", "A 24048-2025")</f>
-        <v/>
-      </c>
-      <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24048-2025 FSC-klagomål.docx", "A 24048-2025")</f>
-        <v/>
-      </c>
-      <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24048-2025 FSC-klagomål mail.docx", "A 24048-2025")</f>
-        <v/>
-      </c>
-      <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24048-2025 tillsynsbegäran.docx", "A 24048-2025")</f>
-        <v/>
-      </c>
-      <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24048-2025 tillsynsbegäran mail.docx", "A 24048-2025")</f>
         <v/>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
         <v>45911</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 15285-2026</t>
+          <t>A 32174-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6683,10 +6683,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46105</v>
+        <v>44781</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6704,13 +6704,13 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" t="n">
         <v>1</v>
@@ -6740,164 +6740,164 @@
         <v>3</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>Backklöver
+Tvåblad
+Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="W54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 32174-2022 artfynd.xlsx", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="X54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 32174-2022 karta.png", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="Y54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 32174-2022 georefererad karta.tif", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="AA54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 32174-2022 FSC-klagomål.docx", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="AB54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 32174-2022 FSC-klagomål mail.docx", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="AC54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 32174-2022 tillsynsbegäran.docx", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="AD54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 32174-2022 tillsynsbegäran mail.docx", "A 32174-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>A 15285-2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>3</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Havsörn
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W54">
+      <c r="W55">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 15285-2026 artfynd.xlsx", "A 15285-2026")</f>
         <v/>
       </c>
-      <c r="X54">
+      <c r="X55">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 15285-2026 karta.png", "A 15285-2026")</f>
         <v/>
       </c>
-      <c r="Y54">
+      <c r="Y55">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 15285-2026 georefererad karta.tif", "A 15285-2026")</f>
         <v/>
       </c>
-      <c r="AA54">
+      <c r="AA55">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 15285-2026 FSC-klagomål.docx", "A 15285-2026")</f>
         <v/>
       </c>
-      <c r="AB54">
+      <c r="AB55">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 15285-2026 FSC-klagomål mail.docx", "A 15285-2026")</f>
         <v/>
       </c>
-      <c r="AC54">
+      <c r="AC55">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 15285-2026 tillsynsbegäran.docx", "A 15285-2026")</f>
         <v/>
       </c>
-      <c r="AD54">
+      <c r="AD55">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 15285-2026 tillsynsbegäran mail.docx", "A 15285-2026")</f>
         <v/>
       </c>
-      <c r="AE54">
+      <c r="AE55">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 15285-2026 prioriterade fågelarter.docx", "A 15285-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>A 32174-2022</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D55" s="1" t="n">
-        <v>44781</v>
-      </c>
-      <c r="E55" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J55" t="n">
-        <v>2</v>
-      </c>
-      <c r="K55" t="n">
-        <v>2</v>
-      </c>
-      <c r="L55" t="n">
-        <v>1</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>1</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>3</v>
-      </c>
-      <c r="T55" t="n">
-        <v>3</v>
-      </c>
-      <c r="U55" t="n">
-        <v>3</v>
-      </c>
-      <c r="V55" s="2" t="inlineStr">
-        <is>
-          <t>Backklöver
-Tvåblad
-Vit skogslilja</t>
-        </is>
-      </c>
-      <c r="W55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 32174-2022 artfynd.xlsx", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="X55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 32174-2022 karta.png", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="Y55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 32174-2022 georefererad karta.tif", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="AA55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 32174-2022 FSC-klagomål.docx", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="AB55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 32174-2022 FSC-klagomål mail.docx", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="AC55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 32174-2022 tillsynsbegäran.docx", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="AD55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 32174-2022 tillsynsbegäran mail.docx", "A 32174-2022")</f>
         <v/>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43756-2022</t>
+          <t>A 26849-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6911,10 +6911,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44837</v>
+        <v>46185</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6926,14 +6926,19 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2.2</v>
+        <v>8.1</v>
       </c>
       <c r="J56" t="n">
         <v>2</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6960,698 +6965,693 @@
         <v>3</v>
       </c>
       <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>Myskmadra
+Purpurknipprot
+Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="W56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26849-2026 artfynd.xlsx", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="X56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26849-2026 karta.png", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="Y56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26849-2026 georefererad karta.tif", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="AA56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26849-2026 FSC-klagomål.docx", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="AB56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26849-2026 FSC-klagomål mail.docx", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="AC56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26849-2026 tillsynsbegäran.docx", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="AD56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26849-2026 tillsynsbegäran mail.docx", "A 26849-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>A 27283-2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>2</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>2</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Mindre poppelglasvinge
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27283-2026 artfynd.xlsx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="X57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27283-2026 karta.png", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="Y57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27283-2026 georefererad karta.tif", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AA57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27283-2026 FSC-klagomål.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AB57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27283-2026 FSC-klagomål mail.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AC57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27283-2026 tillsynsbegäran.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AD57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27283-2026 tillsynsbegäran mail.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>A 43756-2022</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>44837</v>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3</v>
+      </c>
+      <c r="T58" t="n">
         <v>5</v>
       </c>
-      <c r="U56" t="n">
+      <c r="U58" t="n">
         <v>5</v>
       </c>
-      <c r="V56" s="2" t="inlineStr">
+      <c r="V58" s="2" t="inlineStr">
         <is>
           <t>Murgröna
 Blåsippa
 Gullviva</t>
         </is>
       </c>
-      <c r="W56">
+      <c r="W58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 43756-2022 artfynd.xlsx", "A 43756-2022")</f>
         <v/>
       </c>
-      <c r="X56">
+      <c r="X58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 43756-2022 karta.png", "A 43756-2022")</f>
         <v/>
       </c>
-      <c r="Y56">
+      <c r="Y58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 43756-2022 georefererad karta.tif", "A 43756-2022")</f>
         <v/>
       </c>
-      <c r="AA56">
+      <c r="AA58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 43756-2022 FSC-klagomål.docx", "A 43756-2022")</f>
         <v/>
       </c>
-      <c r="AB56">
+      <c r="AB58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 43756-2022 FSC-klagomål mail.docx", "A 43756-2022")</f>
         <v/>
       </c>
-      <c r="AC56">
+      <c r="AC58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 43756-2022 tillsynsbegäran.docx", "A 43756-2022")</f>
         <v/>
       </c>
-      <c r="AD56">
+      <c r="AD58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 43756-2022 tillsynsbegäran mail.docx", "A 43756-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>A 27283-2026</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>A 31520-2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D57" s="1" t="n">
+      <c r="D59" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>3</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>3</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Grönsiska
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31520-2026 artfynd.xlsx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="X59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31520-2026 karta.png", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31520-2026 georefererad karta.tif", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31520-2026 FSC-klagomål.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31520-2026 FSC-klagomål mail.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31520-2026 tillsynsbegäran.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31520-2026 tillsynsbegäran mail.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AE59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 31520-2026 prioriterade fågelarter.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>S 846-2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>3</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Havsörn
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 846-2026 artfynd.xlsx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="X60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 846-2026 karta.png", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="Y60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 846-2026 georefererad karta.tif", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AA60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 846-2026 FSC-klagomål.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AB60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 846-2026 FSC-klagomål mail.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AC60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 846-2026 tillsynsbegäran.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AD60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 846-2026 tillsynsbegäran mail.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AE60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/S 846-2026 prioriterade fågelarter.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>S 1726-2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="n">
         <v>46188</v>
       </c>
-      <c r="E57" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F57" t="inlineStr">
+      <c r="E61" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I57" t="n">
+      <c r="I61" t="n">
         <v>2</v>
       </c>
-      <c r="J57" t="n">
-        <v>1</v>
-      </c>
-      <c r="K57" t="n">
-        <v>1</v>
-      </c>
-      <c r="L57" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>1</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
         <v>2</v>
       </c>
-      <c r="R57" t="n">
-        <v>1</v>
-      </c>
-      <c r="S57" t="n">
+      <c r="R61" t="n">
+        <v>1</v>
+      </c>
+      <c r="S61" t="n">
         <v>3</v>
       </c>
-      <c r="T57" t="n">
+      <c r="T61" t="n">
         <v>3</v>
       </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" s="2" t="inlineStr">
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
         <is>
           <t>Ask
 Mindre poppelglasvinge
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27283-2026 artfynd.xlsx", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="X57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27283-2026 karta.png", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="Y57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27283-2026 georefererad karta.tif", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="AA57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27283-2026 FSC-klagomål.docx", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="AB57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27283-2026 FSC-klagomål mail.docx", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="AC57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27283-2026 tillsynsbegäran.docx", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="AD57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27283-2026 tillsynsbegäran mail.docx", "A 27283-2026")</f>
+      <c r="W61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1726-2026 artfynd.xlsx", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="X61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1726-2026 karta.png", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="Y61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1726-2026 georefererad karta.tif", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="AA61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1726-2026 FSC-klagomål.docx", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="AB61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1726-2026 FSC-klagomål mail.docx", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="AC61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1726-2026 tillsynsbegäran.docx", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="AD61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1726-2026 tillsynsbegäran mail.docx", "S 1726-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>A 26849-2026</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="n">
-        <v>46185</v>
-      </c>
-      <c r="E58" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F58" t="inlineStr">
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>S 2059-2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E62" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I58" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2</v>
-      </c>
-      <c r="K58" t="n">
+      <c r="I62" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J62" t="n">
         <v>3</v>
       </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
         <v>3</v>
       </c>
-      <c r="T58" t="n">
-        <v>3</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" s="2" t="inlineStr">
-        <is>
-          <t>Myskmadra
-Purpurknipprot
-Vit skogslilja</t>
-        </is>
-      </c>
-      <c r="W58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26849-2026 artfynd.xlsx", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="X58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26849-2026 karta.png", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="Y58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26849-2026 georefererad karta.tif", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="AA58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26849-2026 FSC-klagomål.docx", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="AB58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26849-2026 FSC-klagomål mail.docx", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="AC58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26849-2026 tillsynsbegäran.docx", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="AD58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26849-2026 tillsynsbegäran mail.docx", "A 26849-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>A 31520-2026</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E59" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J59" t="n">
-        <v>3</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>1</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>3</v>
-      </c>
-      <c r="T59" t="n">
+      <c r="T62" t="n">
         <v>4</v>
       </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" s="2" t="inlineStr">
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Grönsiska
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31520-2026 artfynd.xlsx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="X59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31520-2026 karta.png", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="Y59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31520-2026 georefererad karta.tif", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AA59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31520-2026 FSC-klagomål.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AB59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31520-2026 FSC-klagomål mail.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AC59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31520-2026 tillsynsbegäran.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AD59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31520-2026 tillsynsbegäran mail.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AE59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 31520-2026 prioriterade fågelarter.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>S 846-2026</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E60" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J60" t="n">
-        <v>3</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>1</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="n">
-        <v>3</v>
-      </c>
-      <c r="T60" t="n">
-        <v>3</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Havsörn
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 846-2026 artfynd.xlsx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="X60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 846-2026 karta.png", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="Y60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 846-2026 georefererad karta.tif", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AA60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 846-2026 FSC-klagomål.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AB60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 846-2026 FSC-klagomål mail.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AC60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 846-2026 tillsynsbegäran.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AD60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 846-2026 tillsynsbegäran mail.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AE60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/S 846-2026 prioriterade fågelarter.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>S 1726-2026</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E61" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I61" t="n">
-        <v>2</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1</v>
-      </c>
-      <c r="K61" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" t="n">
-        <v>1</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>1</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>2</v>
-      </c>
-      <c r="R61" t="n">
-        <v>1</v>
-      </c>
-      <c r="S61" t="n">
-        <v>3</v>
-      </c>
-      <c r="T61" t="n">
-        <v>3</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Mindre poppelglasvinge
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1726-2026 artfynd.xlsx", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="X61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1726-2026 karta.png", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="Y61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1726-2026 georefererad karta.tif", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="AA61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1726-2026 FSC-klagomål.docx", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="AB61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1726-2026 FSC-klagomål mail.docx", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="AC61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1726-2026 tillsynsbegäran.docx", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="AD61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1726-2026 tillsynsbegäran mail.docx", "S 1726-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>S 2059-2026</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E62" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I62" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J62" t="n">
-        <v>3</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>1</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>1</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>3</v>
-      </c>
-      <c r="T62" t="n">
-        <v>4</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Grönsiska
-Kungsfågel</t>
-        </is>
-      </c>
       <c r="W62">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2059-2026 artfynd.xlsx", "S 2059-2026")</f>
         <v/>
@@ -7705,7 +7705,7 @@
         <v>44623</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44725</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 21908-2022</t>
+          <t>A 9253-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7914,10 +7914,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44711</v>
+        <v>46070</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7930,13 +7930,13 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>1</v>
       </c>
       <c r="K65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -7966,40 +7966,40 @@
         <v>2</v>
       </c>
       <c r="U65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra
-Skogsknipprot</t>
+          <t>Murgröna
+Gullviva</t>
         </is>
       </c>
       <c r="W65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21908-2022 artfynd.xlsx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9253-2026 artfynd.xlsx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="X65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21908-2022 karta.png", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9253-2026 karta.png", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="Y65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21908-2022 georefererad karta.tif", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9253-2026 georefererad karta.tif", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AA65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21908-2022 FSC-klagomål.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9253-2026 FSC-klagomål.docx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AB65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21908-2022 FSC-klagomål mail.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9253-2026 FSC-klagomål mail.docx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AC65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21908-2022 tillsynsbegäran.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9253-2026 tillsynsbegäran.docx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AD65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21908-2022 tillsynsbegäran mail.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9253-2026 tillsynsbegäran mail.docx", "A 9253-2026")</f>
         <v/>
       </c>
     </row>
@@ -8023,7 +8023,7 @@
         <v>45994</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>45994</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 9253-2026</t>
+          <t>A 44678-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -8232,10 +8232,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46070</v>
+        <v>44840</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J68" t="n">
         <v>1</v>
@@ -8263,7 +8263,7 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8272,10 +8272,10 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S68" t="n">
         <v>2</v>
@@ -8284,47 +8284,47 @@
         <v>2</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>Murgröna
-Gullviva</t>
+          <t>Ask
+Skogsknipprot</t>
         </is>
       </c>
       <c r="W68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9253-2026 artfynd.xlsx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 44678-2022 artfynd.xlsx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="X68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9253-2026 karta.png", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 44678-2022 karta.png", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="Y68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9253-2026 georefererad karta.tif", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 44678-2022 georefererad karta.tif", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AA68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9253-2026 FSC-klagomål.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 44678-2022 FSC-klagomål.docx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AB68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9253-2026 FSC-klagomål mail.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 44678-2022 FSC-klagomål mail.docx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AC68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9253-2026 tillsynsbegäran.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 44678-2022 tillsynsbegäran.docx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AD68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9253-2026 tillsynsbegäran mail.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 44678-2022 tillsynsbegäran mail.docx", "A 44678-2022")</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 44678-2022</t>
+          <t>A 17699-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -8338,10 +8338,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44840</v>
+        <v>45758</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8354,22 +8354,22 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8378,10 +8378,10 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>2</v>
@@ -8390,40 +8390,40 @@
         <v>2</v>
       </c>
       <c r="U69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>Ask
-Skogsknipprot</t>
+          <t>Backtimjan
+Klibbveronika</t>
         </is>
       </c>
       <c r="W69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 44678-2022 artfynd.xlsx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 17699-2025 artfynd.xlsx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="X69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 44678-2022 karta.png", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 17699-2025 karta.png", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="Y69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 44678-2022 georefererad karta.tif", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 17699-2025 georefererad karta.tif", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AA69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 44678-2022 FSC-klagomål.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 17699-2025 FSC-klagomål.docx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AB69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 44678-2022 FSC-klagomål mail.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 17699-2025 FSC-klagomål mail.docx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AC69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 44678-2022 tillsynsbegäran.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 17699-2025 tillsynsbegäran.docx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AD69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 44678-2022 tillsynsbegäran mail.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 17699-2025 tillsynsbegäran mail.docx", "A 17699-2025")</f>
         <v/>
       </c>
     </row>
@@ -8447,7 +8447,7 @@
         <v>46169</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29411-2026</t>
+          <t>A 21908-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8551,14 +8551,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46203</v>
+        <v>44711</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8570,25 +8570,20 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J71" t="n">
         <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
@@ -8600,10 +8595,10 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>2</v>
@@ -8612,47 +8607,47 @@
         <v>2</v>
       </c>
       <c r="U71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare
-Ekoxe</t>
+          <t>Myskmadra
+Skogsknipprot</t>
         </is>
       </c>
       <c r="W71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 29411-2026 artfynd.xlsx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21908-2022 artfynd.xlsx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="X71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 29411-2026 karta.png", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21908-2022 karta.png", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="Y71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 29411-2026 georefererad karta.tif", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21908-2022 georefererad karta.tif", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AA71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 29411-2026 FSC-klagomål.docx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21908-2022 FSC-klagomål.docx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AB71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 29411-2026 FSC-klagomål mail.docx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21908-2022 FSC-klagomål mail.docx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AC71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 29411-2026 tillsynsbegäran.docx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21908-2022 tillsynsbegäran.docx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AD71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 29411-2026 tillsynsbegäran mail.docx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21908-2022 tillsynsbegäran mail.docx", "A 21908-2022")</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 17699-2025</t>
+          <t>A 29411-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8662,14 +8657,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45758</v>
+        <v>46203</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8681,20 +8676,25 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N72" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S72" t="n">
         <v>2</v>
@@ -8718,40 +8718,40 @@
         <v>2</v>
       </c>
       <c r="U72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan
-Klibbveronika</t>
+          <t>Bredbrämad bastardsvärmare
+Ekoxe</t>
         </is>
       </c>
       <c r="W72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 17699-2025 artfynd.xlsx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 29411-2026 artfynd.xlsx", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="X72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 17699-2025 karta.png", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 29411-2026 karta.png", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="Y72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 17699-2025 georefererad karta.tif", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 29411-2026 georefererad karta.tif", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="AA72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 17699-2025 FSC-klagomål.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 29411-2026 FSC-klagomål.docx", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="AB72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 17699-2025 FSC-klagomål mail.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 29411-2026 FSC-klagomål mail.docx", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="AC72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 17699-2025 tillsynsbegäran.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 29411-2026 tillsynsbegäran.docx", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="AD72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 17699-2025 tillsynsbegäran mail.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 29411-2026 tillsynsbegäran mail.docx", "A 29411-2026")</f>
         <v/>
       </c>
     </row>
@@ -8775,7 +8775,7 @@
         <v>46203</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S 6144-2022</t>
+          <t>S 1650-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8879,14 +8879,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44865</v>
+        <v>44649</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8899,16 +8899,16 @@
         </is>
       </c>
       <c r="I74" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
         <v>2</v>
       </c>
-      <c r="J74" t="n">
-        <v>1</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
-      </c>
       <c r="L74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -8923,7 +8923,7 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
@@ -8932,50 +8932,50 @@
         <v>2</v>
       </c>
       <c r="T74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>Oxtungssvamp
-Fläcknycklar</t>
+          <t>Guldlockmossa
+Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="W74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 6144-2022 artfynd.xlsx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1650-2022 artfynd.xlsx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="X74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 6144-2022 karta.png", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1650-2022 karta.png", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="Y74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 6144-2022 georefererad karta.tif", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1650-2022 georefererad karta.tif", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AA74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 6144-2022 FSC-klagomål.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1650-2022 FSC-klagomål.docx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AB74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 6144-2022 FSC-klagomål mail.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1650-2022 FSC-klagomål mail.docx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AC74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 6144-2022 tillsynsbegäran.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1650-2022 tillsynsbegäran.docx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AD74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 6144-2022 tillsynsbegäran mail.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1650-2022 tillsynsbegäran mail.docx", "S 1650-2022")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S 1650-2022</t>
+          <t>S 6144-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8985,14 +8985,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44649</v>
+        <v>44865</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9005,16 +9005,16 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -9029,7 +9029,7 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -9038,43 +9038,43 @@
         <v>2</v>
       </c>
       <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
         <v>2</v>
       </c>
-      <c r="U75" t="n">
-        <v>0</v>
-      </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa
-Gulpudrad spiklav</t>
+          <t>Oxtungssvamp
+Fläcknycklar</t>
         </is>
       </c>
       <c r="W75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1650-2022 artfynd.xlsx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 6144-2022 artfynd.xlsx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="X75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1650-2022 karta.png", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 6144-2022 karta.png", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="Y75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1650-2022 georefererad karta.tif", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 6144-2022 georefererad karta.tif", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AA75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1650-2022 FSC-klagomål.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 6144-2022 FSC-klagomål.docx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AB75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1650-2022 FSC-klagomål mail.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 6144-2022 FSC-klagomål mail.docx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AC75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1650-2022 tillsynsbegäran.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 6144-2022 tillsynsbegäran.docx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AD75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1650-2022 tillsynsbegäran mail.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 6144-2022 tillsynsbegäran mail.docx", "S 6144-2022")</f>
         <v/>
       </c>
     </row>
@@ -9098,7 +9098,7 @@
         <v>46203</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>46203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44772</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44781</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 24701-2023</t>
+          <t>A 9745-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9537,10 +9537,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45084</v>
+        <v>44984</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9553,13 +9553,13 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -9568,7 +9568,7 @@
         <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9577,58 +9577,58 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
       </c>
       <c r="T80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24701-2023 artfynd.xlsx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9745-2023 artfynd.xlsx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="X80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24701-2023 karta.png", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9745-2023 karta.png", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="Y80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24701-2023 georefererad karta.tif", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9745-2023 georefererad karta.tif", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AA80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24701-2023 FSC-klagomål.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9745-2023 FSC-klagomål.docx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AB80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24701-2023 FSC-klagomål mail.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9745-2023 FSC-klagomål mail.docx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AC80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24701-2023 tillsynsbegäran.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9745-2023 tillsynsbegäran.docx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AD80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24701-2023 tillsynsbegäran mail.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9745-2023 tillsynsbegäran mail.docx", "A 9745-2023")</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 41831-2025</t>
+          <t>A 20878-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45902</v>
+        <v>45439</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J81" t="n">
         <v>1</v>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -9691,49 +9691,49 @@
         <v>1</v>
       </c>
       <c r="T81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 41831-2025 artfynd.xlsx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 20878-2024 artfynd.xlsx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="X81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 41831-2025 karta.png", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 20878-2024 karta.png", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="Y81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 41831-2025 georefererad karta.tif", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 20878-2024 georefererad karta.tif", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AA81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 41831-2025 FSC-klagomål.docx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 20878-2024 FSC-klagomål.docx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AB81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 41831-2025 FSC-klagomål mail.docx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 20878-2024 FSC-klagomål mail.docx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AC81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 41831-2025 tillsynsbegäran.docx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 20878-2024 tillsynsbegäran.docx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AD81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 41831-2025 tillsynsbegäran mail.docx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 20878-2024 tillsynsbegäran mail.docx", "A 20878-2024")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 28785-2025</t>
+          <t>A 41831-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9743,14 +9743,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45820</v>
+        <v>45902</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9762,19 +9762,14 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
         <v>1</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -9808,39 +9803,35 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28785-2025 artfynd.xlsx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 41831-2025 artfynd.xlsx", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="X82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28785-2025 karta.png", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 41831-2025 karta.png", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="Y82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28785-2025 georefererad karta.tif", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 41831-2025 georefererad karta.tif", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="AA82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28785-2025 FSC-klagomål.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 41831-2025 FSC-klagomål.docx", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="AB82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28785-2025 FSC-klagomål mail.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 41831-2025 FSC-klagomål mail.docx", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="AC82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28785-2025 tillsynsbegäran.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 41831-2025 tillsynsbegäran.docx", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="AD82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28785-2025 tillsynsbegäran mail.docx", "A 28785-2025")</f>
-        <v/>
-      </c>
-      <c r="AE82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 28785-2025 prioriterade fågelarter.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 41831-2025 tillsynsbegäran mail.docx", "A 41831-2025")</f>
         <v/>
       </c>
     </row>
@@ -9864,7 +9855,7 @@
         <v>45820</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9961,7 +9952,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 3302-2026</t>
+          <t>A 28785-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9971,14 +9962,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46041</v>
+        <v>45820</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9990,8 +9981,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J84" t="n">
         <v>1</v>
@@ -10031,42 +10027,46 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 3302-2026 artfynd.xlsx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28785-2025 artfynd.xlsx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="X84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 3302-2026 karta.png", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28785-2025 karta.png", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="Y84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 3302-2026 georefererad karta.tif", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28785-2025 georefererad karta.tif", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AA84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 3302-2026 FSC-klagomål.docx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28785-2025 FSC-klagomål.docx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AB84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 3302-2026 FSC-klagomål mail.docx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28785-2025 FSC-klagomål mail.docx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AC84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 3302-2026 tillsynsbegäran.docx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28785-2025 tillsynsbegäran.docx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AD84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 3302-2026 tillsynsbegäran mail.docx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28785-2025 tillsynsbegäran mail.docx", "A 28785-2025")</f>
+        <v/>
+      </c>
+      <c r="AE84">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 28785-2025 prioriterade fågelarter.docx", "A 28785-2025")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 63276-2023</t>
+          <t>A 3302-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10076,14 +10076,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45273</v>
+        <v>46041</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10096,10 +10096,10 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -10108,7 +10108,7 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
         <v>0</v>
@@ -10120,10 +10120,10 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
@@ -10136,42 +10136,42 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>Elaphomyces barrioi</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 63276-2023 artfynd.xlsx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 3302-2026 artfynd.xlsx", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="X85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 63276-2023 karta.png", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 3302-2026 karta.png", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="Y85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 63276-2023 georefererad karta.tif", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 3302-2026 georefererad karta.tif", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="AA85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 63276-2023 FSC-klagomål.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 3302-2026 FSC-klagomål.docx", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="AB85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 63276-2023 FSC-klagomål mail.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 3302-2026 FSC-klagomål mail.docx", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="AC85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 63276-2023 tillsynsbegäran.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 3302-2026 tillsynsbegäran.docx", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="AD85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 63276-2023 tillsynsbegäran mail.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 3302-2026 tillsynsbegäran mail.docx", "A 3302-2026")</f>
         <v/>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 7481-2026</t>
+          <t>A 31720-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10185,10 +10185,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46059</v>
+        <v>44776</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10200,14 +10200,19 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="J86" t="n">
         <v>1</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -10234,49 +10239,49 @@
         <v>1</v>
       </c>
       <c r="T86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 7481-2026 artfynd.xlsx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31720-2022 artfynd.xlsx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="X86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 7481-2026 karta.png", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31720-2022 karta.png", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="Y86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 7481-2026 georefererad karta.tif", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31720-2022 georefererad karta.tif", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AA86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 7481-2026 FSC-klagomål.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31720-2022 FSC-klagomål.docx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AB86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 7481-2026 FSC-klagomål mail.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31720-2022 FSC-klagomål mail.docx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AC86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 7481-2026 tillsynsbegäran.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31720-2022 tillsynsbegäran.docx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AD86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 7481-2026 tillsynsbegäran mail.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31720-2022 tillsynsbegäran mail.docx", "A 31720-2022")</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 9104-2026</t>
+          <t>A 7481-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10286,14 +10291,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46069</v>
+        <v>46059</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10306,10 +10311,10 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -10339,49 +10344,49 @@
         <v>1</v>
       </c>
       <c r="T87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9104-2026 artfynd.xlsx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 7481-2026 artfynd.xlsx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="X87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9104-2026 karta.png", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 7481-2026 karta.png", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="Y87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9104-2026 georefererad karta.tif", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 7481-2026 georefererad karta.tif", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AA87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9104-2026 FSC-klagomål.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 7481-2026 FSC-klagomål.docx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AB87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9104-2026 FSC-klagomål mail.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 7481-2026 FSC-klagomål mail.docx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AC87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9104-2026 tillsynsbegäran.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 7481-2026 tillsynsbegäran.docx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AD87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9104-2026 tillsynsbegäran mail.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 7481-2026 tillsynsbegäran mail.docx", "A 7481-2026")</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 24704-2023</t>
+          <t>A 9104-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10391,14 +10396,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45084</v>
+        <v>46069</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10411,7 +10416,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -10426,7 +10431,7 @@
         <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10435,51 +10440,51 @@
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>1</v>
       </c>
       <c r="T88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="W88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24704-2023 artfynd.xlsx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9104-2026 artfynd.xlsx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="X88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24704-2023 karta.png", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9104-2026 karta.png", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="Y88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24704-2023 georefererad karta.tif", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9104-2026 georefererad karta.tif", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AA88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24704-2023 FSC-klagomål.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9104-2026 FSC-klagomål.docx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AB88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24704-2023 FSC-klagomål mail.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9104-2026 FSC-klagomål mail.docx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AC88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24704-2023 tillsynsbegäran.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9104-2026 tillsynsbegäran.docx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AD88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24704-2023 tillsynsbegäran mail.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9104-2026 tillsynsbegäran mail.docx", "A 9104-2026")</f>
         <v/>
       </c>
     </row>
@@ -10503,7 +10508,7 @@
         <v>46073</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10591,7 +10596,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 9745-2023</t>
+          <t>A 24701-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10605,10 +10610,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44984</v>
+        <v>45084</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10621,13 +10626,13 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -10636,7 +10641,7 @@
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -10645,58 +10650,58 @@
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S90" t="n">
         <v>1</v>
       </c>
       <c r="T90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9745-2023 artfynd.xlsx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24701-2023 artfynd.xlsx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="X90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9745-2023 karta.png", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24701-2023 karta.png", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="Y90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9745-2023 georefererad karta.tif", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24701-2023 georefererad karta.tif", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AA90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9745-2023 FSC-klagomål.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24701-2023 FSC-klagomål.docx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AB90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9745-2023 FSC-klagomål mail.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24701-2023 FSC-klagomål mail.docx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AC90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9745-2023 tillsynsbegäran.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24701-2023 tillsynsbegäran.docx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AD90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9745-2023 tillsynsbegäran mail.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24701-2023 tillsynsbegäran mail.docx", "A 24701-2023")</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 31720-2022</t>
+          <t>A 24704-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10710,10 +10715,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44776</v>
+        <v>45084</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10725,19 +10730,14 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -10746,7 +10746,7 @@
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -10755,58 +10755,58 @@
         <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S91" t="n">
         <v>1</v>
       </c>
       <c r="T91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31720-2022 artfynd.xlsx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24704-2023 artfynd.xlsx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="X91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31720-2022 karta.png", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24704-2023 karta.png", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="Y91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31720-2022 georefererad karta.tif", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24704-2023 georefererad karta.tif", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AA91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31720-2022 FSC-klagomål.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24704-2023 FSC-klagomål.docx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AB91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31720-2022 FSC-klagomål mail.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24704-2023 FSC-klagomål mail.docx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AC91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31720-2022 tillsynsbegäran.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24704-2023 tillsynsbegäran.docx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AD91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31720-2022 tillsynsbegäran mail.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24704-2023 tillsynsbegäran mail.docx", "A 24704-2023")</f>
         <v/>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 19867-2024</t>
+          <t>A 26840-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10816,14 +10816,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45433</v>
+        <v>46185</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10835,8 +10835,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -10845,13 +10850,13 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -10863,55 +10868,55 @@
         <v>1</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S92" t="n">
         <v>1</v>
       </c>
       <c r="T92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>Åkerkulla</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 19867-2024 artfynd.xlsx", "A 19867-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26840-2026 artfynd.xlsx", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="X92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 19867-2024 karta.png", "A 19867-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26840-2026 karta.png", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="Y92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 19867-2024 georefererad karta.tif", "A 19867-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26840-2026 georefererad karta.tif", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="AA92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 19867-2024 FSC-klagomål.docx", "A 19867-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26840-2026 FSC-klagomål.docx", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="AB92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 19867-2024 FSC-klagomål mail.docx", "A 19867-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26840-2026 FSC-klagomål mail.docx", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="AC92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 19867-2024 tillsynsbegäran.docx", "A 19867-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26840-2026 tillsynsbegäran.docx", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="AD92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 19867-2024 tillsynsbegäran mail.docx", "A 19867-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26840-2026 tillsynsbegäran mail.docx", "A 26840-2026")</f>
         <v/>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 26840-2026</t>
+          <t>A 28430-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10925,10 +10930,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46185</v>
+        <v>46197</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10946,7 +10951,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -10955,13 +10960,13 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -10973,48 +10978,48 @@
         <v>1</v>
       </c>
       <c r="R93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>1</v>
       </c>
       <c r="T93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="W93">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26840-2026 artfynd.xlsx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28430-2026 artfynd.xlsx", "A 28430-2026")</f>
         <v/>
       </c>
       <c r="X93">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26840-2026 karta.png", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28430-2026 karta.png", "A 28430-2026")</f>
         <v/>
       </c>
       <c r="Y93">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26840-2026 georefererad karta.tif", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28430-2026 georefererad karta.tif", "A 28430-2026")</f>
         <v/>
       </c>
       <c r="AA93">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26840-2026 FSC-klagomål.docx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28430-2026 FSC-klagomål.docx", "A 28430-2026")</f>
         <v/>
       </c>
       <c r="AB93">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26840-2026 FSC-klagomål mail.docx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28430-2026 FSC-klagomål mail.docx", "A 28430-2026")</f>
         <v/>
       </c>
       <c r="AC93">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26840-2026 tillsynsbegäran.docx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28430-2026 tillsynsbegäran.docx", "A 28430-2026")</f>
         <v/>
       </c>
       <c r="AD93">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26840-2026 tillsynsbegäran mail.docx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28430-2026 tillsynsbegäran mail.docx", "A 28430-2026")</f>
         <v/>
       </c>
     </row>
@@ -11038,7 +11043,7 @@
         <v>46196</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11131,7 +11136,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 28430-2026</t>
+          <t>A 19867-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -11141,14 +11146,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46197</v>
+        <v>45433</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11160,13 +11165,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -11199,49 +11199,49 @@
         <v>1</v>
       </c>
       <c r="T95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Åkerkulla</t>
         </is>
       </c>
       <c r="W95">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28430-2026 artfynd.xlsx", "A 28430-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 19867-2024 artfynd.xlsx", "A 19867-2024")</f>
         <v/>
       </c>
       <c r="X95">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28430-2026 karta.png", "A 28430-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 19867-2024 karta.png", "A 19867-2024")</f>
         <v/>
       </c>
       <c r="Y95">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28430-2026 georefererad karta.tif", "A 28430-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 19867-2024 georefererad karta.tif", "A 19867-2024")</f>
         <v/>
       </c>
       <c r="AA95">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28430-2026 FSC-klagomål.docx", "A 28430-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 19867-2024 FSC-klagomål.docx", "A 19867-2024")</f>
         <v/>
       </c>
       <c r="AB95">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28430-2026 FSC-klagomål mail.docx", "A 28430-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 19867-2024 FSC-klagomål mail.docx", "A 19867-2024")</f>
         <v/>
       </c>
       <c r="AC95">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28430-2026 tillsynsbegäran.docx", "A 28430-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 19867-2024 tillsynsbegäran.docx", "A 19867-2024")</f>
         <v/>
       </c>
       <c r="AD95">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28430-2026 tillsynsbegäran mail.docx", "A 28430-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 19867-2024 tillsynsbegäran mail.docx", "A 19867-2024")</f>
         <v/>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 13043-2024</t>
+          <t>A 63276-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -11255,10 +11255,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45385</v>
+        <v>45273</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11271,19 +11271,19 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N96" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S96" t="n">
         <v>1</v>
@@ -11311,42 +11311,42 @@
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Elaphomyces barrioi</t>
         </is>
       </c>
       <c r="W96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 13043-2024 artfynd.xlsx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 63276-2023 artfynd.xlsx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="X96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 13043-2024 karta.png", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 63276-2023 karta.png", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="Y96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 13043-2024 georefererad karta.tif", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 63276-2023 georefererad karta.tif", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AA96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 13043-2024 FSC-klagomål.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 63276-2023 FSC-klagomål.docx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AB96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 13043-2024 FSC-klagomål mail.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 63276-2023 FSC-klagomål mail.docx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AC96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 13043-2024 tillsynsbegäran.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 63276-2023 tillsynsbegäran.docx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AD96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 13043-2024 tillsynsbegäran mail.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 63276-2023 tillsynsbegäran mail.docx", "A 63276-2023")</f>
         <v/>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 20878-2024</t>
+          <t>A 13043-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -11360,10 +11360,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45439</v>
+        <v>45385</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J97" t="n">
         <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -11409,42 +11409,42 @@
         <v>1</v>
       </c>
       <c r="T97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 20878-2024 artfynd.xlsx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 13043-2024 artfynd.xlsx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="X97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 20878-2024 karta.png", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 13043-2024 karta.png", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="Y97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 20878-2024 georefererad karta.tif", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 13043-2024 georefererad karta.tif", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AA97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 20878-2024 FSC-klagomål.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 13043-2024 FSC-klagomål.docx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AB97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 20878-2024 FSC-klagomål mail.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 13043-2024 FSC-klagomål mail.docx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AC97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 20878-2024 tillsynsbegäran.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 13043-2024 tillsynsbegäran.docx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AD97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 20878-2024 tillsynsbegäran mail.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 13043-2024 tillsynsbegäran mail.docx", "A 13043-2024")</f>
         <v/>
       </c>
     </row>
@@ -11468,7 +11468,7 @@
         <v>46246</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>45111</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>45903</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>46185</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S 1803-2026</t>
+          <t>S 1813-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -11899,10 +11899,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11920,82 +11920,82 @@
         </is>
       </c>
       <c r="I102" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>1</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>1</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>1</v>
+      </c>
+      <c r="T102" t="n">
         <v>2</v>
       </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="n">
-        <v>1</v>
-      </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>1</v>
-      </c>
-      <c r="R102" t="n">
-        <v>1</v>
-      </c>
-      <c r="S102" t="n">
-        <v>1</v>
-      </c>
-      <c r="T102" t="n">
-        <v>1</v>
-      </c>
       <c r="U102" t="n">
         <v>0</v>
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>Purpurmusseron</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="W102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1803-2026 artfynd.xlsx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1813-2026 artfynd.xlsx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="X102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1803-2026 karta.png", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1813-2026 karta.png", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="Y102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1803-2026 georefererad karta.tif", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1813-2026 georefererad karta.tif", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AA102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1803-2026 FSC-klagomål.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1813-2026 FSC-klagomål.docx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AB102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1803-2026 FSC-klagomål mail.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1813-2026 FSC-klagomål mail.docx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AC102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1803-2026 tillsynsbegäran.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1813-2026 tillsynsbegäran.docx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AD102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1803-2026 tillsynsbegäran mail.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1813-2026 tillsynsbegäran mail.docx", "S 1813-2026")</f>
         <v/>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S 1813-2026</t>
+          <t>S 1803-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -12009,10 +12009,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -12039,10 +12039,10 @@
         <v>0</v>
       </c>
       <c r="L103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N103" t="n">
         <v>0</v>
@@ -12057,48 +12057,48 @@
         <v>1</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S103" t="n">
         <v>1</v>
       </c>
       <c r="T103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
       </c>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Purpurmusseron</t>
         </is>
       </c>
       <c r="W103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1813-2026 artfynd.xlsx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1803-2026 artfynd.xlsx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="X103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1813-2026 karta.png", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1803-2026 karta.png", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="Y103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1813-2026 georefererad karta.tif", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1803-2026 georefererad karta.tif", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AA103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1813-2026 FSC-klagomål.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1803-2026 FSC-klagomål.docx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AB103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1813-2026 FSC-klagomål mail.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1803-2026 FSC-klagomål mail.docx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AC103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1813-2026 tillsynsbegäran.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1803-2026 tillsynsbegäran.docx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AD103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1813-2026 tillsynsbegäran mail.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1803-2026 tillsynsbegäran mail.docx", "S 1803-2026")</f>
         <v/>
       </c>
     </row>
@@ -12122,7 +12122,7 @@
         <v>46246</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44783</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>44747</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>44840</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>44783</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>44501</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>44477</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>44742</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44503</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 3878-2023</t>
+          <t>A 31699-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -12823,10 +12823,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44951</v>
+        <v>44776</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12838,8 +12838,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -12882,7 +12887,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 12937-2022</t>
+          <t>A 26160-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12892,14 +12897,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44642</v>
+        <v>45468</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12911,13 +12916,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -12956,11 +12956,35 @@
         <v>0</v>
       </c>
       <c r="V114" s="2" t="inlineStr"/>
+      <c r="X114">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26160-2024 karta.png", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="Y114">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26160-2024 georefererad karta.tif", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AA114">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26160-2024 FSC-klagomål.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AB114">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26160-2024 FSC-klagomål mail.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AC114">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26160-2024 tillsynsbegäran.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AD114">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26160-2024 tillsynsbegäran mail.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 22785-2025</t>
+          <t>A 40339-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -12974,10 +12998,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45789</v>
+        <v>45169</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12990,7 +13014,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -13033,7 +13057,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 40339-2023</t>
+          <t>A 26190-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -13047,10 +13071,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45169</v>
+        <v>45805</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13063,7 +13087,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -13106,7 +13130,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 26190-2025</t>
+          <t>A 41950-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -13120,10 +13144,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45805</v>
+        <v>45903</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13136,7 +13160,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -13179,7 +13203,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 41950-2025</t>
+          <t>A 4159-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13193,10 +13217,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45903</v>
+        <v>45323</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13209,7 +13233,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -13252,7 +13276,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 64303-2023</t>
+          <t>A 45869-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -13262,14 +13286,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45280</v>
+        <v>45923</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13282,7 +13306,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -13325,7 +13349,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 45869-2025</t>
+          <t>A 46845-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -13335,14 +13359,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45923</v>
+        <v>45928</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13355,7 +13379,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -13398,7 +13422,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 55367-2024</t>
+          <t>A 36269-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -13412,10 +13436,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45621</v>
+        <v>45867</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13427,8 +13451,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -13471,7 +13500,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 46845-2025</t>
+          <t>A 4165-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -13481,14 +13510,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45928</v>
+        <v>44953</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13501,7 +13530,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -13544,7 +13573,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 36269-2025</t>
+          <t>A 9259-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -13558,10 +13587,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45867</v>
+        <v>46070</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13573,13 +13602,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -13622,7 +13646,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 4159-2024</t>
+          <t>A 32921-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -13636,10 +13660,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45323</v>
+        <v>45125</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13652,7 +13676,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -13695,7 +13719,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 32921-2023</t>
+          <t>A 15272-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -13705,14 +13729,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45125</v>
+        <v>46105</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13722,6 +13746,11 @@
       <c r="G125" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I125" t="n">
@@ -13768,7 +13797,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 31699-2022</t>
+          <t>A 15279-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -13778,14 +13807,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44776</v>
+        <v>46105</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13803,7 +13832,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -13846,7 +13875,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 1614-2025</t>
+          <t>A 15264-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -13856,14 +13885,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45670</v>
+        <v>46105</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13875,8 +13904,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -13919,7 +13953,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 9259-2026</t>
+          <t>A 64303-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -13929,14 +13963,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46070</v>
+        <v>45280</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13949,7 +13983,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -13992,7 +14026,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 9076-2025</t>
+          <t>A 43603-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -14006,10 +14040,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45713</v>
+        <v>45569</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14021,13 +14055,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -14070,7 +14099,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 1757-2025</t>
+          <t>A 63075-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -14080,14 +14109,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45671</v>
+        <v>45273</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14100,7 +14129,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -14143,7 +14172,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 15272-2026</t>
+          <t>A 1757-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -14153,14 +14182,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46105</v>
+        <v>45671</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14172,13 +14201,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -14221,7 +14245,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 15279-2026</t>
+          <t>A 34780-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -14231,14 +14255,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46105</v>
+        <v>44795</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14256,7 +14280,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>4.6</v>
+        <v>6.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -14299,7 +14323,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 15264-2026</t>
+          <t>A 55367-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -14309,14 +14333,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46105</v>
+        <v>45621</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14328,13 +14352,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -14377,7 +14396,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 9050-2025</t>
+          <t>A 20287-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -14391,10 +14410,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45713</v>
+        <v>45774</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14406,13 +14425,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -14455,7 +14469,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 43603-2024</t>
+          <t>A 9076-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -14469,10 +14483,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45569</v>
+        <v>45713</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14484,8 +14498,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -14545,7 +14564,7 @@
         <v>45812</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14623,7 +14642,7 @@
         <v>45348</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14696,7 +14715,7 @@
         <v>45125</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14769,7 +14788,7 @@
         <v>46169</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14830,7 +14849,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 5175-2024</t>
+          <t>A 34951-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -14840,14 +14859,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45330</v>
+        <v>44796</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14859,8 +14878,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -14903,7 +14927,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 34951-2022</t>
+          <t>A 5175-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -14913,14 +14937,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44796</v>
+        <v>45330</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14932,13 +14956,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -14981,7 +15000,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 13383-2023</t>
+          <t>A 28380-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -14991,14 +15010,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45005</v>
+        <v>46196</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15010,8 +15029,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -15054,7 +15078,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 61438-2023</t>
+          <t>A 28381-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -15064,14 +15088,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45264</v>
+        <v>46196</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15083,8 +15107,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -15127,7 +15156,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 13041-2024</t>
+          <t>A 28411-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -15137,14 +15166,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45385</v>
+        <v>46197</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15154,6 +15183,11 @@
       <c r="G144" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I144" t="n">
@@ -15200,7 +15234,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 4165-2023</t>
+          <t>A 3878-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -15214,10 +15248,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44953</v>
+        <v>44951</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15230,7 +15264,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -15273,7 +15307,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 28381-2026</t>
+          <t>A 29413-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -15287,10 +15321,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46196</v>
+        <v>46203</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15308,7 +15342,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -15351,7 +15385,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 28380-2026</t>
+          <t>A 29414-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -15365,10 +15399,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46196</v>
+        <v>46203</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15386,7 +15420,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -15429,7 +15463,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 28411-2026</t>
+          <t>A 29431-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -15443,10 +15477,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46197</v>
+        <v>46203</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15464,7 +15498,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -15507,7 +15541,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 29413-2026</t>
+          <t>A 29410-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -15524,7 +15558,7 @@
         <v>46203</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15542,7 +15576,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -15585,7 +15619,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 29414-2026</t>
+          <t>A 13383-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -15595,14 +15629,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46203</v>
+        <v>45005</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15614,13 +15648,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -15663,7 +15692,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 29431-2026</t>
+          <t>A 12937-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -15673,14 +15702,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46203</v>
+        <v>44642</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15698,7 +15727,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -15741,7 +15770,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 29410-2026</t>
+          <t>A 61438-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -15751,14 +15780,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46203</v>
+        <v>45264</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15770,13 +15799,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -15819,7 +15843,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 34780-2022</t>
+          <t>A 13041-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -15833,10 +15857,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44795</v>
+        <v>45385</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15848,13 +15872,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>6.7</v>
+        <v>0.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -15897,7 +15916,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 20287-2025</t>
+          <t>A 1614-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -15907,14 +15926,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45774</v>
+        <v>45670</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15927,7 +15946,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -15970,7 +15989,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 26160-2024</t>
+          <t>A 9050-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -15980,14 +15999,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45468</v>
+        <v>45713</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15999,8 +16018,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -16039,35 +16063,11 @@
         <v>0</v>
       </c>
       <c r="V155" s="2" t="inlineStr"/>
-      <c r="X155">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26160-2024 karta.png", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="Y155">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26160-2024 georefererad karta.tif", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AA155">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26160-2024 FSC-klagomål.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AB155">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26160-2024 FSC-klagomål mail.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AC155">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26160-2024 tillsynsbegäran.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AD155">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26160-2024 tillsynsbegäran mail.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
     </row>
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 63075-2023</t>
+          <t>A 22785-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -16077,14 +16077,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45273</v>
+        <v>45789</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -16157,7 +16157,7 @@
         <v>46169</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44756</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>45713</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45812</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>45812</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>45754</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>46105</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>46105</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>46169</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S 1806-2026</t>
+          <t>S 1812-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -16846,10 +16846,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -16910,7 +16910,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S 1807-2026</t>
+          <t>S 1806-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -16927,7 +16927,7 @@
         <v>46196</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -16988,7 +16988,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S 1812-2026</t>
+          <t>S 1807-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -17002,10 +17002,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>46203</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>46203</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>46203</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>46203</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>

--- a/Översikt BORGHOLM.xlsx
+++ b/Översikt BORGHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45029</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>44704</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45433</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>44903</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45903</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>46254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44809</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>44523</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>45107</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44781</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>45161</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>45146</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45918</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>45930</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45918</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12534-2022</t>
+          <t>A 13558-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44638</v>
+        <v>45736</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3233,19 +3233,19 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>8.6</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3260,18 +3260,130 @@
         <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
       </c>
       <c r="T23" t="n">
+        <v>8</v>
+      </c>
+      <c r="U23" t="n">
+        <v>8</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Honungsblomster
+Backruta
+Jordtistel
+Stallört
+Ängsstarr
+Tvåblad
+Kärrknipprot
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 13558-2025 artfynd.xlsx", "A 13558-2025")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 13558-2025 karta.png", "A 13558-2025")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 13558-2025 georefererad karta.tif", "A 13558-2025")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 13558-2025 FSC-klagomål.docx", "A 13558-2025")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 13558-2025 FSC-klagomål mail.docx", "A 13558-2025")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 13558-2025 tillsynsbegäran.docx", "A 13558-2025")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 13558-2025 tillsynsbegäran mail.docx", "A 13558-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 12534-2022</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>44638</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>5</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>8</v>
+      </c>
+      <c r="T24" t="n">
         <v>9</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>9</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Backklöver
 Backtimjan
@@ -3283,151 +3395,39 @@
 Sankt pers nycklar</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 12534-2022 artfynd.xlsx", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 12534-2022 karta.png", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 12534-2022 georefererad karta.tif", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 12534-2022 FSC-klagomål.docx", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 12534-2022 FSC-klagomål mail.docx", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 12534-2022 tillsynsbegäran.docx", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 12534-2022 tillsynsbegäran mail.docx", "A 12534-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 13558-2025</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45736</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J24" t="n">
-        <v>4</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>4</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>8</v>
-      </c>
-      <c r="T24" t="n">
-        <v>8</v>
-      </c>
-      <c r="U24" t="n">
-        <v>8</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Honungsblomster
-Backruta
-Jordtistel
-Stallört
-Ängsstarr
-Tvåblad
-Kärrknipprot
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 13558-2025 artfynd.xlsx", "A 13558-2025")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 13558-2025 karta.png", "A 13558-2025")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 13558-2025 georefererad karta.tif", "A 13558-2025")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 13558-2025 FSC-klagomål.docx", "A 13558-2025")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 13558-2025 FSC-klagomål mail.docx", "A 13558-2025")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 13558-2025 tillsynsbegäran.docx", "A 13558-2025")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 13558-2025 tillsynsbegäran mail.docx", "A 13558-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31515-2026</t>
+          <t>A 31399-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46223</v>
+        <v>46220</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3456,19 +3456,14 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
         <v>3</v>
@@ -3495,12 +3490,129 @@
         <v>8</v>
       </c>
       <c r="T25" t="n">
+        <v>8</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Backklöver
+Jordtistel
+Stallört
+Flugblomster
+Tvåblad
+Grönvit nattviol
+Krutbrännare
+Vanliga ängsnycklar</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31399-2026 artfynd.xlsx", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31399-2026 karta.png", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31399-2026 georefererad karta.tif", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31399-2026 FSC-klagomål.docx", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31399-2026 FSC-klagomål mail.docx", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31399-2026 tillsynsbegäran.docx", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31399-2026 tillsynsbegäran mail.docx", "A 31399-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 31515-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3</v>
+      </c>
+      <c r="L26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>8</v>
+      </c>
+      <c r="T26" t="n">
         <v>10</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Blå slemspindling
 Sårläka
@@ -3512,112 +3624,112 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31515-2026 artfynd.xlsx", "A 31515-2026")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31515-2026 karta.png", "A 31515-2026")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31515-2026 georefererad karta.tif", "A 31515-2026")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31515-2026 FSC-klagomål.docx", "A 31515-2026")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31515-2026 FSC-klagomål mail.docx", "A 31515-2026")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31515-2026 tillsynsbegäran.docx", "A 31515-2026")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31515-2026 tillsynsbegäran mail.docx", "A 31515-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>A 31516-2026</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D26" s="1" t="n">
+      <c r="D27" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="E27" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="I27" t="n">
         <v>0.8</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J27" t="n">
         <v>3</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K27" t="n">
         <v>3</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L27" t="n">
         <v>3</v>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>3</v>
       </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>8</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T27" t="n">
         <v>10</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Blå slemspindling
 Sårläka
@@ -3629,144 +3741,32 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31516-2026 artfynd.xlsx", "A 31516-2026")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31516-2026 karta.png", "A 31516-2026")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31516-2026 georefererad karta.tif", "A 31516-2026")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31516-2026 FSC-klagomål.docx", "A 31516-2026")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31516-2026 FSC-klagomål mail.docx", "A 31516-2026")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31516-2026 tillsynsbegäran.docx", "A 31516-2026")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31516-2026 tillsynsbegäran mail.docx", "A 31516-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 31399-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J27" t="n">
-        <v>5</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2</v>
-      </c>
-      <c r="L27" t="n">
-        <v>3</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>8</v>
-      </c>
-      <c r="T27" t="n">
-        <v>8</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Backklöver
-Jordtistel
-Stallört
-Flugblomster
-Tvåblad
-Grönvit nattviol
-Krutbrännare
-Vanliga ängsnycklar</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31399-2026 artfynd.xlsx", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31399-2026 karta.png", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31399-2026 georefererad karta.tif", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31399-2026 FSC-klagomål.docx", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31399-2026 FSC-klagomål mail.docx", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31399-2026 tillsynsbegäran.docx", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31399-2026 tillsynsbegäran mail.docx", "A 31399-2026")</f>
         <v/>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45175</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>45027</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>45926</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>46188</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>46224</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>44704</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45478</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>46188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>46224</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>44482</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>46169</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>46169</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13556-2025</t>
+          <t>A 4164-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45736</v>
+        <v>44953</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5501,22 +5501,22 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
         <v>2</v>
       </c>
-      <c r="K43" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" t="n">
-        <v>1</v>
-      </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5528,18 +5528,342 @@
         <v>2</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U43" t="n">
         <v>4</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>Crepis tectorum subsp. tectorum
+Kösa
+Murgröna
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 4164-2023 artfynd.xlsx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="X43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 4164-2023 karta.png", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="Y43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 4164-2023 georefererad karta.tif", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AA43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 4164-2023 FSC-klagomål.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AB43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 4164-2023 FSC-klagomål mail.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AC43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 4164-2023 tillsynsbegäran.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AD43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 4164-2023 tillsynsbegäran mail.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>A 21797-2024</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>45442</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>4</v>
+      </c>
+      <c r="T44" t="n">
+        <v>11</v>
+      </c>
+      <c r="U44" t="n">
+        <v>6</v>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Sydlig kantmusseron
+Murgröna
+Skogsknipprot
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21797-2024 artfynd.xlsx", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="X44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21797-2024 karta.png", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="Y44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21797-2024 georefererad karta.tif", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="AA44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21797-2024 FSC-klagomål.docx", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="AB44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21797-2024 FSC-klagomål mail.docx", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="AC44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21797-2024 tillsynsbegäran.docx", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="AD44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21797-2024 tillsynsbegäran mail.docx", "A 21797-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A 7960-2023</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>44973</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" t="n">
+        <v>4</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>Vresalm
+Pilfotsspindling
+Vippärt
+Strävlosta</t>
+        </is>
+      </c>
+      <c r="W45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 7960-2023 artfynd.xlsx", "A 7960-2023")</f>
+        <v/>
+      </c>
+      <c r="X45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 7960-2023 karta.png", "A 7960-2023")</f>
+        <v/>
+      </c>
+      <c r="Y45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 7960-2023 georefererad karta.tif", "A 7960-2023")</f>
+        <v/>
+      </c>
+      <c r="AA45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 7960-2023 FSC-klagomål.docx", "A 7960-2023")</f>
+        <v/>
+      </c>
+      <c r="AB45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 7960-2023 FSC-klagomål mail.docx", "A 7960-2023")</f>
+        <v/>
+      </c>
+      <c r="AC45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 7960-2023 tillsynsbegäran.docx", "A 7960-2023")</f>
+        <v/>
+      </c>
+      <c r="AD45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 7960-2023 tillsynsbegäran mail.docx", "A 7960-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A 13556-2025</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>45736</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>4</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
         <is>
           <t>Ask
 Sårläka
@@ -5547,220 +5871,112 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="W43">
+      <c r="W46">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 13556-2025 artfynd.xlsx", "A 13556-2025")</f>
         <v/>
       </c>
-      <c r="X43">
+      <c r="X46">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 13556-2025 karta.png", "A 13556-2025")</f>
         <v/>
       </c>
-      <c r="Y43">
+      <c r="Y46">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 13556-2025 georefererad karta.tif", "A 13556-2025")</f>
         <v/>
       </c>
-      <c r="AA43">
+      <c r="AA46">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 13556-2025 FSC-klagomål.docx", "A 13556-2025")</f>
         <v/>
       </c>
-      <c r="AB43">
+      <c r="AB46">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 13556-2025 FSC-klagomål mail.docx", "A 13556-2025")</f>
         <v/>
       </c>
-      <c r="AC43">
+      <c r="AC46">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 13556-2025 tillsynsbegäran.docx", "A 13556-2025")</f>
         <v/>
       </c>
-      <c r="AD43">
+      <c r="AD46">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 13556-2025 tillsynsbegäran mail.docx", "A 13556-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>A 21797-2024</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>A 27290-2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="n">
-        <v>45442</v>
-      </c>
-      <c r="E44" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F44" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J44" t="n">
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J47" t="n">
         <v>2</v>
       </c>
-      <c r="K44" t="n">
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
         <v>2</v>
       </c>
-      <c r="L44" t="n">
-        <v>1</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>1</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
+      <c r="R47" t="n">
+        <v>2</v>
+      </c>
+      <c r="S47" t="n">
         <v>4</v>
       </c>
-      <c r="T44" t="n">
-        <v>11</v>
-      </c>
-      <c r="U44" t="n">
-        <v>6</v>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>Sydlig kantmusseron
-Murgröna
-Skogsknipprot
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21797-2024 artfynd.xlsx", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21797-2024 karta.png", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21797-2024 georefererad karta.tif", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21797-2024 FSC-klagomål.docx", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21797-2024 FSC-klagomål mail.docx", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21797-2024 tillsynsbegäran.docx", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21797-2024 tillsynsbegäran mail.docx", "A 21797-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>A 27290-2026</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E45" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>1</v>
-      </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>2</v>
-      </c>
-      <c r="R45" t="n">
-        <v>2</v>
-      </c>
-      <c r="S45" t="n">
+      <c r="T47" t="n">
         <v>4</v>
       </c>
-      <c r="T45" t="n">
-        <v>4</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
         <is>
           <t>Ask
 Gotlandsmåra
@@ -5768,252 +5984,36 @@
 Havsörn</t>
         </is>
       </c>
-      <c r="W45">
+      <c r="W47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27290-2026 artfynd.xlsx", "A 27290-2026")</f>
         <v/>
       </c>
-      <c r="X45">
+      <c r="X47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27290-2026 karta.png", "A 27290-2026")</f>
         <v/>
       </c>
-      <c r="Y45">
+      <c r="Y47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27290-2026 georefererad karta.tif", "A 27290-2026")</f>
         <v/>
       </c>
-      <c r="AA45">
+      <c r="AA47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27290-2026 FSC-klagomål.docx", "A 27290-2026")</f>
         <v/>
       </c>
-      <c r="AB45">
+      <c r="AB47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27290-2026 FSC-klagomål mail.docx", "A 27290-2026")</f>
         <v/>
       </c>
-      <c r="AC45">
+      <c r="AC47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27290-2026 tillsynsbegäran.docx", "A 27290-2026")</f>
         <v/>
       </c>
-      <c r="AD45">
+      <c r="AD47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27290-2026 tillsynsbegäran mail.docx", "A 27290-2026")</f>
         <v/>
       </c>
-      <c r="AE45">
+      <c r="AE47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 27290-2026 prioriterade fågelarter.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>A 4164-2023</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>44953</v>
-      </c>
-      <c r="E46" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" t="n">
-        <v>2</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>2</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>4</v>
-      </c>
-      <c r="T46" t="n">
-        <v>5</v>
-      </c>
-      <c r="U46" t="n">
-        <v>4</v>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>Crepis tectorum subsp. tectorum
-Kösa
-Murgröna
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 4164-2023 artfynd.xlsx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 4164-2023 karta.png", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 4164-2023 georefererad karta.tif", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 4164-2023 FSC-klagomål.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 4164-2023 FSC-klagomål mail.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 4164-2023 tillsynsbegäran.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 4164-2023 tillsynsbegäran mail.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>A 7960-2023</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>44973</v>
-      </c>
-      <c r="E47" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" t="n">
-        <v>2</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>3</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1</v>
-      </c>
-      <c r="S47" t="n">
-        <v>4</v>
-      </c>
-      <c r="T47" t="n">
-        <v>4</v>
-      </c>
-      <c r="U47" t="n">
-        <v>3</v>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>Vresalm
-Pilfotsspindling
-Vippärt
-Strävlosta</t>
-        </is>
-      </c>
-      <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 7960-2023 artfynd.xlsx", "A 7960-2023")</f>
-        <v/>
-      </c>
-      <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 7960-2023 karta.png", "A 7960-2023")</f>
-        <v/>
-      </c>
-      <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 7960-2023 georefererad karta.tif", "A 7960-2023")</f>
-        <v/>
-      </c>
-      <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 7960-2023 FSC-klagomål.docx", "A 7960-2023")</f>
-        <v/>
-      </c>
-      <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 7960-2023 FSC-klagomål mail.docx", "A 7960-2023")</f>
-        <v/>
-      </c>
-      <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 7960-2023 tillsynsbegäran.docx", "A 7960-2023")</f>
-        <v/>
-      </c>
-      <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 7960-2023 tillsynsbegäran mail.docx", "A 7960-2023")</f>
         <v/>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
         <v>44704</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44704</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44783</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 24048-2025</t>
+          <t>A 32174-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6358,14 +6358,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45796</v>
+        <v>44781</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6377,17 +6377,22 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I51" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J51" t="n">
         <v>2</v>
       </c>
-      <c r="J51" t="n">
-        <v>1</v>
-      </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -6402,7 +6407,7 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -6411,1247 +6416,1242 @@
         <v>3</v>
       </c>
       <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>Backklöver
+Tvåblad
+Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="W51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 32174-2022 artfynd.xlsx", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="X51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 32174-2022 karta.png", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="Y51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 32174-2022 georefererad karta.tif", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="AA51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 32174-2022 FSC-klagomål.docx", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="AB51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 32174-2022 FSC-klagomål mail.docx", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="AC51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 32174-2022 tillsynsbegäran.docx", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="AD51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 32174-2022 tillsynsbegäran mail.docx", "A 32174-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>A 43756-2022</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>44837</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3</v>
+      </c>
+      <c r="T52" t="n">
         <v>5</v>
       </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
+      <c r="U52" t="n">
+        <v>5</v>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>Murgröna
+Blåsippa
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 43756-2022 artfynd.xlsx", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="X52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 43756-2022 karta.png", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="Y52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 43756-2022 georefererad karta.tif", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="AA52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 43756-2022 FSC-klagomål.docx", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="AB52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 43756-2022 FSC-klagomål mail.docx", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="AC52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 43756-2022 tillsynsbegäran.docx", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="AD52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 43756-2022 tillsynsbegäran mail.docx", "A 43756-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>A 24048-2025</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>45796</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>2</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>2</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>3</v>
+      </c>
+      <c r="T53" t="n">
+        <v>5</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
         <is>
           <t>Loppstarr
 Ängsstarr
 Kärrknipprot</t>
         </is>
       </c>
-      <c r="W51">
+      <c r="W53">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24048-2025 artfynd.xlsx", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="X51">
+      <c r="X53">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24048-2025 karta.png", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="Y51">
+      <c r="Y53">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24048-2025 georefererad karta.tif", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="AA51">
+      <c r="AA53">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24048-2025 FSC-klagomål.docx", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="AB51">
+      <c r="AB53">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24048-2025 FSC-klagomål mail.docx", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="AC51">
+      <c r="AC53">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24048-2025 tillsynsbegäran.docx", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="AD51">
+      <c r="AD53">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24048-2025 tillsynsbegäran mail.docx", "A 24048-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>A 38860-2025</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D52" s="1" t="n">
+      <c r="D54" s="1" t="n">
         <v>45887</v>
       </c>
-      <c r="E52" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F52" t="inlineStr">
+      <c r="E54" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="I52" t="n">
+      <c r="I54" t="n">
         <v>5.6</v>
       </c>
-      <c r="J52" t="n">
+      <c r="J54" t="n">
         <v>2</v>
       </c>
-      <c r="K52" t="n">
-        <v>1</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>1</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>1</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1</v>
-      </c>
-      <c r="S52" t="n">
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" t="n">
         <v>3</v>
       </c>
-      <c r="T52" t="n">
+      <c r="T54" t="n">
         <v>3</v>
       </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsknipprot
 Revlummer</t>
         </is>
       </c>
-      <c r="W52">
+      <c r="W54">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 38860-2025 artfynd.xlsx", "A 38860-2025")</f>
         <v/>
       </c>
-      <c r="X52">
+      <c r="X54">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 38860-2025 karta.png", "A 38860-2025")</f>
         <v/>
       </c>
-      <c r="Y52">
+      <c r="Y54">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 38860-2025 georefererad karta.tif", "A 38860-2025")</f>
         <v/>
       </c>
-      <c r="AA52">
+      <c r="AA54">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 38860-2025 FSC-klagomål.docx", "A 38860-2025")</f>
         <v/>
       </c>
-      <c r="AB52">
+      <c r="AB54">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 38860-2025 FSC-klagomål mail.docx", "A 38860-2025")</f>
         <v/>
       </c>
-      <c r="AC52">
+      <c r="AC54">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 38860-2025 tillsynsbegäran.docx", "A 38860-2025")</f>
         <v/>
       </c>
-      <c r="AD52">
+      <c r="AD54">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 38860-2025 tillsynsbegäran mail.docx", "A 38860-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>A 43542-2025</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D53" s="1" t="n">
+      <c r="D55" s="1" t="n">
         <v>45911</v>
       </c>
-      <c r="E53" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F53" t="inlineStr">
+      <c r="E55" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="I53" t="n">
+      <c r="I55" t="n">
         <v>2.4</v>
       </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" t="n">
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" t="n">
         <v>2</v>
       </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
         <v>2</v>
       </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
         <v>3</v>
       </c>
-      <c r="T53" t="n">
+      <c r="T55" t="n">
         <v>3</v>
       </c>
-      <c r="U53" t="n">
+      <c r="U55" t="n">
         <v>3</v>
       </c>
-      <c r="V53" s="2" t="inlineStr">
+      <c r="V55" s="2" t="inlineStr">
         <is>
           <t>Vårärt
 Ängsskära
 Underviol</t>
         </is>
       </c>
-      <c r="W53">
+      <c r="W55">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 43542-2025 artfynd.xlsx", "A 43542-2025")</f>
         <v/>
       </c>
-      <c r="X53">
+      <c r="X55">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 43542-2025 karta.png", "A 43542-2025")</f>
         <v/>
       </c>
-      <c r="Y53">
+      <c r="Y55">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 43542-2025 georefererad karta.tif", "A 43542-2025")</f>
         <v/>
       </c>
-      <c r="AA53">
+      <c r="AA55">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 43542-2025 FSC-klagomål.docx", "A 43542-2025")</f>
         <v/>
       </c>
-      <c r="AB53">
+      <c r="AB55">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 43542-2025 FSC-klagomål mail.docx", "A 43542-2025")</f>
         <v/>
       </c>
-      <c r="AC53">
+      <c r="AC55">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 43542-2025 tillsynsbegäran.docx", "A 43542-2025")</f>
         <v/>
       </c>
-      <c r="AD53">
+      <c r="AD55">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 43542-2025 tillsynsbegäran mail.docx", "A 43542-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>A 32174-2022</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>A 15285-2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D54" s="1" t="n">
-        <v>44781</v>
-      </c>
-      <c r="E54" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F54" t="inlineStr">
+      <c r="D56" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I54" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2</v>
-      </c>
-      <c r="K54" t="n">
-        <v>2</v>
-      </c>
-      <c r="L54" t="n">
-        <v>1</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>1</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
+      <c r="I56" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J56" t="n">
         <v>3</v>
       </c>
-      <c r="T54" t="n">
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
         <v>3</v>
       </c>
-      <c r="U54" t="n">
+      <c r="T56" t="n">
         <v>3</v>
       </c>
-      <c r="V54" s="2" t="inlineStr">
-        <is>
-          <t>Backklöver
-Tvåblad
-Vit skogslilja</t>
-        </is>
-      </c>
-      <c r="W54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 32174-2022 artfynd.xlsx", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="X54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 32174-2022 karta.png", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="Y54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 32174-2022 georefererad karta.tif", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="AA54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 32174-2022 FSC-klagomål.docx", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="AB54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 32174-2022 FSC-klagomål mail.docx", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="AC54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 32174-2022 tillsynsbegäran.docx", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="AD54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 32174-2022 tillsynsbegäran mail.docx", "A 32174-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>A 15285-2026</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D55" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E55" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J55" t="n">
-        <v>3</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>1</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>1</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>3</v>
-      </c>
-      <c r="T55" t="n">
-        <v>3</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" s="2" t="inlineStr">
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Havsörn
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W55">
+      <c r="W56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 15285-2026 artfynd.xlsx", "A 15285-2026")</f>
         <v/>
       </c>
-      <c r="X55">
+      <c r="X56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 15285-2026 karta.png", "A 15285-2026")</f>
         <v/>
       </c>
-      <c r="Y55">
+      <c r="Y56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 15285-2026 georefererad karta.tif", "A 15285-2026")</f>
         <v/>
       </c>
-      <c r="AA55">
+      <c r="AA56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 15285-2026 FSC-klagomål.docx", "A 15285-2026")</f>
         <v/>
       </c>
-      <c r="AB55">
+      <c r="AB56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 15285-2026 FSC-klagomål mail.docx", "A 15285-2026")</f>
         <v/>
       </c>
-      <c r="AC55">
+      <c r="AC56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 15285-2026 tillsynsbegäran.docx", "A 15285-2026")</f>
         <v/>
       </c>
-      <c r="AD55">
+      <c r="AD56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 15285-2026 tillsynsbegäran mail.docx", "A 15285-2026")</f>
         <v/>
       </c>
-      <c r="AE55">
+      <c r="AE56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 15285-2026 prioriterade fågelarter.docx", "A 15285-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>A 27283-2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>2</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>2</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Mindre poppelglasvinge
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27283-2026 artfynd.xlsx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="X57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27283-2026 karta.png", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="Y57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27283-2026 georefererad karta.tif", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AA57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27283-2026 FSC-klagomål.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AB57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27283-2026 FSC-klagomål mail.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AC57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27283-2026 tillsynsbegäran.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AD57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27283-2026 tillsynsbegäran mail.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>A 26849-2026</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D56" s="1" t="n">
+      <c r="D58" s="1" t="n">
         <v>46185</v>
       </c>
-      <c r="E56" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F56" t="inlineStr">
+      <c r="E58" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I56" t="n">
+      <c r="I58" t="n">
         <v>8.1</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J58" t="n">
         <v>2</v>
       </c>
-      <c r="K56" t="n">
+      <c r="K58" t="n">
         <v>3</v>
       </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
         <v>3</v>
       </c>
-      <c r="T56" t="n">
+      <c r="T58" t="n">
         <v>3</v>
       </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" s="2" t="inlineStr">
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
         <is>
           <t>Myskmadra
 Purpurknipprot
 Vit skogslilja</t>
         </is>
       </c>
-      <c r="W56">
+      <c r="W58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26849-2026 artfynd.xlsx", "A 26849-2026")</f>
         <v/>
       </c>
-      <c r="X56">
+      <c r="X58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26849-2026 karta.png", "A 26849-2026")</f>
         <v/>
       </c>
-      <c r="Y56">
+      <c r="Y58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26849-2026 georefererad karta.tif", "A 26849-2026")</f>
         <v/>
       </c>
-      <c r="AA56">
+      <c r="AA58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26849-2026 FSC-klagomål.docx", "A 26849-2026")</f>
         <v/>
       </c>
-      <c r="AB56">
+      <c r="AB58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26849-2026 FSC-klagomål mail.docx", "A 26849-2026")</f>
         <v/>
       </c>
-      <c r="AC56">
+      <c r="AC58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26849-2026 tillsynsbegäran.docx", "A 26849-2026")</f>
         <v/>
       </c>
-      <c r="AD56">
+      <c r="AD58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26849-2026 tillsynsbegäran mail.docx", "A 26849-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>A 27283-2026</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>A 31520-2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D57" s="1" t="n">
+      <c r="D59" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>3</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>3</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Grönsiska
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31520-2026 artfynd.xlsx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="X59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31520-2026 karta.png", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31520-2026 georefererad karta.tif", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31520-2026 FSC-klagomål.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31520-2026 FSC-klagomål mail.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31520-2026 tillsynsbegäran.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31520-2026 tillsynsbegäran mail.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AE59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 31520-2026 prioriterade fågelarter.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>S 846-2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>3</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Havsörn
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 846-2026 artfynd.xlsx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="X60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 846-2026 karta.png", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="Y60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 846-2026 georefererad karta.tif", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AA60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 846-2026 FSC-klagomål.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AB60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 846-2026 FSC-klagomål mail.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AC60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 846-2026 tillsynsbegäran.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AD60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 846-2026 tillsynsbegäran mail.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AE60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/S 846-2026 prioriterade fågelarter.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>S 1726-2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="n">
         <v>46188</v>
       </c>
-      <c r="E57" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F57" t="inlineStr">
+      <c r="E61" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I57" t="n">
+      <c r="I61" t="n">
         <v>2</v>
       </c>
-      <c r="J57" t="n">
-        <v>1</v>
-      </c>
-      <c r="K57" t="n">
-        <v>1</v>
-      </c>
-      <c r="L57" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>1</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
         <v>2</v>
       </c>
-      <c r="R57" t="n">
-        <v>1</v>
-      </c>
-      <c r="S57" t="n">
+      <c r="R61" t="n">
+        <v>1</v>
+      </c>
+      <c r="S61" t="n">
         <v>3</v>
       </c>
-      <c r="T57" t="n">
+      <c r="T61" t="n">
         <v>3</v>
       </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" s="2" t="inlineStr">
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
         <is>
           <t>Ask
 Mindre poppelglasvinge
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27283-2026 artfynd.xlsx", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="X57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27283-2026 karta.png", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="Y57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27283-2026 georefererad karta.tif", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="AA57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27283-2026 FSC-klagomål.docx", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="AB57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27283-2026 FSC-klagomål mail.docx", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="AC57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27283-2026 tillsynsbegäran.docx", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="AD57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27283-2026 tillsynsbegäran mail.docx", "A 27283-2026")</f>
+      <c r="W61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1726-2026 artfynd.xlsx", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="X61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1726-2026 karta.png", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="Y61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1726-2026 georefererad karta.tif", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="AA61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1726-2026 FSC-klagomål.docx", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="AB61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1726-2026 FSC-klagomål mail.docx", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="AC61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1726-2026 tillsynsbegäran.docx", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="AD61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1726-2026 tillsynsbegäran mail.docx", "S 1726-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>A 43756-2022</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="n">
-        <v>44837</v>
-      </c>
-      <c r="E58" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F58" t="inlineStr">
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>S 2059-2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E62" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="I58" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2</v>
-      </c>
-      <c r="K58" t="n">
-        <v>1</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J62" t="n">
         <v>3</v>
       </c>
-      <c r="T58" t="n">
-        <v>5</v>
-      </c>
-      <c r="U58" t="n">
-        <v>5</v>
-      </c>
-      <c r="V58" s="2" t="inlineStr">
-        <is>
-          <t>Murgröna
-Blåsippa
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 43756-2022 artfynd.xlsx", "A 43756-2022")</f>
-        <v/>
-      </c>
-      <c r="X58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 43756-2022 karta.png", "A 43756-2022")</f>
-        <v/>
-      </c>
-      <c r="Y58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 43756-2022 georefererad karta.tif", "A 43756-2022")</f>
-        <v/>
-      </c>
-      <c r="AA58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 43756-2022 FSC-klagomål.docx", "A 43756-2022")</f>
-        <v/>
-      </c>
-      <c r="AB58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 43756-2022 FSC-klagomål mail.docx", "A 43756-2022")</f>
-        <v/>
-      </c>
-      <c r="AC58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 43756-2022 tillsynsbegäran.docx", "A 43756-2022")</f>
-        <v/>
-      </c>
-      <c r="AD58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 43756-2022 tillsynsbegäran mail.docx", "A 43756-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>A 31520-2026</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E59" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J59" t="n">
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
         <v>3</v>
       </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>1</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>3</v>
-      </c>
-      <c r="T59" t="n">
+      <c r="T62" t="n">
         <v>4</v>
       </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" s="2" t="inlineStr">
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Grönsiska
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31520-2026 artfynd.xlsx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="X59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31520-2026 karta.png", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="Y59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31520-2026 georefererad karta.tif", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AA59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31520-2026 FSC-klagomål.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AB59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31520-2026 FSC-klagomål mail.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AC59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31520-2026 tillsynsbegäran.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AD59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31520-2026 tillsynsbegäran mail.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AE59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 31520-2026 prioriterade fågelarter.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>S 846-2026</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E60" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J60" t="n">
-        <v>3</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>1</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="n">
-        <v>3</v>
-      </c>
-      <c r="T60" t="n">
-        <v>3</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Havsörn
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 846-2026 artfynd.xlsx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="X60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 846-2026 karta.png", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="Y60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 846-2026 georefererad karta.tif", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AA60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 846-2026 FSC-klagomål.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AB60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 846-2026 FSC-klagomål mail.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AC60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 846-2026 tillsynsbegäran.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AD60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 846-2026 tillsynsbegäran mail.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AE60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/S 846-2026 prioriterade fågelarter.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>S 1726-2026</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E61" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I61" t="n">
-        <v>2</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1</v>
-      </c>
-      <c r="K61" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" t="n">
-        <v>1</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>1</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>2</v>
-      </c>
-      <c r="R61" t="n">
-        <v>1</v>
-      </c>
-      <c r="S61" t="n">
-        <v>3</v>
-      </c>
-      <c r="T61" t="n">
-        <v>3</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Mindre poppelglasvinge
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1726-2026 artfynd.xlsx", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="X61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1726-2026 karta.png", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="Y61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1726-2026 georefererad karta.tif", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="AA61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1726-2026 FSC-klagomål.docx", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="AB61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1726-2026 FSC-klagomål mail.docx", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="AC61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1726-2026 tillsynsbegäran.docx", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="AD61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1726-2026 tillsynsbegäran mail.docx", "S 1726-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>S 2059-2026</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E62" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I62" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J62" t="n">
-        <v>3</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>1</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>1</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>3</v>
-      </c>
-      <c r="T62" t="n">
-        <v>4</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Grönsiska
-Kungsfågel</t>
-        </is>
-      </c>
       <c r="W62">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2059-2026 artfynd.xlsx", "S 2059-2026")</f>
         <v/>
@@ -7705,7 +7705,7 @@
         <v>44623</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 24166-2022</t>
+          <t>A 17699-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7804,14 +7804,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44725</v>
+        <v>45758</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7833,10 +7833,10 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>2</v>
@@ -7860,47 +7860,47 @@
         <v>2</v>
       </c>
       <c r="U64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>Plattsäv
-Jungfrulin</t>
+          <t>Backtimjan
+Klibbveronika</t>
         </is>
       </c>
       <c r="W64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24166-2022 artfynd.xlsx", "A 24166-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 17699-2025 artfynd.xlsx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="X64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24166-2022 karta.png", "A 24166-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 17699-2025 karta.png", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="Y64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24166-2022 georefererad karta.tif", "A 24166-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 17699-2025 georefererad karta.tif", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AA64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24166-2022 FSC-klagomål.docx", "A 24166-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 17699-2025 FSC-klagomål.docx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AB64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24166-2022 FSC-klagomål mail.docx", "A 24166-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 17699-2025 FSC-klagomål mail.docx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AC64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24166-2022 tillsynsbegäran.docx", "A 24166-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 17699-2025 tillsynsbegäran.docx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AD64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24166-2022 tillsynsbegäran mail.docx", "A 24166-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 17699-2025 tillsynsbegäran mail.docx", "A 17699-2025")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 9253-2026</t>
+          <t>A 44678-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7914,10 +7914,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46070</v>
+        <v>44840</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7930,7 +7930,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>1</v>
@@ -7945,7 +7945,7 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -7954,10 +7954,10 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S65" t="n">
         <v>2</v>
@@ -7966,47 +7966,47 @@
         <v>2</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>Murgröna
-Gullviva</t>
+          <t>Ask
+Skogsknipprot</t>
         </is>
       </c>
       <c r="W65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9253-2026 artfynd.xlsx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 44678-2022 artfynd.xlsx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="X65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9253-2026 karta.png", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 44678-2022 karta.png", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="Y65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9253-2026 georefererad karta.tif", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 44678-2022 georefererad karta.tif", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AA65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9253-2026 FSC-klagomål.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 44678-2022 FSC-klagomål.docx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AB65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9253-2026 FSC-klagomål mail.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 44678-2022 FSC-klagomål mail.docx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AC65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9253-2026 tillsynsbegäran.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 44678-2022 tillsynsbegäran.docx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AD65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9253-2026 tillsynsbegäran mail.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 44678-2022 tillsynsbegäran mail.docx", "A 44678-2022")</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 60141-2025</t>
+          <t>A 24166-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -8016,14 +8016,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45994</v>
+        <v>44725</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8036,19 +8036,19 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>10.7</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
@@ -8060,59 +8060,59 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S66" t="n">
         <v>2</v>
       </c>
       <c r="T66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>Strävlosta
-Långbensgroda</t>
+          <t>Plattsäv
+Jungfrulin</t>
         </is>
       </c>
       <c r="W66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 60141-2025 artfynd.xlsx", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24166-2022 artfynd.xlsx", "A 24166-2022")</f>
         <v/>
       </c>
       <c r="X66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 60141-2025 karta.png", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24166-2022 karta.png", "A 24166-2022")</f>
         <v/>
       </c>
       <c r="Y66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 60141-2025 georefererad karta.tif", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24166-2022 georefererad karta.tif", "A 24166-2022")</f>
         <v/>
       </c>
       <c r="AA66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 60141-2025 FSC-klagomål.docx", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24166-2022 FSC-klagomål.docx", "A 24166-2022")</f>
         <v/>
       </c>
       <c r="AB66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 60141-2025 FSC-klagomål mail.docx", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24166-2022 FSC-klagomål mail.docx", "A 24166-2022")</f>
         <v/>
       </c>
       <c r="AC66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 60141-2025 tillsynsbegäran.docx", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24166-2022 tillsynsbegäran.docx", "A 24166-2022")</f>
         <v/>
       </c>
       <c r="AD66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 60141-2025 tillsynsbegäran mail.docx", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24166-2022 tillsynsbegäran mail.docx", "A 24166-2022")</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60140-2025</t>
+          <t>A 21908-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8126,10 +8126,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45994</v>
+        <v>44711</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J67" t="n">
         <v>1</v>
@@ -8175,50 +8175,50 @@
         <v>2</v>
       </c>
       <c r="T67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot
-Strävlosta</t>
+          <t>Myskmadra
+Skogsknipprot</t>
         </is>
       </c>
       <c r="W67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 60140-2025 artfynd.xlsx", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21908-2022 artfynd.xlsx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="X67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 60140-2025 karta.png", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21908-2022 karta.png", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="Y67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 60140-2025 georefererad karta.tif", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21908-2022 georefererad karta.tif", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AA67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 60140-2025 FSC-klagomål.docx", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21908-2022 FSC-klagomål.docx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AB67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 60140-2025 FSC-klagomål mail.docx", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21908-2022 FSC-klagomål mail.docx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AC67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 60140-2025 tillsynsbegäran.docx", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21908-2022 tillsynsbegäran.docx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AD67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 60140-2025 tillsynsbegäran mail.docx", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21908-2022 tillsynsbegäran mail.docx", "A 21908-2022")</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 44678-2022</t>
+          <t>A 60141-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -8232,10 +8232,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44840</v>
+        <v>45994</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>1</v>
@@ -8263,7 +8263,7 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8272,59 +8272,59 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>2</v>
       </c>
       <c r="T68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>Ask
-Skogsknipprot</t>
+          <t>Strävlosta
+Långbensgroda</t>
         </is>
       </c>
       <c r="W68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 44678-2022 artfynd.xlsx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 60141-2025 artfynd.xlsx", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="X68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 44678-2022 karta.png", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 60141-2025 karta.png", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="Y68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 44678-2022 georefererad karta.tif", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 60141-2025 georefererad karta.tif", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="AA68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 44678-2022 FSC-klagomål.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 60141-2025 FSC-klagomål.docx", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="AB68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 44678-2022 FSC-klagomål mail.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 60141-2025 FSC-klagomål mail.docx", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="AC68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 44678-2022 tillsynsbegäran.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 60141-2025 tillsynsbegäran.docx", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="AD68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 44678-2022 tillsynsbegäran mail.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 60141-2025 tillsynsbegäran mail.docx", "A 60141-2025")</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 17699-2025</t>
+          <t>A 60140-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -8338,10 +8338,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45758</v>
+        <v>45994</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8354,16 +8354,16 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -8378,7 +8378,7 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -8387,50 +8387,50 @@
         <v>2</v>
       </c>
       <c r="T69" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan
-Klibbveronika</t>
+          <t>Skogsknipprot
+Strävlosta</t>
         </is>
       </c>
       <c r="W69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 17699-2025 artfynd.xlsx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 60140-2025 artfynd.xlsx", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="X69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 17699-2025 karta.png", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 60140-2025 karta.png", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="Y69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 17699-2025 georefererad karta.tif", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 60140-2025 georefererad karta.tif", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="AA69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 17699-2025 FSC-klagomål.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 60140-2025 FSC-klagomål.docx", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="AB69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 17699-2025 FSC-klagomål mail.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 60140-2025 FSC-klagomål mail.docx", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="AC69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 17699-2025 tillsynsbegäran.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 60140-2025 tillsynsbegäran.docx", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="AD69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 17699-2025 tillsynsbegäran mail.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 60140-2025 tillsynsbegäran mail.docx", "A 60140-2025")</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24322-2026</t>
+          <t>A 9253-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -8444,10 +8444,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46169</v>
+        <v>46070</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8459,19 +8459,14 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -8505,43 +8500,43 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>Purpurknipprot
-Skogsknipprot</t>
+          <t>Murgröna
+Gullviva</t>
         </is>
       </c>
       <c r="W70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24322-2026 artfynd.xlsx", "A 24322-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9253-2026 artfynd.xlsx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="X70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24322-2026 karta.png", "A 24322-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9253-2026 karta.png", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="Y70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24322-2026 georefererad karta.tif", "A 24322-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9253-2026 georefererad karta.tif", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AA70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24322-2026 FSC-klagomål.docx", "A 24322-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9253-2026 FSC-klagomål.docx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AB70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24322-2026 FSC-klagomål mail.docx", "A 24322-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9253-2026 FSC-klagomål mail.docx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AC70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24322-2026 tillsynsbegäran.docx", "A 24322-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9253-2026 tillsynsbegäran.docx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AD70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24322-2026 tillsynsbegäran mail.docx", "A 24322-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9253-2026 tillsynsbegäran mail.docx", "A 9253-2026")</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 21908-2022</t>
+          <t>A 24322-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8555,10 +8550,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44711</v>
+        <v>46169</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8570,11 +8565,16 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K71" t="n">
         <v>2</v>
@@ -8607,40 +8607,40 @@
         <v>2</v>
       </c>
       <c r="U71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra
+          <t>Purpurknipprot
 Skogsknipprot</t>
         </is>
       </c>
       <c r="W71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21908-2022 artfynd.xlsx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24322-2026 artfynd.xlsx", "A 24322-2026")</f>
         <v/>
       </c>
       <c r="X71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21908-2022 karta.png", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24322-2026 karta.png", "A 24322-2026")</f>
         <v/>
       </c>
       <c r="Y71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21908-2022 georefererad karta.tif", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24322-2026 georefererad karta.tif", "A 24322-2026")</f>
         <v/>
       </c>
       <c r="AA71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21908-2022 FSC-klagomål.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24322-2026 FSC-klagomål.docx", "A 24322-2026")</f>
         <v/>
       </c>
       <c r="AB71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21908-2022 FSC-klagomål mail.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24322-2026 FSC-klagomål mail.docx", "A 24322-2026")</f>
         <v/>
       </c>
       <c r="AC71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21908-2022 tillsynsbegäran.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24322-2026 tillsynsbegäran.docx", "A 24322-2026")</f>
         <v/>
       </c>
       <c r="AD71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21908-2022 tillsynsbegäran mail.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24322-2026 tillsynsbegäran mail.docx", "A 24322-2026")</f>
         <v/>
       </c>
     </row>
@@ -8664,7 +8664,7 @@
         <v>46203</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>46203</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S 1650-2022</t>
+          <t>S 6144-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8879,14 +8879,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44649</v>
+        <v>44865</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8899,16 +8899,16 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -8923,7 +8923,7 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
@@ -8932,50 +8932,50 @@
         <v>2</v>
       </c>
       <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
         <v>2</v>
       </c>
-      <c r="U74" t="n">
-        <v>0</v>
-      </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa
-Gulpudrad spiklav</t>
+          <t>Oxtungssvamp
+Fläcknycklar</t>
         </is>
       </c>
       <c r="W74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1650-2022 artfynd.xlsx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 6144-2022 artfynd.xlsx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="X74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1650-2022 karta.png", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 6144-2022 karta.png", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="Y74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1650-2022 georefererad karta.tif", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 6144-2022 georefererad karta.tif", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AA74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1650-2022 FSC-klagomål.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 6144-2022 FSC-klagomål.docx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AB74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1650-2022 FSC-klagomål mail.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 6144-2022 FSC-klagomål mail.docx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AC74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1650-2022 tillsynsbegäran.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 6144-2022 tillsynsbegäran.docx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AD74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1650-2022 tillsynsbegäran mail.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 6144-2022 tillsynsbegäran mail.docx", "S 6144-2022")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S 6144-2022</t>
+          <t>S 1650-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8985,14 +8985,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44865</v>
+        <v>44649</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9005,16 +9005,16 @@
         </is>
       </c>
       <c r="I75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
         <v>2</v>
       </c>
-      <c r="J75" t="n">
-        <v>1</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -9029,7 +9029,7 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -9038,43 +9038,43 @@
         <v>2</v>
       </c>
       <c r="T75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>Oxtungssvamp
-Fläcknycklar</t>
+          <t>Guldlockmossa
+Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="W75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 6144-2022 artfynd.xlsx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1650-2022 artfynd.xlsx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="X75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 6144-2022 karta.png", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1650-2022 karta.png", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="Y75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 6144-2022 georefererad karta.tif", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1650-2022 georefererad karta.tif", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AA75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 6144-2022 FSC-klagomål.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1650-2022 FSC-klagomål.docx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AB75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 6144-2022 FSC-klagomål mail.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1650-2022 FSC-klagomål mail.docx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AC75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 6144-2022 tillsynsbegäran.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1650-2022 tillsynsbegäran.docx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AD75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 6144-2022 tillsynsbegäran mail.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1650-2022 tillsynsbegäran mail.docx", "S 1650-2022")</f>
         <v/>
       </c>
     </row>
@@ -9098,7 +9098,7 @@
         <v>46203</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>46203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44772</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44781</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 9745-2023</t>
+          <t>A 24701-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9537,10 +9537,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44984</v>
+        <v>45084</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9553,13 +9553,13 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -9568,7 +9568,7 @@
         <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9577,58 +9577,58 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
       </c>
       <c r="T80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9745-2023 artfynd.xlsx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24701-2023 artfynd.xlsx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="X80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9745-2023 karta.png", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24701-2023 karta.png", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="Y80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9745-2023 georefererad karta.tif", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24701-2023 georefererad karta.tif", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AA80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9745-2023 FSC-klagomål.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24701-2023 FSC-klagomål.docx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AB80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9745-2023 FSC-klagomål mail.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24701-2023 FSC-klagomål mail.docx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AC80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9745-2023 tillsynsbegäran.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24701-2023 tillsynsbegäran.docx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AD80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9745-2023 tillsynsbegäran mail.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24701-2023 tillsynsbegäran mail.docx", "A 24701-2023")</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 20878-2024</t>
+          <t>A 63276-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45439</v>
+        <v>45273</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9658,10 +9658,10 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -9670,7 +9670,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N81" t="n">
         <v>0</v>
@@ -9682,58 +9682,58 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
       </c>
       <c r="T81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Elaphomyces barrioi</t>
         </is>
       </c>
       <c r="W81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 20878-2024 artfynd.xlsx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 63276-2023 artfynd.xlsx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="X81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 20878-2024 karta.png", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 63276-2023 karta.png", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="Y81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 20878-2024 georefererad karta.tif", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 63276-2023 georefererad karta.tif", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AA81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 20878-2024 FSC-klagomål.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 63276-2023 FSC-klagomål.docx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AB81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 20878-2024 FSC-klagomål mail.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 63276-2023 FSC-klagomål mail.docx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AC81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 20878-2024 tillsynsbegäran.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 63276-2023 tillsynsbegäran.docx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AD81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 20878-2024 tillsynsbegäran mail.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 63276-2023 tillsynsbegäran mail.docx", "A 63276-2023")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 41831-2025</t>
+          <t>A 20878-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9747,10 +9747,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45902</v>
+        <v>45439</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J82" t="n">
         <v>1</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -9796,49 +9796,49 @@
         <v>1</v>
       </c>
       <c r="T82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 41831-2025 artfynd.xlsx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 20878-2024 artfynd.xlsx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="X82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 41831-2025 karta.png", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 20878-2024 karta.png", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="Y82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 41831-2025 georefererad karta.tif", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 20878-2024 georefererad karta.tif", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AA82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 41831-2025 FSC-klagomål.docx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 20878-2024 FSC-klagomål.docx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AB82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 41831-2025 FSC-klagomål mail.docx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 20878-2024 FSC-klagomål mail.docx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AC82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 41831-2025 tillsynsbegäran.docx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 20878-2024 tillsynsbegäran.docx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AD82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 41831-2025 tillsynsbegäran mail.docx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 20878-2024 tillsynsbegäran mail.docx", "A 20878-2024")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 28782-2025</t>
+          <t>A 31720-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9848,14 +9848,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45820</v>
+        <v>44776</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9873,13 +9873,13 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J83" t="n">
         <v>1</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -9909,50 +9909,46 @@
         <v>1</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28782-2025 artfynd.xlsx", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31720-2022 artfynd.xlsx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="X83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28782-2025 karta.png", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31720-2022 karta.png", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="Y83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28782-2025 georefererad karta.tif", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31720-2022 georefererad karta.tif", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AA83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28782-2025 FSC-klagomål.docx", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31720-2022 FSC-klagomål.docx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AB83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28782-2025 FSC-klagomål mail.docx", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31720-2022 FSC-klagomål mail.docx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AC83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28782-2025 tillsynsbegäran.docx", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31720-2022 tillsynsbegäran.docx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AD83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28782-2025 tillsynsbegäran mail.docx", "A 28782-2025")</f>
-        <v/>
-      </c>
-      <c r="AE83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 28782-2025 prioriterade fågelarter.docx", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31720-2022 tillsynsbegäran mail.docx", "A 31720-2022")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 28785-2025</t>
+          <t>A 24704-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9962,14 +9958,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45820</v>
+        <v>45084</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9981,16 +9977,11 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -10002,7 +9993,7 @@
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10011,62 +10002,58 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S84" t="n">
         <v>1</v>
       </c>
       <c r="T84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28785-2025 artfynd.xlsx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24704-2023 artfynd.xlsx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="X84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28785-2025 karta.png", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24704-2023 karta.png", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="Y84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28785-2025 georefererad karta.tif", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24704-2023 georefererad karta.tif", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AA84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28785-2025 FSC-klagomål.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24704-2023 FSC-klagomål.docx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AB84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28785-2025 FSC-klagomål mail.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24704-2023 FSC-klagomål mail.docx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AC84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28785-2025 tillsynsbegäran.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24704-2023 tillsynsbegäran.docx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AD84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28785-2025 tillsynsbegäran mail.docx", "A 28785-2025")</f>
-        <v/>
-      </c>
-      <c r="AE84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 28785-2025 prioriterade fågelarter.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24704-2023 tillsynsbegäran mail.docx", "A 24704-2023")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 3302-2026</t>
+          <t>A 19867-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10076,14 +10063,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46041</v>
+        <v>45433</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10099,13 +10086,13 @@
         <v>3.9</v>
       </c>
       <c r="J85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -10120,7 +10107,7 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85" t="n">
         <v>0</v>
@@ -10132,46 +10119,46 @@
         <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Åkerkulla</t>
         </is>
       </c>
       <c r="W85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 3302-2026 artfynd.xlsx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 19867-2024 artfynd.xlsx", "A 19867-2024")</f>
         <v/>
       </c>
       <c r="X85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 3302-2026 karta.png", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 19867-2024 karta.png", "A 19867-2024")</f>
         <v/>
       </c>
       <c r="Y85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 3302-2026 georefererad karta.tif", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 19867-2024 georefererad karta.tif", "A 19867-2024")</f>
         <v/>
       </c>
       <c r="AA85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 3302-2026 FSC-klagomål.docx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 19867-2024 FSC-klagomål.docx", "A 19867-2024")</f>
         <v/>
       </c>
       <c r="AB85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 3302-2026 FSC-klagomål mail.docx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 19867-2024 FSC-klagomål mail.docx", "A 19867-2024")</f>
         <v/>
       </c>
       <c r="AC85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 3302-2026 tillsynsbegäran.docx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 19867-2024 tillsynsbegäran.docx", "A 19867-2024")</f>
         <v/>
       </c>
       <c r="AD85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 3302-2026 tillsynsbegäran mail.docx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 19867-2024 tillsynsbegäran mail.docx", "A 19867-2024")</f>
         <v/>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 31720-2022</t>
+          <t>A 9745-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10185,10 +10172,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44776</v>
+        <v>44984</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10200,13 +10187,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J86" t="n">
         <v>1</v>
@@ -10239,49 +10221,49 @@
         <v>1</v>
       </c>
       <c r="T86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U86" t="n">
         <v>1</v>
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31720-2022 artfynd.xlsx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9745-2023 artfynd.xlsx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="X86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31720-2022 karta.png", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9745-2023 karta.png", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="Y86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31720-2022 georefererad karta.tif", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9745-2023 georefererad karta.tif", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AA86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31720-2022 FSC-klagomål.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9745-2023 FSC-klagomål.docx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AB86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31720-2022 FSC-klagomål mail.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9745-2023 FSC-klagomål mail.docx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AC86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31720-2022 tillsynsbegäran.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9745-2023 tillsynsbegäran.docx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AD86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31720-2022 tillsynsbegäran mail.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9745-2023 tillsynsbegäran mail.docx", "A 9745-2023")</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 7481-2026</t>
+          <t>A 13043-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10295,10 +10277,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46059</v>
+        <v>45385</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10311,13 +10293,13 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>1</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -10344,49 +10326,49 @@
         <v>1</v>
       </c>
       <c r="T87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 7481-2026 artfynd.xlsx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 13043-2024 artfynd.xlsx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="X87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 7481-2026 karta.png", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 13043-2024 karta.png", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="Y87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 7481-2026 georefererad karta.tif", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 13043-2024 georefererad karta.tif", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AA87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 7481-2026 FSC-klagomål.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 13043-2024 FSC-klagomål.docx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AB87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 7481-2026 FSC-klagomål mail.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 13043-2024 FSC-klagomål mail.docx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AC87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 7481-2026 tillsynsbegäran.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 13043-2024 tillsynsbegäran.docx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AD87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 7481-2026 tillsynsbegäran mail.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 13043-2024 tillsynsbegäran mail.docx", "A 13043-2024")</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 9104-2026</t>
+          <t>A 28785-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10396,14 +10378,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46069</v>
+        <v>45820</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10415,11 +10397,16 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -10452,46 +10439,50 @@
         <v>1</v>
       </c>
       <c r="U88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9104-2026 artfynd.xlsx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28785-2025 artfynd.xlsx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="X88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9104-2026 karta.png", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28785-2025 karta.png", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="Y88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9104-2026 georefererad karta.tif", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28785-2025 georefererad karta.tif", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AA88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9104-2026 FSC-klagomål.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28785-2025 FSC-klagomål.docx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AB88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9104-2026 FSC-klagomål mail.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28785-2025 FSC-klagomål mail.docx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AC88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9104-2026 tillsynsbegäran.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28785-2025 tillsynsbegäran.docx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AD88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9104-2026 tillsynsbegäran mail.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28785-2025 tillsynsbegäran mail.docx", "A 28785-2025")</f>
+        <v/>
+      </c>
+      <c r="AE88">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 28785-2025 prioriterade fågelarter.docx", "A 28785-2025")</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 9905-2026</t>
+          <t>A 28782-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10501,14 +10492,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46073</v>
+        <v>45820</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10520,11 +10511,16 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -10536,7 +10532,7 @@
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -10545,10 +10541,10 @@
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>1</v>
@@ -10561,42 +10557,46 @@
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9905-2026 artfynd.xlsx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28782-2025 artfynd.xlsx", "A 28782-2025")</f>
         <v/>
       </c>
       <c r="X89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9905-2026 karta.png", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28782-2025 karta.png", "A 28782-2025")</f>
         <v/>
       </c>
       <c r="Y89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9905-2026 georefererad karta.tif", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28782-2025 georefererad karta.tif", "A 28782-2025")</f>
         <v/>
       </c>
       <c r="AA89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9905-2026 FSC-klagomål.docx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28782-2025 FSC-klagomål.docx", "A 28782-2025")</f>
         <v/>
       </c>
       <c r="AB89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9905-2026 FSC-klagomål mail.docx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28782-2025 FSC-klagomål mail.docx", "A 28782-2025")</f>
         <v/>
       </c>
       <c r="AC89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9905-2026 tillsynsbegäran.docx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28782-2025 tillsynsbegäran.docx", "A 28782-2025")</f>
         <v/>
       </c>
       <c r="AD89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9905-2026 tillsynsbegäran mail.docx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28782-2025 tillsynsbegäran mail.docx", "A 28782-2025")</f>
+        <v/>
+      </c>
+      <c r="AE89">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 28782-2025 prioriterade fågelarter.docx", "A 28782-2025")</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 24701-2023</t>
+          <t>A 41831-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45084</v>
+        <v>45902</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10626,13 +10626,13 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -10641,7 +10641,7 @@
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -10650,58 +10650,58 @@
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>1</v>
       </c>
       <c r="T90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U90" t="n">
         <v>0</v>
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24701-2023 artfynd.xlsx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 41831-2025 artfynd.xlsx", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="X90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24701-2023 karta.png", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 41831-2025 karta.png", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="Y90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24701-2023 georefererad karta.tif", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 41831-2025 georefererad karta.tif", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="AA90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24701-2023 FSC-klagomål.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 41831-2025 FSC-klagomål.docx", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="AB90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24701-2023 FSC-klagomål mail.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 41831-2025 FSC-klagomål mail.docx", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="AC90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24701-2023 tillsynsbegäran.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 41831-2025 tillsynsbegäran.docx", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="AD90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24701-2023 tillsynsbegäran mail.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 41831-2025 tillsynsbegäran mail.docx", "A 41831-2025")</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 24704-2023</t>
+          <t>A 3302-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10711,14 +10711,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45084</v>
+        <v>46041</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10731,10 +10731,10 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -10746,7 +10746,7 @@
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -10755,58 +10755,58 @@
         <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>1</v>
       </c>
       <c r="T91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24704-2023 artfynd.xlsx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 3302-2026 artfynd.xlsx", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="X91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24704-2023 karta.png", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 3302-2026 karta.png", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="Y91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24704-2023 georefererad karta.tif", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 3302-2026 georefererad karta.tif", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="AA91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24704-2023 FSC-klagomål.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 3302-2026 FSC-klagomål.docx", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="AB91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24704-2023 FSC-klagomål mail.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 3302-2026 FSC-klagomål mail.docx", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="AC91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24704-2023 tillsynsbegäran.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 3302-2026 tillsynsbegäran.docx", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="AD91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24704-2023 tillsynsbegäran mail.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 3302-2026 tillsynsbegäran mail.docx", "A 3302-2026")</f>
         <v/>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 26840-2026</t>
+          <t>A 7481-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10816,14 +10816,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46185</v>
+        <v>46059</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10835,16 +10835,11 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -10856,7 +10851,7 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -10865,58 +10860,58 @@
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>1</v>
       </c>
       <c r="T92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26840-2026 artfynd.xlsx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 7481-2026 artfynd.xlsx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="X92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26840-2026 karta.png", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 7481-2026 karta.png", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="Y92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26840-2026 georefererad karta.tif", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 7481-2026 georefererad karta.tif", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AA92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26840-2026 FSC-klagomål.docx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 7481-2026 FSC-klagomål.docx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AB92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26840-2026 FSC-klagomål mail.docx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 7481-2026 FSC-klagomål mail.docx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AC92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26840-2026 tillsynsbegäran.docx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 7481-2026 tillsynsbegäran.docx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AD92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26840-2026 tillsynsbegäran mail.docx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 7481-2026 tillsynsbegäran mail.docx", "A 7481-2026")</f>
         <v/>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 28430-2026</t>
+          <t>A 9104-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10926,14 +10921,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46197</v>
+        <v>46069</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10945,13 +10940,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -10960,7 +10950,7 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
@@ -10975,7 +10965,7 @@
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
         <v>0</v>
@@ -10984,49 +10974,49 @@
         <v>1</v>
       </c>
       <c r="T93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="W93">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28430-2026 artfynd.xlsx", "A 28430-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9104-2026 artfynd.xlsx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="X93">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28430-2026 karta.png", "A 28430-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9104-2026 karta.png", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="Y93">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28430-2026 georefererad karta.tif", "A 28430-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9104-2026 georefererad karta.tif", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AA93">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28430-2026 FSC-klagomål.docx", "A 28430-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9104-2026 FSC-klagomål.docx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AB93">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28430-2026 FSC-klagomål mail.docx", "A 28430-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9104-2026 FSC-klagomål mail.docx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AC93">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28430-2026 tillsynsbegäran.docx", "A 28430-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9104-2026 tillsynsbegäran.docx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AD93">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28430-2026 tillsynsbegäran mail.docx", "A 28430-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9104-2026 tillsynsbegäran mail.docx", "A 9104-2026")</f>
         <v/>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 28374-2026</t>
+          <t>A 9905-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -11036,14 +11026,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46196</v>
+        <v>46073</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11055,13 +11045,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -11073,10 +11058,10 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11101,42 +11086,42 @@
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>Purpurmusseron</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28374-2026 artfynd.xlsx", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9905-2026 artfynd.xlsx", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="X94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28374-2026 karta.png", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9905-2026 karta.png", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="Y94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28374-2026 georefererad karta.tif", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9905-2026 georefererad karta.tif", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="AA94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28374-2026 FSC-klagomål.docx", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9905-2026 FSC-klagomål.docx", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="AB94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28374-2026 FSC-klagomål mail.docx", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9905-2026 FSC-klagomål mail.docx", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="AC94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28374-2026 tillsynsbegäran.docx", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9905-2026 tillsynsbegäran.docx", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="AD94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28374-2026 tillsynsbegäran mail.docx", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9905-2026 tillsynsbegäran mail.docx", "A 9905-2026")</f>
         <v/>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 19867-2024</t>
+          <t>A 26840-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -11146,14 +11131,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45433</v>
+        <v>46185</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11165,8 +11150,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -11175,13 +11165,13 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11193,55 +11183,55 @@
         <v>1</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S95" t="n">
         <v>1</v>
       </c>
       <c r="T95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>Åkerkulla</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W95">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 19867-2024 artfynd.xlsx", "A 19867-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26840-2026 artfynd.xlsx", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="X95">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 19867-2024 karta.png", "A 19867-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26840-2026 karta.png", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="Y95">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 19867-2024 georefererad karta.tif", "A 19867-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26840-2026 georefererad karta.tif", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="AA95">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 19867-2024 FSC-klagomål.docx", "A 19867-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26840-2026 FSC-klagomål.docx", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="AB95">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 19867-2024 FSC-klagomål mail.docx", "A 19867-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26840-2026 FSC-klagomål mail.docx", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="AC95">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 19867-2024 tillsynsbegäran.docx", "A 19867-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26840-2026 tillsynsbegäran.docx", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="AD95">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 19867-2024 tillsynsbegäran mail.docx", "A 19867-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26840-2026 tillsynsbegäran mail.docx", "A 26840-2026")</f>
         <v/>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 63276-2023</t>
+          <t>A 28374-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -11251,14 +11241,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45273</v>
+        <v>46196</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11270,8 +11260,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -11311,42 +11306,42 @@
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>Elaphomyces barrioi</t>
+          <t>Purpurmusseron</t>
         </is>
       </c>
       <c r="W96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 63276-2023 artfynd.xlsx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28374-2026 artfynd.xlsx", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="X96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 63276-2023 karta.png", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28374-2026 karta.png", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="Y96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 63276-2023 georefererad karta.tif", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28374-2026 georefererad karta.tif", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="AA96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 63276-2023 FSC-klagomål.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28374-2026 FSC-klagomål.docx", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="AB96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 63276-2023 FSC-klagomål mail.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28374-2026 FSC-klagomål mail.docx", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="AC96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 63276-2023 tillsynsbegäran.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28374-2026 tillsynsbegäran.docx", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="AD96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 63276-2023 tillsynsbegäran mail.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28374-2026 tillsynsbegäran mail.docx", "A 28374-2026")</f>
         <v/>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 13043-2024</t>
+          <t>A 28430-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -11356,14 +11351,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45385</v>
+        <v>46197</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11375,17 +11370,22 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -11400,7 +11400,7 @@
         <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" t="n">
         <v>0</v>
@@ -11409,42 +11409,42 @@
         <v>1</v>
       </c>
       <c r="T97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="W97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 13043-2024 artfynd.xlsx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28430-2026 artfynd.xlsx", "A 28430-2026")</f>
         <v/>
       </c>
       <c r="X97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 13043-2024 karta.png", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28430-2026 karta.png", "A 28430-2026")</f>
         <v/>
       </c>
       <c r="Y97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 13043-2024 georefererad karta.tif", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28430-2026 georefererad karta.tif", "A 28430-2026")</f>
         <v/>
       </c>
       <c r="AA97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 13043-2024 FSC-klagomål.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28430-2026 FSC-klagomål.docx", "A 28430-2026")</f>
         <v/>
       </c>
       <c r="AB97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 13043-2024 FSC-klagomål mail.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28430-2026 FSC-klagomål mail.docx", "A 28430-2026")</f>
         <v/>
       </c>
       <c r="AC97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 13043-2024 tillsynsbegäran.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28430-2026 tillsynsbegäran.docx", "A 28430-2026")</f>
         <v/>
       </c>
       <c r="AD97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 13043-2024 tillsynsbegäran mail.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28430-2026 tillsynsbegäran mail.docx", "A 28430-2026")</f>
         <v/>
       </c>
     </row>
@@ -11468,7 +11468,7 @@
         <v>46246</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>45111</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>45903</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>46185</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S 1813-2026</t>
+          <t>S 1803-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -11899,10 +11899,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -11929,10 +11929,10 @@
         <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N102" t="n">
         <v>0</v>
@@ -11947,55 +11947,55 @@
         <v>1</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S102" t="n">
         <v>1</v>
       </c>
       <c r="T102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Purpurmusseron</t>
         </is>
       </c>
       <c r="W102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1813-2026 artfynd.xlsx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1803-2026 artfynd.xlsx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="X102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1813-2026 karta.png", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1803-2026 karta.png", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="Y102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1813-2026 georefererad karta.tif", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1803-2026 georefererad karta.tif", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AA102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1813-2026 FSC-klagomål.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1803-2026 FSC-klagomål.docx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AB102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1813-2026 FSC-klagomål mail.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1803-2026 FSC-klagomål mail.docx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AC102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1813-2026 tillsynsbegäran.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1803-2026 tillsynsbegäran.docx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AD102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1813-2026 tillsynsbegäran mail.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1803-2026 tillsynsbegäran mail.docx", "S 1803-2026")</f>
         <v/>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S 1803-2026</t>
+          <t>S 1813-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -12009,10 +12009,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12030,75 +12030,75 @@
         </is>
       </c>
       <c r="I103" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>1</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>1</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="n">
+        <v>1</v>
+      </c>
+      <c r="T103" t="n">
         <v>2</v>
       </c>
-      <c r="J103" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" t="n">
-        <v>1</v>
-      </c>
-      <c r="N103" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>1</v>
-      </c>
-      <c r="R103" t="n">
-        <v>1</v>
-      </c>
-      <c r="S103" t="n">
-        <v>1</v>
-      </c>
-      <c r="T103" t="n">
-        <v>1</v>
-      </c>
       <c r="U103" t="n">
         <v>0</v>
       </c>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>Purpurmusseron</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="W103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1803-2026 artfynd.xlsx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1813-2026 artfynd.xlsx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="X103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1803-2026 karta.png", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1813-2026 karta.png", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="Y103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1803-2026 georefererad karta.tif", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1813-2026 georefererad karta.tif", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AA103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1803-2026 FSC-klagomål.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1813-2026 FSC-klagomål.docx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AB103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1803-2026 FSC-klagomål mail.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1813-2026 FSC-klagomål mail.docx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AC103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1803-2026 tillsynsbegäran.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1813-2026 tillsynsbegäran.docx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AD103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1803-2026 tillsynsbegäran mail.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1813-2026 tillsynsbegäran mail.docx", "S 1813-2026")</f>
         <v/>
       </c>
     </row>
@@ -12122,7 +12122,7 @@
         <v>46246</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44783</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>44747</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>44840</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>44783</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>44501</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 56188-2021</t>
+          <t>A 27437-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44477</v>
+        <v>44742</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -12663,7 +12663,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 27437-2022</t>
+          <t>A 62631-2021</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -12677,10 +12677,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44742</v>
+        <v>44503</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -12736,7 +12736,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 62631-2021</t>
+          <t>A 56188-2021</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -12750,10 +12750,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44503</v>
+        <v>44477</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -12809,7 +12809,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 31699-2022</t>
+          <t>A 3878-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -12823,10 +12823,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44776</v>
+        <v>44951</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12838,13 +12838,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -12887,7 +12882,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 26160-2024</t>
+          <t>A 32921-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12897,14 +12892,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45468</v>
+        <v>45125</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12917,7 +12912,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -12956,35 +12951,11 @@
         <v>0</v>
       </c>
       <c r="V114" s="2" t="inlineStr"/>
-      <c r="X114">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26160-2024 karta.png", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="Y114">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26160-2024 georefererad karta.tif", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AA114">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26160-2024 FSC-klagomål.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AB114">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26160-2024 FSC-klagomål mail.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AC114">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26160-2024 tillsynsbegäran.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AD114">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26160-2024 tillsynsbegäran mail.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 40339-2023</t>
+          <t>A 12937-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -12998,10 +12969,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45169</v>
+        <v>44642</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13013,8 +12984,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -13057,7 +13033,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 26190-2025</t>
+          <t>A 31699-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -13071,10 +13047,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45805</v>
+        <v>44776</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13086,8 +13062,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -13130,7 +13111,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 41950-2025</t>
+          <t>A 20287-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -13140,14 +13121,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45903</v>
+        <v>45774</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13160,7 +13141,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -13203,7 +13184,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 4159-2024</t>
+          <t>A 26160-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13213,14 +13194,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45323</v>
+        <v>45468</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13233,7 +13214,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -13272,11 +13253,35 @@
         <v>0</v>
       </c>
       <c r="V118" s="2" t="inlineStr"/>
+      <c r="X118">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26160-2024 karta.png", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="Y118">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26160-2024 georefererad karta.tif", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AA118">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26160-2024 FSC-klagomål.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AB118">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26160-2024 FSC-klagomål mail.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AC118">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26160-2024 tillsynsbegäran.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AD118">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26160-2024 tillsynsbegäran mail.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 45869-2025</t>
+          <t>A 32919-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -13290,10 +13295,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45923</v>
+        <v>45125</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13306,7 +13311,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -13349,7 +13354,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 46845-2025</t>
+          <t>A 1614-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -13359,14 +13364,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45928</v>
+        <v>45670</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13379,7 +13384,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -13422,7 +13427,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 36269-2025</t>
+          <t>A 5175-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -13436,10 +13441,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45867</v>
+        <v>45330</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13451,13 +13456,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -13500,7 +13500,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 4165-2023</t>
+          <t>A 34951-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -13510,14 +13510,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44953</v>
+        <v>44796</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13529,8 +13529,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -13573,7 +13578,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 9259-2026</t>
+          <t>A 63075-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -13583,14 +13588,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46070</v>
+        <v>45273</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13603,7 +13608,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -13646,7 +13651,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 32921-2023</t>
+          <t>A 13383-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -13660,10 +13665,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45125</v>
+        <v>45005</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13676,7 +13681,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -13719,7 +13724,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 15272-2026</t>
+          <t>A 9076-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -13729,14 +13734,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46105</v>
+        <v>45713</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13754,7 +13759,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -13797,7 +13802,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 15279-2026</t>
+          <t>A 1757-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -13807,14 +13812,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46105</v>
+        <v>45671</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13826,13 +13831,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -13875,7 +13875,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 15264-2026</t>
+          <t>A 61438-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -13885,14 +13885,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46105</v>
+        <v>45264</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13904,13 +13904,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -13953,7 +13948,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 64303-2023</t>
+          <t>A 13041-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -13963,14 +13958,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45280</v>
+        <v>45385</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13983,7 +13978,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -14026,7 +14021,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 43603-2024</t>
+          <t>A 4165-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -14040,10 +14035,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45569</v>
+        <v>44953</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14056,7 +14051,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -14099,7 +14094,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 63075-2023</t>
+          <t>A 22785-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -14109,14 +14104,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45273</v>
+        <v>45789</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14129,7 +14124,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -14172,7 +14167,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 1757-2025</t>
+          <t>A 40339-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -14186,10 +14181,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45671</v>
+        <v>45169</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14202,7 +14197,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -14245,7 +14240,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 34780-2022</t>
+          <t>A 64303-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -14255,14 +14250,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44795</v>
+        <v>45280</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14274,13 +14269,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>6.7</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -14323,7 +14313,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 55367-2024</t>
+          <t>A 26190-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -14337,10 +14327,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45621</v>
+        <v>45805</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14353,7 +14343,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -14396,7 +14386,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 20287-2025</t>
+          <t>A 9050-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -14410,10 +14400,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45774</v>
+        <v>45713</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14425,8 +14415,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -14469,7 +14464,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 9076-2025</t>
+          <t>A 34780-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -14483,10 +14478,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45713</v>
+        <v>44795</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14504,7 +14499,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>4.2</v>
+        <v>6.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -14547,7 +14542,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 27357-2025</t>
+          <t>A 55367-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -14557,14 +14552,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45812</v>
+        <v>45621</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14576,13 +14571,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -14625,7 +14615,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 7669-2024</t>
+          <t>A 43603-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -14639,10 +14629,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45348</v>
+        <v>45569</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14655,7 +14645,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -14698,7 +14688,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 32919-2023</t>
+          <t>A 36269-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -14712,10 +14702,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45125</v>
+        <v>45867</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14727,8 +14717,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -14771,7 +14766,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 24323-2026</t>
+          <t>A 4159-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -14785,10 +14780,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46169</v>
+        <v>45323</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14800,13 +14795,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -14849,7 +14839,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 34951-2022</t>
+          <t>A 41950-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -14859,14 +14849,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44796</v>
+        <v>45903</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14878,13 +14868,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -14927,7 +14912,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 5175-2024</t>
+          <t>A 45869-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -14941,10 +14926,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45330</v>
+        <v>45923</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14957,7 +14942,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -15000,7 +14985,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 28380-2026</t>
+          <t>A 46845-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -15010,14 +14995,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46196</v>
+        <v>45928</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15029,13 +15014,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -15078,7 +15058,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 28381-2026</t>
+          <t>A 9259-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -15088,14 +15068,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46196</v>
+        <v>46070</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15107,13 +15087,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -15156,7 +15131,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 28411-2026</t>
+          <t>A 15272-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -15170,10 +15145,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46197</v>
+        <v>46105</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15191,7 +15166,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -15234,7 +15209,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 3878-2023</t>
+          <t>A 15279-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -15244,14 +15219,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44951</v>
+        <v>46105</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15263,8 +15238,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -15307,7 +15287,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 29413-2026</t>
+          <t>A 15264-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -15321,10 +15301,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46203</v>
+        <v>46105</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15342,7 +15322,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -15385,7 +15365,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 29414-2026</t>
+          <t>A 27357-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -15399,10 +15379,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46203</v>
+        <v>45812</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15420,7 +15400,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -15463,7 +15443,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 29431-2026</t>
+          <t>A 7669-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -15473,14 +15453,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46203</v>
+        <v>45348</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15492,13 +15472,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -15541,7 +15516,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 29410-2026</t>
+          <t>A 24323-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -15551,14 +15526,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46203</v>
+        <v>46169</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15576,7 +15551,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -15619,7 +15594,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 13383-2023</t>
+          <t>A 28381-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -15629,14 +15604,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45005</v>
+        <v>46196</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15648,8 +15623,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -15692,7 +15672,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 12937-2022</t>
+          <t>A 28380-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -15702,14 +15682,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44642</v>
+        <v>46196</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15727,7 +15707,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -15770,7 +15750,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 61438-2023</t>
+          <t>A 28411-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -15780,14 +15760,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45264</v>
+        <v>46197</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15799,8 +15779,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -15843,7 +15828,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 13041-2024</t>
+          <t>A 29413-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -15853,14 +15838,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45385</v>
+        <v>46203</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15872,8 +15857,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -15916,7 +15906,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 1614-2025</t>
+          <t>A 29414-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -15926,14 +15916,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45670</v>
+        <v>46203</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15945,8 +15935,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -15989,7 +15984,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 9050-2025</t>
+          <t>A 29431-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -16003,10 +15998,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45713</v>
+        <v>46203</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16024,7 +16019,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -16067,7 +16062,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 22785-2025</t>
+          <t>A 29410-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -16077,14 +16072,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45789</v>
+        <v>46203</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16096,8 +16091,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -16157,7 +16157,7 @@
         <v>46169</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44756</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>45713</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45812</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>45812</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>45754</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>46105</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>46105</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>46169</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S 1812-2026</t>
+          <t>S 1806-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -16846,10 +16846,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -16910,7 +16910,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S 1806-2026</t>
+          <t>S 1807-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -16927,7 +16927,7 @@
         <v>46196</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -16988,7 +16988,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S 1807-2026</t>
+          <t>S 1812-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -17002,10 +17002,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>46203</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>46203</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>46203</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>46203</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>

--- a/Översikt BORGHOLM.xlsx
+++ b/Översikt BORGHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45029</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>44704</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45433</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>44903</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45903</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>46254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44809</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>44523</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>45107</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44781</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>45161</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>45146</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45918</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>45930</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45918</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12534-2022</t>
+          <t>A 13558-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44638</v>
+        <v>45736</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3233,19 +3233,19 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>8.6</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3260,18 +3260,130 @@
         <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
       </c>
       <c r="T23" t="n">
+        <v>8</v>
+      </c>
+      <c r="U23" t="n">
+        <v>8</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Honungsblomster
+Backruta
+Jordtistel
+Stallört
+Ängsstarr
+Tvåblad
+Kärrknipprot
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 13558-2025 artfynd.xlsx", "A 13558-2025")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 13558-2025 karta.png", "A 13558-2025")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 13558-2025 georefererad karta.tif", "A 13558-2025")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 13558-2025 FSC-klagomål.docx", "A 13558-2025")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 13558-2025 FSC-klagomål mail.docx", "A 13558-2025")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 13558-2025 tillsynsbegäran.docx", "A 13558-2025")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 13558-2025 tillsynsbegäran mail.docx", "A 13558-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 12534-2022</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>44638</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>5</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>8</v>
+      </c>
+      <c r="T24" t="n">
         <v>9</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>9</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Backklöver
 Backtimjan
@@ -3283,151 +3395,39 @@
 Sankt pers nycklar</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 12534-2022 artfynd.xlsx", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 12534-2022 karta.png", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 12534-2022 georefererad karta.tif", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 12534-2022 FSC-klagomål.docx", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 12534-2022 FSC-klagomål mail.docx", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 12534-2022 tillsynsbegäran.docx", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 12534-2022 tillsynsbegäran mail.docx", "A 12534-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 13558-2025</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45736</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J24" t="n">
-        <v>4</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>4</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>8</v>
-      </c>
-      <c r="T24" t="n">
-        <v>8</v>
-      </c>
-      <c r="U24" t="n">
-        <v>8</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Honungsblomster
-Backruta
-Jordtistel
-Stallört
-Ängsstarr
-Tvåblad
-Kärrknipprot
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 13558-2025 artfynd.xlsx", "A 13558-2025")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 13558-2025 karta.png", "A 13558-2025")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 13558-2025 georefererad karta.tif", "A 13558-2025")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 13558-2025 FSC-klagomål.docx", "A 13558-2025")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 13558-2025 FSC-klagomål mail.docx", "A 13558-2025")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 13558-2025 tillsynsbegäran.docx", "A 13558-2025")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 13558-2025 tillsynsbegäran mail.docx", "A 13558-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31515-2026</t>
+          <t>A 31399-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46223</v>
+        <v>46220</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3456,19 +3456,14 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
         <v>3</v>
@@ -3495,12 +3490,129 @@
         <v>8</v>
       </c>
       <c r="T25" t="n">
+        <v>8</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Backklöver
+Jordtistel
+Stallört
+Flugblomster
+Tvåblad
+Grönvit nattviol
+Krutbrännare
+Vanliga ängsnycklar</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31399-2026 artfynd.xlsx", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31399-2026 karta.png", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31399-2026 georefererad karta.tif", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31399-2026 FSC-klagomål.docx", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31399-2026 FSC-klagomål mail.docx", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31399-2026 tillsynsbegäran.docx", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31399-2026 tillsynsbegäran mail.docx", "A 31399-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 31515-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3</v>
+      </c>
+      <c r="L26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>8</v>
+      </c>
+      <c r="T26" t="n">
         <v>10</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Blå slemspindling
 Sårläka
@@ -3512,112 +3624,112 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31515-2026 artfynd.xlsx", "A 31515-2026")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31515-2026 karta.png", "A 31515-2026")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31515-2026 georefererad karta.tif", "A 31515-2026")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31515-2026 FSC-klagomål.docx", "A 31515-2026")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31515-2026 FSC-klagomål mail.docx", "A 31515-2026")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31515-2026 tillsynsbegäran.docx", "A 31515-2026")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31515-2026 tillsynsbegäran mail.docx", "A 31515-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>A 31516-2026</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D26" s="1" t="n">
+      <c r="D27" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="E27" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="I27" t="n">
         <v>0.8</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J27" t="n">
         <v>3</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K27" t="n">
         <v>3</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L27" t="n">
         <v>3</v>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>3</v>
       </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>8</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T27" t="n">
         <v>10</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Blå slemspindling
 Sårläka
@@ -3629,144 +3741,32 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31516-2026 artfynd.xlsx", "A 31516-2026")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31516-2026 karta.png", "A 31516-2026")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31516-2026 georefererad karta.tif", "A 31516-2026")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31516-2026 FSC-klagomål.docx", "A 31516-2026")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31516-2026 FSC-klagomål mail.docx", "A 31516-2026")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31516-2026 tillsynsbegäran.docx", "A 31516-2026")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31516-2026 tillsynsbegäran mail.docx", "A 31516-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 31399-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J27" t="n">
-        <v>5</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2</v>
-      </c>
-      <c r="L27" t="n">
-        <v>3</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>8</v>
-      </c>
-      <c r="T27" t="n">
-        <v>8</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Backklöver
-Jordtistel
-Stallört
-Flugblomster
-Tvåblad
-Grönvit nattviol
-Krutbrännare
-Vanliga ängsnycklar</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31399-2026 artfynd.xlsx", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31399-2026 karta.png", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31399-2026 georefererad karta.tif", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31399-2026 FSC-klagomål.docx", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31399-2026 FSC-klagomål mail.docx", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31399-2026 tillsynsbegäran.docx", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31399-2026 tillsynsbegäran mail.docx", "A 31399-2026")</f>
         <v/>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45175</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>45926</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 16171-2023</t>
+          <t>A 27298-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4350,14 +4350,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45027</v>
+        <v>46188</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4369,17 +4369,22 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>12.2</v>
+        <v>3.3</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4394,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4403,12 +4408,237 @@
         <v>6</v>
       </c>
       <c r="T33" t="n">
+        <v>6</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Grenplattnos
+Jungfrulin
+Skugglosta
+Sårläka
+Älg
+Murgröna</t>
+        </is>
+      </c>
+      <c r="W33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27298-2026 artfynd.xlsx", "A 27298-2026")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27298-2026 karta.png", "A 27298-2026")</f>
+        <v/>
+      </c>
+      <c r="Y33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27298-2026 georefererad karta.tif", "A 27298-2026")</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27298-2026 FSC-klagomål.docx", "A 27298-2026")</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27298-2026 FSC-klagomål mail.docx", "A 27298-2026")</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27298-2026 tillsynsbegäran.docx", "A 27298-2026")</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27298-2026 tillsynsbegäran mail.docx", "A 27298-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A 31558-2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>6</v>
+      </c>
+      <c r="T34" t="n">
         <v>7</v>
       </c>
-      <c r="U33" t="n">
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Blå slemspindling
+Sårläka
+Vårärt
+Anisspindling
+Skogsknipprot
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31558-2026 artfynd.xlsx", "A 31558-2026")</f>
+        <v/>
+      </c>
+      <c r="X34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31558-2026 karta.png", "A 31558-2026")</f>
+        <v/>
+      </c>
+      <c r="Y34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31558-2026 georefererad karta.tif", "A 31558-2026")</f>
+        <v/>
+      </c>
+      <c r="AA34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31558-2026 FSC-klagomål.docx", "A 31558-2026")</f>
+        <v/>
+      </c>
+      <c r="AB34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31558-2026 FSC-klagomål mail.docx", "A 31558-2026")</f>
+        <v/>
+      </c>
+      <c r="AC34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31558-2026 tillsynsbegäran.docx", "A 31558-2026")</f>
+        <v/>
+      </c>
+      <c r="AD34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31558-2026 tillsynsbegäran mail.docx", "A 31558-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A 16171-2023</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>45027</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>6</v>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="T35" t="n">
+        <v>7</v>
+      </c>
+      <c r="U35" t="n">
+        <v>6</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Sårläka
 Älg
@@ -4418,112 +4648,332 @@
 Bredarun</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 16171-2023 artfynd.xlsx", "A 16171-2023")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 16171-2023 karta.png", "A 16171-2023")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 16171-2023 georefererad karta.tif", "A 16171-2023")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 16171-2023 FSC-klagomål.docx", "A 16171-2023")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 16171-2023 FSC-klagomål mail.docx", "A 16171-2023")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 16171-2023 tillsynsbegäran.docx", "A 16171-2023")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 16171-2023 tillsynsbegäran mail.docx", "A 16171-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 27298-2026</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>S 2737-2022</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>44704</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4</v>
+      </c>
+      <c r="R36" t="n">
+        <v>3</v>
+      </c>
+      <c r="S36" t="n">
+        <v>6</v>
+      </c>
+      <c r="T36" t="n">
+        <v>23</v>
+      </c>
+      <c r="U36" t="n">
+        <v>18</v>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Mörk kraterlav
+Skogskorn
+Orangepudrad klotterlav
+Ekoxe
+Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="W36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2737-2022 artfynd.xlsx", "S 2737-2022")</f>
+        <v/>
+      </c>
+      <c r="X36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 2737-2022 karta.png", "S 2737-2022")</f>
+        <v/>
+      </c>
+      <c r="Y36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 2737-2022 georefererad karta.tif", "S 2737-2022")</f>
+        <v/>
+      </c>
+      <c r="AA36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 2737-2022 FSC-klagomål.docx", "S 2737-2022")</f>
+        <v/>
+      </c>
+      <c r="AB36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 2737-2022 FSC-klagomål mail.docx", "S 2737-2022")</f>
+        <v/>
+      </c>
+      <c r="AC36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 2737-2022 tillsynsbegäran.docx", "S 2737-2022")</f>
+        <v/>
+      </c>
+      <c r="AD36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 2737-2022 tillsynsbegäran mail.docx", "S 2737-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>S 2679-2024</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>45478</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>4</v>
+      </c>
+      <c r="S37" t="n">
+        <v>6</v>
+      </c>
+      <c r="T37" t="n">
+        <v>14</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Almlav
+Ask
+Skogsalm
+Blek kraterlav
+Slät lönnlav
+Vitskivlav</t>
+        </is>
+      </c>
+      <c r="W37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2679-2024 artfynd.xlsx", "S 2679-2024")</f>
+        <v/>
+      </c>
+      <c r="X37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 2679-2024 karta.png", "S 2679-2024")</f>
+        <v/>
+      </c>
+      <c r="Y37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 2679-2024 georefererad karta.tif", "S 2679-2024")</f>
+        <v/>
+      </c>
+      <c r="AA37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 2679-2024 FSC-klagomål.docx", "S 2679-2024")</f>
+        <v/>
+      </c>
+      <c r="AB37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 2679-2024 FSC-klagomål mail.docx", "S 2679-2024")</f>
+        <v/>
+      </c>
+      <c r="AC37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 2679-2024 tillsynsbegäran.docx", "S 2679-2024")</f>
+        <v/>
+      </c>
+      <c r="AD37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 2679-2024 tillsynsbegäran mail.docx", "S 2679-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>S 1728-2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
         <v>46188</v>
       </c>
-      <c r="E34" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="E38" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I34" t="n">
+      <c r="I38" t="n">
         <v>3.3</v>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="n">
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
         <v>5</v>
       </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
         <v>5</v>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
         <v>6</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T38" t="n">
         <v>6</v>
       </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Grenplattnos
 Jungfrulin
@@ -4533,112 +4983,112 @@
 Murgröna</t>
         </is>
       </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27298-2026 artfynd.xlsx", "A 27298-2026")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27298-2026 karta.png", "A 27298-2026")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27298-2026 georefererad karta.tif", "A 27298-2026")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27298-2026 FSC-klagomål.docx", "A 27298-2026")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27298-2026 FSC-klagomål mail.docx", "A 27298-2026")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27298-2026 tillsynsbegäran.docx", "A 27298-2026")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27298-2026 tillsynsbegäran mail.docx", "A 27298-2026")</f>
+      <c r="W38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1728-2026 artfynd.xlsx", "S 1728-2026")</f>
+        <v/>
+      </c>
+      <c r="X38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1728-2026 karta.png", "S 1728-2026")</f>
+        <v/>
+      </c>
+      <c r="Y38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1728-2026 georefererad karta.tif", "S 1728-2026")</f>
+        <v/>
+      </c>
+      <c r="AA38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1728-2026 FSC-klagomål.docx", "S 1728-2026")</f>
+        <v/>
+      </c>
+      <c r="AB38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1728-2026 FSC-klagomål mail.docx", "S 1728-2026")</f>
+        <v/>
+      </c>
+      <c r="AC38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1728-2026 tillsynsbegäran.docx", "S 1728-2026")</f>
+        <v/>
+      </c>
+      <c r="AD38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1728-2026 tillsynsbegäran mail.docx", "S 1728-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 31558-2026</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>S 2060-2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="n">
         <v>46224</v>
       </c>
-      <c r="E35" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F35" t="inlineStr">
+      <c r="E39" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" t="n">
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
         <v>2</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K39" t="n">
         <v>2</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L39" t="n">
         <v>3</v>
       </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
         <v>3</v>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
         <v>6</v>
       </c>
-      <c r="T35" t="n">
+      <c r="T39" t="n">
         <v>7</v>
       </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Blå slemspindling
 Sårläka
@@ -4648,456 +5098,6 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31558-2026 artfynd.xlsx", "A 31558-2026")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31558-2026 karta.png", "A 31558-2026")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31558-2026 georefererad karta.tif", "A 31558-2026")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31558-2026 FSC-klagomål.docx", "A 31558-2026")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31558-2026 FSC-klagomål mail.docx", "A 31558-2026")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31558-2026 tillsynsbegäran.docx", "A 31558-2026")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31558-2026 tillsynsbegäran mail.docx", "A 31558-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>S 2737-2022</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>44704</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" t="n">
-        <v>2</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>4</v>
-      </c>
-      <c r="R36" t="n">
-        <v>3</v>
-      </c>
-      <c r="S36" t="n">
-        <v>6</v>
-      </c>
-      <c r="T36" t="n">
-        <v>23</v>
-      </c>
-      <c r="U36" t="n">
-        <v>18</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Mörk kraterlav
-Skogskorn
-Orangepudrad klotterlav
-Ekoxe
-Guldlockmossa</t>
-        </is>
-      </c>
-      <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2737-2022 artfynd.xlsx", "S 2737-2022")</f>
-        <v/>
-      </c>
-      <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 2737-2022 karta.png", "S 2737-2022")</f>
-        <v/>
-      </c>
-      <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 2737-2022 georefererad karta.tif", "S 2737-2022")</f>
-        <v/>
-      </c>
-      <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 2737-2022 FSC-klagomål.docx", "S 2737-2022")</f>
-        <v/>
-      </c>
-      <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 2737-2022 FSC-klagomål mail.docx", "S 2737-2022")</f>
-        <v/>
-      </c>
-      <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 2737-2022 tillsynsbegäran.docx", "S 2737-2022")</f>
-        <v/>
-      </c>
-      <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 2737-2022 tillsynsbegäran mail.docx", "S 2737-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>S 2679-2024</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>45478</v>
-      </c>
-      <c r="E37" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>2</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" t="n">
-        <v>3</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>4</v>
-      </c>
-      <c r="R37" t="n">
-        <v>4</v>
-      </c>
-      <c r="S37" t="n">
-        <v>6</v>
-      </c>
-      <c r="T37" t="n">
-        <v>14</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>Almlav
-Ask
-Skogsalm
-Blek kraterlav
-Slät lönnlav
-Vitskivlav</t>
-        </is>
-      </c>
-      <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2679-2024 artfynd.xlsx", "S 2679-2024")</f>
-        <v/>
-      </c>
-      <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 2679-2024 karta.png", "S 2679-2024")</f>
-        <v/>
-      </c>
-      <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 2679-2024 georefererad karta.tif", "S 2679-2024")</f>
-        <v/>
-      </c>
-      <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 2679-2024 FSC-klagomål.docx", "S 2679-2024")</f>
-        <v/>
-      </c>
-      <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 2679-2024 FSC-klagomål mail.docx", "S 2679-2024")</f>
-        <v/>
-      </c>
-      <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 2679-2024 tillsynsbegäran.docx", "S 2679-2024")</f>
-        <v/>
-      </c>
-      <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 2679-2024 tillsynsbegäran mail.docx", "S 2679-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>S 1728-2026</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" t="n">
-        <v>5</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>5</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>6</v>
-      </c>
-      <c r="T38" t="n">
-        <v>6</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>Grenplattnos
-Jungfrulin
-Skugglosta
-Sårläka
-Älg
-Murgröna</t>
-        </is>
-      </c>
-      <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1728-2026 artfynd.xlsx", "S 1728-2026")</f>
-        <v/>
-      </c>
-      <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1728-2026 karta.png", "S 1728-2026")</f>
-        <v/>
-      </c>
-      <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1728-2026 georefererad karta.tif", "S 1728-2026")</f>
-        <v/>
-      </c>
-      <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1728-2026 FSC-klagomål.docx", "S 1728-2026")</f>
-        <v/>
-      </c>
-      <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1728-2026 FSC-klagomål mail.docx", "S 1728-2026")</f>
-        <v/>
-      </c>
-      <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1728-2026 tillsynsbegäran.docx", "S 1728-2026")</f>
-        <v/>
-      </c>
-      <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1728-2026 tillsynsbegäran mail.docx", "S 1728-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>S 2060-2026</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="n">
-        <v>46224</v>
-      </c>
-      <c r="E39" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2</v>
-      </c>
-      <c r="K39" t="n">
-        <v>2</v>
-      </c>
-      <c r="L39" t="n">
-        <v>3</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>6</v>
-      </c>
-      <c r="T39" t="n">
-        <v>7</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>Blå slemspindling
-Sårläka
-Vårärt
-Anisspindling
-Skogsknipprot
-Grönvit nattviol</t>
-        </is>
-      </c>
       <c r="W39">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2060-2026 artfynd.xlsx", "S 2060-2026")</f>
         <v/>
@@ -5147,7 +5147,7 @@
         <v>44482</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>46169</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>46169</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45736</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 27290-2026</t>
+          <t>A 7960-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5589,14 +5589,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46188</v>
+        <v>44973</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5608,40 +5608,35 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
         <v>2</v>
       </c>
-      <c r="K44" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5650,9 +5645,122 @@
         <v>4</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Vresalm
+Pilfotsspindling
+Vippärt
+Strävlosta</t>
+        </is>
+      </c>
+      <c r="W44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 7960-2023 artfynd.xlsx", "A 7960-2023")</f>
+        <v/>
+      </c>
+      <c r="X44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 7960-2023 karta.png", "A 7960-2023")</f>
+        <v/>
+      </c>
+      <c r="Y44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 7960-2023 georefererad karta.tif", "A 7960-2023")</f>
+        <v/>
+      </c>
+      <c r="AA44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 7960-2023 FSC-klagomål.docx", "A 7960-2023")</f>
+        <v/>
+      </c>
+      <c r="AB44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 7960-2023 FSC-klagomål mail.docx", "A 7960-2023")</f>
+        <v/>
+      </c>
+      <c r="AC44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 7960-2023 tillsynsbegäran.docx", "A 7960-2023")</f>
+        <v/>
+      </c>
+      <c r="AD44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 7960-2023 tillsynsbegäran mail.docx", "A 7960-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A 27290-2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>2</v>
+      </c>
+      <c r="S45" t="n">
+        <v>4</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
         <is>
           <t>Ask
 Gotlandsmåra
@@ -5660,111 +5768,219 @@
 Havsörn</t>
         </is>
       </c>
-      <c r="W44">
+      <c r="W45">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27290-2026 artfynd.xlsx", "A 27290-2026")</f>
         <v/>
       </c>
-      <c r="X44">
+      <c r="X45">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27290-2026 karta.png", "A 27290-2026")</f>
         <v/>
       </c>
-      <c r="Y44">
+      <c r="Y45">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27290-2026 georefererad karta.tif", "A 27290-2026")</f>
         <v/>
       </c>
-      <c r="AA44">
+      <c r="AA45">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27290-2026 FSC-klagomål.docx", "A 27290-2026")</f>
         <v/>
       </c>
-      <c r="AB44">
+      <c r="AB45">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27290-2026 FSC-klagomål mail.docx", "A 27290-2026")</f>
         <v/>
       </c>
-      <c r="AC44">
+      <c r="AC45">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27290-2026 tillsynsbegäran.docx", "A 27290-2026")</f>
         <v/>
       </c>
-      <c r="AD44">
+      <c r="AD45">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27290-2026 tillsynsbegäran mail.docx", "A 27290-2026")</f>
         <v/>
       </c>
-      <c r="AE44">
+      <c r="AE45">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 27290-2026 prioriterade fågelarter.docx", "A 27290-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A 4164-2023</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>44953</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>2</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>4</v>
+      </c>
+      <c r="T46" t="n">
+        <v>5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Crepis tectorum subsp. tectorum
+Kösa
+Murgröna
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 4164-2023 artfynd.xlsx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="X46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 4164-2023 karta.png", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="Y46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 4164-2023 georefererad karta.tif", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AA46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 4164-2023 FSC-klagomål.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AB46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 4164-2023 FSC-klagomål mail.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AC46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 4164-2023 tillsynsbegäran.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AD46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 4164-2023 tillsynsbegäran mail.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>A 21797-2024</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D45" s="1" t="n">
+      <c r="D47" s="1" t="n">
         <v>45442</v>
       </c>
-      <c r="E45" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F45" t="inlineStr">
+      <c r="E47" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="I45" t="n">
+      <c r="I47" t="n">
         <v>1.4</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J47" t="n">
         <v>2</v>
       </c>
-      <c r="K45" t="n">
+      <c r="K47" t="n">
         <v>2</v>
       </c>
-      <c r="L45" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
         <v>4</v>
       </c>
-      <c r="T45" t="n">
+      <c r="T47" t="n">
         <v>11</v>
       </c>
-      <c r="U45" t="n">
+      <c r="U47" t="n">
         <v>6</v>
       </c>
-      <c r="V45" s="2" t="inlineStr">
+      <c r="V47" s="2" t="inlineStr">
         <is>
           <t>Sydlig kantmusseron
 Murgröna
@@ -5772,248 +5988,32 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W45">
+      <c r="W47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21797-2024 artfynd.xlsx", "A 21797-2024")</f>
         <v/>
       </c>
-      <c r="X45">
+      <c r="X47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21797-2024 karta.png", "A 21797-2024")</f>
         <v/>
       </c>
-      <c r="Y45">
+      <c r="Y47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21797-2024 georefererad karta.tif", "A 21797-2024")</f>
         <v/>
       </c>
-      <c r="AA45">
+      <c r="AA47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21797-2024 FSC-klagomål.docx", "A 21797-2024")</f>
         <v/>
       </c>
-      <c r="AB45">
+      <c r="AB47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21797-2024 FSC-klagomål mail.docx", "A 21797-2024")</f>
         <v/>
       </c>
-      <c r="AC45">
+      <c r="AC47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21797-2024 tillsynsbegäran.docx", "A 21797-2024")</f>
         <v/>
       </c>
-      <c r="AD45">
+      <c r="AD47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21797-2024 tillsynsbegäran mail.docx", "A 21797-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>A 4164-2023</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>44953</v>
-      </c>
-      <c r="E46" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" t="n">
-        <v>2</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>2</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>4</v>
-      </c>
-      <c r="T46" t="n">
-        <v>5</v>
-      </c>
-      <c r="U46" t="n">
-        <v>4</v>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>Crepis tectorum subsp. tectorum
-Kösa
-Murgröna
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 4164-2023 artfynd.xlsx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 4164-2023 karta.png", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 4164-2023 georefererad karta.tif", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 4164-2023 FSC-klagomål.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 4164-2023 FSC-klagomål mail.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 4164-2023 tillsynsbegäran.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 4164-2023 tillsynsbegäran mail.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>A 7960-2023</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>44973</v>
-      </c>
-      <c r="E47" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" t="n">
-        <v>2</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>3</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1</v>
-      </c>
-      <c r="S47" t="n">
-        <v>4</v>
-      </c>
-      <c r="T47" t="n">
-        <v>4</v>
-      </c>
-      <c r="U47" t="n">
-        <v>3</v>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>Vresalm
-Pilfotsspindling
-Vippärt
-Strävlosta</t>
-        </is>
-      </c>
-      <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 7960-2023 artfynd.xlsx", "A 7960-2023")</f>
-        <v/>
-      </c>
-      <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 7960-2023 karta.png", "A 7960-2023")</f>
-        <v/>
-      </c>
-      <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 7960-2023 georefererad karta.tif", "A 7960-2023")</f>
-        <v/>
-      </c>
-      <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 7960-2023 FSC-klagomål.docx", "A 7960-2023")</f>
-        <v/>
-      </c>
-      <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 7960-2023 FSC-klagomål mail.docx", "A 7960-2023")</f>
-        <v/>
-      </c>
-      <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 7960-2023 tillsynsbegäran.docx", "A 7960-2023")</f>
-        <v/>
-      </c>
-      <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 7960-2023 tillsynsbegäran mail.docx", "A 7960-2023")</f>
         <v/>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
         <v>44704</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6083,10 +6083,10 @@
         <v>4</v>
       </c>
       <c r="T48" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U48" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44704</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44783</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 24048-2025</t>
+          <t>A 38860-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6362,10 +6362,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45796</v>
+        <v>45887</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6378,22 +6378,22 @@
         </is>
       </c>
       <c r="I51" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J51" t="n">
         <v>2</v>
       </c>
-      <c r="J51" t="n">
-        <v>1</v>
-      </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6402,267 +6402,267 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
       </c>
       <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsknipprot
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 38860-2025 artfynd.xlsx", "A 38860-2025")</f>
+        <v/>
+      </c>
+      <c r="X51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 38860-2025 karta.png", "A 38860-2025")</f>
+        <v/>
+      </c>
+      <c r="Y51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 38860-2025 georefererad karta.tif", "A 38860-2025")</f>
+        <v/>
+      </c>
+      <c r="AA51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 38860-2025 FSC-klagomål.docx", "A 38860-2025")</f>
+        <v/>
+      </c>
+      <c r="AB51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 38860-2025 FSC-klagomål mail.docx", "A 38860-2025")</f>
+        <v/>
+      </c>
+      <c r="AC51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 38860-2025 tillsynsbegäran.docx", "A 38860-2025")</f>
+        <v/>
+      </c>
+      <c r="AD51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 38860-2025 tillsynsbegäran mail.docx", "A 38860-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>A 43542-2025</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>45911</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>2</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>2</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>Vårärt
+Ängsskära
+Underviol</t>
+        </is>
+      </c>
+      <c r="W52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 43542-2025 artfynd.xlsx", "A 43542-2025")</f>
+        <v/>
+      </c>
+      <c r="X52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 43542-2025 karta.png", "A 43542-2025")</f>
+        <v/>
+      </c>
+      <c r="Y52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 43542-2025 georefererad karta.tif", "A 43542-2025")</f>
+        <v/>
+      </c>
+      <c r="AA52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 43542-2025 FSC-klagomål.docx", "A 43542-2025")</f>
+        <v/>
+      </c>
+      <c r="AB52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 43542-2025 FSC-klagomål mail.docx", "A 43542-2025")</f>
+        <v/>
+      </c>
+      <c r="AC52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 43542-2025 tillsynsbegäran.docx", "A 43542-2025")</f>
+        <v/>
+      </c>
+      <c r="AD52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 43542-2025 tillsynsbegäran mail.docx", "A 43542-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>A 24048-2025</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>45796</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>2</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>2</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>3</v>
+      </c>
+      <c r="T53" t="n">
         <v>5</v>
       </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
         <is>
           <t>Loppstarr
 Ängsstarr
 Kärrknipprot</t>
         </is>
       </c>
-      <c r="W51">
+      <c r="W53">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24048-2025 artfynd.xlsx", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="X51">
+      <c r="X53">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24048-2025 karta.png", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="Y51">
+      <c r="Y53">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24048-2025 georefererad karta.tif", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="AA51">
+      <c r="AA53">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24048-2025 FSC-klagomål.docx", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="AB51">
+      <c r="AB53">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24048-2025 FSC-klagomål mail.docx", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="AC51">
+      <c r="AC53">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24048-2025 tillsynsbegäran.docx", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="AD51">
+      <c r="AD53">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24048-2025 tillsynsbegäran mail.docx", "A 24048-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>A 38860-2025</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="n">
-        <v>45887</v>
-      </c>
-      <c r="E52" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J52" t="n">
-        <v>2</v>
-      </c>
-      <c r="K52" t="n">
-        <v>1</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>1</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>1</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1</v>
-      </c>
-      <c r="S52" t="n">
-        <v>3</v>
-      </c>
-      <c r="T52" t="n">
-        <v>3</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsknipprot
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 38860-2025 artfynd.xlsx", "A 38860-2025")</f>
-        <v/>
-      </c>
-      <c r="X52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 38860-2025 karta.png", "A 38860-2025")</f>
-        <v/>
-      </c>
-      <c r="Y52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 38860-2025 georefererad karta.tif", "A 38860-2025")</f>
-        <v/>
-      </c>
-      <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 38860-2025 FSC-klagomål.docx", "A 38860-2025")</f>
-        <v/>
-      </c>
-      <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 38860-2025 FSC-klagomål mail.docx", "A 38860-2025")</f>
-        <v/>
-      </c>
-      <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 38860-2025 tillsynsbegäran.docx", "A 38860-2025")</f>
-        <v/>
-      </c>
-      <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 38860-2025 tillsynsbegäran mail.docx", "A 38860-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>A 43542-2025</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="n">
-        <v>45911</v>
-      </c>
-      <c r="E53" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" t="n">
-        <v>2</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>2</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>3</v>
-      </c>
-      <c r="T53" t="n">
-        <v>3</v>
-      </c>
-      <c r="U53" t="n">
-        <v>3</v>
-      </c>
-      <c r="V53" s="2" t="inlineStr">
-        <is>
-          <t>Vårärt
-Ängsskära
-Underviol</t>
-        </is>
-      </c>
-      <c r="W53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 43542-2025 artfynd.xlsx", "A 43542-2025")</f>
-        <v/>
-      </c>
-      <c r="X53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 43542-2025 karta.png", "A 43542-2025")</f>
-        <v/>
-      </c>
-      <c r="Y53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 43542-2025 georefererad karta.tif", "A 43542-2025")</f>
-        <v/>
-      </c>
-      <c r="AA53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 43542-2025 FSC-klagomål.docx", "A 43542-2025")</f>
-        <v/>
-      </c>
-      <c r="AB53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 43542-2025 FSC-klagomål mail.docx", "A 43542-2025")</f>
-        <v/>
-      </c>
-      <c r="AC53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 43542-2025 tillsynsbegäran.docx", "A 43542-2025")</f>
-        <v/>
-      </c>
-      <c r="AD53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 43542-2025 tillsynsbegäran mail.docx", "A 43542-2025")</f>
         <v/>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
         <v>46105</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>44781</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26849-2026</t>
+          <t>A 27283-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6907,14 +6907,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6932,34 +6932,34 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8.1</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
         <v>2</v>
       </c>
-      <c r="K56" t="n">
-        <v>3</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6971,687 +6971,687 @@
         <v>0</v>
       </c>
       <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Mindre poppelglasvinge
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27283-2026 artfynd.xlsx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="X56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27283-2026 karta.png", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="Y56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27283-2026 georefererad karta.tif", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AA56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27283-2026 FSC-klagomål.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AB56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27283-2026 FSC-klagomål mail.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AC56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27283-2026 tillsynsbegäran.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AD56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27283-2026 tillsynsbegäran mail.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>A 43756-2022</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>44837</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3</v>
+      </c>
+      <c r="T57" t="n">
+        <v>5</v>
+      </c>
+      <c r="U57" t="n">
+        <v>5</v>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>Murgröna
+Blåsippa
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 43756-2022 artfynd.xlsx", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="X57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 43756-2022 karta.png", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="Y57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 43756-2022 georefererad karta.tif", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="AA57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 43756-2022 FSC-klagomål.docx", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="AB57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 43756-2022 FSC-klagomål mail.docx", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="AC57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 43756-2022 tillsynsbegäran.docx", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="AD57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 43756-2022 tillsynsbegäran mail.docx", "A 43756-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>A 26849-2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
         <is>
           <t>Myskmadra
 Purpurknipprot
 Vit skogslilja</t>
         </is>
       </c>
-      <c r="W56">
+      <c r="W58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26849-2026 artfynd.xlsx", "A 26849-2026")</f>
         <v/>
       </c>
-      <c r="X56">
+      <c r="X58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26849-2026 karta.png", "A 26849-2026")</f>
         <v/>
       </c>
-      <c r="Y56">
+      <c r="Y58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26849-2026 georefererad karta.tif", "A 26849-2026")</f>
         <v/>
       </c>
-      <c r="AA56">
+      <c r="AA58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26849-2026 FSC-klagomål.docx", "A 26849-2026")</f>
         <v/>
       </c>
-      <c r="AB56">
+      <c r="AB58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26849-2026 FSC-klagomål mail.docx", "A 26849-2026")</f>
         <v/>
       </c>
-      <c r="AC56">
+      <c r="AC58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26849-2026 tillsynsbegäran.docx", "A 26849-2026")</f>
         <v/>
       </c>
-      <c r="AD56">
+      <c r="AD58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26849-2026 tillsynsbegäran mail.docx", "A 26849-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>A 27283-2026</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>A 31520-2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D57" s="1" t="n">
+      <c r="D59" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>3</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>3</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Grönsiska
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31520-2026 artfynd.xlsx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="X59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31520-2026 karta.png", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31520-2026 georefererad karta.tif", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31520-2026 FSC-klagomål.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31520-2026 FSC-klagomål mail.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31520-2026 tillsynsbegäran.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31520-2026 tillsynsbegäran mail.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AE59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 31520-2026 prioriterade fågelarter.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>S 846-2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>3</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Havsörn
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 846-2026 artfynd.xlsx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="X60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 846-2026 karta.png", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="Y60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 846-2026 georefererad karta.tif", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AA60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 846-2026 FSC-klagomål.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AB60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 846-2026 FSC-klagomål mail.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AC60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 846-2026 tillsynsbegäran.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AD60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 846-2026 tillsynsbegäran mail.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AE60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/S 846-2026 prioriterade fågelarter.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>S 1726-2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="n">
         <v>46188</v>
       </c>
-      <c r="E57" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F57" t="inlineStr">
+      <c r="E61" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I57" t="n">
+      <c r="I61" t="n">
         <v>2</v>
       </c>
-      <c r="J57" t="n">
-        <v>1</v>
-      </c>
-      <c r="K57" t="n">
-        <v>1</v>
-      </c>
-      <c r="L57" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>1</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
         <v>2</v>
       </c>
-      <c r="R57" t="n">
-        <v>1</v>
-      </c>
-      <c r="S57" t="n">
+      <c r="R61" t="n">
+        <v>1</v>
+      </c>
+      <c r="S61" t="n">
         <v>3</v>
       </c>
-      <c r="T57" t="n">
+      <c r="T61" t="n">
         <v>3</v>
       </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" s="2" t="inlineStr">
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
         <is>
           <t>Ask
 Mindre poppelglasvinge
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27283-2026 artfynd.xlsx", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="X57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27283-2026 karta.png", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="Y57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27283-2026 georefererad karta.tif", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="AA57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27283-2026 FSC-klagomål.docx", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="AB57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27283-2026 FSC-klagomål mail.docx", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="AC57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27283-2026 tillsynsbegäran.docx", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="AD57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27283-2026 tillsynsbegäran mail.docx", "A 27283-2026")</f>
+      <c r="W61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1726-2026 artfynd.xlsx", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="X61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1726-2026 karta.png", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="Y61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1726-2026 georefererad karta.tif", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="AA61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1726-2026 FSC-klagomål.docx", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="AB61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1726-2026 FSC-klagomål mail.docx", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="AC61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1726-2026 tillsynsbegäran.docx", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="AD61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1726-2026 tillsynsbegäran mail.docx", "S 1726-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>A 31520-2026</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="n">
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>S 2059-2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E58" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F58" t="inlineStr">
+      <c r="E62" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I58" t="n">
+      <c r="I62" t="n">
         <v>1.1</v>
       </c>
-      <c r="J58" t="n">
+      <c r="J62" t="n">
         <v>3</v>
       </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>1</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
         <v>3</v>
       </c>
-      <c r="T58" t="n">
+      <c r="T62" t="n">
         <v>4</v>
       </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" s="2" t="inlineStr">
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Grönsiska
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31520-2026 artfynd.xlsx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="X58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31520-2026 karta.png", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="Y58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31520-2026 georefererad karta.tif", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AA58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31520-2026 FSC-klagomål.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AB58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31520-2026 FSC-klagomål mail.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AC58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31520-2026 tillsynsbegäran.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AD58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31520-2026 tillsynsbegäran mail.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AE58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 31520-2026 prioriterade fågelarter.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>A 43756-2022</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="n">
-        <v>44837</v>
-      </c>
-      <c r="E59" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J59" t="n">
-        <v>2</v>
-      </c>
-      <c r="K59" t="n">
-        <v>1</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>3</v>
-      </c>
-      <c r="T59" t="n">
-        <v>5</v>
-      </c>
-      <c r="U59" t="n">
-        <v>5</v>
-      </c>
-      <c r="V59" s="2" t="inlineStr">
-        <is>
-          <t>Murgröna
-Blåsippa
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 43756-2022 artfynd.xlsx", "A 43756-2022")</f>
-        <v/>
-      </c>
-      <c r="X59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 43756-2022 karta.png", "A 43756-2022")</f>
-        <v/>
-      </c>
-      <c r="Y59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 43756-2022 georefererad karta.tif", "A 43756-2022")</f>
-        <v/>
-      </c>
-      <c r="AA59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 43756-2022 FSC-klagomål.docx", "A 43756-2022")</f>
-        <v/>
-      </c>
-      <c r="AB59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 43756-2022 FSC-klagomål mail.docx", "A 43756-2022")</f>
-        <v/>
-      </c>
-      <c r="AC59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 43756-2022 tillsynsbegäran.docx", "A 43756-2022")</f>
-        <v/>
-      </c>
-      <c r="AD59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 43756-2022 tillsynsbegäran mail.docx", "A 43756-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>S 846-2026</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E60" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J60" t="n">
-        <v>3</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>1</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="n">
-        <v>3</v>
-      </c>
-      <c r="T60" t="n">
-        <v>3</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Havsörn
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 846-2026 artfynd.xlsx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="X60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 846-2026 karta.png", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="Y60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 846-2026 georefererad karta.tif", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AA60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 846-2026 FSC-klagomål.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AB60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 846-2026 FSC-klagomål mail.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AC60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 846-2026 tillsynsbegäran.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AD60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 846-2026 tillsynsbegäran mail.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AE60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/S 846-2026 prioriterade fågelarter.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>S 1726-2026</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E61" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I61" t="n">
-        <v>2</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1</v>
-      </c>
-      <c r="K61" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" t="n">
-        <v>1</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>1</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>2</v>
-      </c>
-      <c r="R61" t="n">
-        <v>1</v>
-      </c>
-      <c r="S61" t="n">
-        <v>3</v>
-      </c>
-      <c r="T61" t="n">
-        <v>3</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Mindre poppelglasvinge
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1726-2026 artfynd.xlsx", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="X61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1726-2026 karta.png", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="Y61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1726-2026 georefererad karta.tif", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="AA61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1726-2026 FSC-klagomål.docx", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="AB61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1726-2026 FSC-klagomål mail.docx", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="AC61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1726-2026 tillsynsbegäran.docx", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="AD61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1726-2026 tillsynsbegäran mail.docx", "S 1726-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>S 2059-2026</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E62" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I62" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J62" t="n">
-        <v>3</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>1</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>1</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>3</v>
-      </c>
-      <c r="T62" t="n">
-        <v>4</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Grönsiska
-Kungsfågel</t>
-        </is>
-      </c>
       <c r="W62">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2059-2026 artfynd.xlsx", "S 2059-2026")</f>
         <v/>
@@ -7705,7 +7705,7 @@
         <v>44623</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 24166-2022</t>
+          <t>A 21908-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7804,14 +7804,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44725</v>
+        <v>44711</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7824,19 +7824,19 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>10.7</v>
+        <v>4.7</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -7848,10 +7848,10 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>2</v>
@@ -7860,47 +7860,47 @@
         <v>2</v>
       </c>
       <c r="U64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>Plattsäv
-Jungfrulin</t>
+          <t>Myskmadra
+Skogsknipprot</t>
         </is>
       </c>
       <c r="W64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24166-2022 artfynd.xlsx", "A 24166-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21908-2022 artfynd.xlsx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="X64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24166-2022 karta.png", "A 24166-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21908-2022 karta.png", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="Y64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24166-2022 georefererad karta.tif", "A 24166-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21908-2022 georefererad karta.tif", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AA64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24166-2022 FSC-klagomål.docx", "A 24166-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21908-2022 FSC-klagomål.docx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AB64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24166-2022 FSC-klagomål mail.docx", "A 24166-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21908-2022 FSC-klagomål mail.docx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AC64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24166-2022 tillsynsbegäran.docx", "A 24166-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21908-2022 tillsynsbegäran.docx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AD64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24166-2022 tillsynsbegäran mail.docx", "A 24166-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21908-2022 tillsynsbegäran mail.docx", "A 21908-2022")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 9253-2026</t>
+          <t>A 24166-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7910,14 +7910,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46070</v>
+        <v>44725</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7930,19 +7930,19 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>10.7</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -7954,10 +7954,10 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S65" t="n">
         <v>2</v>
@@ -7966,47 +7966,47 @@
         <v>2</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>Murgröna
-Gullviva</t>
+          <t>Plattsäv
+Jungfrulin</t>
         </is>
       </c>
       <c r="W65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9253-2026 artfynd.xlsx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24166-2022 artfynd.xlsx", "A 24166-2022")</f>
         <v/>
       </c>
       <c r="X65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9253-2026 karta.png", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24166-2022 karta.png", "A 24166-2022")</f>
         <v/>
       </c>
       <c r="Y65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9253-2026 georefererad karta.tif", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24166-2022 georefererad karta.tif", "A 24166-2022")</f>
         <v/>
       </c>
       <c r="AA65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9253-2026 FSC-klagomål.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24166-2022 FSC-klagomål.docx", "A 24166-2022")</f>
         <v/>
       </c>
       <c r="AB65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9253-2026 FSC-klagomål mail.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24166-2022 FSC-klagomål mail.docx", "A 24166-2022")</f>
         <v/>
       </c>
       <c r="AC65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9253-2026 tillsynsbegäran.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24166-2022 tillsynsbegäran.docx", "A 24166-2022")</f>
         <v/>
       </c>
       <c r="AD65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9253-2026 tillsynsbegäran mail.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24166-2022 tillsynsbegäran mail.docx", "A 24166-2022")</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 60141-2025</t>
+          <t>A 9253-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -8020,10 +8020,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45994</v>
+        <v>46070</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>1</v>
@@ -8069,50 +8069,50 @@
         <v>2</v>
       </c>
       <c r="T66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>Strävlosta
-Långbensgroda</t>
+          <t>Murgröna
+Gullviva</t>
         </is>
       </c>
       <c r="W66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 60141-2025 artfynd.xlsx", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9253-2026 artfynd.xlsx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="X66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 60141-2025 karta.png", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9253-2026 karta.png", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="Y66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 60141-2025 georefererad karta.tif", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9253-2026 georefererad karta.tif", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AA66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 60141-2025 FSC-klagomål.docx", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9253-2026 FSC-klagomål.docx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AB66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 60141-2025 FSC-klagomål mail.docx", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9253-2026 FSC-klagomål mail.docx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AC66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 60141-2025 tillsynsbegäran.docx", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9253-2026 tillsynsbegäran.docx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AD66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 60141-2025 tillsynsbegäran mail.docx", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9253-2026 tillsynsbegäran mail.docx", "A 9253-2026")</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60140-2025</t>
+          <t>A 60141-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8129,7 +8129,7 @@
         <v>45994</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8142,13 +8142,13 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -8175,50 +8175,50 @@
         <v>2</v>
       </c>
       <c r="T67" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot
-Strävlosta</t>
+          <t>Strävlosta
+Långbensgroda</t>
         </is>
       </c>
       <c r="W67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 60140-2025 artfynd.xlsx", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 60141-2025 artfynd.xlsx", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="X67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 60140-2025 karta.png", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 60141-2025 karta.png", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="Y67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 60140-2025 georefererad karta.tif", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 60141-2025 georefererad karta.tif", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="AA67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 60140-2025 FSC-klagomål.docx", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 60141-2025 FSC-klagomål.docx", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="AB67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 60140-2025 FSC-klagomål mail.docx", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 60141-2025 FSC-klagomål mail.docx", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="AC67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 60140-2025 tillsynsbegäran.docx", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 60141-2025 tillsynsbegäran.docx", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="AD67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 60140-2025 tillsynsbegäran mail.docx", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 60141-2025 tillsynsbegäran mail.docx", "A 60141-2025")</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 44678-2022</t>
+          <t>A 60140-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -8232,10 +8232,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44840</v>
+        <v>45994</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8248,13 +8248,13 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>1</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -8263,7 +8263,7 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8272,52 +8272,52 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>2</v>
       </c>
       <c r="T68" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>Ask
-Skogsknipprot</t>
+          <t>Skogsknipprot
+Strävlosta</t>
         </is>
       </c>
       <c r="W68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 44678-2022 artfynd.xlsx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 60140-2025 artfynd.xlsx", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="X68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 44678-2022 karta.png", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 60140-2025 karta.png", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="Y68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 44678-2022 georefererad karta.tif", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 60140-2025 georefererad karta.tif", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="AA68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 44678-2022 FSC-klagomål.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 60140-2025 FSC-klagomål.docx", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="AB68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 44678-2022 FSC-klagomål mail.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 60140-2025 FSC-klagomål mail.docx", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="AC68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 44678-2022 tillsynsbegäran.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 60140-2025 tillsynsbegäran.docx", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="AD68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 44678-2022 tillsynsbegäran mail.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 60140-2025 tillsynsbegäran mail.docx", "A 60140-2025")</f>
         <v/>
       </c>
     </row>
@@ -8341,7 +8341,7 @@
         <v>46169</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 17699-2025</t>
+          <t>A 29411-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -8445,14 +8445,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45758</v>
+        <v>46203</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8464,20 +8464,25 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N70" t="n">
         <v>0</v>
@@ -8489,10 +8494,10 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S70" t="n">
         <v>2</v>
@@ -8501,47 +8506,47 @@
         <v>2</v>
       </c>
       <c r="U70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan
-Klibbveronika</t>
+          <t>Bredbrämad bastardsvärmare
+Ekoxe</t>
         </is>
       </c>
       <c r="W70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 17699-2025 artfynd.xlsx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 29411-2026 artfynd.xlsx", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="X70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 17699-2025 karta.png", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 29411-2026 karta.png", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="Y70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 17699-2025 georefererad karta.tif", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 29411-2026 georefererad karta.tif", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="AA70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 17699-2025 FSC-klagomål.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 29411-2026 FSC-klagomål.docx", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="AB70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 17699-2025 FSC-klagomål mail.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 29411-2026 FSC-klagomål mail.docx", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="AC70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 17699-2025 tillsynsbegäran.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 29411-2026 tillsynsbegäran.docx", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="AD70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 17699-2025 tillsynsbegäran mail.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 29411-2026 tillsynsbegäran mail.docx", "A 29411-2026")</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29411-2026</t>
+          <t>A 44678-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8551,14 +8556,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46203</v>
+        <v>44840</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8570,13 +8575,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J71" t="n">
         <v>1</v>
@@ -8588,10 +8588,10 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8616,43 +8616,43 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare
-Ekoxe</t>
+          <t>Ask
+Skogsknipprot</t>
         </is>
       </c>
       <c r="W71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 29411-2026 artfynd.xlsx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 44678-2022 artfynd.xlsx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="X71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 29411-2026 karta.png", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 44678-2022 karta.png", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="Y71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 29411-2026 georefererad karta.tif", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 44678-2022 georefererad karta.tif", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AA71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 29411-2026 FSC-klagomål.docx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 44678-2022 FSC-klagomål.docx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AB71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 29411-2026 FSC-klagomål mail.docx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 44678-2022 FSC-klagomål mail.docx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AC71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 29411-2026 tillsynsbegäran.docx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 44678-2022 tillsynsbegäran.docx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AD71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 29411-2026 tillsynsbegäran mail.docx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 44678-2022 tillsynsbegäran mail.docx", "A 44678-2022")</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 21908-2022</t>
+          <t>A 29434-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8662,14 +8662,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44711</v>
+        <v>46203</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8681,21 +8681,26 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
         <v>2</v>
       </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
       <c r="N72" t="n">
         <v>0</v>
       </c>
@@ -8706,10 +8711,10 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S72" t="n">
         <v>2</v>
@@ -8718,47 +8723,47 @@
         <v>2</v>
       </c>
       <c r="U72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra
-Skogsknipprot</t>
+          <t>Bredbrämad bastardsvärmare
+Purpurmusseron</t>
         </is>
       </c>
       <c r="W72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21908-2022 artfynd.xlsx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 29434-2026 artfynd.xlsx", "A 29434-2026")</f>
         <v/>
       </c>
       <c r="X72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21908-2022 karta.png", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 29434-2026 karta.png", "A 29434-2026")</f>
         <v/>
       </c>
       <c r="Y72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21908-2022 georefererad karta.tif", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 29434-2026 georefererad karta.tif", "A 29434-2026")</f>
         <v/>
       </c>
       <c r="AA72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21908-2022 FSC-klagomål.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 29434-2026 FSC-klagomål.docx", "A 29434-2026")</f>
         <v/>
       </c>
       <c r="AB72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21908-2022 FSC-klagomål mail.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 29434-2026 FSC-klagomål mail.docx", "A 29434-2026")</f>
         <v/>
       </c>
       <c r="AC72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21908-2022 tillsynsbegäran.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 29434-2026 tillsynsbegäran.docx", "A 29434-2026")</f>
         <v/>
       </c>
       <c r="AD72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21908-2022 tillsynsbegäran mail.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 29434-2026 tillsynsbegäran mail.docx", "A 29434-2026")</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 29434-2026</t>
+          <t>A 17699-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8768,14 +8773,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46203</v>
+        <v>45758</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8787,13 +8792,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8802,10 +8802,10 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
@@ -8820,7 +8820,7 @@
         <v>2</v>
       </c>
       <c r="R73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>2</v>
@@ -8829,47 +8829,47 @@
         <v>2</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare
-Purpurmusseron</t>
+          <t>Backtimjan
+Klibbveronika</t>
         </is>
       </c>
       <c r="W73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 29434-2026 artfynd.xlsx", "A 29434-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 17699-2025 artfynd.xlsx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="X73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 29434-2026 karta.png", "A 29434-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 17699-2025 karta.png", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="Y73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 29434-2026 georefererad karta.tif", "A 29434-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 17699-2025 georefererad karta.tif", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AA73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 29434-2026 FSC-klagomål.docx", "A 29434-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 17699-2025 FSC-klagomål.docx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AB73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 29434-2026 FSC-klagomål mail.docx", "A 29434-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 17699-2025 FSC-klagomål mail.docx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AC73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 29434-2026 tillsynsbegäran.docx", "A 29434-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 17699-2025 tillsynsbegäran.docx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AD73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 29434-2026 tillsynsbegäran mail.docx", "A 29434-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 17699-2025 tillsynsbegäran mail.docx", "A 17699-2025")</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S 1650-2022</t>
+          <t>S 6144-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8879,14 +8879,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44649</v>
+        <v>44865</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8899,16 +8899,16 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -8923,7 +8923,7 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
@@ -8932,50 +8932,50 @@
         <v>2</v>
       </c>
       <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
         <v>2</v>
       </c>
-      <c r="U74" t="n">
-        <v>0</v>
-      </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa
-Gulpudrad spiklav</t>
+          <t>Oxtungssvamp
+Fläcknycklar</t>
         </is>
       </c>
       <c r="W74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1650-2022 artfynd.xlsx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 6144-2022 artfynd.xlsx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="X74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1650-2022 karta.png", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 6144-2022 karta.png", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="Y74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1650-2022 georefererad karta.tif", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 6144-2022 georefererad karta.tif", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AA74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1650-2022 FSC-klagomål.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 6144-2022 FSC-klagomål.docx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AB74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1650-2022 FSC-klagomål mail.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 6144-2022 FSC-klagomål mail.docx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AC74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1650-2022 tillsynsbegäran.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 6144-2022 tillsynsbegäran.docx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AD74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1650-2022 tillsynsbegäran mail.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 6144-2022 tillsynsbegäran mail.docx", "S 6144-2022")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S 6144-2022</t>
+          <t>S 1650-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8985,14 +8985,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44865</v>
+        <v>44649</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9005,16 +9005,16 @@
         </is>
       </c>
       <c r="I75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
         <v>2</v>
       </c>
-      <c r="J75" t="n">
-        <v>1</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -9029,7 +9029,7 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -9038,43 +9038,43 @@
         <v>2</v>
       </c>
       <c r="T75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>Oxtungssvamp
-Fläcknycklar</t>
+          <t>Guldlockmossa
+Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="W75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 6144-2022 artfynd.xlsx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1650-2022 artfynd.xlsx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="X75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 6144-2022 karta.png", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1650-2022 karta.png", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="Y75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 6144-2022 georefererad karta.tif", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1650-2022 georefererad karta.tif", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AA75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 6144-2022 FSC-klagomål.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1650-2022 FSC-klagomål.docx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AB75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 6144-2022 FSC-klagomål mail.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1650-2022 FSC-klagomål mail.docx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AC75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 6144-2022 tillsynsbegäran.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1650-2022 tillsynsbegäran.docx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AD75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 6144-2022 tillsynsbegäran mail.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1650-2022 tillsynsbegäran mail.docx", "S 1650-2022")</f>
         <v/>
       </c>
     </row>
@@ -9098,7 +9098,7 @@
         <v>46203</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>46203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44772</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44781</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 3302-2026</t>
+          <t>A 24701-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9533,14 +9533,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46041</v>
+        <v>45084</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9553,10 +9553,10 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="J80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -9568,7 +9568,7 @@
         <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9577,58 +9577,58 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
       </c>
       <c r="T80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 3302-2026 artfynd.xlsx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24701-2023 artfynd.xlsx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="X80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 3302-2026 karta.png", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24701-2023 karta.png", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="Y80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 3302-2026 georefererad karta.tif", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24701-2023 georefererad karta.tif", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AA80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 3302-2026 FSC-klagomål.docx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24701-2023 FSC-klagomål.docx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AB80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 3302-2026 FSC-klagomål mail.docx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24701-2023 FSC-klagomål mail.docx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AC80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 3302-2026 tillsynsbegäran.docx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24701-2023 tillsynsbegäran.docx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AD80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 3302-2026 tillsynsbegäran mail.docx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24701-2023 tillsynsbegäran mail.docx", "A 24701-2023")</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 9745-2023</t>
+          <t>A 41831-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44984</v>
+        <v>45902</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>1</v>
@@ -9691,10 +9691,10 @@
         <v>1</v>
       </c>
       <c r="T81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
@@ -9702,38 +9702,38 @@
         </is>
       </c>
       <c r="W81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9745-2023 artfynd.xlsx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 41831-2025 artfynd.xlsx", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="X81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9745-2023 karta.png", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 41831-2025 karta.png", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="Y81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9745-2023 georefererad karta.tif", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 41831-2025 georefererad karta.tif", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="AA81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9745-2023 FSC-klagomål.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 41831-2025 FSC-klagomål.docx", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="AB81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9745-2023 FSC-klagomål mail.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 41831-2025 FSC-klagomål mail.docx", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="AC81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9745-2023 tillsynsbegäran.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 41831-2025 tillsynsbegäran.docx", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="AD81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9745-2023 tillsynsbegäran mail.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 41831-2025 tillsynsbegäran mail.docx", "A 41831-2025")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 41831-2025</t>
+          <t>A 3302-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9743,14 +9743,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45902</v>
+        <v>46041</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J82" t="n">
         <v>1</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -9803,42 +9803,42 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 41831-2025 artfynd.xlsx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 3302-2026 artfynd.xlsx", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="X82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 41831-2025 karta.png", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 3302-2026 karta.png", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="Y82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 41831-2025 georefererad karta.tif", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 3302-2026 georefererad karta.tif", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="AA82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 41831-2025 FSC-klagomål.docx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 3302-2026 FSC-klagomål.docx", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="AB82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 41831-2025 FSC-klagomål mail.docx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 3302-2026 FSC-klagomål mail.docx", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="AC82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 41831-2025 tillsynsbegäran.docx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 3302-2026 tillsynsbegäran.docx", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="AD82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 41831-2025 tillsynsbegäran mail.docx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 3302-2026 tillsynsbegäran mail.docx", "A 3302-2026")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 20878-2024</t>
+          <t>A 7481-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9852,10 +9852,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45439</v>
+        <v>46059</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9912,38 +9912,38 @@
         </is>
       </c>
       <c r="W83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 20878-2024 artfynd.xlsx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 7481-2026 artfynd.xlsx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="X83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 20878-2024 karta.png", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 7481-2026 karta.png", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="Y83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 20878-2024 georefererad karta.tif", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 7481-2026 georefererad karta.tif", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AA83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 20878-2024 FSC-klagomål.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 7481-2026 FSC-klagomål.docx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AB83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 20878-2024 FSC-klagomål mail.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 7481-2026 FSC-klagomål mail.docx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AC83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 20878-2024 tillsynsbegäran.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 7481-2026 tillsynsbegäran.docx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AD83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 20878-2024 tillsynsbegäran mail.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 7481-2026 tillsynsbegäran mail.docx", "A 7481-2026")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 7481-2026</t>
+          <t>A 9104-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9953,14 +9953,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46059</v>
+        <v>46069</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9973,10 +9973,10 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -10006,49 +10006,49 @@
         <v>1</v>
       </c>
       <c r="T84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="W84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 7481-2026 artfynd.xlsx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9104-2026 artfynd.xlsx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="X84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 7481-2026 karta.png", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9104-2026 karta.png", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="Y84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 7481-2026 georefererad karta.tif", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9104-2026 georefererad karta.tif", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AA84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 7481-2026 FSC-klagomål.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9104-2026 FSC-klagomål.docx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AB84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 7481-2026 FSC-klagomål mail.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9104-2026 FSC-klagomål mail.docx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AC84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 7481-2026 tillsynsbegäran.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9104-2026 tillsynsbegäran.docx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AD84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 7481-2026 tillsynsbegäran mail.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9104-2026 tillsynsbegäran mail.docx", "A 9104-2026")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 9104-2026</t>
+          <t>A 9905-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10058,14 +10058,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46069</v>
+        <v>46073</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -10093,7 +10093,7 @@
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10102,10 +10102,10 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
@@ -10114,46 +10114,46 @@
         <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9104-2026 artfynd.xlsx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9905-2026 artfynd.xlsx", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="X85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9104-2026 karta.png", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9905-2026 karta.png", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="Y85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9104-2026 georefererad karta.tif", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9905-2026 georefererad karta.tif", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="AA85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9104-2026 FSC-klagomål.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9905-2026 FSC-klagomål.docx", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="AB85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9104-2026 FSC-klagomål mail.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9905-2026 FSC-klagomål mail.docx", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="AC85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9104-2026 tillsynsbegäran.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9905-2026 tillsynsbegäran.docx", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="AD85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9104-2026 tillsynsbegäran mail.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9905-2026 tillsynsbegäran mail.docx", "A 9905-2026")</f>
         <v/>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 9905-2026</t>
+          <t>A 63276-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46073</v>
+        <v>45273</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -10195,10 +10195,10 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10223,42 +10223,42 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Elaphomyces barrioi</t>
         </is>
       </c>
       <c r="W86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9905-2026 artfynd.xlsx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 63276-2023 artfynd.xlsx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="X86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9905-2026 karta.png", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 63276-2023 karta.png", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="Y86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9905-2026 georefererad karta.tif", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 63276-2023 georefererad karta.tif", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AA86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9905-2026 FSC-klagomål.docx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 63276-2023 FSC-klagomål.docx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AB86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9905-2026 FSC-klagomål mail.docx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 63276-2023 FSC-klagomål mail.docx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AC86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9905-2026 tillsynsbegäran.docx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 63276-2023 tillsynsbegäran.docx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AD86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9905-2026 tillsynsbegäran mail.docx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 63276-2023 tillsynsbegäran mail.docx", "A 63276-2023")</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 31720-2022</t>
+          <t>A 28785-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10268,14 +10268,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44776</v>
+        <v>45820</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10293,13 +10293,13 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="J87" t="n">
         <v>1</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -10329,39 +10329,43 @@
         <v>1</v>
       </c>
       <c r="U87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31720-2022 artfynd.xlsx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28785-2025 artfynd.xlsx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="X87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31720-2022 karta.png", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28785-2025 karta.png", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="Y87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31720-2022 georefererad karta.tif", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28785-2025 georefererad karta.tif", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AA87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31720-2022 FSC-klagomål.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28785-2025 FSC-klagomål.docx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AB87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31720-2022 FSC-klagomål mail.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28785-2025 FSC-klagomål mail.docx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AC87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31720-2022 tillsynsbegäran.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28785-2025 tillsynsbegäran.docx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AD87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31720-2022 tillsynsbegäran mail.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28785-2025 tillsynsbegäran mail.docx", "A 28785-2025")</f>
+        <v/>
+      </c>
+      <c r="AE87">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 28785-2025 prioriterade fågelarter.docx", "A 28785-2025")</f>
         <v/>
       </c>
     </row>
@@ -10385,7 +10389,7 @@
         <v>45820</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10482,7 +10486,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 28785-2025</t>
+          <t>A 24704-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10492,14 +10496,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45820</v>
+        <v>45084</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10511,16 +10515,11 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -10532,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -10541,62 +10540,58 @@
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S89" t="n">
         <v>1</v>
       </c>
       <c r="T89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U89" t="n">
         <v>0</v>
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28785-2025 artfynd.xlsx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24704-2023 artfynd.xlsx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="X89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28785-2025 karta.png", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24704-2023 karta.png", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="Y89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28785-2025 georefererad karta.tif", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24704-2023 georefererad karta.tif", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AA89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28785-2025 FSC-klagomål.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24704-2023 FSC-klagomål.docx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AB89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28785-2025 FSC-klagomål mail.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24704-2023 FSC-klagomål mail.docx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AC89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28785-2025 tillsynsbegäran.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24704-2023 tillsynsbegäran.docx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AD89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28785-2025 tillsynsbegäran mail.docx", "A 28785-2025")</f>
-        <v/>
-      </c>
-      <c r="AE89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 28785-2025 prioriterade fågelarter.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24704-2023 tillsynsbegäran mail.docx", "A 24704-2023")</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 24701-2023</t>
+          <t>A 9745-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10610,10 +10605,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45084</v>
+        <v>44984</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10626,13 +10621,13 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -10641,7 +10636,7 @@
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -10650,58 +10645,58 @@
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>1</v>
       </c>
       <c r="T90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24701-2023 artfynd.xlsx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9745-2023 artfynd.xlsx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="X90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24701-2023 karta.png", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9745-2023 karta.png", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="Y90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24701-2023 georefererad karta.tif", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9745-2023 georefererad karta.tif", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AA90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24701-2023 FSC-klagomål.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9745-2023 FSC-klagomål.docx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AB90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24701-2023 FSC-klagomål mail.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9745-2023 FSC-klagomål mail.docx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AC90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24701-2023 tillsynsbegäran.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9745-2023 tillsynsbegäran.docx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AD90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24701-2023 tillsynsbegäran mail.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9745-2023 tillsynsbegäran mail.docx", "A 9745-2023")</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 24704-2023</t>
+          <t>A 26840-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10711,14 +10706,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45084</v>
+        <v>46185</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10730,8 +10725,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -10764,7 +10764,7 @@
         <v>1</v>
       </c>
       <c r="T91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
@@ -10775,38 +10775,38 @@
         </is>
       </c>
       <c r="W91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24704-2023 artfynd.xlsx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26840-2026 artfynd.xlsx", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="X91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24704-2023 karta.png", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26840-2026 karta.png", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="Y91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24704-2023 georefererad karta.tif", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26840-2026 georefererad karta.tif", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="AA91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24704-2023 FSC-klagomål.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26840-2026 FSC-klagomål.docx", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="AB91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24704-2023 FSC-klagomål mail.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26840-2026 FSC-klagomål mail.docx", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="AC91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24704-2023 tillsynsbegäran.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26840-2026 tillsynsbegäran.docx", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="AD91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24704-2023 tillsynsbegäran mail.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26840-2026 tillsynsbegäran mail.docx", "A 26840-2026")</f>
         <v/>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 26840-2026</t>
+          <t>A 28374-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10820,10 +10820,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46185</v>
+        <v>46196</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -10853,10 +10853,10 @@
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -10874,42 +10874,42 @@
         <v>1</v>
       </c>
       <c r="T92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Purpurmusseron</t>
         </is>
       </c>
       <c r="W92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26840-2026 artfynd.xlsx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28374-2026 artfynd.xlsx", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="X92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26840-2026 karta.png", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28374-2026 karta.png", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="Y92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26840-2026 georefererad karta.tif", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28374-2026 georefererad karta.tif", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="AA92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26840-2026 FSC-klagomål.docx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28374-2026 FSC-klagomål.docx", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="AB92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26840-2026 FSC-klagomål mail.docx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28374-2026 FSC-klagomål mail.docx", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="AC92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26840-2026 tillsynsbegäran.docx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28374-2026 tillsynsbegäran.docx", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="AD92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26840-2026 tillsynsbegäran mail.docx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28374-2026 tillsynsbegäran mail.docx", "A 28374-2026")</f>
         <v/>
       </c>
     </row>
@@ -10933,7 +10933,7 @@
         <v>46197</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 28374-2026</t>
+          <t>A 31720-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -11036,14 +11036,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46196</v>
+        <v>44776</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11061,19 +11061,19 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
         <v>0</v>
@@ -11085,10 +11085,10 @@
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>1</v>
@@ -11097,39 +11097,39 @@
         <v>1</v>
       </c>
       <c r="U94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>Purpurmusseron</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28374-2026 artfynd.xlsx", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31720-2022 artfynd.xlsx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="X94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28374-2026 karta.png", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31720-2022 karta.png", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="Y94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28374-2026 georefererad karta.tif", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31720-2022 georefererad karta.tif", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AA94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28374-2026 FSC-klagomål.docx", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31720-2022 FSC-klagomål.docx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AB94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28374-2026 FSC-klagomål mail.docx", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31720-2022 FSC-klagomål mail.docx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AC94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28374-2026 tillsynsbegäran.docx", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31720-2022 tillsynsbegäran.docx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AD94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28374-2026 tillsynsbegäran mail.docx", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31720-2022 tillsynsbegäran mail.docx", "A 31720-2022")</f>
         <v/>
       </c>
     </row>
@@ -11153,7 +11153,7 @@
         <v>45433</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>46246</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 63276-2023</t>
+          <t>A 13043-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -11365,10 +11365,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45273</v>
+        <v>45385</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11381,19 +11381,19 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
         <v>0</v>
@@ -11405,10 +11405,10 @@
         <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>1</v>
@@ -11421,42 +11421,42 @@
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>Elaphomyces barrioi</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 63276-2023 artfynd.xlsx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 13043-2024 artfynd.xlsx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="X97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 63276-2023 karta.png", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 13043-2024 karta.png", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="Y97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 63276-2023 georefererad karta.tif", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 13043-2024 georefererad karta.tif", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AA97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 63276-2023 FSC-klagomål.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 13043-2024 FSC-klagomål.docx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AB97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 63276-2023 FSC-klagomål mail.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 13043-2024 FSC-klagomål mail.docx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AC97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 63276-2023 tillsynsbegäran.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 13043-2024 tillsynsbegäran.docx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AD97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 63276-2023 tillsynsbegäran mail.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 13043-2024 tillsynsbegäran mail.docx", "A 13043-2024")</f>
         <v/>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 13043-2024</t>
+          <t>A 20878-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -11470,10 +11470,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45385</v>
+        <v>45439</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11486,13 +11486,13 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J98" t="n">
         <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -11519,42 +11519,42 @@
         <v>1</v>
       </c>
       <c r="T98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 13043-2024 artfynd.xlsx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 20878-2024 artfynd.xlsx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="X98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 13043-2024 karta.png", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 20878-2024 karta.png", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="Y98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 13043-2024 georefererad karta.tif", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 20878-2024 georefererad karta.tif", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AA98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 13043-2024 FSC-klagomål.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 20878-2024 FSC-klagomål.docx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AB98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 13043-2024 FSC-klagomål mail.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 20878-2024 FSC-klagomål mail.docx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AC98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 13043-2024 tillsynsbegäran.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 20878-2024 tillsynsbegäran.docx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AD98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 13043-2024 tillsynsbegäran mail.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 20878-2024 tillsynsbegäran mail.docx", "A 20878-2024")</f>
         <v/>
       </c>
     </row>
@@ -11578,7 +11578,7 @@
         <v>45111</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>45903</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>46185</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S 1813-2026</t>
+          <t>S 1803-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -11899,10 +11899,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -11929,10 +11929,10 @@
         <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N102" t="n">
         <v>0</v>
@@ -11947,55 +11947,55 @@
         <v>1</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S102" t="n">
         <v>1</v>
       </c>
       <c r="T102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Purpurmusseron</t>
         </is>
       </c>
       <c r="W102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1813-2026 artfynd.xlsx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1803-2026 artfynd.xlsx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="X102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1813-2026 karta.png", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1803-2026 karta.png", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="Y102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1813-2026 georefererad karta.tif", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1803-2026 georefererad karta.tif", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AA102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1813-2026 FSC-klagomål.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1803-2026 FSC-klagomål.docx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AB102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1813-2026 FSC-klagomål mail.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1803-2026 FSC-klagomål mail.docx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AC102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1813-2026 tillsynsbegäran.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1803-2026 tillsynsbegäran.docx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AD102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1813-2026 tillsynsbegäran mail.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1803-2026 tillsynsbegäran mail.docx", "S 1803-2026")</f>
         <v/>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S 1803-2026</t>
+          <t>S 1813-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -12009,10 +12009,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12030,75 +12030,75 @@
         </is>
       </c>
       <c r="I103" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>1</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>1</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="n">
+        <v>1</v>
+      </c>
+      <c r="T103" t="n">
         <v>2</v>
       </c>
-      <c r="J103" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" t="n">
-        <v>1</v>
-      </c>
-      <c r="N103" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>1</v>
-      </c>
-      <c r="R103" t="n">
-        <v>1</v>
-      </c>
-      <c r="S103" t="n">
-        <v>1</v>
-      </c>
-      <c r="T103" t="n">
-        <v>1</v>
-      </c>
       <c r="U103" t="n">
         <v>0</v>
       </c>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>Purpurmusseron</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="W103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1803-2026 artfynd.xlsx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1813-2026 artfynd.xlsx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="X103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1803-2026 karta.png", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1813-2026 karta.png", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="Y103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1803-2026 georefererad karta.tif", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1813-2026 georefererad karta.tif", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AA103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1803-2026 FSC-klagomål.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1813-2026 FSC-klagomål.docx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AB103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1803-2026 FSC-klagomål mail.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1813-2026 FSC-klagomål mail.docx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AC103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1803-2026 tillsynsbegäran.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1813-2026 tillsynsbegäran.docx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AD103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1803-2026 tillsynsbegäran mail.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1813-2026 tillsynsbegäran mail.docx", "S 1813-2026")</f>
         <v/>
       </c>
     </row>
@@ -12122,7 +12122,7 @@
         <v>46246</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44783</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>44747</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>44840</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>44783</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>44501</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>44477</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>44742</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44503</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 31699-2022</t>
+          <t>A 3878-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -12823,10 +12823,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44776</v>
+        <v>44951</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12838,13 +12838,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -12887,7 +12882,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 26160-2024</t>
+          <t>A 12937-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12897,14 +12892,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45468</v>
+        <v>44642</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12916,8 +12911,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -12956,35 +12956,11 @@
         <v>0</v>
       </c>
       <c r="V114" s="2" t="inlineStr"/>
-      <c r="X114">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26160-2024 karta.png", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="Y114">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26160-2024 georefererad karta.tif", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AA114">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26160-2024 FSC-klagomål.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AB114">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26160-2024 FSC-klagomål mail.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AC114">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26160-2024 tillsynsbegäran.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AD114">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26160-2024 tillsynsbegäran mail.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 41950-2025</t>
+          <t>A 22785-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -12998,10 +12974,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45903</v>
+        <v>45789</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13014,7 +12990,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -13057,7 +13033,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 40339-2023</t>
+          <t>A 64303-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -13067,14 +13043,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45169</v>
+        <v>45280</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13087,7 +13063,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -13130,7 +13106,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 9259-2026</t>
+          <t>A 41950-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -13144,10 +13120,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46070</v>
+        <v>45903</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13160,7 +13136,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -13203,7 +13179,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 45869-2025</t>
+          <t>A 40339-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13217,10 +13193,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45923</v>
+        <v>45169</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13233,7 +13209,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -13276,7 +13252,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 46845-2025</t>
+          <t>A 55367-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -13286,14 +13262,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45928</v>
+        <v>45621</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13306,7 +13282,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -13349,7 +13325,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 4159-2024</t>
+          <t>A 26190-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -13363,10 +13339,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45323</v>
+        <v>45805</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13379,7 +13355,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -13422,7 +13398,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 26190-2025</t>
+          <t>A 45869-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -13436,10 +13412,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45805</v>
+        <v>45923</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13452,7 +13428,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -13495,7 +13471,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 15272-2026</t>
+          <t>A 46845-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -13505,14 +13481,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46105</v>
+        <v>45928</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13524,13 +13500,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -13573,7 +13544,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 15279-2026</t>
+          <t>A 9259-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -13583,14 +13554,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46105</v>
+        <v>46070</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13602,13 +13573,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -13651,7 +13617,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 15264-2026</t>
+          <t>A 4159-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -13661,14 +13627,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46105</v>
+        <v>45323</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13680,13 +13646,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -13729,7 +13690,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 4165-2023</t>
+          <t>A 32921-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -13743,10 +13704,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44953</v>
+        <v>45125</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13759,7 +13720,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -13802,7 +13763,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 32921-2023</t>
+          <t>A 31699-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -13816,10 +13777,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45125</v>
+        <v>44776</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13831,8 +13792,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -13875,7 +13841,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 36269-2025</t>
+          <t>A 15272-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -13885,14 +13851,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45867</v>
+        <v>46105</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13910,7 +13876,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -13953,7 +13919,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 64303-2023</t>
+          <t>A 15279-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -13963,14 +13929,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45280</v>
+        <v>46105</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13982,8 +13948,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -14026,7 +13997,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 27357-2025</t>
+          <t>A 15264-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -14040,10 +14011,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45812</v>
+        <v>46105</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14061,7 +14032,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -14104,7 +14075,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 43603-2024</t>
+          <t>A 1614-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -14118,10 +14089,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45569</v>
+        <v>45670</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14134,7 +14105,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -14177,7 +14148,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 63075-2023</t>
+          <t>A 9076-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -14187,14 +14158,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45273</v>
+        <v>45713</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14206,8 +14177,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -14250,7 +14226,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 7669-2024</t>
+          <t>A 1757-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -14264,10 +14240,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45348</v>
+        <v>45671</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14280,7 +14256,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -14323,7 +14299,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 24323-2026</t>
+          <t>A 36269-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -14337,10 +14313,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46169</v>
+        <v>45867</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14358,7 +14334,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -14401,7 +14377,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 1757-2025</t>
+          <t>A 9050-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -14411,14 +14387,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45671</v>
+        <v>45713</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14430,8 +14406,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -14474,7 +14455,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 34780-2022</t>
+          <t>A 43603-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -14488,10 +14469,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44795</v>
+        <v>45569</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14503,13 +14484,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>6.7</v>
+        <v>3.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -14552,7 +14528,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 55367-2024</t>
+          <t>A 27357-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -14562,14 +14538,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45621</v>
+        <v>45812</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14581,8 +14557,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -14625,7 +14606,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 20287-2025</t>
+          <t>A 7669-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -14635,14 +14616,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45774</v>
+        <v>45348</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14655,7 +14636,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -14698,7 +14679,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 9076-2025</t>
+          <t>A 24323-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -14712,10 +14693,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45713</v>
+        <v>46169</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14733,7 +14714,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -14776,7 +14757,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 28380-2026</t>
+          <t>A 28381-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -14793,7 +14774,7 @@
         <v>46196</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14811,7 +14792,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -14854,7 +14835,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 28381-2026</t>
+          <t>A 28380-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -14871,7 +14852,7 @@
         <v>46196</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14889,7 +14870,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -14949,7 +14930,7 @@
         <v>46197</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15027,7 +15008,7 @@
         <v>45125</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15100,7 +15081,7 @@
         <v>46203</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15178,7 +15159,7 @@
         <v>46203</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15256,7 +15237,7 @@
         <v>46203</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15334,7 +15315,7 @@
         <v>46203</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15395,7 +15376,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 34951-2022</t>
+          <t>A 5175-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -15405,14 +15386,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44796</v>
+        <v>45330</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15424,13 +15405,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -15473,7 +15449,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 5175-2024</t>
+          <t>A 34951-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -15483,14 +15459,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45330</v>
+        <v>44796</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15502,8 +15478,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -15546,7 +15527,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 3878-2023</t>
+          <t>A 13383-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -15560,10 +15541,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44951</v>
+        <v>45005</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15576,7 +15557,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -15619,7 +15600,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 13383-2023</t>
+          <t>A 61438-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -15629,14 +15610,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45005</v>
+        <v>45264</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15649,7 +15630,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -15692,7 +15673,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 12937-2022</t>
+          <t>A 13041-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -15706,10 +15687,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44642</v>
+        <v>45385</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15721,13 +15702,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -15770,7 +15746,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 61438-2023</t>
+          <t>A 4165-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -15780,14 +15756,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45264</v>
+        <v>44953</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15800,7 +15776,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -15843,7 +15819,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 13041-2024</t>
+          <t>A 34780-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -15857,10 +15833,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45385</v>
+        <v>44795</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15872,8 +15848,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>0.5</v>
+        <v>6.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -15933,7 +15914,7 @@
         <v>46169</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15994,7 +15975,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 1614-2025</t>
+          <t>A 20287-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -16004,14 +15985,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45670</v>
+        <v>45774</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16024,7 +16005,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -16067,7 +16048,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 9050-2025</t>
+          <t>A 26160-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -16077,14 +16058,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45713</v>
+        <v>45468</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16096,13 +16077,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -16141,11 +16117,35 @@
         <v>0</v>
       </c>
       <c r="V156" s="2" t="inlineStr"/>
+      <c r="X156">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26160-2024 karta.png", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="Y156">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26160-2024 georefererad karta.tif", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AA156">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26160-2024 FSC-klagomål.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AB156">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26160-2024 FSC-klagomål mail.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AC156">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26160-2024 tillsynsbegäran.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AD156">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26160-2024 tillsynsbegäran mail.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
     </row>
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 22785-2025</t>
+          <t>A 63075-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -16155,14 +16155,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45789</v>
+        <v>45273</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -16235,7 +16235,7 @@
         <v>44756</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>45713</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45812</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>45812</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>45754</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>46105</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>46105</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>46169</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S 1812-2026</t>
+          <t>S 1806-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -16846,10 +16846,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -16910,7 +16910,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S 1806-2026</t>
+          <t>S 1807-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -16927,7 +16927,7 @@
         <v>46196</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -16988,7 +16988,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S 1807-2026</t>
+          <t>S 1812-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -17002,10 +17002,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>46203</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>46203</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>46203</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>46203</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>

--- a/Översikt BORGHOLM.xlsx
+++ b/Översikt BORGHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45029</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>44704</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45433</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>44903</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45903</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>46254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44809</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>44523</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>45107</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44781</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>45161</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>45146</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45918</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>45930</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45918</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>45736</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>44638</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>46220</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45175</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>45926</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>46188</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>46224</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>45027</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>44704</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45478</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>46188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>46224</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>44482</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>46169</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>46169</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45736</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>44973</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>46188</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>44953</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>45442</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>44704</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44704</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44783</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>45887</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45911</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>45796</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>46105</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>44781</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>46188</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>44837</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>46185</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>46223</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>46105</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>46188</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>46223</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>44623</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44711</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>44725</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>46070</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>45994</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45994</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>46169</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>46203</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>44840</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>46203</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>45758</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>44865</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>44649</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>46203</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>46203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44772</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44781</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>45084</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45902</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>46041</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>46059</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>46069</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>46073</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>45273</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>45820</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>45820</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>45084</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>44984</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>46185</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>46196</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>46197</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>44776</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>45433</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>46246</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>45385</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>45439</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>45111</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>45903</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>46185</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>46196</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>46197</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         <v>46246</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44783</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>44747</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>44840</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>44783</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>44501</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>44477</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>44742</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44503</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>44951</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>44642</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>45789</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>45280</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45903</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>45169</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>45621</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>45805</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45923</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>45928</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>46070</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>45323</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>45125</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44776</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>46105</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>46105</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>46105</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>45670</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>45713</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>45671</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>45867</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>45713</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45569</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>45812</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>45348</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>46169</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>46196</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>46196</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>46197</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>45125</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>46203</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>46203</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>46203</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>46203</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>45330</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>44796</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         <v>45005</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>45264</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>45385</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44953</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>44795</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>46169</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>45774</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>45468</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>45273</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44756</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>45713</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45812</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>45812</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>45754</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>46105</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>46105</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>46169</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         <v>46196</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>46196</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>46197</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>46203</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>46203</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>46203</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>46203</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>

--- a/Översikt BORGHOLM.xlsx
+++ b/Översikt BORGHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45029</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>44704</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45433</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>44903</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45903</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>46254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44809</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>44523</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>45107</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44781</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>45161</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>45146</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45918</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>45930</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45918</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>45736</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>44638</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>46220</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45175</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>45926</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>46188</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>46224</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>45027</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>44704</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45478</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>46188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>46224</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>44482</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>46169</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>46169</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45736</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>44973</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>46188</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>44953</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>45442</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>44704</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44704</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44783</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>45887</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45911</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>45796</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>46105</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>44781</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>46188</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>44837</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>46185</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>46223</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>46105</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>46188</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>46223</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>44623</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44711</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>44725</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>46070</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>45994</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45994</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>46169</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>46203</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>44840</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>46203</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>45758</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>44865</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>44649</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>46203</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>46203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44772</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44781</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>45084</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45902</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>46041</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>46059</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>46069</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>46073</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>45273</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>45820</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>45820</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>45084</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>44984</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>46185</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>46196</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>46197</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>44776</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>45433</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>46246</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>45385</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>45439</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>45111</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>45903</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>46185</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>46196</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>46197</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         <v>46246</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44783</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>44747</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>44840</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>44783</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>44501</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>44477</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>44742</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44503</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>44951</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>44642</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>45789</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>45280</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45903</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>45169</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>45621</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>45805</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45923</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>45928</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>46070</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>45323</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>45125</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44776</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>46105</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>46105</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>46105</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>45670</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>45713</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>45671</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>45867</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>45713</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45569</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>45812</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>45348</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>46169</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>46196</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>46196</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>46197</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>45125</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>46203</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>46203</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>46203</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>46203</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>45330</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>44796</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         <v>45005</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>45264</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>45385</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44953</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>44795</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>46169</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>45774</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>45468</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>45273</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44756</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>45713</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45812</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>45812</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>45754</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>46105</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>46105</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>46169</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         <v>46196</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>46196</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>46197</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>46203</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>46203</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>46203</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>46203</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>

--- a/Översikt BORGHOLM.xlsx
+++ b/Översikt BORGHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45029</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>44704</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45433</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>44903</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45903</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>46254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44809</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>44523</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>45107</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44781</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>45161</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>45146</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45918</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>45930</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45918</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>45736</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 12534-2022</t>
+          <t>A 31515-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3325,14 +3325,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44638</v>
+        <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3344,17 +3344,22 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>8.6</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3369,7 +3374,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3378,12 +3383,353 @@
         <v>8</v>
       </c>
       <c r="T24" t="n">
+        <v>10</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Blå slemspindling
+Sårläka
+Vårärt
+Anisspindling
+Skogsknipprot
+Strävlosta
+Blåsippa
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31515-2026 artfynd.xlsx", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31515-2026 karta.png", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31515-2026 georefererad karta.tif", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31515-2026 FSC-klagomål.docx", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31515-2026 FSC-klagomål mail.docx", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31515-2026 tillsynsbegäran.docx", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31515-2026 tillsynsbegäran mail.docx", "A 31515-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 31516-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>8</v>
+      </c>
+      <c r="T25" t="n">
+        <v>10</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Blå slemspindling
+Sårläka
+Vårärt
+Anisspindling
+Skogsknipprot
+Strävlosta
+Blåsippa
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31516-2026 artfynd.xlsx", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31516-2026 karta.png", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31516-2026 georefererad karta.tif", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31516-2026 FSC-klagomål.docx", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31516-2026 FSC-klagomål mail.docx", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31516-2026 tillsynsbegäran.docx", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31516-2026 tillsynsbegäran mail.docx", "A 31516-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 31399-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>8</v>
+      </c>
+      <c r="T26" t="n">
+        <v>8</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Backklöver
+Jordtistel
+Stallört
+Flugblomster
+Tvåblad
+Grönvit nattviol
+Krutbrännare
+Vanliga ängsnycklar</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31399-2026 artfynd.xlsx", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31399-2026 karta.png", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31399-2026 georefererad karta.tif", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31399-2026 FSC-klagomål.docx", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31399-2026 FSC-klagomål mail.docx", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31399-2026 tillsynsbegäran.docx", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31399-2026 tillsynsbegäran mail.docx", "A 31399-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 12534-2022</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>44638</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>5</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>8</v>
+      </c>
+      <c r="T27" t="n">
         <v>9</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U27" t="n">
         <v>9</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Backklöver
 Backtimjan
@@ -3395,224 +3741,224 @@
 Sankt pers nycklar</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 12534-2022 artfynd.xlsx", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 12534-2022 karta.png", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 12534-2022 georefererad karta.tif", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 12534-2022 FSC-klagomål.docx", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 12534-2022 FSC-klagomål mail.docx", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 12534-2022 tillsynsbegäran.docx", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 12534-2022 tillsynsbegäran mail.docx", "A 12534-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 31399-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F25" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>S 2741-2022</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>44704</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="I25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="I28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
         <v>5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="L25" t="n">
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
         <v>3</v>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>55</v>
+      </c>
+      <c r="U28" t="n">
+        <v>49</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Almlav
+Ask
+Korskovall
+Ekoxe
+Slät lönnlav
+Stor häxört
+Underviol
+Vitskivlav</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2741-2022 artfynd.xlsx", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 2741-2022 karta.png", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 2741-2022 georefererad karta.tif", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 2741-2022 FSC-klagomål.docx", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 2741-2022 FSC-klagomål mail.docx", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 2741-2022 tillsynsbegäran.docx", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 2741-2022 tillsynsbegäran mail.docx", "S 2741-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S 2057-2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J29" t="n">
         <v>3</v>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="K29" t="n">
+        <v>3</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>8</v>
       </c>
-      <c r="T25" t="n">
-        <v>8</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Backklöver
-Jordtistel
-Stallört
-Flugblomster
-Tvåblad
-Grönvit nattviol
-Krutbrännare
-Vanliga ängsnycklar</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31399-2026 artfynd.xlsx", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31399-2026 karta.png", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31399-2026 georefererad karta.tif", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31399-2026 FSC-klagomål.docx", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31399-2026 FSC-klagomål mail.docx", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31399-2026 tillsynsbegäran.docx", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31399-2026 tillsynsbegäran mail.docx", "A 31399-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 31515-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3</v>
-      </c>
-      <c r="L26" t="n">
-        <v>3</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>8</v>
-      </c>
-      <c r="T26" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Blå slemspindling
 Sårläka
@@ -3624,112 +3970,112 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31515-2026 artfynd.xlsx", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31515-2026 karta.png", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31515-2026 georefererad karta.tif", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31515-2026 FSC-klagomål.docx", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31515-2026 FSC-klagomål mail.docx", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31515-2026 tillsynsbegäran.docx", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31515-2026 tillsynsbegäran mail.docx", "A 31515-2026")</f>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2057-2026 artfynd.xlsx", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 2057-2026 karta.png", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 2057-2026 georefererad karta.tif", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 2057-2026 FSC-klagomål.docx", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 2057-2026 FSC-klagomål mail.docx", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 2057-2026 tillsynsbegäran.docx", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 2057-2026 tillsynsbegäran mail.docx", "S 2057-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 31516-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>S 2058-2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E27" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="E30" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I27" t="n">
+      <c r="I30" t="n">
         <v>0.8</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J30" t="n">
         <v>3</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K30" t="n">
         <v>3</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L30" t="n">
         <v>3</v>
       </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>3</v>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>8</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T30" t="n">
         <v>10</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Blå slemspindling
 Sårläka
@@ -3741,352 +4087,6 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31516-2026 artfynd.xlsx", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31516-2026 karta.png", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31516-2026 georefererad karta.tif", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31516-2026 FSC-klagomål.docx", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31516-2026 FSC-klagomål mail.docx", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31516-2026 tillsynsbegäran.docx", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31516-2026 tillsynsbegäran mail.docx", "A 31516-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>S 2741-2022</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>44704</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>5</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3</v>
-      </c>
-      <c r="R28" t="n">
-        <v>2</v>
-      </c>
-      <c r="S28" t="n">
-        <v>8</v>
-      </c>
-      <c r="T28" t="n">
-        <v>55</v>
-      </c>
-      <c r="U28" t="n">
-        <v>49</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Almlav
-Ask
-Korskovall
-Ekoxe
-Slät lönnlav
-Stor häxört
-Underviol
-Vitskivlav</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2741-2022 artfynd.xlsx", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 2741-2022 karta.png", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 2741-2022 georefererad karta.tif", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 2741-2022 FSC-klagomål.docx", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 2741-2022 FSC-klagomål mail.docx", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 2741-2022 tillsynsbegäran.docx", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 2741-2022 tillsynsbegäran mail.docx", "S 2741-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>S 2057-2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3</v>
-      </c>
-      <c r="L29" t="n">
-        <v>3</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>8</v>
-      </c>
-      <c r="T29" t="n">
-        <v>10</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Blå slemspindling
-Sårläka
-Vårärt
-Anisspindling
-Skogsknipprot
-Strävlosta
-Blåsippa
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2057-2026 artfynd.xlsx", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 2057-2026 karta.png", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 2057-2026 georefererad karta.tif", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 2057-2026 FSC-klagomål.docx", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 2057-2026 FSC-klagomål mail.docx", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 2057-2026 tillsynsbegäran.docx", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 2057-2026 tillsynsbegäran mail.docx", "S 2057-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>S 2058-2026</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3</v>
-      </c>
-      <c r="L30" t="n">
-        <v>3</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>10</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Blå slemspindling
-Sårläka
-Vårärt
-Anisspindling
-Skogsknipprot
-Strävlosta
-Blåsippa
-Grönvit nattviol</t>
-        </is>
-      </c>
       <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2058-2026 artfynd.xlsx", "S 2058-2026")</f>
         <v/>
@@ -4136,7 +4136,7 @@
         <v>45175</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 46794-2025</t>
+          <t>A 16171-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4240,14 +4240,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45926</v>
+        <v>45027</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4260,13 +4260,13 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>12.2</v>
       </c>
       <c r="J32" t="n">
         <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>2</v>
@@ -4293,12 +4293,122 @@
         <v>6</v>
       </c>
       <c r="T32" t="n">
+        <v>7</v>
+      </c>
+      <c r="U32" t="n">
+        <v>6</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Sårläka
+Älg
+Murgröna
+Blåsippa
+Rostticka
+Bredarun</t>
+        </is>
+      </c>
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 16171-2023 artfynd.xlsx", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 16171-2023 karta.png", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 16171-2023 georefererad karta.tif", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 16171-2023 FSC-klagomål.docx", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 16171-2023 FSC-klagomål mail.docx", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 16171-2023 tillsynsbegäran.docx", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 16171-2023 tillsynsbegäran mail.docx", "A 16171-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 46794-2025</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>45926</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>6</v>
+      </c>
+      <c r="T33" t="n">
         <v>10</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U33" t="n">
         <v>9</v>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Mindre ekbock
 Sårläka
@@ -4308,112 +4418,112 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 46794-2025 artfynd.xlsx", "A 46794-2025")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 46794-2025 karta.png", "A 46794-2025")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 46794-2025 georefererad karta.tif", "A 46794-2025")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 46794-2025 FSC-klagomål.docx", "A 46794-2025")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 46794-2025 FSC-klagomål mail.docx", "A 46794-2025")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 46794-2025 tillsynsbegäran.docx", "A 46794-2025")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 46794-2025 tillsynsbegäran mail.docx", "A 46794-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A 27298-2026</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D33" s="1" t="n">
+      <c r="D34" s="1" t="n">
         <v>46188</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="E34" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="I34" t="n">
         <v>3.3</v>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="n">
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
         <v>5</v>
       </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>5</v>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>6</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T34" t="n">
         <v>6</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Grenplattnos
 Jungfrulin
@@ -4423,112 +4533,112 @@
 Murgröna</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27298-2026 artfynd.xlsx", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27298-2026 karta.png", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27298-2026 georefererad karta.tif", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27298-2026 FSC-klagomål.docx", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27298-2026 FSC-klagomål mail.docx", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27298-2026 tillsynsbegäran.docx", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27298-2026 tillsynsbegäran mail.docx", "A 27298-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>A 31558-2026</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D34" s="1" t="n">
+      <c r="D35" s="1" t="n">
         <v>46224</v>
       </c>
-      <c r="E34" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="E35" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" t="n">
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K35" t="n">
         <v>2</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L35" t="n">
         <v>3</v>
       </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
         <v>3</v>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>6</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T35" t="n">
         <v>7</v>
       </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Blå slemspindling
 Sårläka
@@ -4538,142 +4648,32 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W34">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31558-2026 artfynd.xlsx", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="X34">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31558-2026 karta.png", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="Y34">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31558-2026 georefererad karta.tif", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="AA34">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31558-2026 FSC-klagomål.docx", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="AB34">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31558-2026 FSC-klagomål mail.docx", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="AC34">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31558-2026 tillsynsbegäran.docx", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="AD34">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31558-2026 tillsynsbegäran mail.docx", "A 31558-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 16171-2023</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>45027</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>2</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>6</v>
-      </c>
-      <c r="T35" t="n">
-        <v>7</v>
-      </c>
-      <c r="U35" t="n">
-        <v>6</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka
-Älg
-Murgröna
-Blåsippa
-Rostticka
-Bredarun</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 16171-2023 artfynd.xlsx", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 16171-2023 karta.png", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 16171-2023 georefererad karta.tif", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 16171-2023 FSC-klagomål.docx", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 16171-2023 FSC-klagomål mail.docx", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 16171-2023 tillsynsbegäran.docx", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 16171-2023 tillsynsbegäran mail.docx", "A 16171-2023")</f>
         <v/>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
         <v>44704</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45478</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>46188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>46224</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>44482</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>46169</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>46169</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45736</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7960-2023</t>
+          <t>A 21797-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44973</v>
+        <v>45442</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5609,16 +5609,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5627,27 +5627,360 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
       </c>
       <c r="T44" t="n">
+        <v>11</v>
+      </c>
+      <c r="U44" t="n">
+        <v>6</v>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Sydlig kantmusseron
+Murgröna
+Skogsknipprot
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21797-2024 artfynd.xlsx", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="X44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21797-2024 karta.png", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="Y44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21797-2024 georefererad karta.tif", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="AA44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21797-2024 FSC-klagomål.docx", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="AB44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21797-2024 FSC-klagomål mail.docx", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="AC44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21797-2024 tillsynsbegäran.docx", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="AD44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21797-2024 tillsynsbegäran mail.docx", "A 21797-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A 27290-2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>2</v>
+      </c>
+      <c r="S45" t="n">
         <v>4</v>
       </c>
-      <c r="U44" t="n">
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Gotlandsmåra
+Skogsknipprot
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27290-2026 artfynd.xlsx", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="X45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27290-2026 karta.png", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="Y45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27290-2026 georefererad karta.tif", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="AA45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27290-2026 FSC-klagomål.docx", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="AB45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27290-2026 FSC-klagomål mail.docx", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="AC45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27290-2026 tillsynsbegäran.docx", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="AD45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27290-2026 tillsynsbegäran mail.docx", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="AE45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 27290-2026 prioriterade fågelarter.docx", "A 27290-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A 4164-2023</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>44953</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>2</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>4</v>
+      </c>
+      <c r="T46" t="n">
+        <v>5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Crepis tectorum subsp. tectorum
+Kösa
+Murgröna
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 4164-2023 artfynd.xlsx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="X46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 4164-2023 karta.png", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="Y46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 4164-2023 georefererad karta.tif", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AA46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 4164-2023 FSC-klagomål.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AB46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 4164-2023 FSC-klagomål mail.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AC46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 4164-2023 tillsynsbegäran.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AD46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 4164-2023 tillsynsbegäran mail.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>A 7960-2023</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>44973</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
         <v>3</v>
       </c>
-      <c r="V44" s="2" t="inlineStr">
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>4</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
         <is>
           <t>Vresalm
 Pilfotsspindling
@@ -5655,365 +5988,32 @@
 Strävlosta</t>
         </is>
       </c>
-      <c r="W44">
+      <c r="W47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 7960-2023 artfynd.xlsx", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="X44">
+      <c r="X47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 7960-2023 karta.png", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="Y44">
+      <c r="Y47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 7960-2023 georefererad karta.tif", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="AA44">
+      <c r="AA47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 7960-2023 FSC-klagomål.docx", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="AB44">
+      <c r="AB47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 7960-2023 FSC-klagomål mail.docx", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="AC44">
+      <c r="AC47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 7960-2023 tillsynsbegäran.docx", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="AD44">
+      <c r="AD47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 7960-2023 tillsynsbegäran mail.docx", "A 7960-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>A 27290-2026</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E45" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>1</v>
-      </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>2</v>
-      </c>
-      <c r="R45" t="n">
-        <v>2</v>
-      </c>
-      <c r="S45" t="n">
-        <v>4</v>
-      </c>
-      <c r="T45" t="n">
-        <v>4</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Gotlandsmåra
-Skogsknipprot
-Havsörn</t>
-        </is>
-      </c>
-      <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27290-2026 artfynd.xlsx", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27290-2026 karta.png", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27290-2026 georefererad karta.tif", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27290-2026 FSC-klagomål.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27290-2026 FSC-klagomål mail.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27290-2026 tillsynsbegäran.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27290-2026 tillsynsbegäran mail.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="AE45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 27290-2026 prioriterade fågelarter.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>A 4164-2023</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>44953</v>
-      </c>
-      <c r="E46" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" t="n">
-        <v>2</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>2</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>4</v>
-      </c>
-      <c r="T46" t="n">
-        <v>5</v>
-      </c>
-      <c r="U46" t="n">
-        <v>4</v>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>Crepis tectorum subsp. tectorum
-Kösa
-Murgröna
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 4164-2023 artfynd.xlsx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 4164-2023 karta.png", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 4164-2023 georefererad karta.tif", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 4164-2023 FSC-klagomål.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 4164-2023 FSC-klagomål mail.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 4164-2023 tillsynsbegäran.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 4164-2023 tillsynsbegäran mail.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>A 21797-2024</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>45442</v>
-      </c>
-      <c r="E47" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2</v>
-      </c>
-      <c r="L47" t="n">
-        <v>1</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>4</v>
-      </c>
-      <c r="T47" t="n">
-        <v>11</v>
-      </c>
-      <c r="U47" t="n">
-        <v>6</v>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>Sydlig kantmusseron
-Murgröna
-Skogsknipprot
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21797-2024 artfynd.xlsx", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21797-2024 karta.png", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21797-2024 georefererad karta.tif", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21797-2024 FSC-klagomål.docx", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21797-2024 FSC-klagomål mail.docx", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21797-2024 tillsynsbegäran.docx", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21797-2024 tillsynsbegäran mail.docx", "A 21797-2024")</f>
         <v/>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
         <v>44704</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44704</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44783</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>45887</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45911</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 24048-2025</t>
+          <t>A 32174-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6572,14 +6572,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45796</v>
+        <v>44781</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6591,17 +6591,22 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J53" t="n">
         <v>2</v>
       </c>
-      <c r="J53" t="n">
-        <v>1</v>
-      </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -6616,7 +6621,7 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -6625,1033 +6630,1028 @@
         <v>3</v>
       </c>
       <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>Backklöver
+Tvåblad
+Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="W53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 32174-2022 artfynd.xlsx", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="X53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 32174-2022 karta.png", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="Y53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 32174-2022 georefererad karta.tif", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="AA53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 32174-2022 FSC-klagomål.docx", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="AB53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 32174-2022 FSC-klagomål mail.docx", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="AC53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 32174-2022 tillsynsbegäran.docx", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="AD53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 32174-2022 tillsynsbegäran mail.docx", "A 32174-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>A 15285-2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J54" t="n">
+        <v>3</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>3</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Havsörn
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 15285-2026 artfynd.xlsx", "A 15285-2026")</f>
+        <v/>
+      </c>
+      <c r="X54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 15285-2026 karta.png", "A 15285-2026")</f>
+        <v/>
+      </c>
+      <c r="Y54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 15285-2026 georefererad karta.tif", "A 15285-2026")</f>
+        <v/>
+      </c>
+      <c r="AA54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 15285-2026 FSC-klagomål.docx", "A 15285-2026")</f>
+        <v/>
+      </c>
+      <c r="AB54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 15285-2026 FSC-klagomål mail.docx", "A 15285-2026")</f>
+        <v/>
+      </c>
+      <c r="AC54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 15285-2026 tillsynsbegäran.docx", "A 15285-2026")</f>
+        <v/>
+      </c>
+      <c r="AD54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 15285-2026 tillsynsbegäran mail.docx", "A 15285-2026")</f>
+        <v/>
+      </c>
+      <c r="AE54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 15285-2026 prioriterade fågelarter.docx", "A 15285-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>A 26849-2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>3</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>Myskmadra
+Purpurknipprot
+Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="W55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26849-2026 artfynd.xlsx", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="X55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26849-2026 karta.png", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="Y55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26849-2026 georefererad karta.tif", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="AA55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26849-2026 FSC-klagomål.docx", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="AB55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26849-2026 FSC-klagomål mail.docx", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="AC55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26849-2026 tillsynsbegäran.docx", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="AD55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26849-2026 tillsynsbegäran mail.docx", "A 26849-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>A 27283-2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>2</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
+      <c r="S56" t="n">
+        <v>3</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Mindre poppelglasvinge
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27283-2026 artfynd.xlsx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="X56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27283-2026 karta.png", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="Y56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27283-2026 georefererad karta.tif", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AA56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27283-2026 FSC-klagomål.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AB56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27283-2026 FSC-klagomål mail.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AC56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27283-2026 tillsynsbegäran.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AD56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27283-2026 tillsynsbegäran mail.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>A 43756-2022</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>44837</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3</v>
+      </c>
+      <c r="T57" t="n">
         <v>5</v>
       </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" s="2" t="inlineStr">
+      <c r="U57" t="n">
+        <v>5</v>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>Murgröna
+Blåsippa
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 43756-2022 artfynd.xlsx", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="X57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 43756-2022 karta.png", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="Y57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 43756-2022 georefererad karta.tif", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="AA57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 43756-2022 FSC-klagomål.docx", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="AB57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 43756-2022 FSC-klagomål mail.docx", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="AC57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 43756-2022 tillsynsbegäran.docx", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="AD57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 43756-2022 tillsynsbegäran mail.docx", "A 43756-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>A 31520-2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Grönsiska
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31520-2026 artfynd.xlsx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="X58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31520-2026 karta.png", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31520-2026 georefererad karta.tif", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31520-2026 FSC-klagomål.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31520-2026 FSC-klagomål mail.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31520-2026 tillsynsbegäran.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31520-2026 tillsynsbegäran mail.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AE58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 31520-2026 prioriterade fågelarter.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>A 24048-2025</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>45796</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>2</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>2</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>2</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>3</v>
+      </c>
+      <c r="T59" t="n">
+        <v>5</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
         <is>
           <t>Loppstarr
 Ängsstarr
 Kärrknipprot</t>
         </is>
       </c>
-      <c r="W53">
+      <c r="W59">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24048-2025 artfynd.xlsx", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="X53">
+      <c r="X59">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24048-2025 karta.png", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="Y53">
+      <c r="Y59">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24048-2025 georefererad karta.tif", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="AA53">
+      <c r="AA59">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24048-2025 FSC-klagomål.docx", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="AB53">
+      <c r="AB59">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24048-2025 FSC-klagomål mail.docx", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="AC53">
+      <c r="AC59">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24048-2025 tillsynsbegäran.docx", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="AD53">
+      <c r="AD59">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24048-2025 tillsynsbegäran mail.docx", "A 24048-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>A 15285-2026</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="n">
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>S 846-2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="n">
         <v>46105</v>
       </c>
-      <c r="E54" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F54" t="inlineStr">
+      <c r="E60" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I54" t="n">
+      <c r="I60" t="n">
         <v>1.7</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J60" t="n">
         <v>3</v>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>1</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>1</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
         <v>3</v>
       </c>
-      <c r="T54" t="n">
+      <c r="T60" t="n">
         <v>3</v>
       </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" s="2" t="inlineStr">
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Havsörn
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 15285-2026 artfynd.xlsx", "A 15285-2026")</f>
-        <v/>
-      </c>
-      <c r="X54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 15285-2026 karta.png", "A 15285-2026")</f>
-        <v/>
-      </c>
-      <c r="Y54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 15285-2026 georefererad karta.tif", "A 15285-2026")</f>
-        <v/>
-      </c>
-      <c r="AA54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 15285-2026 FSC-klagomål.docx", "A 15285-2026")</f>
-        <v/>
-      </c>
-      <c r="AB54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 15285-2026 FSC-klagomål mail.docx", "A 15285-2026")</f>
-        <v/>
-      </c>
-      <c r="AC54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 15285-2026 tillsynsbegäran.docx", "A 15285-2026")</f>
-        <v/>
-      </c>
-      <c r="AD54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 15285-2026 tillsynsbegäran mail.docx", "A 15285-2026")</f>
-        <v/>
-      </c>
-      <c r="AE54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 15285-2026 prioriterade fågelarter.docx", "A 15285-2026")</f>
+      <c r="W60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 846-2026 artfynd.xlsx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="X60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 846-2026 karta.png", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="Y60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 846-2026 georefererad karta.tif", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AA60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 846-2026 FSC-klagomål.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AB60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 846-2026 FSC-klagomål mail.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AC60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 846-2026 tillsynsbegäran.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AD60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 846-2026 tillsynsbegäran mail.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AE60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/S 846-2026 prioriterade fågelarter.docx", "S 846-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>A 32174-2022</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D55" s="1" t="n">
-        <v>44781</v>
-      </c>
-      <c r="E55" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F55" t="inlineStr">
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>S 1726-2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E61" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I55" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J55" t="n">
+      <c r="I61" t="n">
         <v>2</v>
       </c>
-      <c r="K55" t="n">
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
         <v>2</v>
       </c>
-      <c r="L55" t="n">
-        <v>1</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>1</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
+      <c r="R61" t="n">
+        <v>1</v>
+      </c>
+      <c r="S61" t="n">
         <v>3</v>
       </c>
-      <c r="T55" t="n">
+      <c r="T61" t="n">
         <v>3</v>
       </c>
-      <c r="U55" t="n">
-        <v>3</v>
-      </c>
-      <c r="V55" s="2" t="inlineStr">
-        <is>
-          <t>Backklöver
-Tvåblad
-Vit skogslilja</t>
-        </is>
-      </c>
-      <c r="W55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 32174-2022 artfynd.xlsx", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="X55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 32174-2022 karta.png", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="Y55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 32174-2022 georefererad karta.tif", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="AA55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 32174-2022 FSC-klagomål.docx", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="AB55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 32174-2022 FSC-klagomål mail.docx", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="AC55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 32174-2022 tillsynsbegäran.docx", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="AD55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 32174-2022 tillsynsbegäran mail.docx", "A 32174-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>A 27283-2026</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E56" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" t="n">
-        <v>1</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>2</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
-      <c r="S56" t="n">
-        <v>3</v>
-      </c>
-      <c r="T56" t="n">
-        <v>3</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" s="2" t="inlineStr">
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
         <is>
           <t>Ask
 Mindre poppelglasvinge
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27283-2026 artfynd.xlsx", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="X56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27283-2026 karta.png", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="Y56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27283-2026 georefererad karta.tif", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="AA56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27283-2026 FSC-klagomål.docx", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="AB56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27283-2026 FSC-klagomål mail.docx", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="AC56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27283-2026 tillsynsbegäran.docx", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="AD56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27283-2026 tillsynsbegäran mail.docx", "A 27283-2026")</f>
+      <c r="W61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1726-2026 artfynd.xlsx", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="X61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1726-2026 karta.png", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="Y61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1726-2026 georefererad karta.tif", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="AA61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1726-2026 FSC-klagomål.docx", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="AB61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1726-2026 FSC-klagomål mail.docx", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="AC61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1726-2026 tillsynsbegäran.docx", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="AD61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1726-2026 tillsynsbegäran mail.docx", "S 1726-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>A 43756-2022</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="n">
-        <v>44837</v>
-      </c>
-      <c r="E57" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F57" t="inlineStr">
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>S 2059-2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E62" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="I57" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J57" t="n">
-        <v>2</v>
-      </c>
-      <c r="K57" t="n">
-        <v>1</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J62" t="n">
         <v>3</v>
       </c>
-      <c r="T57" t="n">
-        <v>5</v>
-      </c>
-      <c r="U57" t="n">
-        <v>5</v>
-      </c>
-      <c r="V57" s="2" t="inlineStr">
-        <is>
-          <t>Murgröna
-Blåsippa
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 43756-2022 artfynd.xlsx", "A 43756-2022")</f>
-        <v/>
-      </c>
-      <c r="X57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 43756-2022 karta.png", "A 43756-2022")</f>
-        <v/>
-      </c>
-      <c r="Y57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 43756-2022 georefererad karta.tif", "A 43756-2022")</f>
-        <v/>
-      </c>
-      <c r="AA57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 43756-2022 FSC-klagomål.docx", "A 43756-2022")</f>
-        <v/>
-      </c>
-      <c r="AB57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 43756-2022 FSC-klagomål mail.docx", "A 43756-2022")</f>
-        <v/>
-      </c>
-      <c r="AC57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 43756-2022 tillsynsbegäran.docx", "A 43756-2022")</f>
-        <v/>
-      </c>
-      <c r="AD57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 43756-2022 tillsynsbegäran mail.docx", "A 43756-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>A 26849-2026</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="n">
-        <v>46185</v>
-      </c>
-      <c r="E58" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I58" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2</v>
-      </c>
-      <c r="K58" t="n">
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
         <v>3</v>
       </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>3</v>
-      </c>
-      <c r="T58" t="n">
-        <v>3</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" s="2" t="inlineStr">
-        <is>
-          <t>Myskmadra
-Purpurknipprot
-Vit skogslilja</t>
-        </is>
-      </c>
-      <c r="W58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26849-2026 artfynd.xlsx", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="X58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26849-2026 karta.png", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="Y58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26849-2026 georefererad karta.tif", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="AA58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26849-2026 FSC-klagomål.docx", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="AB58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26849-2026 FSC-klagomål mail.docx", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="AC58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26849-2026 tillsynsbegäran.docx", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="AD58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26849-2026 tillsynsbegäran mail.docx", "A 26849-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>A 31520-2026</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E59" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J59" t="n">
-        <v>3</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>1</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>3</v>
-      </c>
-      <c r="T59" t="n">
+      <c r="T62" t="n">
         <v>4</v>
       </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" s="2" t="inlineStr">
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Grönsiska
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31520-2026 artfynd.xlsx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="X59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31520-2026 karta.png", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="Y59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31520-2026 georefererad karta.tif", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AA59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31520-2026 FSC-klagomål.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AB59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31520-2026 FSC-klagomål mail.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AC59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31520-2026 tillsynsbegäran.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AD59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31520-2026 tillsynsbegäran mail.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AE59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 31520-2026 prioriterade fågelarter.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>S 846-2026</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E60" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J60" t="n">
-        <v>3</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>1</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="n">
-        <v>3</v>
-      </c>
-      <c r="T60" t="n">
-        <v>3</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Havsörn
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 846-2026 artfynd.xlsx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="X60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 846-2026 karta.png", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="Y60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 846-2026 georefererad karta.tif", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AA60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 846-2026 FSC-klagomål.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AB60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 846-2026 FSC-klagomål mail.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AC60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 846-2026 tillsynsbegäran.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AD60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 846-2026 tillsynsbegäran mail.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AE60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/S 846-2026 prioriterade fågelarter.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>S 1726-2026</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E61" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I61" t="n">
-        <v>2</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1</v>
-      </c>
-      <c r="K61" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" t="n">
-        <v>1</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>1</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>2</v>
-      </c>
-      <c r="R61" t="n">
-        <v>1</v>
-      </c>
-      <c r="S61" t="n">
-        <v>3</v>
-      </c>
-      <c r="T61" t="n">
-        <v>3</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Mindre poppelglasvinge
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1726-2026 artfynd.xlsx", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="X61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1726-2026 karta.png", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="Y61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1726-2026 georefererad karta.tif", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="AA61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1726-2026 FSC-klagomål.docx", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="AB61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1726-2026 FSC-klagomål mail.docx", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="AC61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1726-2026 tillsynsbegäran.docx", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="AD61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1726-2026 tillsynsbegäran mail.docx", "S 1726-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>S 2059-2026</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E62" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I62" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J62" t="n">
-        <v>3</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>1</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>1</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>3</v>
-      </c>
-      <c r="T62" t="n">
-        <v>4</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Grönsiska
-Kungsfågel</t>
-        </is>
-      </c>
       <c r="W62">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2059-2026 artfynd.xlsx", "S 2059-2026")</f>
         <v/>
@@ -7705,7 +7705,7 @@
         <v>44623</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 21908-2022</t>
+          <t>A 9253-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44711</v>
+        <v>46070</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7824,13 +7824,13 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -7860,47 +7860,47 @@
         <v>2</v>
       </c>
       <c r="U64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra
-Skogsknipprot</t>
+          <t>Murgröna
+Gullviva</t>
         </is>
       </c>
       <c r="W64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21908-2022 artfynd.xlsx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9253-2026 artfynd.xlsx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="X64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21908-2022 karta.png", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9253-2026 karta.png", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="Y64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21908-2022 georefererad karta.tif", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9253-2026 georefererad karta.tif", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AA64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21908-2022 FSC-klagomål.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9253-2026 FSC-klagomål.docx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AB64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21908-2022 FSC-klagomål mail.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9253-2026 FSC-klagomål mail.docx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AC64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21908-2022 tillsynsbegäran.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9253-2026 tillsynsbegäran.docx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AD64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21908-2022 tillsynsbegäran mail.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9253-2026 tillsynsbegäran mail.docx", "A 9253-2026")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 24166-2022</t>
+          <t>A 44678-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7910,14 +7910,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44725</v>
+        <v>44840</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7930,22 +7930,22 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>10.7</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -7954,7 +7954,7 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R65" t="n">
         <v>1</v>
@@ -7970,43 +7970,43 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>Plattsäv
-Jungfrulin</t>
+          <t>Ask
+Skogsknipprot</t>
         </is>
       </c>
       <c r="W65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24166-2022 artfynd.xlsx", "A 24166-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 44678-2022 artfynd.xlsx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="X65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24166-2022 karta.png", "A 24166-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 44678-2022 karta.png", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="Y65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24166-2022 georefererad karta.tif", "A 24166-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 44678-2022 georefererad karta.tif", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AA65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24166-2022 FSC-klagomål.docx", "A 24166-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 44678-2022 FSC-klagomål.docx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AB65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24166-2022 FSC-klagomål mail.docx", "A 24166-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 44678-2022 FSC-klagomål mail.docx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AC65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24166-2022 tillsynsbegäran.docx", "A 24166-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 44678-2022 tillsynsbegäran.docx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AD65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24166-2022 tillsynsbegäran mail.docx", "A 24166-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 44678-2022 tillsynsbegäran mail.docx", "A 44678-2022")</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 9253-2026</t>
+          <t>A 60141-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -8020,10 +8020,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46070</v>
+        <v>45994</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>1</v>
@@ -8069,50 +8069,50 @@
         <v>2</v>
       </c>
       <c r="T66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>Murgröna
-Gullviva</t>
+          <t>Strävlosta
+Långbensgroda</t>
         </is>
       </c>
       <c r="W66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9253-2026 artfynd.xlsx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 60141-2025 artfynd.xlsx", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="X66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9253-2026 karta.png", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 60141-2025 karta.png", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="Y66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9253-2026 georefererad karta.tif", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 60141-2025 georefererad karta.tif", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="AA66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9253-2026 FSC-klagomål.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 60141-2025 FSC-klagomål.docx", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="AB66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9253-2026 FSC-klagomål mail.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 60141-2025 FSC-klagomål mail.docx", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="AC66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9253-2026 tillsynsbegäran.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 60141-2025 tillsynsbegäran.docx", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="AD66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9253-2026 tillsynsbegäran mail.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 60141-2025 tillsynsbegäran mail.docx", "A 60141-2025")</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60141-2025</t>
+          <t>A 60140-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8129,7 +8129,7 @@
         <v>45994</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8142,13 +8142,13 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -8175,50 +8175,50 @@
         <v>2</v>
       </c>
       <c r="T67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>Strävlosta
-Långbensgroda</t>
+          <t>Skogsknipprot
+Strävlosta</t>
         </is>
       </c>
       <c r="W67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 60141-2025 artfynd.xlsx", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 60140-2025 artfynd.xlsx", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="X67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 60141-2025 karta.png", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 60140-2025 karta.png", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="Y67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 60141-2025 georefererad karta.tif", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 60140-2025 georefererad karta.tif", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="AA67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 60141-2025 FSC-klagomål.docx", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 60140-2025 FSC-klagomål.docx", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="AB67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 60141-2025 FSC-klagomål mail.docx", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 60140-2025 FSC-klagomål mail.docx", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="AC67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 60141-2025 tillsynsbegäran.docx", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 60140-2025 tillsynsbegäran.docx", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="AD67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 60141-2025 tillsynsbegäran mail.docx", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 60140-2025 tillsynsbegäran mail.docx", "A 60140-2025")</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60140-2025</t>
+          <t>A 17699-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -8232,10 +8232,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45994</v>
+        <v>45758</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8248,17 +8248,17 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
         <v>2</v>
       </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
       <c r="M68" t="n">
         <v>0</v>
       </c>
@@ -8272,7 +8272,7 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -8281,43 +8281,43 @@
         <v>2</v>
       </c>
       <c r="T68" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot
-Strävlosta</t>
+          <t>Backtimjan
+Klibbveronika</t>
         </is>
       </c>
       <c r="W68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 60140-2025 artfynd.xlsx", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 17699-2025 artfynd.xlsx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="X68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 60140-2025 karta.png", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 17699-2025 karta.png", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="Y68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 60140-2025 georefererad karta.tif", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 17699-2025 georefererad karta.tif", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AA68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 60140-2025 FSC-klagomål.docx", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 17699-2025 FSC-klagomål.docx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AB68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 60140-2025 FSC-klagomål mail.docx", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 17699-2025 FSC-klagomål mail.docx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AC68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 60140-2025 tillsynsbegäran.docx", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 17699-2025 tillsynsbegäran.docx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AD68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 60140-2025 tillsynsbegäran mail.docx", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 17699-2025 tillsynsbegäran mail.docx", "A 17699-2025")</f>
         <v/>
       </c>
     </row>
@@ -8341,7 +8341,7 @@
         <v>46169</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 29411-2026</t>
+          <t>A 21908-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -8445,14 +8445,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46203</v>
+        <v>44711</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8464,25 +8464,20 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J70" t="n">
         <v>1</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
         <v>0</v>
@@ -8494,10 +8489,10 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>2</v>
@@ -8506,47 +8501,47 @@
         <v>2</v>
       </c>
       <c r="U70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare
-Ekoxe</t>
+          <t>Myskmadra
+Skogsknipprot</t>
         </is>
       </c>
       <c r="W70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 29411-2026 artfynd.xlsx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21908-2022 artfynd.xlsx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="X70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 29411-2026 karta.png", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21908-2022 karta.png", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="Y70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 29411-2026 georefererad karta.tif", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21908-2022 georefererad karta.tif", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AA70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 29411-2026 FSC-klagomål.docx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21908-2022 FSC-klagomål.docx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AB70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 29411-2026 FSC-klagomål mail.docx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21908-2022 FSC-klagomål mail.docx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AC70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 29411-2026 tillsynsbegäran.docx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21908-2022 tillsynsbegäran.docx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AD70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 29411-2026 tillsynsbegäran mail.docx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21908-2022 tillsynsbegäran mail.docx", "A 21908-2022")</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 44678-2022</t>
+          <t>A 29411-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8556,14 +8551,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44840</v>
+        <v>46203</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8575,8 +8570,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>1</v>
@@ -8588,10 +8588,10 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8616,36 +8616,36 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>Ask
-Skogsknipprot</t>
+          <t>Bredbrämad bastardsvärmare
+Ekoxe</t>
         </is>
       </c>
       <c r="W71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 44678-2022 artfynd.xlsx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 29411-2026 artfynd.xlsx", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="X71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 44678-2022 karta.png", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 29411-2026 karta.png", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="Y71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 44678-2022 georefererad karta.tif", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 29411-2026 georefererad karta.tif", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="AA71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 44678-2022 FSC-klagomål.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 29411-2026 FSC-klagomål.docx", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="AB71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 44678-2022 FSC-klagomål mail.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 29411-2026 FSC-klagomål mail.docx", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="AC71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 44678-2022 tillsynsbegäran.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 29411-2026 tillsynsbegäran.docx", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="AD71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 44678-2022 tillsynsbegäran mail.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 29411-2026 tillsynsbegäran mail.docx", "A 29411-2026")</f>
         <v/>
       </c>
     </row>
@@ -8669,7 +8669,7 @@
         <v>46203</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 17699-2025</t>
+          <t>A 24166-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8773,14 +8773,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45758</v>
+        <v>44725</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>10.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8802,10 +8802,10 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
@@ -8820,7 +8820,7 @@
         <v>2</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S73" t="n">
         <v>2</v>
@@ -8829,47 +8829,47 @@
         <v>2</v>
       </c>
       <c r="U73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan
-Klibbveronika</t>
+          <t>Plattsäv
+Jungfrulin</t>
         </is>
       </c>
       <c r="W73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 17699-2025 artfynd.xlsx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24166-2022 artfynd.xlsx", "A 24166-2022")</f>
         <v/>
       </c>
       <c r="X73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 17699-2025 karta.png", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24166-2022 karta.png", "A 24166-2022")</f>
         <v/>
       </c>
       <c r="Y73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 17699-2025 georefererad karta.tif", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24166-2022 georefererad karta.tif", "A 24166-2022")</f>
         <v/>
       </c>
       <c r="AA73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 17699-2025 FSC-klagomål.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24166-2022 FSC-klagomål.docx", "A 24166-2022")</f>
         <v/>
       </c>
       <c r="AB73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 17699-2025 FSC-klagomål mail.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24166-2022 FSC-klagomål mail.docx", "A 24166-2022")</f>
         <v/>
       </c>
       <c r="AC73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 17699-2025 tillsynsbegäran.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24166-2022 tillsynsbegäran.docx", "A 24166-2022")</f>
         <v/>
       </c>
       <c r="AD73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 17699-2025 tillsynsbegäran mail.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24166-2022 tillsynsbegäran mail.docx", "A 24166-2022")</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S 6144-2022</t>
+          <t>S 1650-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8879,14 +8879,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44865</v>
+        <v>44649</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8899,16 +8899,16 @@
         </is>
       </c>
       <c r="I74" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
         <v>2</v>
       </c>
-      <c r="J74" t="n">
-        <v>1</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
-      </c>
       <c r="L74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -8923,7 +8923,7 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
@@ -8932,50 +8932,50 @@
         <v>2</v>
       </c>
       <c r="T74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>Oxtungssvamp
-Fläcknycklar</t>
+          <t>Guldlockmossa
+Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="W74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 6144-2022 artfynd.xlsx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1650-2022 artfynd.xlsx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="X74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 6144-2022 karta.png", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1650-2022 karta.png", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="Y74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 6144-2022 georefererad karta.tif", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1650-2022 georefererad karta.tif", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AA74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 6144-2022 FSC-klagomål.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1650-2022 FSC-klagomål.docx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AB74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 6144-2022 FSC-klagomål mail.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1650-2022 FSC-klagomål mail.docx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AC74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 6144-2022 tillsynsbegäran.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1650-2022 tillsynsbegäran.docx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AD74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 6144-2022 tillsynsbegäran mail.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1650-2022 tillsynsbegäran mail.docx", "S 1650-2022")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S 1650-2022</t>
+          <t>S 6144-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8985,14 +8985,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44649</v>
+        <v>44865</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9005,16 +9005,16 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -9029,7 +9029,7 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -9038,43 +9038,43 @@
         <v>2</v>
       </c>
       <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
         <v>2</v>
       </c>
-      <c r="U75" t="n">
-        <v>0</v>
-      </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa
-Gulpudrad spiklav</t>
+          <t>Oxtungssvamp
+Fläcknycklar</t>
         </is>
       </c>
       <c r="W75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1650-2022 artfynd.xlsx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 6144-2022 artfynd.xlsx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="X75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1650-2022 karta.png", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 6144-2022 karta.png", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="Y75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1650-2022 georefererad karta.tif", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 6144-2022 georefererad karta.tif", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AA75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1650-2022 FSC-klagomål.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 6144-2022 FSC-klagomål.docx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AB75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1650-2022 FSC-klagomål mail.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 6144-2022 FSC-klagomål mail.docx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AC75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1650-2022 tillsynsbegäran.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 6144-2022 tillsynsbegäran.docx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AD75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1650-2022 tillsynsbegäran mail.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 6144-2022 tillsynsbegäran mail.docx", "S 6144-2022")</f>
         <v/>
       </c>
     </row>
@@ -9098,7 +9098,7 @@
         <v>46203</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>46203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44772</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44781</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 24701-2023</t>
+          <t>A 20878-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9537,10 +9537,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45084</v>
+        <v>45439</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9553,10 +9553,10 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -9568,7 +9568,7 @@
         <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9577,58 +9577,58 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
       </c>
       <c r="T80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24701-2023 artfynd.xlsx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 20878-2024 artfynd.xlsx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="X80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24701-2023 karta.png", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 20878-2024 karta.png", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="Y80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24701-2023 georefererad karta.tif", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 20878-2024 georefererad karta.tif", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AA80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24701-2023 FSC-klagomål.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 20878-2024 FSC-klagomål.docx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AB80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24701-2023 FSC-klagomål mail.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 20878-2024 FSC-klagomål mail.docx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AC80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24701-2023 tillsynsbegäran.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 20878-2024 tillsynsbegäran.docx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AD80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24701-2023 tillsynsbegäran mail.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 20878-2024 tillsynsbegäran mail.docx", "A 20878-2024")</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 41831-2025</t>
+          <t>A 9745-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45902</v>
+        <v>44984</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>1</v>
@@ -9691,10 +9691,10 @@
         <v>1</v>
       </c>
       <c r="T81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
@@ -9702,31 +9702,31 @@
         </is>
       </c>
       <c r="W81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 41831-2025 artfynd.xlsx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9745-2023 artfynd.xlsx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="X81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 41831-2025 karta.png", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9745-2023 karta.png", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="Y81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 41831-2025 georefererad karta.tif", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9745-2023 georefererad karta.tif", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AA81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 41831-2025 FSC-klagomål.docx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9745-2023 FSC-klagomål.docx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AB81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 41831-2025 FSC-klagomål mail.docx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9745-2023 FSC-klagomål mail.docx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AC81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 41831-2025 tillsynsbegäran.docx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9745-2023 tillsynsbegäran.docx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AD81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 41831-2025 tillsynsbegäran mail.docx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9745-2023 tillsynsbegäran mail.docx", "A 9745-2023")</f>
         <v/>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
         <v>46041</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 7481-2026</t>
+          <t>A 28782-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9848,14 +9848,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46059</v>
+        <v>45820</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9867,8 +9867,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>1</v>
@@ -9901,49 +9906,53 @@
         <v>1</v>
       </c>
       <c r="T83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 7481-2026 artfynd.xlsx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28782-2025 artfynd.xlsx", "A 28782-2025")</f>
         <v/>
       </c>
       <c r="X83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 7481-2026 karta.png", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28782-2025 karta.png", "A 28782-2025")</f>
         <v/>
       </c>
       <c r="Y83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 7481-2026 georefererad karta.tif", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28782-2025 georefererad karta.tif", "A 28782-2025")</f>
         <v/>
       </c>
       <c r="AA83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 7481-2026 FSC-klagomål.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28782-2025 FSC-klagomål.docx", "A 28782-2025")</f>
         <v/>
       </c>
       <c r="AB83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 7481-2026 FSC-klagomål mail.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28782-2025 FSC-klagomål mail.docx", "A 28782-2025")</f>
         <v/>
       </c>
       <c r="AC83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 7481-2026 tillsynsbegäran.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28782-2025 tillsynsbegäran.docx", "A 28782-2025")</f>
         <v/>
       </c>
       <c r="AD83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 7481-2026 tillsynsbegäran mail.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28782-2025 tillsynsbegäran mail.docx", "A 28782-2025")</f>
+        <v/>
+      </c>
+      <c r="AE83">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 28782-2025 prioriterade fågelarter.docx", "A 28782-2025")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 9104-2026</t>
+          <t>A 28785-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9953,14 +9962,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46069</v>
+        <v>45820</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9972,11 +9981,16 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -10009,46 +10023,50 @@
         <v>1</v>
       </c>
       <c r="U84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9104-2026 artfynd.xlsx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28785-2025 artfynd.xlsx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="X84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9104-2026 karta.png", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28785-2025 karta.png", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="Y84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9104-2026 georefererad karta.tif", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28785-2025 georefererad karta.tif", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AA84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9104-2026 FSC-klagomål.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28785-2025 FSC-klagomål.docx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AB84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9104-2026 FSC-klagomål mail.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28785-2025 FSC-klagomål mail.docx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AC84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9104-2026 tillsynsbegäran.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28785-2025 tillsynsbegäran.docx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AD84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9104-2026 tillsynsbegäran mail.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28785-2025 tillsynsbegäran mail.docx", "A 28785-2025")</f>
+        <v/>
+      </c>
+      <c r="AE84">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 28785-2025 prioriterade fågelarter.docx", "A 28785-2025")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 9905-2026</t>
+          <t>A 41831-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10062,10 +10080,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46073</v>
+        <v>45902</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10078,13 +10096,13 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -10093,7 +10111,7 @@
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10102,10 +10120,10 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
@@ -10118,42 +10136,42 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9905-2026 artfynd.xlsx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 41831-2025 artfynd.xlsx", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="X85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9905-2026 karta.png", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 41831-2025 karta.png", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="Y85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9905-2026 georefererad karta.tif", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 41831-2025 georefererad karta.tif", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="AA85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9905-2026 FSC-klagomål.docx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 41831-2025 FSC-klagomål.docx", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="AB85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9905-2026 FSC-klagomål mail.docx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 41831-2025 FSC-klagomål mail.docx", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="AC85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9905-2026 tillsynsbegäran.docx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 41831-2025 tillsynsbegäran.docx", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="AD85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9905-2026 tillsynsbegäran mail.docx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 41831-2025 tillsynsbegäran mail.docx", "A 41831-2025")</f>
         <v/>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 63276-2023</t>
+          <t>A 31720-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10167,10 +10185,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45273</v>
+        <v>44776</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10182,20 +10200,25 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
         <v>0</v>
@@ -10207,10 +10230,10 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>1</v>
@@ -10219,46 +10242,46 @@
         <v>1</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>Elaphomyces barrioi</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 63276-2023 artfynd.xlsx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31720-2022 artfynd.xlsx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="X86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 63276-2023 karta.png", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31720-2022 karta.png", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="Y86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 63276-2023 georefererad karta.tif", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31720-2022 georefererad karta.tif", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AA86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 63276-2023 FSC-klagomål.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31720-2022 FSC-klagomål.docx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AB86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 63276-2023 FSC-klagomål mail.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31720-2022 FSC-klagomål mail.docx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AC86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 63276-2023 tillsynsbegäran.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31720-2022 tillsynsbegäran.docx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AD86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 63276-2023 tillsynsbegäran mail.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31720-2022 tillsynsbegäran mail.docx", "A 31720-2022")</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 28785-2025</t>
+          <t>A 7481-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10268,14 +10291,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45820</v>
+        <v>46059</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10287,13 +10310,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J87" t="n">
         <v>1</v>
@@ -10326,53 +10344,49 @@
         <v>1</v>
       </c>
       <c r="T87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28785-2025 artfynd.xlsx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 7481-2026 artfynd.xlsx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="X87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28785-2025 karta.png", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 7481-2026 karta.png", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="Y87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28785-2025 georefererad karta.tif", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 7481-2026 georefererad karta.tif", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AA87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28785-2025 FSC-klagomål.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 7481-2026 FSC-klagomål.docx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AB87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28785-2025 FSC-klagomål mail.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 7481-2026 FSC-klagomål mail.docx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AC87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28785-2025 tillsynsbegäran.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 7481-2026 tillsynsbegäran.docx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AD87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28785-2025 tillsynsbegäran mail.docx", "A 28785-2025")</f>
-        <v/>
-      </c>
-      <c r="AE87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 28785-2025 prioriterade fågelarter.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 7481-2026 tillsynsbegäran mail.docx", "A 7481-2026")</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 28782-2025</t>
+          <t>A 9104-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10382,14 +10396,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45820</v>
+        <v>46069</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10401,16 +10415,11 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -10443,50 +10452,46 @@
         <v>1</v>
       </c>
       <c r="U88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="W88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28782-2025 artfynd.xlsx", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9104-2026 artfynd.xlsx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="X88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28782-2025 karta.png", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9104-2026 karta.png", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="Y88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28782-2025 georefererad karta.tif", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9104-2026 georefererad karta.tif", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AA88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28782-2025 FSC-klagomål.docx", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9104-2026 FSC-klagomål.docx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AB88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28782-2025 FSC-klagomål mail.docx", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9104-2026 FSC-klagomål mail.docx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AC88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28782-2025 tillsynsbegäran.docx", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9104-2026 tillsynsbegäran.docx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AD88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28782-2025 tillsynsbegäran mail.docx", "A 28782-2025")</f>
-        <v/>
-      </c>
-      <c r="AE88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 28782-2025 prioriterade fågelarter.docx", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9104-2026 tillsynsbegäran mail.docx", "A 9104-2026")</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 24704-2023</t>
+          <t>A 9905-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10500,10 +10505,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45084</v>
+        <v>46073</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10516,7 +10521,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -10549,7 +10554,7 @@
         <v>1</v>
       </c>
       <c r="T89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U89" t="n">
         <v>0</v>
@@ -10560,38 +10565,38 @@
         </is>
       </c>
       <c r="W89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24704-2023 artfynd.xlsx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9905-2026 artfynd.xlsx", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="X89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24704-2023 karta.png", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9905-2026 karta.png", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="Y89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24704-2023 georefererad karta.tif", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9905-2026 georefererad karta.tif", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="AA89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24704-2023 FSC-klagomål.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9905-2026 FSC-klagomål.docx", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="AB89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24704-2023 FSC-klagomål mail.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9905-2026 FSC-klagomål mail.docx", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="AC89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24704-2023 tillsynsbegäran.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9905-2026 tillsynsbegäran.docx", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="AD89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24704-2023 tillsynsbegäran mail.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9905-2026 tillsynsbegäran mail.docx", "A 9905-2026")</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 9745-2023</t>
+          <t>A 24701-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10605,10 +10610,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44984</v>
+        <v>45084</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10621,13 +10626,13 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -10636,7 +10641,7 @@
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -10645,58 +10650,58 @@
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S90" t="n">
         <v>1</v>
       </c>
       <c r="T90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9745-2023 artfynd.xlsx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24701-2023 artfynd.xlsx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="X90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9745-2023 karta.png", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24701-2023 karta.png", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="Y90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9745-2023 georefererad karta.tif", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24701-2023 georefererad karta.tif", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AA90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9745-2023 FSC-klagomål.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24701-2023 FSC-klagomål.docx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AB90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9745-2023 FSC-klagomål mail.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24701-2023 FSC-klagomål mail.docx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AC90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9745-2023 tillsynsbegäran.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24701-2023 tillsynsbegäran.docx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AD90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9745-2023 tillsynsbegäran mail.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24701-2023 tillsynsbegäran mail.docx", "A 24701-2023")</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 26840-2026</t>
+          <t>A 24704-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10706,14 +10711,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46185</v>
+        <v>45084</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10725,13 +10730,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -10764,7 +10764,7 @@
         <v>1</v>
       </c>
       <c r="T91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
@@ -10775,38 +10775,38 @@
         </is>
       </c>
       <c r="W91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26840-2026 artfynd.xlsx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24704-2023 artfynd.xlsx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="X91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26840-2026 karta.png", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24704-2023 karta.png", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="Y91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26840-2026 georefererad karta.tif", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24704-2023 georefererad karta.tif", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AA91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26840-2026 FSC-klagomål.docx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24704-2023 FSC-klagomål.docx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AB91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26840-2026 FSC-klagomål mail.docx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24704-2023 FSC-klagomål mail.docx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AC91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26840-2026 tillsynsbegäran.docx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24704-2023 tillsynsbegäran.docx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AD91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26840-2026 tillsynsbegäran mail.docx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24704-2023 tillsynsbegäran mail.docx", "A 24704-2023")</f>
         <v/>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 28374-2026</t>
+          <t>A 26840-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10820,10 +10820,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46196</v>
+        <v>46185</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -10853,10 +10853,10 @@
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -10874,42 +10874,42 @@
         <v>1</v>
       </c>
       <c r="T92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>Purpurmusseron</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28374-2026 artfynd.xlsx", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26840-2026 artfynd.xlsx", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="X92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28374-2026 karta.png", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26840-2026 karta.png", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="Y92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28374-2026 georefererad karta.tif", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26840-2026 georefererad karta.tif", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="AA92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28374-2026 FSC-klagomål.docx", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26840-2026 FSC-klagomål.docx", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="AB92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28374-2026 FSC-klagomål mail.docx", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26840-2026 FSC-klagomål mail.docx", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="AC92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28374-2026 tillsynsbegäran.docx", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26840-2026 tillsynsbegäran.docx", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="AD92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28374-2026 tillsynsbegäran mail.docx", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26840-2026 tillsynsbegäran mail.docx", "A 26840-2026")</f>
         <v/>
       </c>
     </row>
@@ -10933,7 +10933,7 @@
         <v>46197</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 31720-2022</t>
+          <t>A 28374-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -11036,14 +11036,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44776</v>
+        <v>46196</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11061,19 +11061,19 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N94" t="n">
         <v>0</v>
@@ -11085,10 +11085,10 @@
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S94" t="n">
         <v>1</v>
@@ -11097,39 +11097,39 @@
         <v>1</v>
       </c>
       <c r="U94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Purpurmusseron</t>
         </is>
       </c>
       <c r="W94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31720-2022 artfynd.xlsx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28374-2026 artfynd.xlsx", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="X94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31720-2022 karta.png", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28374-2026 karta.png", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="Y94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31720-2022 georefererad karta.tif", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28374-2026 georefererad karta.tif", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="AA94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31720-2022 FSC-klagomål.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28374-2026 FSC-klagomål.docx", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="AB94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31720-2022 FSC-klagomål mail.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28374-2026 FSC-klagomål mail.docx", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="AC94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31720-2022 tillsynsbegäran.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28374-2026 tillsynsbegäran.docx", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="AD94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31720-2022 tillsynsbegäran mail.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28374-2026 tillsynsbegäran mail.docx", "A 28374-2026")</f>
         <v/>
       </c>
     </row>
@@ -11153,7 +11153,7 @@
         <v>45433</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 33293-2026</t>
+          <t>A 63276-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -11251,14 +11251,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46246</v>
+        <v>45273</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11270,25 +11270,20 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N96" t="n">
         <v>0</v>
@@ -11300,58 +11295,58 @@
         <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S96" t="n">
         <v>1</v>
       </c>
       <c r="T96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U96" t="n">
         <v>0</v>
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Elaphomyces barrioi</t>
         </is>
       </c>
       <c r="W96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 33293-2026 artfynd.xlsx", "A 33293-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 63276-2023 artfynd.xlsx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="X96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 33293-2026 karta.png", "A 33293-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 63276-2023 karta.png", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="Y96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 33293-2026 georefererad karta.tif", "A 33293-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 63276-2023 georefererad karta.tif", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AA96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 33293-2026 FSC-klagomål.docx", "A 33293-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 63276-2023 FSC-klagomål.docx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AB96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 33293-2026 FSC-klagomål mail.docx", "A 33293-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 63276-2023 FSC-klagomål mail.docx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AC96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 33293-2026 tillsynsbegäran.docx", "A 33293-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 63276-2023 tillsynsbegäran.docx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AD96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 33293-2026 tillsynsbegäran mail.docx", "A 33293-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 63276-2023 tillsynsbegäran mail.docx", "A 63276-2023")</f>
         <v/>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 13043-2024</t>
+          <t>A 33293-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -11361,14 +11356,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45385</v>
+        <v>46246</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11380,8 +11375,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="J97" t="n">
         <v>1</v>
@@ -11414,49 +11414,49 @@
         <v>1</v>
       </c>
       <c r="T97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 13043-2024 artfynd.xlsx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 33293-2026 artfynd.xlsx", "A 33293-2026")</f>
         <v/>
       </c>
       <c r="X97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 13043-2024 karta.png", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 33293-2026 karta.png", "A 33293-2026")</f>
         <v/>
       </c>
       <c r="Y97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 13043-2024 georefererad karta.tif", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 33293-2026 georefererad karta.tif", "A 33293-2026")</f>
         <v/>
       </c>
       <c r="AA97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 13043-2024 FSC-klagomål.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 33293-2026 FSC-klagomål.docx", "A 33293-2026")</f>
         <v/>
       </c>
       <c r="AB97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 13043-2024 FSC-klagomål mail.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 33293-2026 FSC-klagomål mail.docx", "A 33293-2026")</f>
         <v/>
       </c>
       <c r="AC97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 13043-2024 tillsynsbegäran.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 33293-2026 tillsynsbegäran.docx", "A 33293-2026")</f>
         <v/>
       </c>
       <c r="AD97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 13043-2024 tillsynsbegäran mail.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 33293-2026 tillsynsbegäran mail.docx", "A 33293-2026")</f>
         <v/>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 20878-2024</t>
+          <t>A 13043-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -11470,10 +11470,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45439</v>
+        <v>45385</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11486,13 +11486,13 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J98" t="n">
         <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -11519,42 +11519,42 @@
         <v>1</v>
       </c>
       <c r="T98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 20878-2024 artfynd.xlsx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 13043-2024 artfynd.xlsx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="X98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 20878-2024 karta.png", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 13043-2024 karta.png", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="Y98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 20878-2024 georefererad karta.tif", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 13043-2024 georefererad karta.tif", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AA98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 20878-2024 FSC-klagomål.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 13043-2024 FSC-klagomål.docx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AB98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 20878-2024 FSC-klagomål mail.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 13043-2024 FSC-klagomål mail.docx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AC98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 20878-2024 tillsynsbegäran.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 13043-2024 tillsynsbegäran.docx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AD98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 20878-2024 tillsynsbegäran mail.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 13043-2024 tillsynsbegäran mail.docx", "A 13043-2024")</f>
         <v/>
       </c>
     </row>
@@ -11578,7 +11578,7 @@
         <v>45111</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>45903</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>46185</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S 1803-2026</t>
+          <t>S 1813-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -11899,10 +11899,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11920,82 +11920,82 @@
         </is>
       </c>
       <c r="I102" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>1</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>1</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>1</v>
+      </c>
+      <c r="T102" t="n">
         <v>2</v>
       </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="n">
-        <v>1</v>
-      </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>1</v>
-      </c>
-      <c r="R102" t="n">
-        <v>1</v>
-      </c>
-      <c r="S102" t="n">
-        <v>1</v>
-      </c>
-      <c r="T102" t="n">
-        <v>1</v>
-      </c>
       <c r="U102" t="n">
         <v>0</v>
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>Purpurmusseron</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="W102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1803-2026 artfynd.xlsx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1813-2026 artfynd.xlsx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="X102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1803-2026 karta.png", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1813-2026 karta.png", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="Y102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1803-2026 georefererad karta.tif", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1813-2026 georefererad karta.tif", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AA102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1803-2026 FSC-klagomål.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1813-2026 FSC-klagomål.docx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AB102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1803-2026 FSC-klagomål mail.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1813-2026 FSC-klagomål mail.docx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AC102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1803-2026 tillsynsbegäran.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1813-2026 tillsynsbegäran.docx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AD102">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1803-2026 tillsynsbegäran mail.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1813-2026 tillsynsbegäran mail.docx", "S 1813-2026")</f>
         <v/>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S 1813-2026</t>
+          <t>S 1803-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -12009,10 +12009,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -12039,10 +12039,10 @@
         <v>0</v>
       </c>
       <c r="L103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N103" t="n">
         <v>0</v>
@@ -12057,48 +12057,48 @@
         <v>1</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S103" t="n">
         <v>1</v>
       </c>
       <c r="T103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
       </c>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Purpurmusseron</t>
         </is>
       </c>
       <c r="W103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1813-2026 artfynd.xlsx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1803-2026 artfynd.xlsx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="X103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1813-2026 karta.png", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1803-2026 karta.png", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="Y103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1813-2026 georefererad karta.tif", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1803-2026 georefererad karta.tif", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AA103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1813-2026 FSC-klagomål.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1803-2026 FSC-klagomål.docx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AB103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1813-2026 FSC-klagomål mail.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1803-2026 FSC-klagomål mail.docx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AC103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1813-2026 tillsynsbegäran.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1803-2026 tillsynsbegäran.docx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AD103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1813-2026 tillsynsbegäran mail.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1803-2026 tillsynsbegäran mail.docx", "S 1803-2026")</f>
         <v/>
       </c>
     </row>
@@ -12122,7 +12122,7 @@
         <v>46246</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44783</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>44747</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>44840</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>44783</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>44501</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>44477</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>44742</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44503</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 3878-2023</t>
+          <t>A 31699-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -12823,10 +12823,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44951</v>
+        <v>44776</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12838,8 +12838,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -12882,7 +12887,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 12937-2022</t>
+          <t>A 26160-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12892,14 +12897,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44642</v>
+        <v>45468</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12911,13 +12916,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -12956,11 +12956,35 @@
         <v>0</v>
       </c>
       <c r="V114" s="2" t="inlineStr"/>
+      <c r="X114">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26160-2024 karta.png", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="Y114">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26160-2024 georefererad karta.tif", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AA114">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26160-2024 FSC-klagomål.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AB114">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26160-2024 FSC-klagomål mail.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AC114">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26160-2024 tillsynsbegäran.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AD114">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26160-2024 tillsynsbegäran mail.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 22785-2025</t>
+          <t>A 26190-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -12974,10 +12998,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45789</v>
+        <v>45805</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12990,7 +13014,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -13033,7 +13057,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 64303-2023</t>
+          <t>A 4159-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -13043,14 +13067,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45280</v>
+        <v>45323</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13063,7 +13087,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -13123,7 +13147,7 @@
         <v>45903</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13179,7 +13203,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 40339-2023</t>
+          <t>A 36269-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13193,10 +13217,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45169</v>
+        <v>45867</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13208,8 +13232,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -13252,7 +13281,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 55367-2024</t>
+          <t>A 45869-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -13266,10 +13295,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45621</v>
+        <v>45923</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13282,7 +13311,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -13325,7 +13354,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 26190-2025</t>
+          <t>A 46845-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -13335,14 +13364,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45805</v>
+        <v>45928</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13355,7 +13384,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -13398,7 +13427,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 45869-2025</t>
+          <t>A 4165-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -13412,10 +13441,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45923</v>
+        <v>44953</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13428,7 +13457,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -13471,7 +13500,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 46845-2025</t>
+          <t>A 9259-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -13481,14 +13510,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45928</v>
+        <v>46070</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13501,7 +13530,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -13544,7 +13573,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 9259-2026</t>
+          <t>A 32921-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -13558,10 +13587,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46070</v>
+        <v>45125</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13574,7 +13603,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -13617,7 +13646,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 4159-2024</t>
+          <t>A 15272-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -13627,14 +13656,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45323</v>
+        <v>46105</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13646,8 +13675,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -13690,7 +13724,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 32921-2023</t>
+          <t>A 15279-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -13700,14 +13734,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45125</v>
+        <v>46105</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13719,8 +13753,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -13763,7 +13802,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 31699-2022</t>
+          <t>A 15264-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -13773,14 +13812,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44776</v>
+        <v>46105</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13798,7 +13837,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -13841,7 +13880,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 15272-2026</t>
+          <t>A 64303-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -13851,14 +13890,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46105</v>
+        <v>45280</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13870,13 +13909,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -13919,7 +13953,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 15279-2026</t>
+          <t>A 43603-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -13929,14 +13963,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46105</v>
+        <v>45569</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13948,13 +13982,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -13997,7 +14026,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 15264-2026</t>
+          <t>A 63075-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -14007,14 +14036,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46105</v>
+        <v>45273</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14026,13 +14055,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -14075,7 +14099,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 1614-2025</t>
+          <t>A 1757-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -14089,10 +14113,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45670</v>
+        <v>45671</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14148,7 +14172,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 9076-2025</t>
+          <t>A 34780-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -14162,10 +14186,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45713</v>
+        <v>44795</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14183,7 +14207,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4.2</v>
+        <v>6.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -14226,7 +14250,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 1757-2025</t>
+          <t>A 55367-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -14240,10 +14264,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45671</v>
+        <v>45621</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14256,7 +14280,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -14299,7 +14323,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 36269-2025</t>
+          <t>A 27357-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -14309,14 +14333,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45867</v>
+        <v>45812</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14334,7 +14358,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -14377,7 +14401,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 9050-2025</t>
+          <t>A 7669-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -14387,14 +14411,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45713</v>
+        <v>45348</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14406,13 +14430,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -14455,7 +14474,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 43603-2024</t>
+          <t>A 20287-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -14465,14 +14484,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45569</v>
+        <v>45774</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14485,7 +14504,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -14528,7 +14547,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 27357-2025</t>
+          <t>A 9076-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -14538,14 +14557,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45812</v>
+        <v>45713</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14563,7 +14582,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -14606,7 +14625,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 7669-2024</t>
+          <t>A 24323-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -14620,10 +14639,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45348</v>
+        <v>46169</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14635,8 +14654,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -14679,7 +14703,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 24323-2026</t>
+          <t>A 32919-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -14693,10 +14717,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46169</v>
+        <v>45125</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14708,13 +14732,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -14757,7 +14776,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 28381-2026</t>
+          <t>A 34951-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -14771,10 +14790,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46196</v>
+        <v>44796</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14792,7 +14811,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -14852,7 +14871,7 @@
         <v>46196</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14913,7 +14932,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 28411-2026</t>
+          <t>A 5175-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -14923,14 +14942,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46197</v>
+        <v>45330</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14942,13 +14961,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -14991,7 +15005,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 32919-2023</t>
+          <t>A 28381-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -15001,14 +15015,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45125</v>
+        <v>46196</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15020,8 +15034,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -15064,7 +15083,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 29413-2026</t>
+          <t>A 28411-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -15078,10 +15097,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46203</v>
+        <v>46197</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15099,7 +15118,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -15142,7 +15161,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 29414-2026</t>
+          <t>A 29413-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -15159,7 +15178,7 @@
         <v>46203</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15177,7 +15196,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -15220,7 +15239,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 29431-2026</t>
+          <t>A 29414-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -15237,7 +15256,7 @@
         <v>46203</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15255,7 +15274,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -15298,7 +15317,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 29410-2026</t>
+          <t>A 29431-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -15315,7 +15334,7 @@
         <v>46203</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15333,7 +15352,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -15376,7 +15395,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 5175-2024</t>
+          <t>A 29410-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -15386,14 +15405,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45330</v>
+        <v>46203</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15403,6 +15422,11 @@
       <c r="G147" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I147" t="n">
@@ -15449,7 +15473,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 34951-2022</t>
+          <t>A 3878-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -15459,14 +15483,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44796</v>
+        <v>44951</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15478,13 +15502,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -15544,7 +15563,7 @@
         <v>45005</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15600,7 +15619,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 61438-2023</t>
+          <t>A 12937-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -15610,14 +15629,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45264</v>
+        <v>44642</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15629,8 +15648,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -15673,7 +15697,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 13041-2024</t>
+          <t>A 61438-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -15683,14 +15707,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45385</v>
+        <v>45264</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15703,7 +15727,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -15746,7 +15770,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 4165-2023</t>
+          <t>A 13041-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -15760,10 +15784,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44953</v>
+        <v>45385</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15776,7 +15800,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -15819,7 +15843,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 34780-2022</t>
+          <t>A 1614-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -15833,10 +15857,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44795</v>
+        <v>45670</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15848,13 +15872,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>6.7</v>
+        <v>1.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -15897,7 +15916,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 24338-2026</t>
+          <t>A 9050-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -15911,10 +15930,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46169</v>
+        <v>45713</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15932,7 +15951,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -15975,7 +15994,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 20287-2025</t>
+          <t>A 24338-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -15989,10 +16008,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45774</v>
+        <v>46169</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16004,8 +16023,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -16048,7 +16072,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 26160-2024</t>
+          <t>A 22785-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -16058,14 +16082,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45468</v>
+        <v>45789</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16078,7 +16102,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -16117,35 +16141,11 @@
         <v>0</v>
       </c>
       <c r="V156" s="2" t="inlineStr"/>
-      <c r="X156">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26160-2024 karta.png", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="Y156">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26160-2024 georefererad karta.tif", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AA156">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26160-2024 FSC-klagomål.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AB156">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26160-2024 FSC-klagomål mail.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AC156">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26160-2024 tillsynsbegäran.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AD156">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26160-2024 tillsynsbegäran mail.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
     </row>
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 63075-2023</t>
+          <t>A 40339-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -16155,14 +16155,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45273</v>
+        <v>45169</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -16235,7 +16235,7 @@
         <v>44756</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>45713</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45812</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>45812</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>45754</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>46105</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>46105</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>46169</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S 1806-2026</t>
+          <t>S 1812-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -16846,10 +16846,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -16910,7 +16910,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S 1807-2026</t>
+          <t>S 1806-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -16927,7 +16927,7 @@
         <v>46196</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -16988,7 +16988,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S 1812-2026</t>
+          <t>S 1807-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -17002,10 +17002,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>46203</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>46203</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>46203</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>46203</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>

--- a/Översikt BORGHOLM.xlsx
+++ b/Översikt BORGHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45029</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>44704</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45433</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>44903</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45903</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>46254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44809</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>44523</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>45918</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>45107</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>44781</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>45161</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>45146</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>45930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>44638</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>45736</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>46220</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>45175</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45027</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>45926</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>46188</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>46224</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>44704</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45478</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>46188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>46224</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>44482</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>46169</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>46169</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>45280</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>45442</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>45736</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>44953</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>44973</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>46188</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44704</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>44704</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>44783</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>45887</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>45911</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>45796</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>44781</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>46105</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>44837</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>46185</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>46188</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>46223</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>46105</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>46188</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>46223</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>44623</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>45758</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>44725</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>44711</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>44840</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>45994</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>45994</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>46070</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>46169</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>46203</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>46203</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>44649</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>44865</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>46203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>46203</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44772</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>44781</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>45273</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>44984</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>45902</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>45439</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>45385</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45084</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>44776</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>45820</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>45820</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>45084</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>45433</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>46041</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>46059</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>46069</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>46073</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>46185</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>46197</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>46196</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>46246</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>45111</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>45903</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>46185</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>46197</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>46196</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>46246</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>44783</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>44747</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>44840</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>44783</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>44501</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>44742</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>44503</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>45264</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>45385</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>44776</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>45670</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>45569</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>45273</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>45468</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45713</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>45903</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>45671</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>45323</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>45923</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>45789</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44795</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>45621</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>45774</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>45928</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>45713</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>45169</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>45805</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>45125</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>44953</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>44796</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>45125</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>45330</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>45867</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>46105</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>46105</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>44951</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>45005</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>44642</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>46070</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45812</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>45348</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>46169</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>46196</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>46196</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>46197</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>46203</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>46203</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>46203</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>46203</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16055,7 +16055,7 @@
         <v>46169</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>44756</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>45713</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>45812</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>45812</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>45754</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>46105</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>46105</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>46169</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>46197</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>46196</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>46196</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>46203</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>46203</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>46203</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>46203</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>

--- a/Översikt BORGHOLM.xlsx
+++ b/Översikt BORGHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45029</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>44704</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45433</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>44903</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45903</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>46254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44809</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>44523</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>45918</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>45107</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>44781</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>45161</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>45146</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>45930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>44638</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>45736</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>46220</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>44704</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>45175</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45027</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>45926</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>46188</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>46224</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>44704</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45478</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>46188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>46224</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>44482</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>46169</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>46169</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>45280</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>45442</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>45736</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>44953</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>44973</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>46188</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44704</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>44704</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>44783</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>45887</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>45911</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>45796</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>44781</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>46105</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>44837</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>46185</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>46188</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>46223</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>46105</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>46188</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>46223</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>44623</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>45758</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>44725</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>44711</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>44840</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>45994</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>45994</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>46070</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>46169</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>46203</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>46203</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>44649</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>44865</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>46203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>46203</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44772</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>44781</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>45273</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>44984</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>45902</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>45439</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>45385</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45084</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>44776</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>45820</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>45820</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>45084</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>45433</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>46041</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>46059</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>46069</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>46073</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>46185</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>46197</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>46196</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>46246</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>45111</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>45903</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>46185</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>46197</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>46196</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>46246</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>44783</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>44747</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>44840</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>44783</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>44501</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>44742</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>44503</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>45264</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>45385</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>44776</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>45670</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>45569</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>45273</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>45468</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45713</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>45903</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>45671</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>45323</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>45923</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>45789</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44795</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>45621</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>45774</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>45928</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>45713</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>45169</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>45805</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>45125</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>44953</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>44796</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>45125</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>45330</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>45867</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>46105</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>46105</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>44951</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>45005</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>44642</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>46070</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45812</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>45348</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>46169</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>46196</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>46196</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>46197</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>46203</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>46203</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>46203</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>46203</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16055,7 +16055,7 @@
         <v>46169</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>44756</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>45713</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>45812</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>45812</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>45754</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>46105</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>46105</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>46169</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>46197</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>46196</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>46196</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>46203</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>46203</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>46203</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>46203</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>

--- a/Översikt BORGHOLM.xlsx
+++ b/Översikt BORGHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45029</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>44704</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45433</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>44903</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45903</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>46254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44809</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>46307</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45918</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>44523</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>45107</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>44781</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>45161</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>45146</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>45930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45736</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>46220</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>44638</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>45175</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>45926</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>46188</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>46224</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>45027</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>44704</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45478</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>46188</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>46224</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>46169</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>46169</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>45736</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45280</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>44973</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>46188</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>44953</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>45442</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>44704</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>44704</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>44783</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>45887</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>45911</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>44781</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>44837</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>46188</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>46185</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>46105</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>46223</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>45796</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>46105</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>46188</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>46223</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44623</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>44711</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>45994</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>45994</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>46169</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>46070</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44840</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>46203</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         <v>45758</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>44725</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>46203</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>44865</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44649</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>46203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>46203</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>44772</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44781</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>45084</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>45273</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>45084</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>45902</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>44984</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>46041</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>46059</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>46069</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>46073</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>46185</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>44776</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>45433</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>46196</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>46197</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>45385</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>45439</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>46246</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45820</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>45820</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>45111</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45903</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>46185</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>46196</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>46197</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>46246</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>44783</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>44747</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>44840</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>44783</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>44501</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>44742</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>44503</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>44951</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>44642</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>45621</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>45323</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>45125</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         <v>44776</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>45670</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>45903</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>45713</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>45923</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>45671</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>45928</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>45812</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>45348</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>45713</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>45569</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>46169</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>46070</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>45125</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>45330</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>44796</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>46105</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>46105</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>46196</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>46196</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>46197</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>45005</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>45264</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>45385</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>44953</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>46203</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>46203</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>46203</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>46203</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>44795</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>45774</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>45468</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>46169</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>45273</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>45789</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45169</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>45805</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>45867</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>44756</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>45713</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>45812</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>45812</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>45754</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>46105</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>46105</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>46169</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>46196</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>46196</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>46197</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>46203</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>46203</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>46203</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>46203</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>

--- a/Översikt BORGHOLM.xlsx
+++ b/Översikt BORGHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45029</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>44704</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45433</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>44903</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45903</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>46254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44809</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>46307</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45918</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>44523</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>45107</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>44781</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>45161</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>45146</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>45930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45736</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>46220</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>44638</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>45175</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>45926</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>46188</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>46224</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>45027</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>44704</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45478</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>46188</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>46224</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>46169</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>46169</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>45736</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45280</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>44973</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>46188</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>44953</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>45442</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>44704</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>44704</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>44783</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>45887</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>45911</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>44781</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>44837</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>46188</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>46185</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>46105</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>46223</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>45796</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>46105</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>46188</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>46223</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44623</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>44711</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>45994</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>45994</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>46169</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>46070</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44840</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>46203</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         <v>45758</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>44725</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>46203</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>44865</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44649</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>46203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>46203</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>44772</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44781</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>45084</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>45273</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>45084</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>45902</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>44984</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>46041</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>46059</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>46069</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>46073</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>46185</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>44776</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>45433</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>46196</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>46197</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>45385</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>45439</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>46246</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45820</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>45820</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>45111</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45903</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>46185</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>46196</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>46197</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>46246</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>44783</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>44747</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>44840</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>44783</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>44501</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>44742</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>44503</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>44951</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>44642</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>45621</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>45323</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>45125</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         <v>44776</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>45670</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>45903</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>45713</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>45923</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>45671</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>45928</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>45812</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>45348</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>45713</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>45569</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>46169</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>46070</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>45125</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>45330</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>44796</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>46105</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>46105</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>46196</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>46196</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>46197</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>45005</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>45264</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>45385</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>44953</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>46203</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>46203</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>46203</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>46203</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>44795</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>45774</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>45468</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>46169</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>45273</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>45789</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45169</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>45805</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>45867</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>44756</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>45713</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>45812</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>45812</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>45754</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>46105</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>46105</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>46169</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>46196</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>46196</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>46197</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>46203</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>46203</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>46203</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>46203</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>

--- a/Översikt BORGHOLM.xlsx
+++ b/Översikt BORGHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45029</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>44704</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45433</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>44903</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45903</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>46254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 37421-2022</t>
+          <t>A 45006-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44809</v>
+        <v>45918</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2074,19 +2074,19 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.4</v>
+        <v>7.8</v>
       </c>
       <c r="J13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
+        <v>6</v>
+      </c>
+      <c r="L13" t="n">
         <v>5</v>
       </c>
-      <c r="L13" t="n">
-        <v>4</v>
-      </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2098,21 +2098,140 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
       </c>
       <c r="T13" t="n">
+        <v>22</v>
+      </c>
+      <c r="U13" t="n">
+        <v>21</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Skogskorn
+Axveronika
+Kattfotslav
+Mindre ekbock
+Skugglosta
+Vårstarr
+Gulpudrad spiklav
+Murgröna
+Myskmadra
+Skogsknipprot
+Tvåblad
+Vit skogslilja
+Johannesnycklar
+Krutbrännare
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 45006-2025 artfynd.xlsx", "A 45006-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 45006-2025 karta.png", "A 45006-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 45006-2025 georefererad karta.tif", "A 45006-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 45006-2025 FSC-klagomål.docx", "A 45006-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 45006-2025 FSC-klagomål mail.docx", "A 45006-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 45006-2025 tillsynsbegäran.docx", "A 45006-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 45006-2025 tillsynsbegäran mail.docx", "A 45006-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 37421-2022</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>44809</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="n">
         <v>37</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>33</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Höstlåsbräken
 Loppstarr
@@ -2131,155 +2250,36 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 37421-2022 artfynd.xlsx", "A 37421-2022")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 37421-2022 karta.png", "A 37421-2022")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 37421-2022 georefererad karta.tif", "A 37421-2022")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 37421-2022 FSC-klagomål.docx", "A 37421-2022")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 37421-2022 FSC-klagomål mail.docx", "A 37421-2022")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 37421-2022 tillsynsbegäran.docx", "A 37421-2022")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 37421-2022 tillsynsbegäran mail.docx", "A 37421-2022")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 37421-2022 prioriterade fågelarter.docx", "A 37421-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 45006-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45918</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>6</v>
-      </c>
-      <c r="L14" t="n">
-        <v>5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>15</v>
-      </c>
-      <c r="T14" t="n">
-        <v>21</v>
-      </c>
-      <c r="U14" t="n">
-        <v>20</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Skogskorn
-Axveronika
-Kattfotslav
-Mindre ekbock
-Skugglosta
-Vårstarr
-Gulpudrad spiklav
-Murgröna
-Myskmadra
-Skogsknipprot
-Tvåblad
-Vit skogslilja
-Johannesnycklar
-Krutbrännare
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 45006-2025 artfynd.xlsx", "A 45006-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 45006-2025 karta.png", "A 45006-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 45006-2025 georefererad karta.tif", "A 45006-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 45006-2025 FSC-klagomål.docx", "A 45006-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 45006-2025 FSC-klagomål mail.docx", "A 45006-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 45006-2025 tillsynsbegäran.docx", "A 45006-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 45006-2025 tillsynsbegäran mail.docx", "A 45006-2025")</f>
         <v/>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
         <v>46307</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45918</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>44523</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>45107</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>44781</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>45161</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>45146</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>45930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45736</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31399-2026</t>
+          <t>A 31515-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3456,14 +3456,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3475,14 +3475,19 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L25" t="n">
         <v>3</v>
@@ -3509,12 +3514,241 @@
         <v>8</v>
       </c>
       <c r="T25" t="n">
+        <v>11</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Blå slemspindling
+Sårläka
+Vårärt
+Anisspindling
+Skogsknipprot
+Strävlosta
+Blåsippa
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31515-2026 artfynd.xlsx", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31515-2026 karta.png", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31515-2026 georefererad karta.tif", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31515-2026 FSC-klagomål.docx", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31515-2026 FSC-klagomål mail.docx", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31515-2026 tillsynsbegäran.docx", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31515-2026 tillsynsbegäran mail.docx", "A 31515-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 31516-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3</v>
+      </c>
+      <c r="L26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>8</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="T26" t="n">
+        <v>11</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Blå slemspindling
+Sårläka
+Vårärt
+Anisspindling
+Skogsknipprot
+Strävlosta
+Blåsippa
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31516-2026 artfynd.xlsx", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31516-2026 karta.png", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31516-2026 georefererad karta.tif", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31516-2026 FSC-klagomål.docx", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31516-2026 FSC-klagomål mail.docx", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31516-2026 tillsynsbegäran.docx", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31516-2026 tillsynsbegäran mail.docx", "A 31516-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 31399-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>8</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Backklöver
 Jordtistel
@@ -3526,112 +3760,336 @@
 Vanliga ängsnycklar</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31399-2026 artfynd.xlsx", "A 31399-2026")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31399-2026 karta.png", "A 31399-2026")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31399-2026 georefererad karta.tif", "A 31399-2026")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31399-2026 FSC-klagomål.docx", "A 31399-2026")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31399-2026 FSC-klagomål mail.docx", "A 31399-2026")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31399-2026 tillsynsbegäran.docx", "A 31399-2026")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31399-2026 tillsynsbegäran mail.docx", "A 31399-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 31515-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 12534-2022</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>44638</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>5</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>5</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>9</v>
+      </c>
+      <c r="U28" t="n">
+        <v>9</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Backklöver
+Backtimjan
+Jordtistel
+Sårläka
+Vårstarr
+Krutbrännare
+Nattviol
+Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 12534-2022 artfynd.xlsx", "A 12534-2022")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 12534-2022 karta.png", "A 12534-2022")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 12534-2022 georefererad karta.tif", "A 12534-2022")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 12534-2022 FSC-klagomål.docx", "A 12534-2022")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 12534-2022 FSC-klagomål mail.docx", "A 12534-2022")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 12534-2022 tillsynsbegäran.docx", "A 12534-2022")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 12534-2022 tillsynsbegäran mail.docx", "A 12534-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S 2741-2022</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>44704</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="n">
+        <v>55</v>
+      </c>
+      <c r="U29" t="n">
+        <v>49</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Almlav
+Ask
+Korskovall
+Ekoxe
+Slät lönnlav
+Stor häxört
+Underviol
+Vitskivlav</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2741-2022 artfynd.xlsx", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 2741-2022 karta.png", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 2741-2022 georefererad karta.tif", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 2741-2022 FSC-klagomål.docx", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 2741-2022 FSC-klagomål mail.docx", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 2741-2022 tillsynsbegäran.docx", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 2741-2022 tillsynsbegäran mail.docx", "S 2741-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>S 2057-2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="E30" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="I30" t="n">
         <v>0.8</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J30" t="n">
         <v>3</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K30" t="n">
         <v>3</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L30" t="n">
         <v>3</v>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>3</v>
       </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>8</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T30" t="n">
         <v>11</v>
       </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Blå slemspindling
 Sårläka
@@ -3643,112 +4101,112 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31515-2026 artfynd.xlsx", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31515-2026 karta.png", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31515-2026 georefererad karta.tif", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31515-2026 FSC-klagomål.docx", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31515-2026 FSC-klagomål mail.docx", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31515-2026 tillsynsbegäran.docx", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31515-2026 tillsynsbegäran mail.docx", "A 31515-2026")</f>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2057-2026 artfynd.xlsx", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 2057-2026 karta.png", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 2057-2026 georefererad karta.tif", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 2057-2026 FSC-klagomål.docx", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 2057-2026 FSC-klagomål mail.docx", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 2057-2026 tillsynsbegäran.docx", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 2057-2026 tillsynsbegäran mail.docx", "S 2057-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 31516-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>S 2058-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E27" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="E31" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I27" t="n">
+      <c r="I31" t="n">
         <v>0.8</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J31" t="n">
         <v>3</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K31" t="n">
         <v>3</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L31" t="n">
         <v>3</v>
       </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
         <v>3</v>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
         <v>8</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T31" t="n">
         <v>11</v>
       </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Blå slemspindling
 Sårläka
@@ -3760,464 +4218,6 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31516-2026 artfynd.xlsx", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31516-2026 karta.png", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31516-2026 georefererad karta.tif", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31516-2026 FSC-klagomål.docx", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31516-2026 FSC-klagomål mail.docx", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31516-2026 tillsynsbegäran.docx", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31516-2026 tillsynsbegäran mail.docx", "A 31516-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 12534-2022</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>44638</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>5</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>5</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>8</v>
-      </c>
-      <c r="T28" t="n">
-        <v>9</v>
-      </c>
-      <c r="U28" t="n">
-        <v>9</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Backklöver
-Backtimjan
-Jordtistel
-Sårläka
-Vårstarr
-Krutbrännare
-Nattviol
-Sankt pers nycklar</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 12534-2022 artfynd.xlsx", "A 12534-2022")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 12534-2022 karta.png", "A 12534-2022")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 12534-2022 georefererad karta.tif", "A 12534-2022")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 12534-2022 FSC-klagomål.docx", "A 12534-2022")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 12534-2022 FSC-klagomål mail.docx", "A 12534-2022")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 12534-2022 tillsynsbegäran.docx", "A 12534-2022")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 12534-2022 tillsynsbegäran mail.docx", "A 12534-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>S 2741-2022</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>44704</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>5</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2</v>
-      </c>
-      <c r="S29" t="n">
-        <v>8</v>
-      </c>
-      <c r="T29" t="n">
-        <v>55</v>
-      </c>
-      <c r="U29" t="n">
-        <v>49</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Almlav
-Ask
-Korskovall
-Ekoxe
-Slät lönnlav
-Stor häxört
-Underviol
-Vitskivlav</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2741-2022 artfynd.xlsx", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 2741-2022 karta.png", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 2741-2022 georefererad karta.tif", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 2741-2022 FSC-klagomål.docx", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 2741-2022 FSC-klagomål mail.docx", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 2741-2022 tillsynsbegäran.docx", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 2741-2022 tillsynsbegäran mail.docx", "S 2741-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>S 2057-2026</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3</v>
-      </c>
-      <c r="L30" t="n">
-        <v>3</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>11</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Blå slemspindling
-Sårläka
-Vårärt
-Anisspindling
-Skogsknipprot
-Strävlosta
-Blåsippa
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2057-2026 artfynd.xlsx", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 2057-2026 karta.png", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 2057-2026 georefererad karta.tif", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 2057-2026 FSC-klagomål.docx", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 2057-2026 FSC-klagomål mail.docx", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 2057-2026 tillsynsbegäran.docx", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 2057-2026 tillsynsbegäran mail.docx", "S 2057-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>S 2058-2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J31" t="n">
-        <v>3</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3</v>
-      </c>
-      <c r="L31" t="n">
-        <v>3</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>11</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Blå slemspindling
-Sårläka
-Vårärt
-Anisspindling
-Skogsknipprot
-Strävlosta
-Blåsippa
-Grönvit nattviol</t>
-        </is>
-      </c>
       <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2058-2026 artfynd.xlsx", "S 2058-2026")</f>
         <v/>
@@ -4267,7 +4267,7 @@
         <v>45175</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>45926</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 27298-2026</t>
+          <t>A 16171-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4481,14 +4481,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46188</v>
+        <v>45027</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4500,22 +4500,17 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>3.3</v>
+        <v>12.2</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4530,7 +4525,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4539,12 +4534,127 @@
         <v>6</v>
       </c>
       <c r="T34" t="n">
+        <v>7</v>
+      </c>
+      <c r="U34" t="n">
         <v>6</v>
       </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
       <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Sårläka
+Älg
+Murgröna
+Blåsippa
+Rostticka
+Bredarun</t>
+        </is>
+      </c>
+      <c r="W34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 16171-2023 artfynd.xlsx", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="X34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 16171-2023 karta.png", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="Y34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 16171-2023 georefererad karta.tif", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="AA34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 16171-2023 FSC-klagomål.docx", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="AB34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 16171-2023 FSC-klagomål mail.docx", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="AC34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 16171-2023 tillsynsbegäran.docx", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="AD34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 16171-2023 tillsynsbegäran mail.docx", "A 16171-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A 27298-2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>5</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>6</v>
+      </c>
+      <c r="T35" t="n">
+        <v>6</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Grenplattnos
 Jungfrulin
@@ -4554,112 +4664,112 @@
 Murgröna</t>
         </is>
       </c>
-      <c r="W34">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27298-2026 artfynd.xlsx", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="X34">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27298-2026 karta.png", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="Y34">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27298-2026 georefererad karta.tif", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="AA34">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27298-2026 FSC-klagomål.docx", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="AB34">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27298-2026 FSC-klagomål mail.docx", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="AC34">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27298-2026 tillsynsbegäran.docx", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="AD34">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27298-2026 tillsynsbegäran mail.docx", "A 27298-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>A 31558-2026</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D35" s="1" t="n">
+      <c r="D36" s="1" t="n">
         <v>46224</v>
       </c>
-      <c r="E35" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F35" t="inlineStr">
+      <c r="E36" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" t="n">
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
         <v>2</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K36" t="n">
         <v>2</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
         <v>3</v>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
         <v>6</v>
       </c>
-      <c r="T35" t="n">
+      <c r="T36" t="n">
         <v>8</v>
       </c>
-      <c r="U35" t="n">
-        <v>1</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="U36" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Blå slemspindling
 Sårläka
@@ -4669,142 +4779,32 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W35">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31558-2026 artfynd.xlsx", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="X35">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31558-2026 karta.png", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31558-2026 georefererad karta.tif", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31558-2026 FSC-klagomål.docx", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31558-2026 FSC-klagomål mail.docx", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31558-2026 tillsynsbegäran.docx", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="AD35">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31558-2026 tillsynsbegäran mail.docx", "A 31558-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A 16171-2023</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>45027</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="n">
-        <v>2</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>6</v>
-      </c>
-      <c r="T36" t="n">
-        <v>7</v>
-      </c>
-      <c r="U36" t="n">
-        <v>6</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka
-Älg
-Murgröna
-Blåsippa
-Rostticka
-Bredarun</t>
-        </is>
-      </c>
-      <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 16171-2023 artfynd.xlsx", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 16171-2023 karta.png", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 16171-2023 georefererad karta.tif", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 16171-2023 FSC-klagomål.docx", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 16171-2023 FSC-klagomål mail.docx", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 16171-2023 tillsynsbegäran.docx", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 16171-2023 tillsynsbegäran mail.docx", "A 16171-2023")</f>
         <v/>
       </c>
     </row>
@@ -4828,7 +4828,7 @@
         <v>44704</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45478</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>46188</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>46224</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>46169</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>46169</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>45736</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45280</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7960-2023</t>
+          <t>A 21797-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44973</v>
+        <v>45442</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5735,16 +5735,16 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5753,27 +5753,360 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
       </c>
       <c r="T45" t="n">
+        <v>11</v>
+      </c>
+      <c r="U45" t="n">
+        <v>6</v>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>Sydlig kantmusseron
+Murgröna
+Skogsknipprot
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21797-2024 artfynd.xlsx", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="X45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21797-2024 karta.png", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="Y45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21797-2024 georefererad karta.tif", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="AA45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21797-2024 FSC-klagomål.docx", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="AB45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21797-2024 FSC-klagomål mail.docx", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="AC45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21797-2024 tillsynsbegäran.docx", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="AD45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21797-2024 tillsynsbegäran mail.docx", "A 21797-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A 27290-2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2</v>
+      </c>
+      <c r="R46" t="n">
+        <v>2</v>
+      </c>
+      <c r="S46" t="n">
         <v>4</v>
       </c>
-      <c r="U45" t="n">
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Gotlandsmåra
+Skogsknipprot
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27290-2026 artfynd.xlsx", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="X46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27290-2026 karta.png", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="Y46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27290-2026 georefererad karta.tif", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="AA46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27290-2026 FSC-klagomål.docx", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="AB46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27290-2026 FSC-klagomål mail.docx", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="AC46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27290-2026 tillsynsbegäran.docx", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="AD46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27290-2026 tillsynsbegäran mail.docx", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="AE46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 27290-2026 prioriterade fågelarter.docx", "A 27290-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>A 4164-2023</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>44953</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>4</v>
+      </c>
+      <c r="T47" t="n">
+        <v>5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>4</v>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>Crepis tectorum subsp. tectorum
+Kösa
+Murgröna
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 4164-2023 artfynd.xlsx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="X47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 4164-2023 karta.png", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="Y47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 4164-2023 georefererad karta.tif", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AA47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 4164-2023 FSC-klagomål.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AB47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 4164-2023 FSC-klagomål mail.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AC47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 4164-2023 tillsynsbegäran.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AD47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 4164-2023 tillsynsbegäran mail.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>A 7960-2023</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>44973</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
         <v>3</v>
       </c>
-      <c r="V45" s="2" t="inlineStr">
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="n">
+        <v>4</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>Vresalm
 Pilfotsspindling
@@ -5781,365 +6114,32 @@
 Strävlosta</t>
         </is>
       </c>
-      <c r="W45">
+      <c r="W48">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 7960-2023 artfynd.xlsx", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="X45">
+      <c r="X48">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 7960-2023 karta.png", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="Y45">
+      <c r="Y48">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 7960-2023 georefererad karta.tif", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="AA45">
+      <c r="AA48">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 7960-2023 FSC-klagomål.docx", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="AB45">
+      <c r="AB48">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 7960-2023 FSC-klagomål mail.docx", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="AC45">
+      <c r="AC48">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 7960-2023 tillsynsbegäran.docx", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="AD45">
+      <c r="AD48">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 7960-2023 tillsynsbegäran mail.docx", "A 7960-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>A 27290-2026</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E46" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J46" t="n">
-        <v>2</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>1</v>
-      </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>2</v>
-      </c>
-      <c r="R46" t="n">
-        <v>2</v>
-      </c>
-      <c r="S46" t="n">
-        <v>4</v>
-      </c>
-      <c r="T46" t="n">
-        <v>4</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Gotlandsmåra
-Skogsknipprot
-Havsörn</t>
-        </is>
-      </c>
-      <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27290-2026 artfynd.xlsx", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27290-2026 karta.png", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27290-2026 georefererad karta.tif", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27290-2026 FSC-klagomål.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27290-2026 FSC-klagomål mail.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27290-2026 tillsynsbegäran.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27290-2026 tillsynsbegäran mail.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="AE46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 27290-2026 prioriterade fågelarter.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>A 4164-2023</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>44953</v>
-      </c>
-      <c r="E47" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J47" t="n">
-        <v>1</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" t="n">
-        <v>2</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>2</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>4</v>
-      </c>
-      <c r="T47" t="n">
-        <v>5</v>
-      </c>
-      <c r="U47" t="n">
-        <v>4</v>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>Crepis tectorum subsp. tectorum
-Kösa
-Murgröna
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 4164-2023 artfynd.xlsx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 4164-2023 karta.png", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 4164-2023 georefererad karta.tif", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 4164-2023 FSC-klagomål.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 4164-2023 FSC-klagomål mail.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 4164-2023 tillsynsbegäran.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 4164-2023 tillsynsbegäran mail.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>A 21797-2024</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>45442</v>
-      </c>
-      <c r="E48" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2</v>
-      </c>
-      <c r="L48" t="n">
-        <v>1</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>4</v>
-      </c>
-      <c r="T48" t="n">
-        <v>11</v>
-      </c>
-      <c r="U48" t="n">
-        <v>6</v>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>Sydlig kantmusseron
-Murgröna
-Skogsknipprot
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21797-2024 artfynd.xlsx", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21797-2024 karta.png", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21797-2024 georefererad karta.tif", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21797-2024 FSC-klagomål.docx", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21797-2024 FSC-klagomål mail.docx", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21797-2024 tillsynsbegäran.docx", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21797-2024 tillsynsbegäran mail.docx", "A 21797-2024")</f>
         <v/>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
         <v>44704</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>44704</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>44783</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>45887</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 43542-2025</t>
+          <t>A 32174-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6591,14 +6591,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45911</v>
+        <v>44781</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6610,17 +6610,22 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -6635,7 +6640,7 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -6650,157 +6655,152 @@
         <v>3</v>
       </c>
       <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>Backklöver
+Tvåblad
+Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="W53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 32174-2022 artfynd.xlsx", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="X53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 32174-2022 karta.png", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="Y53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 32174-2022 georefererad karta.tif", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="AA53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 32174-2022 FSC-klagomål.docx", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="AB53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 32174-2022 FSC-klagomål mail.docx", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="AC53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 32174-2022 tillsynsbegäran.docx", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="AD53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 32174-2022 tillsynsbegäran mail.docx", "A 32174-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>A 43542-2025</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>45911</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>3</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
         <is>
           <t>Vårärt
 Ängsskära
 Underviol</t>
         </is>
       </c>
-      <c r="W53">
+      <c r="W54">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 43542-2025 artfynd.xlsx", "A 43542-2025")</f>
         <v/>
       </c>
-      <c r="X53">
+      <c r="X54">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 43542-2025 karta.png", "A 43542-2025")</f>
         <v/>
       </c>
-      <c r="Y53">
+      <c r="Y54">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 43542-2025 georefererad karta.tif", "A 43542-2025")</f>
         <v/>
       </c>
-      <c r="AA53">
+      <c r="AA54">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 43542-2025 FSC-klagomål.docx", "A 43542-2025")</f>
         <v/>
       </c>
-      <c r="AB53">
+      <c r="AB54">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 43542-2025 FSC-klagomål mail.docx", "A 43542-2025")</f>
         <v/>
       </c>
-      <c r="AC53">
+      <c r="AC54">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 43542-2025 tillsynsbegäran.docx", "A 43542-2025")</f>
         <v/>
       </c>
-      <c r="AD53">
+      <c r="AD54">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 43542-2025 tillsynsbegäran mail.docx", "A 43542-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>A 32174-2022</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="n">
-        <v>44781</v>
-      </c>
-      <c r="E54" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2</v>
-      </c>
-      <c r="K54" t="n">
-        <v>2</v>
-      </c>
-      <c r="L54" t="n">
-        <v>1</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>1</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>3</v>
-      </c>
-      <c r="T54" t="n">
-        <v>3</v>
-      </c>
-      <c r="U54" t="n">
-        <v>3</v>
-      </c>
-      <c r="V54" s="2" t="inlineStr">
-        <is>
-          <t>Backklöver
-Tvåblad
-Vit skogslilja</t>
-        </is>
-      </c>
-      <c r="W54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 32174-2022 artfynd.xlsx", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="X54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 32174-2022 karta.png", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="Y54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 32174-2022 georefererad karta.tif", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="AA54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 32174-2022 FSC-klagomål.docx", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="AB54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 32174-2022 FSC-klagomål mail.docx", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="AC54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 32174-2022 tillsynsbegäran.docx", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="AD54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 32174-2022 tillsynsbegäran mail.docx", "A 32174-2022")</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 43756-2022</t>
+          <t>A 26849-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44837</v>
+        <v>46185</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6829,14 +6829,19 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>8.1</v>
       </c>
       <c r="J55" t="n">
         <v>2</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -6863,921 +6868,916 @@
         <v>3</v>
       </c>
       <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>Myskmadra
+Purpurknipprot
+Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="W55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26849-2026 artfynd.xlsx", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="X55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26849-2026 karta.png", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="Y55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26849-2026 georefererad karta.tif", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="AA55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26849-2026 FSC-klagomål.docx", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="AB55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26849-2026 FSC-klagomål mail.docx", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="AC55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26849-2026 tillsynsbegäran.docx", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="AD55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26849-2026 tillsynsbegäran mail.docx", "A 26849-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>A 27283-2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>2</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
+      <c r="S56" t="n">
+        <v>3</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Mindre poppelglasvinge
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27283-2026 artfynd.xlsx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="X56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27283-2026 karta.png", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="Y56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27283-2026 georefererad karta.tif", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AA56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27283-2026 FSC-klagomål.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AB56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27283-2026 FSC-klagomål mail.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AC56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27283-2026 tillsynsbegäran.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AD56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27283-2026 tillsynsbegäran mail.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>A 15285-2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Havsörn
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 15285-2026 artfynd.xlsx", "A 15285-2026")</f>
+        <v/>
+      </c>
+      <c r="X57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 15285-2026 karta.png", "A 15285-2026")</f>
+        <v/>
+      </c>
+      <c r="Y57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 15285-2026 georefererad karta.tif", "A 15285-2026")</f>
+        <v/>
+      </c>
+      <c r="AA57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 15285-2026 FSC-klagomål.docx", "A 15285-2026")</f>
+        <v/>
+      </c>
+      <c r="AB57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 15285-2026 FSC-klagomål mail.docx", "A 15285-2026")</f>
+        <v/>
+      </c>
+      <c r="AC57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 15285-2026 tillsynsbegäran.docx", "A 15285-2026")</f>
+        <v/>
+      </c>
+      <c r="AD57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 15285-2026 tillsynsbegäran mail.docx", "A 15285-2026")</f>
+        <v/>
+      </c>
+      <c r="AE57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 15285-2026 prioriterade fågelarter.docx", "A 15285-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>A 43756-2022</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>44837</v>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3</v>
+      </c>
+      <c r="T58" t="n">
         <v>5</v>
       </c>
-      <c r="U55" t="n">
+      <c r="U58" t="n">
         <v>5</v>
       </c>
-      <c r="V55" s="2" t="inlineStr">
+      <c r="V58" s="2" t="inlineStr">
         <is>
           <t>Murgröna
 Blåsippa
 Gullviva</t>
         </is>
       </c>
-      <c r="W55">
+      <c r="W58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 43756-2022 artfynd.xlsx", "A 43756-2022")</f>
         <v/>
       </c>
-      <c r="X55">
+      <c r="X58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 43756-2022 karta.png", "A 43756-2022")</f>
         <v/>
       </c>
-      <c r="Y55">
+      <c r="Y58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 43756-2022 georefererad karta.tif", "A 43756-2022")</f>
         <v/>
       </c>
-      <c r="AA55">
+      <c r="AA58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 43756-2022 FSC-klagomål.docx", "A 43756-2022")</f>
         <v/>
       </c>
-      <c r="AB55">
+      <c r="AB58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 43756-2022 FSC-klagomål mail.docx", "A 43756-2022")</f>
         <v/>
       </c>
-      <c r="AC55">
+      <c r="AC58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 43756-2022 tillsynsbegäran.docx", "A 43756-2022")</f>
         <v/>
       </c>
-      <c r="AD55">
+      <c r="AD58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 43756-2022 tillsynsbegäran mail.docx", "A 43756-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>A 27283-2026</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>A 31520-2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D56" s="1" t="n">
+      <c r="D59" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>3</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>3</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Grönsiska
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31520-2026 artfynd.xlsx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="X59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31520-2026 karta.png", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31520-2026 georefererad karta.tif", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31520-2026 FSC-klagomål.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31520-2026 FSC-klagomål mail.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31520-2026 tillsynsbegäran.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31520-2026 tillsynsbegäran mail.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AE59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 31520-2026 prioriterade fågelarter.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>A 24048-2025</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>45796</v>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>2</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>2</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>2</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>3</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>Loppstarr
+Ängsstarr
+Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="W60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24048-2025 artfynd.xlsx", "A 24048-2025")</f>
+        <v/>
+      </c>
+      <c r="X60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24048-2025 karta.png", "A 24048-2025")</f>
+        <v/>
+      </c>
+      <c r="Y60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24048-2025 georefererad karta.tif", "A 24048-2025")</f>
+        <v/>
+      </c>
+      <c r="AA60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24048-2025 FSC-klagomål.docx", "A 24048-2025")</f>
+        <v/>
+      </c>
+      <c r="AB60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24048-2025 FSC-klagomål mail.docx", "A 24048-2025")</f>
+        <v/>
+      </c>
+      <c r="AC60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24048-2025 tillsynsbegäran.docx", "A 24048-2025")</f>
+        <v/>
+      </c>
+      <c r="AD60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24048-2025 tillsynsbegäran mail.docx", "A 24048-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>S 846-2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E61" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J61" t="n">
+        <v>3</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>3</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Havsörn
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 846-2026 artfynd.xlsx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="X61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 846-2026 karta.png", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="Y61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 846-2026 georefererad karta.tif", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AA61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 846-2026 FSC-klagomål.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AB61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 846-2026 FSC-klagomål mail.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AC61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 846-2026 tillsynsbegäran.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AD61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 846-2026 tillsynsbegäran mail.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AE61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/S 846-2026 prioriterade fågelarter.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>S 1726-2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="n">
         <v>46188</v>
       </c>
-      <c r="E56" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F56" t="inlineStr">
+      <c r="E62" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I56" t="n">
+      <c r="I62" t="n">
         <v>2</v>
       </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" t="n">
-        <v>1</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
         <v>2</v>
       </c>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
-      <c r="S56" t="n">
+      <c r="R62" t="n">
+        <v>1</v>
+      </c>
+      <c r="S62" t="n">
         <v>3</v>
       </c>
-      <c r="T56" t="n">
+      <c r="T62" t="n">
         <v>3</v>
       </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" s="2" t="inlineStr">
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
         <is>
           <t>Ask
 Mindre poppelglasvinge
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27283-2026 artfynd.xlsx", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="X56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27283-2026 karta.png", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="Y56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27283-2026 georefererad karta.tif", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="AA56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27283-2026 FSC-klagomål.docx", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="AB56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27283-2026 FSC-klagomål mail.docx", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="AC56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27283-2026 tillsynsbegäran.docx", "A 27283-2026")</f>
-        <v/>
-      </c>
-      <c r="AD56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27283-2026 tillsynsbegäran mail.docx", "A 27283-2026")</f>
+      <c r="W62">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1726-2026 artfynd.xlsx", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="X62">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1726-2026 karta.png", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="Y62">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1726-2026 georefererad karta.tif", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="AA62">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1726-2026 FSC-klagomål.docx", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="AB62">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1726-2026 FSC-klagomål mail.docx", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="AC62">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1726-2026 tillsynsbegäran.docx", "S 1726-2026")</f>
+        <v/>
+      </c>
+      <c r="AD62">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1726-2026 tillsynsbegäran mail.docx", "S 1726-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>A 26849-2026</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="n">
-        <v>46185</v>
-      </c>
-      <c r="E57" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F57" t="inlineStr">
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>S 2059-2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E63" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I57" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J57" t="n">
-        <v>2</v>
-      </c>
-      <c r="K57" t="n">
+      <c r="I63" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J63" t="n">
         <v>3</v>
       </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
         <v>3</v>
       </c>
-      <c r="T57" t="n">
-        <v>3</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" s="2" t="inlineStr">
-        <is>
-          <t>Myskmadra
-Purpurknipprot
-Vit skogslilja</t>
-        </is>
-      </c>
-      <c r="W57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26849-2026 artfynd.xlsx", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="X57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26849-2026 karta.png", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="Y57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26849-2026 georefererad karta.tif", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="AA57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26849-2026 FSC-klagomål.docx", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="AB57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26849-2026 FSC-klagomål mail.docx", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="AC57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26849-2026 tillsynsbegäran.docx", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="AD57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26849-2026 tillsynsbegäran mail.docx", "A 26849-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>A 15285-2026</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E58" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I58" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J58" t="n">
-        <v>3</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>1</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>3</v>
-      </c>
-      <c r="T58" t="n">
-        <v>3</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Havsörn
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 15285-2026 artfynd.xlsx", "A 15285-2026")</f>
-        <v/>
-      </c>
-      <c r="X58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 15285-2026 karta.png", "A 15285-2026")</f>
-        <v/>
-      </c>
-      <c r="Y58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 15285-2026 georefererad karta.tif", "A 15285-2026")</f>
-        <v/>
-      </c>
-      <c r="AA58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 15285-2026 FSC-klagomål.docx", "A 15285-2026")</f>
-        <v/>
-      </c>
-      <c r="AB58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 15285-2026 FSC-klagomål mail.docx", "A 15285-2026")</f>
-        <v/>
-      </c>
-      <c r="AC58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 15285-2026 tillsynsbegäran.docx", "A 15285-2026")</f>
-        <v/>
-      </c>
-      <c r="AD58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 15285-2026 tillsynsbegäran mail.docx", "A 15285-2026")</f>
-        <v/>
-      </c>
-      <c r="AE58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 15285-2026 prioriterade fågelarter.docx", "A 15285-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>A 31520-2026</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E59" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J59" t="n">
-        <v>3</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>1</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>3</v>
-      </c>
-      <c r="T59" t="n">
+      <c r="T63" t="n">
         <v>4</v>
       </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" s="2" t="inlineStr">
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Grönsiska
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31520-2026 artfynd.xlsx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="X59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31520-2026 karta.png", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="Y59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31520-2026 georefererad karta.tif", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AA59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31520-2026 FSC-klagomål.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AB59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31520-2026 FSC-klagomål mail.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AC59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31520-2026 tillsynsbegäran.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AD59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31520-2026 tillsynsbegäran mail.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-      <c r="AE59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 31520-2026 prioriterade fågelarter.docx", "A 31520-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>A 24048-2025</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="n">
-        <v>45796</v>
-      </c>
-      <c r="E60" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>2</v>
-      </c>
-      <c r="J60" t="n">
-        <v>1</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>2</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>2</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="n">
-        <v>3</v>
-      </c>
-      <c r="T60" t="n">
-        <v>5</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" s="2" t="inlineStr">
-        <is>
-          <t>Loppstarr
-Ängsstarr
-Kärrknipprot</t>
-        </is>
-      </c>
-      <c r="W60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24048-2025 artfynd.xlsx", "A 24048-2025")</f>
-        <v/>
-      </c>
-      <c r="X60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24048-2025 karta.png", "A 24048-2025")</f>
-        <v/>
-      </c>
-      <c r="Y60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24048-2025 georefererad karta.tif", "A 24048-2025")</f>
-        <v/>
-      </c>
-      <c r="AA60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24048-2025 FSC-klagomål.docx", "A 24048-2025")</f>
-        <v/>
-      </c>
-      <c r="AB60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24048-2025 FSC-klagomål mail.docx", "A 24048-2025")</f>
-        <v/>
-      </c>
-      <c r="AC60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24048-2025 tillsynsbegäran.docx", "A 24048-2025")</f>
-        <v/>
-      </c>
-      <c r="AD60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24048-2025 tillsynsbegäran mail.docx", "A 24048-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>S 846-2026</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E61" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I61" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J61" t="n">
-        <v>3</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>1</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>1</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>3</v>
-      </c>
-      <c r="T61" t="n">
-        <v>3</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Havsörn
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 846-2026 artfynd.xlsx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="X61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 846-2026 karta.png", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="Y61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 846-2026 georefererad karta.tif", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AA61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 846-2026 FSC-klagomål.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AB61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 846-2026 FSC-klagomål mail.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AC61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 846-2026 tillsynsbegäran.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AD61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 846-2026 tillsynsbegäran mail.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-      <c r="AE61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/S 846-2026 prioriterade fågelarter.docx", "S 846-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>S 1726-2026</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E62" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I62" t="n">
-        <v>2</v>
-      </c>
-      <c r="J62" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" t="n">
-        <v>1</v>
-      </c>
-      <c r="L62" t="n">
-        <v>1</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>1</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>2</v>
-      </c>
-      <c r="R62" t="n">
-        <v>1</v>
-      </c>
-      <c r="S62" t="n">
-        <v>3</v>
-      </c>
-      <c r="T62" t="n">
-        <v>3</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Mindre poppelglasvinge
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1726-2026 artfynd.xlsx", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="X62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1726-2026 karta.png", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="Y62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1726-2026 georefererad karta.tif", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="AA62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1726-2026 FSC-klagomål.docx", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="AB62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1726-2026 FSC-klagomål mail.docx", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="AC62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1726-2026 tillsynsbegäran.docx", "S 1726-2026")</f>
-        <v/>
-      </c>
-      <c r="AD62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1726-2026 tillsynsbegäran mail.docx", "S 1726-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>S 2059-2026</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D63" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E63" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I63" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J63" t="n">
-        <v>3</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>1</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>1</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="n">
-        <v>3</v>
-      </c>
-      <c r="T63" t="n">
-        <v>4</v>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Grönsiska
-Kungsfågel</t>
-        </is>
-      </c>
       <c r="W63">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2059-2026 artfynd.xlsx", "S 2059-2026")</f>
         <v/>
@@ -7831,7 +7831,7 @@
         <v>44623</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 21908-2022</t>
+          <t>A 44678-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7934,10 +7934,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44711</v>
+        <v>44840</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>1</v>
       </c>
       <c r="K65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -7965,7 +7965,7 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -7974,10 +7974,10 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S65" t="n">
         <v>2</v>
@@ -7986,40 +7986,40 @@
         <v>2</v>
       </c>
       <c r="U65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra
+          <t>Ask
 Skogsknipprot</t>
         </is>
       </c>
       <c r="W65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21908-2022 artfynd.xlsx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 44678-2022 artfynd.xlsx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="X65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21908-2022 karta.png", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 44678-2022 karta.png", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="Y65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21908-2022 georefererad karta.tif", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 44678-2022 georefererad karta.tif", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AA65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21908-2022 FSC-klagomål.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 44678-2022 FSC-klagomål.docx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AB65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21908-2022 FSC-klagomål mail.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 44678-2022 FSC-klagomål mail.docx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AC65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21908-2022 tillsynsbegäran.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 44678-2022 tillsynsbegäran.docx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AD65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21908-2022 tillsynsbegäran mail.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 44678-2022 tillsynsbegäran mail.docx", "A 44678-2022")</f>
         <v/>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
         <v>45994</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>45994</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>46169</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 9253-2026</t>
+          <t>A 17699-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -8363,10 +8363,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46070</v>
+        <v>45758</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8379,16 +8379,16 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -8403,7 +8403,7 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -8415,47 +8415,47 @@
         <v>2</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>Murgröna
-Gullviva</t>
+          <t>Backtimjan
+Klibbveronika</t>
         </is>
       </c>
       <c r="W69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9253-2026 artfynd.xlsx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 17699-2025 artfynd.xlsx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="X69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9253-2026 karta.png", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 17699-2025 karta.png", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="Y69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9253-2026 georefererad karta.tif", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 17699-2025 georefererad karta.tif", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AA69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9253-2026 FSC-klagomål.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 17699-2025 FSC-klagomål.docx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AB69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9253-2026 FSC-klagomål mail.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 17699-2025 FSC-klagomål mail.docx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AC69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9253-2026 tillsynsbegäran.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 17699-2025 tillsynsbegäran.docx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AD69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9253-2026 tillsynsbegäran mail.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 17699-2025 tillsynsbegäran mail.docx", "A 17699-2025")</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 44678-2022</t>
+          <t>A 9253-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -8469,10 +8469,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44840</v>
+        <v>46070</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>1</v>
@@ -8500,7 +8500,7 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8509,10 +8509,10 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>2</v>
@@ -8521,47 +8521,47 @@
         <v>2</v>
       </c>
       <c r="U70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>Ask
-Skogsknipprot</t>
+          <t>Murgröna
+Gullviva</t>
         </is>
       </c>
       <c r="W70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 44678-2022 artfynd.xlsx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9253-2026 artfynd.xlsx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="X70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 44678-2022 karta.png", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9253-2026 karta.png", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="Y70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 44678-2022 georefererad karta.tif", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9253-2026 georefererad karta.tif", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AA70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 44678-2022 FSC-klagomål.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9253-2026 FSC-klagomål.docx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AB70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 44678-2022 FSC-klagomål mail.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9253-2026 FSC-klagomål mail.docx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AC70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 44678-2022 tillsynsbegäran.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9253-2026 tillsynsbegäran.docx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AD70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 44678-2022 tillsynsbegäran mail.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9253-2026 tillsynsbegäran mail.docx", "A 9253-2026")</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29411-2026</t>
+          <t>A 21908-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8571,14 +8571,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46203</v>
+        <v>44711</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8590,25 +8590,20 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J71" t="n">
         <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
@@ -8620,10 +8615,10 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>2</v>
@@ -8632,47 +8627,47 @@
         <v>2</v>
       </c>
       <c r="U71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare
-Ekoxe</t>
+          <t>Myskmadra
+Skogsknipprot</t>
         </is>
       </c>
       <c r="W71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 29411-2026 artfynd.xlsx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21908-2022 artfynd.xlsx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="X71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 29411-2026 karta.png", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21908-2022 karta.png", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="Y71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 29411-2026 georefererad karta.tif", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21908-2022 georefererad karta.tif", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AA71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 29411-2026 FSC-klagomål.docx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21908-2022 FSC-klagomål.docx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AB71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 29411-2026 FSC-klagomål mail.docx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21908-2022 FSC-klagomål mail.docx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AC71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 29411-2026 tillsynsbegäran.docx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21908-2022 tillsynsbegäran.docx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AD71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 29411-2026 tillsynsbegäran mail.docx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21908-2022 tillsynsbegäran mail.docx", "A 21908-2022")</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 17699-2025</t>
+          <t>A 29411-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8682,14 +8677,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45758</v>
+        <v>46203</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8701,20 +8696,25 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N72" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S72" t="n">
         <v>2</v>
@@ -8738,40 +8738,40 @@
         <v>2</v>
       </c>
       <c r="U72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan
-Klibbveronika</t>
+          <t>Bredbrämad bastardsvärmare
+Ekoxe</t>
         </is>
       </c>
       <c r="W72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 17699-2025 artfynd.xlsx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 29411-2026 artfynd.xlsx", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="X72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 17699-2025 karta.png", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 29411-2026 karta.png", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="Y72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 17699-2025 georefererad karta.tif", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 29411-2026 georefererad karta.tif", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="AA72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 17699-2025 FSC-klagomål.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 29411-2026 FSC-klagomål.docx", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="AB72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 17699-2025 FSC-klagomål mail.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 29411-2026 FSC-klagomål mail.docx", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="AC72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 17699-2025 tillsynsbegäran.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 29411-2026 tillsynsbegäran.docx", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="AD72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 17699-2025 tillsynsbegäran mail.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 29411-2026 tillsynsbegäran mail.docx", "A 29411-2026")</f>
         <v/>
       </c>
     </row>
@@ -8795,7 +8795,7 @@
         <v>44725</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>46203</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S 6144-2022</t>
+          <t>S 1650-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9005,14 +9005,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44865</v>
+        <v>44649</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9025,16 +9025,16 @@
         </is>
       </c>
       <c r="I75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
         <v>2</v>
       </c>
-      <c r="J75" t="n">
-        <v>1</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -9049,7 +9049,7 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -9058,50 +9058,50 @@
         <v>2</v>
       </c>
       <c r="T75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>Oxtungssvamp
-Fläcknycklar</t>
+          <t>Guldlockmossa
+Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="W75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 6144-2022 artfynd.xlsx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1650-2022 artfynd.xlsx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="X75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 6144-2022 karta.png", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1650-2022 karta.png", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="Y75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 6144-2022 georefererad karta.tif", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1650-2022 georefererad karta.tif", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AA75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 6144-2022 FSC-klagomål.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1650-2022 FSC-klagomål.docx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AB75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 6144-2022 FSC-klagomål mail.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1650-2022 FSC-klagomål mail.docx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AC75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 6144-2022 tillsynsbegäran.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1650-2022 tillsynsbegäran.docx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AD75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 6144-2022 tillsynsbegäran mail.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1650-2022 tillsynsbegäran mail.docx", "S 1650-2022")</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S 1650-2022</t>
+          <t>S 6144-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9111,14 +9111,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44649</v>
+        <v>44865</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9131,16 +9131,16 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -9155,7 +9155,7 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
@@ -9164,43 +9164,43 @@
         <v>2</v>
       </c>
       <c r="T76" t="n">
+        <v>3</v>
+      </c>
+      <c r="U76" t="n">
         <v>2</v>
       </c>
-      <c r="U76" t="n">
-        <v>0</v>
-      </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa
-Gulpudrad spiklav</t>
+          <t>Oxtungssvamp
+Fläcknycklar</t>
         </is>
       </c>
       <c r="W76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1650-2022 artfynd.xlsx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 6144-2022 artfynd.xlsx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="X76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1650-2022 karta.png", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 6144-2022 karta.png", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="Y76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1650-2022 georefererad karta.tif", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 6144-2022 georefererad karta.tif", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AA76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1650-2022 FSC-klagomål.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 6144-2022 FSC-klagomål.docx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AB76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1650-2022 FSC-klagomål mail.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 6144-2022 FSC-klagomål mail.docx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AC76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1650-2022 tillsynsbegäran.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 6144-2022 tillsynsbegäran.docx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AD76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1650-2022 tillsynsbegäran mail.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 6144-2022 tillsynsbegäran mail.docx", "S 6144-2022")</f>
         <v/>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
         <v>46203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>46203</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>44772</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44781</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 24701-2023</t>
+          <t>A 20878-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9663,10 +9663,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45084</v>
+        <v>45439</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -9694,7 +9694,7 @@
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -9703,58 +9703,58 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
       </c>
       <c r="T81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24701-2023 artfynd.xlsx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 20878-2024 artfynd.xlsx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="X81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24701-2023 karta.png", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 20878-2024 karta.png", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="Y81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24701-2023 georefererad karta.tif", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 20878-2024 georefererad karta.tif", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AA81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24701-2023 FSC-klagomål.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 20878-2024 FSC-klagomål.docx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AB81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24701-2023 FSC-klagomål mail.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 20878-2024 FSC-klagomål mail.docx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AC81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24701-2023 tillsynsbegäran.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 20878-2024 tillsynsbegäran.docx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AD81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24701-2023 tillsynsbegäran mail.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 20878-2024 tillsynsbegäran mail.docx", "A 20878-2024")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 63276-2023</t>
+          <t>A 9745-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9768,10 +9768,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45273</v>
+        <v>44984</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9784,19 +9784,19 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
         <v>0</v>
@@ -9808,58 +9808,58 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
       </c>
       <c r="T82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>Elaphomyces barrioi</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 63276-2023 artfynd.xlsx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9745-2023 artfynd.xlsx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="X82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 63276-2023 karta.png", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9745-2023 karta.png", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="Y82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 63276-2023 georefererad karta.tif", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9745-2023 georefererad karta.tif", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AA82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 63276-2023 FSC-klagomål.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9745-2023 FSC-klagomål.docx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AB82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 63276-2023 FSC-klagomål mail.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9745-2023 FSC-klagomål mail.docx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AC82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 63276-2023 tillsynsbegäran.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9745-2023 tillsynsbegäran.docx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AD82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 63276-2023 tillsynsbegäran mail.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9745-2023 tillsynsbegäran mail.docx", "A 9745-2023")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 24704-2023</t>
+          <t>A 31720-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9873,10 +9873,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45084</v>
+        <v>44776</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9888,14 +9888,19 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -9904,7 +9909,7 @@
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -9913,51 +9918,51 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>
       </c>
       <c r="T83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24704-2023 artfynd.xlsx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31720-2022 artfynd.xlsx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="X83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24704-2023 karta.png", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31720-2022 karta.png", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="Y83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24704-2023 georefererad karta.tif", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31720-2022 georefererad karta.tif", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AA83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24704-2023 FSC-klagomål.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31720-2022 FSC-klagomål.docx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AB83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24704-2023 FSC-klagomål mail.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31720-2022 FSC-klagomål mail.docx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AC83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24704-2023 tillsynsbegäran.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31720-2022 tillsynsbegäran.docx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AD83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24704-2023 tillsynsbegäran mail.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31720-2022 tillsynsbegäran mail.docx", "A 31720-2022")</f>
         <v/>
       </c>
     </row>
@@ -9981,7 +9986,7 @@
         <v>45902</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10069,7 +10074,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 9745-2023</t>
+          <t>A 24701-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10083,10 +10088,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44984</v>
+        <v>45084</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10099,13 +10104,13 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -10114,7 +10119,7 @@
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10123,58 +10128,58 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
       </c>
       <c r="T85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9745-2023 artfynd.xlsx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24701-2023 artfynd.xlsx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="X85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9745-2023 karta.png", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24701-2023 karta.png", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="Y85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9745-2023 georefererad karta.tif", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24701-2023 georefererad karta.tif", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AA85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9745-2023 FSC-klagomål.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24701-2023 FSC-klagomål.docx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AB85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9745-2023 FSC-klagomål mail.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24701-2023 FSC-klagomål mail.docx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AC85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9745-2023 tillsynsbegäran.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24701-2023 tillsynsbegäran.docx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AD85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9745-2023 tillsynsbegäran mail.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24701-2023 tillsynsbegäran mail.docx", "A 24701-2023")</f>
         <v/>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3302-2026</t>
+          <t>A 24704-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10184,14 +10189,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46041</v>
+        <v>45084</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10204,10 +10209,10 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -10219,7 +10224,7 @@
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10228,58 +10233,58 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S86" t="n">
         <v>1</v>
       </c>
       <c r="T86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 3302-2026 artfynd.xlsx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24704-2023 artfynd.xlsx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="X86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 3302-2026 karta.png", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24704-2023 karta.png", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="Y86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 3302-2026 georefererad karta.tif", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24704-2023 georefererad karta.tif", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AA86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 3302-2026 FSC-klagomål.docx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24704-2023 FSC-klagomål.docx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AB86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 3302-2026 FSC-klagomål mail.docx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24704-2023 FSC-klagomål mail.docx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AC86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 3302-2026 tillsynsbegäran.docx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24704-2023 tillsynsbegäran.docx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AD86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 3302-2026 tillsynsbegäran mail.docx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24704-2023 tillsynsbegäran mail.docx", "A 24704-2023")</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 7481-2026</t>
+          <t>A 3302-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10289,14 +10294,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46059</v>
+        <v>46041</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10309,7 +10314,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J87" t="n">
         <v>1</v>
@@ -10342,49 +10347,49 @@
         <v>1</v>
       </c>
       <c r="T87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 7481-2026 artfynd.xlsx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 3302-2026 artfynd.xlsx", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="X87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 7481-2026 karta.png", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 3302-2026 karta.png", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="Y87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 7481-2026 georefererad karta.tif", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 3302-2026 georefererad karta.tif", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="AA87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 7481-2026 FSC-klagomål.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 3302-2026 FSC-klagomål.docx", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="AB87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 7481-2026 FSC-klagomål mail.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 3302-2026 FSC-klagomål mail.docx", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="AC87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 7481-2026 tillsynsbegäran.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 3302-2026 tillsynsbegäran.docx", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="AD87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 7481-2026 tillsynsbegäran mail.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 3302-2026 tillsynsbegäran mail.docx", "A 3302-2026")</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 9104-2026</t>
+          <t>A 7481-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10394,14 +10399,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46069</v>
+        <v>46059</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10414,10 +10419,10 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -10447,49 +10452,49 @@
         <v>1</v>
       </c>
       <c r="T88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9104-2026 artfynd.xlsx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 7481-2026 artfynd.xlsx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="X88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9104-2026 karta.png", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 7481-2026 karta.png", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="Y88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9104-2026 georefererad karta.tif", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 7481-2026 georefererad karta.tif", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AA88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9104-2026 FSC-klagomål.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 7481-2026 FSC-klagomål.docx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AB88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9104-2026 FSC-klagomål mail.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 7481-2026 FSC-klagomål mail.docx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AC88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9104-2026 tillsynsbegäran.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 7481-2026 tillsynsbegäran.docx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AD88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9104-2026 tillsynsbegäran mail.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 7481-2026 tillsynsbegäran mail.docx", "A 7481-2026")</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 9905-2026</t>
+          <t>A 9104-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10499,14 +10504,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46073</v>
+        <v>46069</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10519,7 +10524,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -10534,7 +10539,7 @@
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -10543,10 +10548,10 @@
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>1</v>
@@ -10555,39 +10560,39 @@
         <v>1</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="W89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9905-2026 artfynd.xlsx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9104-2026 artfynd.xlsx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="X89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9905-2026 karta.png", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9104-2026 karta.png", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="Y89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9905-2026 georefererad karta.tif", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9104-2026 georefererad karta.tif", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AA89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9905-2026 FSC-klagomål.docx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9104-2026 FSC-klagomål.docx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AB89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9905-2026 FSC-klagomål mail.docx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9104-2026 FSC-klagomål mail.docx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AC89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9905-2026 tillsynsbegäran.docx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9104-2026 tillsynsbegäran.docx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AD89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9905-2026 tillsynsbegäran mail.docx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9104-2026 tillsynsbegäran mail.docx", "A 9104-2026")</f>
         <v/>
       </c>
     </row>
@@ -10611,7 +10616,7 @@
         <v>46185</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10704,7 +10709,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 31720-2022</t>
+          <t>A 9905-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10718,10 +10723,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44776</v>
+        <v>46073</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10733,19 +10738,14 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -10754,7 +10754,7 @@
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -10763,10 +10763,10 @@
         <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S91" t="n">
         <v>1</v>
@@ -10775,46 +10775,46 @@
         <v>1</v>
       </c>
       <c r="U91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31720-2022 artfynd.xlsx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9905-2026 artfynd.xlsx", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="X91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31720-2022 karta.png", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9905-2026 karta.png", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="Y91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31720-2022 georefererad karta.tif", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9905-2026 georefererad karta.tif", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="AA91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31720-2022 FSC-klagomål.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9905-2026 FSC-klagomål.docx", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="AB91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31720-2022 FSC-klagomål mail.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9905-2026 FSC-klagomål mail.docx", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="AC91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31720-2022 tillsynsbegäran.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9905-2026 tillsynsbegäran.docx", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="AD91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31720-2022 tillsynsbegäran mail.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9905-2026 tillsynsbegäran mail.docx", "A 9905-2026")</f>
         <v/>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 19867-2024</t>
+          <t>A 28430-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10824,14 +10824,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45433</v>
+        <v>46197</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10843,8 +10843,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -10877,42 +10882,42 @@
         <v>1</v>
       </c>
       <c r="T92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>Åkerkulla</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="W92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 19867-2024 artfynd.xlsx", "A 19867-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28430-2026 artfynd.xlsx", "A 28430-2026")</f>
         <v/>
       </c>
       <c r="X92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 19867-2024 karta.png", "A 19867-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28430-2026 karta.png", "A 28430-2026")</f>
         <v/>
       </c>
       <c r="Y92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 19867-2024 georefererad karta.tif", "A 19867-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28430-2026 georefererad karta.tif", "A 28430-2026")</f>
         <v/>
       </c>
       <c r="AA92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 19867-2024 FSC-klagomål.docx", "A 19867-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28430-2026 FSC-klagomål.docx", "A 28430-2026")</f>
         <v/>
       </c>
       <c r="AB92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 19867-2024 FSC-klagomål mail.docx", "A 19867-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28430-2026 FSC-klagomål mail.docx", "A 28430-2026")</f>
         <v/>
       </c>
       <c r="AC92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 19867-2024 tillsynsbegäran.docx", "A 19867-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28430-2026 tillsynsbegäran.docx", "A 28430-2026")</f>
         <v/>
       </c>
       <c r="AD92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 19867-2024 tillsynsbegäran mail.docx", "A 19867-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28430-2026 tillsynsbegäran mail.docx", "A 28430-2026")</f>
         <v/>
       </c>
     </row>
@@ -10936,7 +10941,7 @@
         <v>46196</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11029,7 +11034,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 28430-2026</t>
+          <t>A 19867-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -11039,14 +11044,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46197</v>
+        <v>45433</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11058,13 +11063,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -11097,49 +11097,49 @@
         <v>1</v>
       </c>
       <c r="T94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Åkerkulla</t>
         </is>
       </c>
       <c r="W94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28430-2026 artfynd.xlsx", "A 28430-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 19867-2024 artfynd.xlsx", "A 19867-2024")</f>
         <v/>
       </c>
       <c r="X94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28430-2026 karta.png", "A 28430-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 19867-2024 karta.png", "A 19867-2024")</f>
         <v/>
       </c>
       <c r="Y94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28430-2026 georefererad karta.tif", "A 28430-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 19867-2024 georefererad karta.tif", "A 19867-2024")</f>
         <v/>
       </c>
       <c r="AA94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28430-2026 FSC-klagomål.docx", "A 28430-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 19867-2024 FSC-klagomål.docx", "A 19867-2024")</f>
         <v/>
       </c>
       <c r="AB94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28430-2026 FSC-klagomål mail.docx", "A 28430-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 19867-2024 FSC-klagomål mail.docx", "A 19867-2024")</f>
         <v/>
       </c>
       <c r="AC94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28430-2026 tillsynsbegäran.docx", "A 28430-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 19867-2024 tillsynsbegäran.docx", "A 19867-2024")</f>
         <v/>
       </c>
       <c r="AD94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28430-2026 tillsynsbegäran mail.docx", "A 28430-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 19867-2024 tillsynsbegäran mail.docx", "A 19867-2024")</f>
         <v/>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 13043-2024</t>
+          <t>A 63276-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -11153,10 +11153,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45385</v>
+        <v>45273</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11169,19 +11169,19 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N95" t="n">
         <v>0</v>
@@ -11193,10 +11193,10 @@
         <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S95" t="n">
         <v>1</v>
@@ -11209,42 +11209,42 @@
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Elaphomyces barrioi</t>
         </is>
       </c>
       <c r="W95">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 13043-2024 artfynd.xlsx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 63276-2023 artfynd.xlsx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="X95">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 13043-2024 karta.png", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 63276-2023 karta.png", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="Y95">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 13043-2024 georefererad karta.tif", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 63276-2023 georefererad karta.tif", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AA95">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 13043-2024 FSC-klagomål.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 63276-2023 FSC-klagomål.docx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AB95">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 13043-2024 FSC-klagomål mail.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 63276-2023 FSC-klagomål mail.docx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AC95">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 13043-2024 tillsynsbegäran.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 63276-2023 tillsynsbegäran.docx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AD95">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 13043-2024 tillsynsbegäran mail.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 63276-2023 tillsynsbegäran mail.docx", "A 63276-2023")</f>
         <v/>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 20878-2024</t>
+          <t>A 33293-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -11254,14 +11254,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45439</v>
+        <v>46246</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11273,14 +11273,19 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J96" t="n">
         <v>1</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -11314,42 +11319,42 @@
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 20878-2024 artfynd.xlsx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 33293-2026 artfynd.xlsx", "A 33293-2026")</f>
         <v/>
       </c>
       <c r="X96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 20878-2024 karta.png", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 33293-2026 karta.png", "A 33293-2026")</f>
         <v/>
       </c>
       <c r="Y96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 20878-2024 georefererad karta.tif", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 33293-2026 georefererad karta.tif", "A 33293-2026")</f>
         <v/>
       </c>
       <c r="AA96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 20878-2024 FSC-klagomål.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 33293-2026 FSC-klagomål.docx", "A 33293-2026")</f>
         <v/>
       </c>
       <c r="AB96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 20878-2024 FSC-klagomål mail.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 33293-2026 FSC-klagomål mail.docx", "A 33293-2026")</f>
         <v/>
       </c>
       <c r="AC96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 20878-2024 tillsynsbegäran.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 33293-2026 tillsynsbegäran.docx", "A 33293-2026")</f>
         <v/>
       </c>
       <c r="AD96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 20878-2024 tillsynsbegäran mail.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 33293-2026 tillsynsbegäran mail.docx", "A 33293-2026")</f>
         <v/>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 33293-2026</t>
+          <t>A 13043-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -11359,14 +11364,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46246</v>
+        <v>45385</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11378,13 +11383,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="J97" t="n">
         <v>1</v>
@@ -11417,49 +11417,49 @@
         <v>1</v>
       </c>
       <c r="T97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 33293-2026 artfynd.xlsx", "A 33293-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 13043-2024 artfynd.xlsx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="X97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 33293-2026 karta.png", "A 33293-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 13043-2024 karta.png", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="Y97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 33293-2026 georefererad karta.tif", "A 33293-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 13043-2024 georefererad karta.tif", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AA97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 33293-2026 FSC-klagomål.docx", "A 33293-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 13043-2024 FSC-klagomål.docx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AB97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 33293-2026 FSC-klagomål mail.docx", "A 33293-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 13043-2024 FSC-klagomål mail.docx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AC97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 33293-2026 tillsynsbegäran.docx", "A 33293-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 13043-2024 tillsynsbegäran.docx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AD97">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 33293-2026 tillsynsbegäran mail.docx", "A 33293-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 13043-2024 tillsynsbegäran mail.docx", "A 13043-2024")</f>
         <v/>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 28785-2025</t>
+          <t>A 28782-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -11476,7 +11476,7 @@
         <v>45820</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>1</v>
@@ -11538,42 +11538,42 @@
         </is>
       </c>
       <c r="W98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28785-2025 artfynd.xlsx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28782-2025 artfynd.xlsx", "A 28782-2025")</f>
         <v/>
       </c>
       <c r="X98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28785-2025 karta.png", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28782-2025 karta.png", "A 28782-2025")</f>
         <v/>
       </c>
       <c r="Y98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28785-2025 georefererad karta.tif", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28782-2025 georefererad karta.tif", "A 28782-2025")</f>
         <v/>
       </c>
       <c r="AA98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28785-2025 FSC-klagomål.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28782-2025 FSC-klagomål.docx", "A 28782-2025")</f>
         <v/>
       </c>
       <c r="AB98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28785-2025 FSC-klagomål mail.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28782-2025 FSC-klagomål mail.docx", "A 28782-2025")</f>
         <v/>
       </c>
       <c r="AC98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28785-2025 tillsynsbegäran.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28782-2025 tillsynsbegäran.docx", "A 28782-2025")</f>
         <v/>
       </c>
       <c r="AD98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28785-2025 tillsynsbegäran mail.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28782-2025 tillsynsbegäran mail.docx", "A 28782-2025")</f>
         <v/>
       </c>
       <c r="AE98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 28785-2025 prioriterade fågelarter.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 28782-2025 prioriterade fågelarter.docx", "A 28782-2025")</f>
         <v/>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 28782-2025</t>
+          <t>A 28785-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -11590,7 +11590,7 @@
         <v>45820</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J99" t="n">
         <v>1</v>
@@ -11652,35 +11652,35 @@
         </is>
       </c>
       <c r="W99">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28782-2025 artfynd.xlsx", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28785-2025 artfynd.xlsx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="X99">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28782-2025 karta.png", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28785-2025 karta.png", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="Y99">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28782-2025 georefererad karta.tif", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28785-2025 georefererad karta.tif", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AA99">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28782-2025 FSC-klagomål.docx", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28785-2025 FSC-klagomål.docx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AB99">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28782-2025 FSC-klagomål mail.docx", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28785-2025 FSC-klagomål mail.docx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AC99">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28782-2025 tillsynsbegäran.docx", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28785-2025 tillsynsbegäran.docx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AD99">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28782-2025 tillsynsbegäran mail.docx", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28785-2025 tillsynsbegäran mail.docx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AE99">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 28782-2025 prioriterade fågelarter.docx", "A 28782-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 28785-2025 prioriterade fågelarter.docx", "A 28785-2025")</f>
         <v/>
       </c>
     </row>
@@ -11704,7 +11704,7 @@
         <v>45111</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45903</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>46185</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S 1803-2026</t>
+          <t>S 1813-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -12025,10 +12025,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12046,82 +12046,82 @@
         </is>
       </c>
       <c r="I103" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>1</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>1</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="n">
+        <v>1</v>
+      </c>
+      <c r="T103" t="n">
         <v>2</v>
       </c>
-      <c r="J103" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" t="n">
-        <v>1</v>
-      </c>
-      <c r="N103" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>1</v>
-      </c>
-      <c r="R103" t="n">
-        <v>1</v>
-      </c>
-      <c r="S103" t="n">
-        <v>1</v>
-      </c>
-      <c r="T103" t="n">
-        <v>1</v>
-      </c>
       <c r="U103" t="n">
         <v>0</v>
       </c>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>Purpurmusseron</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="W103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1803-2026 artfynd.xlsx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1813-2026 artfynd.xlsx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="X103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1803-2026 karta.png", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1813-2026 karta.png", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="Y103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1803-2026 georefererad karta.tif", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1813-2026 georefererad karta.tif", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AA103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1803-2026 FSC-klagomål.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1813-2026 FSC-klagomål.docx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AB103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1803-2026 FSC-klagomål mail.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1813-2026 FSC-klagomål mail.docx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AC103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1803-2026 tillsynsbegäran.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1813-2026 tillsynsbegäran.docx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AD103">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1803-2026 tillsynsbegäran mail.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1813-2026 tillsynsbegäran mail.docx", "S 1813-2026")</f>
         <v/>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S 1813-2026</t>
+          <t>S 1803-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -12135,10 +12135,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -12165,10 +12165,10 @@
         <v>0</v>
       </c>
       <c r="L104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N104" t="n">
         <v>0</v>
@@ -12183,48 +12183,48 @@
         <v>1</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S104" t="n">
         <v>1</v>
       </c>
       <c r="T104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Purpurmusseron</t>
         </is>
       </c>
       <c r="W104">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1813-2026 artfynd.xlsx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1803-2026 artfynd.xlsx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="X104">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1813-2026 karta.png", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1803-2026 karta.png", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="Y104">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1813-2026 georefererad karta.tif", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1803-2026 georefererad karta.tif", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AA104">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1813-2026 FSC-klagomål.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1803-2026 FSC-klagomål.docx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AB104">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1813-2026 FSC-klagomål mail.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1803-2026 FSC-klagomål mail.docx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AC104">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1813-2026 tillsynsbegäran.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1803-2026 tillsynsbegäran.docx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AD104">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1813-2026 tillsynsbegäran mail.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1803-2026 tillsynsbegäran mail.docx", "S 1803-2026")</f>
         <v/>
       </c>
     </row>
@@ -12248,7 +12248,7 @@
         <v>46246</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>44783</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>44747</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>44840</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>44783</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>44501</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>44742</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>44503</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 3878-2023</t>
+          <t>A 31699-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -12876,10 +12876,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44951</v>
+        <v>44776</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12891,8 +12891,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -12935,7 +12940,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 12937-2022</t>
+          <t>A 26160-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12945,14 +12950,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44642</v>
+        <v>45468</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12964,13 +12969,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -13009,11 +13009,35 @@
         <v>0</v>
       </c>
       <c r="V114" s="2" t="inlineStr"/>
+      <c r="X114">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26160-2024 karta.png", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="Y114">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26160-2024 georefererad karta.tif", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AA114">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26160-2024 FSC-klagomål.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AB114">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26160-2024 FSC-klagomål mail.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AC114">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26160-2024 tillsynsbegäran.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AD114">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26160-2024 tillsynsbegäran mail.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 55367-2024</t>
+          <t>A 4159-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -13027,10 +13051,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45621</v>
+        <v>45323</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13043,7 +13067,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -13086,7 +13110,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 4159-2024</t>
+          <t>A 4165-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -13100,10 +13124,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45323</v>
+        <v>44953</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13116,7 +13140,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -13176,7 +13200,7 @@
         <v>45125</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13232,7 +13256,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 31699-2022</t>
+          <t>A 41950-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13246,10 +13270,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44776</v>
+        <v>45903</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13261,13 +13285,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -13310,7 +13329,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 1614-2025</t>
+          <t>A 45869-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -13324,10 +13343,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45670</v>
+        <v>45923</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13340,7 +13359,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -13383,7 +13402,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 41950-2025</t>
+          <t>A 46845-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -13393,14 +13412,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45903</v>
+        <v>45928</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13413,7 +13432,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -13456,7 +13475,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 9076-2025</t>
+          <t>A 43603-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -13470,10 +13489,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45713</v>
+        <v>45569</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13485,13 +13504,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -13534,7 +13548,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 45869-2025</t>
+          <t>A 63075-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -13544,14 +13558,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45923</v>
+        <v>45273</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13564,7 +13578,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -13607,7 +13621,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 1757-2025</t>
+          <t>A 27357-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -13617,14 +13631,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45671</v>
+        <v>45812</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13636,8 +13650,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -13680,7 +13699,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 46845-2025</t>
+          <t>A 7669-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -13690,14 +13709,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45928</v>
+        <v>45348</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13710,7 +13729,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -13753,7 +13772,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 27357-2025</t>
+          <t>A 1757-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -13763,14 +13782,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45812</v>
+        <v>45671</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13782,13 +13801,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -13831,7 +13845,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 7669-2024</t>
+          <t>A 24323-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -13845,10 +13859,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45348</v>
+        <v>46169</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13860,8 +13874,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -13904,7 +13923,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 9050-2025</t>
+          <t>A 34780-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -13914,14 +13933,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45713</v>
+        <v>44795</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13939,7 +13958,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.5</v>
+        <v>6.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -13982,7 +14001,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 43603-2024</t>
+          <t>A 55367-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -13996,10 +14015,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45569</v>
+        <v>45621</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14012,7 +14031,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -14055,7 +14074,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 24323-2026</t>
+          <t>A 20287-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -14065,14 +14084,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46169</v>
+        <v>45774</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14082,11 +14101,6 @@
       <c r="G129" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I129" t="n">
@@ -14133,7 +14147,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 9259-2026</t>
+          <t>A 9076-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -14147,10 +14161,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46070</v>
+        <v>45713</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14162,8 +14176,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -14223,7 +14242,7 @@
         <v>45125</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14279,7 +14298,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 5175-2024</t>
+          <t>A 9259-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -14293,10 +14312,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45330</v>
+        <v>46070</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14309,7 +14328,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -14369,7 +14388,7 @@
         <v>44796</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14430,7 +14449,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 15272-2026</t>
+          <t>A 5175-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -14440,14 +14459,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46105</v>
+        <v>45330</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14459,13 +14478,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -14508,7 +14522,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 15264-2026</t>
+          <t>A 28380-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -14522,10 +14536,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46105</v>
+        <v>46196</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14543,7 +14557,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -14586,7 +14600,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 28381-2026</t>
+          <t>A 15272-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -14600,10 +14614,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46196</v>
+        <v>46105</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14621,7 +14635,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -14664,7 +14678,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 28380-2026</t>
+          <t>A 15264-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -14678,10 +14692,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46196</v>
+        <v>46105</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14699,7 +14713,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -14742,7 +14756,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 28411-2026</t>
+          <t>A 28381-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -14756,10 +14770,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14820,7 +14834,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 13383-2023</t>
+          <t>A 28411-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -14830,14 +14844,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45005</v>
+        <v>46197</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14849,8 +14863,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -14893,7 +14912,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 61438-2023</t>
+          <t>A 29413-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -14903,14 +14922,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45264</v>
+        <v>46203</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14922,8 +14941,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -14966,7 +14990,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 13041-2024</t>
+          <t>A 29414-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -14976,14 +15000,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45385</v>
+        <v>46203</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14995,8 +15019,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -15039,7 +15068,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 4165-2023</t>
+          <t>A 29431-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -15049,14 +15078,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44953</v>
+        <v>46203</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15068,8 +15097,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -15112,7 +15146,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 29413-2026</t>
+          <t>A 29410-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -15129,7 +15163,7 @@
         <v>46203</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15147,7 +15181,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -15190,7 +15224,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 29414-2026</t>
+          <t>A 3878-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -15200,14 +15234,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46203</v>
+        <v>44951</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15219,13 +15253,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -15268,7 +15297,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 29431-2026</t>
+          <t>A 13383-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -15278,14 +15307,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46203</v>
+        <v>45005</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15297,13 +15326,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -15346,7 +15370,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 29410-2026</t>
+          <t>A 12937-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -15356,14 +15380,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46203</v>
+        <v>44642</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15381,7 +15405,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -15424,7 +15448,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 34780-2022</t>
+          <t>A 61438-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -15434,14 +15458,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44795</v>
+        <v>45264</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15453,13 +15477,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>6.7</v>
+        <v>1.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -15502,7 +15521,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 20287-2025</t>
+          <t>A 13041-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -15512,14 +15531,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45774</v>
+        <v>45385</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15532,7 +15551,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -15575,7 +15594,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 26160-2024</t>
+          <t>A 1614-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -15585,14 +15604,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45468</v>
+        <v>45670</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15605,7 +15624,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -15644,35 +15663,11 @@
         <v>0</v>
       </c>
       <c r="V149" s="2" t="inlineStr"/>
-      <c r="X149">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26160-2024 karta.png", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="Y149">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26160-2024 georefererad karta.tif", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AA149">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26160-2024 FSC-klagomål.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AB149">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26160-2024 FSC-klagomål mail.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AC149">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26160-2024 tillsynsbegäran.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AD149">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26160-2024 tillsynsbegäran mail.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
     </row>
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 24338-2026</t>
+          <t>A 9050-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -15686,10 +15681,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46169</v>
+        <v>45713</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15707,7 +15702,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -15750,7 +15745,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 63075-2023</t>
+          <t>A 24338-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -15760,14 +15755,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45273</v>
+        <v>46169</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15777,6 +15772,11 @@
       <c r="G151" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I151" t="n">
@@ -15840,7 +15840,7 @@
         <v>45789</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45169</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>45805</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>45867</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>44756</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>45713</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>45812</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>45812</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>45754</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>46105</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>46105</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>46169</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>S 1806-2026</t>
+          <t>S 1812-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -16748,10 +16748,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -16812,7 +16812,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S 1807-2026</t>
+          <t>S 1806-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -16829,7 +16829,7 @@
         <v>46196</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -16890,7 +16890,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S 1812-2026</t>
+          <t>S 1807-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -16904,10 +16904,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>46203</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>46203</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>46203</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>46203</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>

--- a/Översikt BORGHOLM.xlsx
+++ b/Översikt BORGHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45029</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>44704</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45433</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>44903</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45903</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>46254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 37421-2022</t>
+          <t>A 45006-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44809</v>
+        <v>45918</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2074,19 +2074,19 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.4</v>
+        <v>7.8</v>
       </c>
       <c r="J13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
+        <v>6</v>
+      </c>
+      <c r="L13" t="n">
         <v>5</v>
       </c>
-      <c r="L13" t="n">
-        <v>4</v>
-      </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2098,21 +2098,140 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
       </c>
       <c r="T13" t="n">
+        <v>22</v>
+      </c>
+      <c r="U13" t="n">
+        <v>21</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Skogskorn
+Axveronika
+Kattfotslav
+Mindre ekbock
+Skugglosta
+Vårstarr
+Gulpudrad spiklav
+Murgröna
+Myskmadra
+Skogsknipprot
+Tvåblad
+Vit skogslilja
+Johannesnycklar
+Krutbrännare
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 45006-2025 artfynd.xlsx", "A 45006-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 45006-2025 karta.png", "A 45006-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 45006-2025 georefererad karta.tif", "A 45006-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 45006-2025 FSC-klagomål.docx", "A 45006-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 45006-2025 FSC-klagomål mail.docx", "A 45006-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 45006-2025 tillsynsbegäran.docx", "A 45006-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 45006-2025 tillsynsbegäran mail.docx", "A 45006-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 37421-2022</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>44809</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="n">
         <v>37</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>33</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Höstlåsbräken
 Loppstarr
@@ -2131,155 +2250,36 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 37421-2022 artfynd.xlsx", "A 37421-2022")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 37421-2022 karta.png", "A 37421-2022")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 37421-2022 georefererad karta.tif", "A 37421-2022")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 37421-2022 FSC-klagomål.docx", "A 37421-2022")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 37421-2022 FSC-klagomål mail.docx", "A 37421-2022")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 37421-2022 tillsynsbegäran.docx", "A 37421-2022")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 37421-2022 tillsynsbegäran mail.docx", "A 37421-2022")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 37421-2022 prioriterade fågelarter.docx", "A 37421-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 45006-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45918</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>6</v>
-      </c>
-      <c r="L14" t="n">
-        <v>5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>15</v>
-      </c>
-      <c r="T14" t="n">
-        <v>22</v>
-      </c>
-      <c r="U14" t="n">
-        <v>21</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Skogskorn
-Axveronika
-Kattfotslav
-Mindre ekbock
-Skugglosta
-Vårstarr
-Gulpudrad spiklav
-Murgröna
-Myskmadra
-Skogsknipprot
-Tvåblad
-Vit skogslilja
-Johannesnycklar
-Krutbrännare
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 45006-2025 artfynd.xlsx", "A 45006-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 45006-2025 karta.png", "A 45006-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 45006-2025 georefererad karta.tif", "A 45006-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 45006-2025 FSC-klagomål.docx", "A 45006-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 45006-2025 FSC-klagomål mail.docx", "A 45006-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 45006-2025 tillsynsbegäran.docx", "A 45006-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 45006-2025 tillsynsbegäran mail.docx", "A 45006-2025")</f>
         <v/>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
         <v>46307</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45918</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>44523</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>45107</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>44781</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>45161</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>45146</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>45930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 13558-2025</t>
+          <t>A 12534-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45736</v>
+        <v>44638</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3364,19 +3364,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>8.6</v>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3391,18 +3391,130 @@
         <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
       </c>
       <c r="T24" t="n">
+        <v>9</v>
+      </c>
+      <c r="U24" t="n">
+        <v>9</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Backklöver
+Backtimjan
+Jordtistel
+Sårläka
+Vårstarr
+Krutbrännare
+Nattviol
+Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 12534-2022 artfynd.xlsx", "A 12534-2022")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 12534-2022 karta.png", "A 12534-2022")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 12534-2022 georefererad karta.tif", "A 12534-2022")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 12534-2022 FSC-klagomål.docx", "A 12534-2022")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 12534-2022 FSC-klagomål mail.docx", "A 12534-2022")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 12534-2022 tillsynsbegäran.docx", "A 12534-2022")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 12534-2022 tillsynsbegäran mail.docx", "A 12534-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 13558-2025</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45736</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>4</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
         <v>8</v>
       </c>
-      <c r="U24" t="n">
+      <c r="T25" t="n">
         <v>8</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="U25" t="n">
+        <v>8</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Honungsblomster
 Backruta
@@ -3414,151 +3526,39 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 13558-2025 artfynd.xlsx", "A 13558-2025")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 13558-2025 karta.png", "A 13558-2025")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 13558-2025 georefererad karta.tif", "A 13558-2025")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 13558-2025 FSC-klagomål.docx", "A 13558-2025")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 13558-2025 FSC-klagomål mail.docx", "A 13558-2025")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 13558-2025 tillsynsbegäran.docx", "A 13558-2025")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 13558-2025 tillsynsbegäran mail.docx", "A 13558-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 12534-2022</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>44638</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>5</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>8</v>
-      </c>
-      <c r="T25" t="n">
-        <v>9</v>
-      </c>
-      <c r="U25" t="n">
-        <v>9</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Backklöver
-Backtimjan
-Jordtistel
-Sårläka
-Vårstarr
-Krutbrännare
-Nattviol
-Sankt pers nycklar</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 12534-2022 artfynd.xlsx", "A 12534-2022")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 12534-2022 karta.png", "A 12534-2022")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 12534-2022 georefererad karta.tif", "A 12534-2022")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 12534-2022 FSC-klagomål.docx", "A 12534-2022")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 12534-2022 FSC-klagomål mail.docx", "A 12534-2022")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 12534-2022 tillsynsbegäran.docx", "A 12534-2022")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 12534-2022 tillsynsbegäran mail.docx", "A 12534-2022")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 31399-2026</t>
+          <t>A 31515-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3568,14 +3568,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3587,14 +3587,19 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
         <v>3</v>
@@ -3621,12 +3626,241 @@
         <v>8</v>
       </c>
       <c r="T26" t="n">
+        <v>11</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Blå slemspindling
+Sårläka
+Vårärt
+Anisspindling
+Skogsknipprot
+Strävlosta
+Blåsippa
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31515-2026 artfynd.xlsx", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31515-2026 karta.png", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31515-2026 georefererad karta.tif", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31515-2026 FSC-klagomål.docx", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31515-2026 FSC-klagomål mail.docx", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31515-2026 tillsynsbegäran.docx", "A 31515-2026")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31515-2026 tillsynsbegäran mail.docx", "A 31515-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 31516-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>8</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="T27" t="n">
+        <v>11</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Blå slemspindling
+Sårläka
+Vårärt
+Anisspindling
+Skogsknipprot
+Strävlosta
+Blåsippa
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31516-2026 artfynd.xlsx", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31516-2026 karta.png", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31516-2026 georefererad karta.tif", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31516-2026 FSC-klagomål.docx", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31516-2026 FSC-klagomål mail.docx", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31516-2026 tillsynsbegäran.docx", "A 31516-2026")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31516-2026 tillsynsbegäran mail.docx", "A 31516-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 31399-2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>8</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Backklöver
 Jordtistel
@@ -3638,112 +3872,224 @@
 Vanliga ängsnycklar</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31399-2026 artfynd.xlsx", "A 31399-2026")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31399-2026 karta.png", "A 31399-2026")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31399-2026 georefererad karta.tif", "A 31399-2026")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31399-2026 FSC-klagomål.docx", "A 31399-2026")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31399-2026 FSC-klagomål mail.docx", "A 31399-2026")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31399-2026 tillsynsbegäran.docx", "A 31399-2026")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31399-2026 tillsynsbegäran mail.docx", "A 31399-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 31515-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S 2741-2022</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>44704</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="n">
+        <v>55</v>
+      </c>
+      <c r="U29" t="n">
+        <v>49</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Almlav
+Ask
+Korskovall
+Ekoxe
+Slät lönnlav
+Stor häxört
+Underviol
+Vitskivlav</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2741-2022 artfynd.xlsx", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 2741-2022 karta.png", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 2741-2022 georefererad karta.tif", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 2741-2022 FSC-klagomål.docx", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 2741-2022 FSC-klagomål mail.docx", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 2741-2022 tillsynsbegäran.docx", "S 2741-2022")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 2741-2022 tillsynsbegäran mail.docx", "S 2741-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>S 2057-2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E27" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="E30" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I27" t="n">
+      <c r="I30" t="n">
         <v>0.8</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J30" t="n">
         <v>3</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K30" t="n">
         <v>3</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L30" t="n">
         <v>3</v>
       </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>3</v>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>8</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T30" t="n">
         <v>11</v>
       </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Blå slemspindling
 Sårläka
@@ -3755,112 +4101,112 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31515-2026 artfynd.xlsx", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31515-2026 karta.png", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31515-2026 georefererad karta.tif", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31515-2026 FSC-klagomål.docx", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31515-2026 FSC-klagomål mail.docx", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31515-2026 tillsynsbegäran.docx", "A 31515-2026")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31515-2026 tillsynsbegäran mail.docx", "A 31515-2026")</f>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2057-2026 artfynd.xlsx", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 2057-2026 karta.png", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 2057-2026 georefererad karta.tif", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 2057-2026 FSC-klagomål.docx", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 2057-2026 FSC-klagomål mail.docx", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 2057-2026 tillsynsbegäran.docx", "S 2057-2026")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 2057-2026 tillsynsbegäran mail.docx", "S 2057-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 31516-2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>S 2058-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E28" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F28" t="inlineStr">
+      <c r="E31" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="I31" t="n">
         <v>0.8</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J31" t="n">
         <v>3</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K31" t="n">
         <v>3</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L31" t="n">
         <v>3</v>
       </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
         <v>3</v>
       </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
         <v>8</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T31" t="n">
         <v>11</v>
       </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Blå slemspindling
 Sårläka
@@ -3872,352 +4218,6 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31516-2026 artfynd.xlsx", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31516-2026 karta.png", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31516-2026 georefererad karta.tif", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31516-2026 FSC-klagomål.docx", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31516-2026 FSC-klagomål mail.docx", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31516-2026 tillsynsbegäran.docx", "A 31516-2026")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31516-2026 tillsynsbegäran mail.docx", "A 31516-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>S 2741-2022</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>44704</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>5</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2</v>
-      </c>
-      <c r="S29" t="n">
-        <v>8</v>
-      </c>
-      <c r="T29" t="n">
-        <v>55</v>
-      </c>
-      <c r="U29" t="n">
-        <v>49</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Almlav
-Ask
-Korskovall
-Ekoxe
-Slät lönnlav
-Stor häxört
-Underviol
-Vitskivlav</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2741-2022 artfynd.xlsx", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 2741-2022 karta.png", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 2741-2022 georefererad karta.tif", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 2741-2022 FSC-klagomål.docx", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 2741-2022 FSC-klagomål mail.docx", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 2741-2022 tillsynsbegäran.docx", "S 2741-2022")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 2741-2022 tillsynsbegäran mail.docx", "S 2741-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>S 2057-2026</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3</v>
-      </c>
-      <c r="L30" t="n">
-        <v>3</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>11</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Blå slemspindling
-Sårläka
-Vårärt
-Anisspindling
-Skogsknipprot
-Strävlosta
-Blåsippa
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2057-2026 artfynd.xlsx", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 2057-2026 karta.png", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 2057-2026 georefererad karta.tif", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 2057-2026 FSC-klagomål.docx", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 2057-2026 FSC-klagomål mail.docx", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 2057-2026 tillsynsbegäran.docx", "S 2057-2026")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 2057-2026 tillsynsbegäran mail.docx", "S 2057-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>S 2058-2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J31" t="n">
-        <v>3</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3</v>
-      </c>
-      <c r="L31" t="n">
-        <v>3</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>11</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Blå slemspindling
-Sårläka
-Vårärt
-Anisspindling
-Skogsknipprot
-Strävlosta
-Blåsippa
-Grönvit nattviol</t>
-        </is>
-      </c>
       <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 2058-2026 artfynd.xlsx", "S 2058-2026")</f>
         <v/>
@@ -4267,7 +4267,7 @@
         <v>45175</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 46794-2025</t>
+          <t>A 16171-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4371,14 +4371,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45926</v>
+        <v>45027</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4391,13 +4391,13 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>12.2</v>
       </c>
       <c r="J33" t="n">
         <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
         <v>2</v>
@@ -4424,12 +4424,122 @@
         <v>6</v>
       </c>
       <c r="T33" t="n">
+        <v>7</v>
+      </c>
+      <c r="U33" t="n">
+        <v>6</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Sårläka
+Älg
+Murgröna
+Blåsippa
+Rostticka
+Bredarun</t>
+        </is>
+      </c>
+      <c r="W33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 16171-2023 artfynd.xlsx", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 16171-2023 karta.png", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="Y33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 16171-2023 georefererad karta.tif", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 16171-2023 FSC-klagomål.docx", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 16171-2023 FSC-klagomål mail.docx", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 16171-2023 tillsynsbegäran.docx", "A 16171-2023")</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 16171-2023 tillsynsbegäran mail.docx", "A 16171-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A 46794-2025</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>45926</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3</v>
+      </c>
+      <c r="L34" t="n">
+        <v>2</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>6</v>
+      </c>
+      <c r="T34" t="n">
         <v>10</v>
       </c>
-      <c r="U33" t="n">
+      <c r="U34" t="n">
         <v>9</v>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Mindre ekbock
 Sårläka
@@ -4439,112 +4549,112 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 46794-2025 artfynd.xlsx", "A 46794-2025")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 46794-2025 karta.png", "A 46794-2025")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 46794-2025 georefererad karta.tif", "A 46794-2025")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 46794-2025 FSC-klagomål.docx", "A 46794-2025")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 46794-2025 FSC-klagomål mail.docx", "A 46794-2025")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 46794-2025 tillsynsbegäran.docx", "A 46794-2025")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 46794-2025 tillsynsbegäran mail.docx", "A 46794-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>A 27298-2026</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D34" s="1" t="n">
+      <c r="D35" s="1" t="n">
         <v>46188</v>
       </c>
-      <c r="E34" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="E35" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I34" t="n">
+      <c r="I35" t="n">
         <v>3.3</v>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="n">
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
         <v>5</v>
       </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
         <v>5</v>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>6</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Grenplattnos
 Jungfrulin
@@ -4554,112 +4664,112 @@
 Murgröna</t>
         </is>
       </c>
-      <c r="W34">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27298-2026 artfynd.xlsx", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="X34">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27298-2026 karta.png", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="Y34">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27298-2026 georefererad karta.tif", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="AA34">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27298-2026 FSC-klagomål.docx", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="AB34">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27298-2026 FSC-klagomål mail.docx", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="AC34">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27298-2026 tillsynsbegäran.docx", "A 27298-2026")</f>
         <v/>
       </c>
-      <c r="AD34">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27298-2026 tillsynsbegäran mail.docx", "A 27298-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>A 31558-2026</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D35" s="1" t="n">
+      <c r="D36" s="1" t="n">
         <v>46224</v>
       </c>
-      <c r="E35" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F35" t="inlineStr">
+      <c r="E36" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" t="n">
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
         <v>2</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K36" t="n">
         <v>2</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
         <v>3</v>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
         <v>6</v>
       </c>
-      <c r="T35" t="n">
+      <c r="T36" t="n">
         <v>8</v>
       </c>
-      <c r="U35" t="n">
-        <v>1</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="U36" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Blå slemspindling
 Sårläka
@@ -4669,142 +4779,32 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W35">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31558-2026 artfynd.xlsx", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="X35">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31558-2026 karta.png", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31558-2026 georefererad karta.tif", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31558-2026 FSC-klagomål.docx", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31558-2026 FSC-klagomål mail.docx", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31558-2026 tillsynsbegäran.docx", "A 31558-2026")</f>
         <v/>
       </c>
-      <c r="AD35">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31558-2026 tillsynsbegäran mail.docx", "A 31558-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A 16171-2023</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>45027</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="n">
-        <v>2</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>6</v>
-      </c>
-      <c r="T36" t="n">
-        <v>7</v>
-      </c>
-      <c r="U36" t="n">
-        <v>6</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka
-Älg
-Murgröna
-Blåsippa
-Rostticka
-Bredarun</t>
-        </is>
-      </c>
-      <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 16171-2023 artfynd.xlsx", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 16171-2023 karta.png", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 16171-2023 georefererad karta.tif", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 16171-2023 FSC-klagomål.docx", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 16171-2023 FSC-klagomål mail.docx", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 16171-2023 tillsynsbegäran.docx", "A 16171-2023")</f>
-        <v/>
-      </c>
-      <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 16171-2023 tillsynsbegäran mail.docx", "A 16171-2023")</f>
         <v/>
       </c>
     </row>
@@ -4828,7 +4828,7 @@
         <v>44704</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45478</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>46188</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>46224</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>46169</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>46169</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>45736</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45280</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7960-2023</t>
+          <t>A 21797-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44973</v>
+        <v>45442</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5735,16 +5735,16 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5753,27 +5753,360 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
       </c>
       <c r="T45" t="n">
+        <v>11</v>
+      </c>
+      <c r="U45" t="n">
+        <v>6</v>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>Sydlig kantmusseron
+Murgröna
+Skogsknipprot
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21797-2024 artfynd.xlsx", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="X45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21797-2024 karta.png", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="Y45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21797-2024 georefererad karta.tif", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="AA45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21797-2024 FSC-klagomål.docx", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="AB45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21797-2024 FSC-klagomål mail.docx", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="AC45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21797-2024 tillsynsbegäran.docx", "A 21797-2024")</f>
+        <v/>
+      </c>
+      <c r="AD45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21797-2024 tillsynsbegäran mail.docx", "A 21797-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A 27290-2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2</v>
+      </c>
+      <c r="R46" t="n">
+        <v>2</v>
+      </c>
+      <c r="S46" t="n">
         <v>4</v>
       </c>
-      <c r="U45" t="n">
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Gotlandsmåra
+Skogsknipprot
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27290-2026 artfynd.xlsx", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="X46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27290-2026 karta.png", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="Y46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27290-2026 georefererad karta.tif", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="AA46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27290-2026 FSC-klagomål.docx", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="AB46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27290-2026 FSC-klagomål mail.docx", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="AC46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27290-2026 tillsynsbegäran.docx", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="AD46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27290-2026 tillsynsbegäran mail.docx", "A 27290-2026")</f>
+        <v/>
+      </c>
+      <c r="AE46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 27290-2026 prioriterade fågelarter.docx", "A 27290-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>A 4164-2023</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>44953</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>4</v>
+      </c>
+      <c r="T47" t="n">
+        <v>5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>4</v>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>Crepis tectorum subsp. tectorum
+Kösa
+Murgröna
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 4164-2023 artfynd.xlsx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="X47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 4164-2023 karta.png", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="Y47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 4164-2023 georefererad karta.tif", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AA47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 4164-2023 FSC-klagomål.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AB47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 4164-2023 FSC-klagomål mail.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AC47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 4164-2023 tillsynsbegäran.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AD47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 4164-2023 tillsynsbegäran mail.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>A 7960-2023</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>44973</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
         <v>3</v>
       </c>
-      <c r="V45" s="2" t="inlineStr">
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="n">
+        <v>4</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>Vresalm
 Pilfotsspindling
@@ -5781,365 +6114,32 @@
 Strävlosta</t>
         </is>
       </c>
-      <c r="W45">
+      <c r="W48">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 7960-2023 artfynd.xlsx", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="X45">
+      <c r="X48">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 7960-2023 karta.png", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="Y45">
+      <c r="Y48">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 7960-2023 georefererad karta.tif", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="AA45">
+      <c r="AA48">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 7960-2023 FSC-klagomål.docx", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="AB45">
+      <c r="AB48">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 7960-2023 FSC-klagomål mail.docx", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="AC45">
+      <c r="AC48">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 7960-2023 tillsynsbegäran.docx", "A 7960-2023")</f>
         <v/>
       </c>
-      <c r="AD45">
+      <c r="AD48">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 7960-2023 tillsynsbegäran mail.docx", "A 7960-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>A 27290-2026</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E46" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J46" t="n">
-        <v>2</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>1</v>
-      </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>2</v>
-      </c>
-      <c r="R46" t="n">
-        <v>2</v>
-      </c>
-      <c r="S46" t="n">
-        <v>4</v>
-      </c>
-      <c r="T46" t="n">
-        <v>4</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Gotlandsmåra
-Skogsknipprot
-Havsörn</t>
-        </is>
-      </c>
-      <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27290-2026 artfynd.xlsx", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27290-2026 karta.png", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27290-2026 georefererad karta.tif", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27290-2026 FSC-klagomål.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27290-2026 FSC-klagomål mail.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27290-2026 tillsynsbegäran.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27290-2026 tillsynsbegäran mail.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-      <c r="AE46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 27290-2026 prioriterade fågelarter.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>A 4164-2023</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>44953</v>
-      </c>
-      <c r="E47" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J47" t="n">
-        <v>1</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" t="n">
-        <v>2</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>2</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>4</v>
-      </c>
-      <c r="T47" t="n">
-        <v>5</v>
-      </c>
-      <c r="U47" t="n">
-        <v>4</v>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>Crepis tectorum subsp. tectorum
-Kösa
-Murgröna
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 4164-2023 artfynd.xlsx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 4164-2023 karta.png", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 4164-2023 georefererad karta.tif", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 4164-2023 FSC-klagomål.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 4164-2023 FSC-klagomål mail.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 4164-2023 tillsynsbegäran.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 4164-2023 tillsynsbegäran mail.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>A 21797-2024</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>45442</v>
-      </c>
-      <c r="E48" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2</v>
-      </c>
-      <c r="L48" t="n">
-        <v>1</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>4</v>
-      </c>
-      <c r="T48" t="n">
-        <v>11</v>
-      </c>
-      <c r="U48" t="n">
-        <v>6</v>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>Sydlig kantmusseron
-Murgröna
-Skogsknipprot
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21797-2024 artfynd.xlsx", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21797-2024 karta.png", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21797-2024 georefererad karta.tif", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21797-2024 FSC-klagomål.docx", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21797-2024 FSC-klagomål mail.docx", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21797-2024 tillsynsbegäran.docx", "A 21797-2024")</f>
-        <v/>
-      </c>
-      <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21797-2024 tillsynsbegäran mail.docx", "A 21797-2024")</f>
         <v/>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
         <v>44704</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>44704</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>44783</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 38860-2025</t>
+          <t>A 24048-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45887</v>
+        <v>45796</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6504,22 +6504,22 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
         <v>2</v>
       </c>
-      <c r="K52" t="n">
-        <v>1</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6528,160 +6528,160 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
       </c>
       <c r="T52" t="n">
+        <v>5</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>Loppstarr
+Ängsstarr
+Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="W52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24048-2025 artfynd.xlsx", "A 24048-2025")</f>
+        <v/>
+      </c>
+      <c r="X52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24048-2025 karta.png", "A 24048-2025")</f>
+        <v/>
+      </c>
+      <c r="Y52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24048-2025 georefererad karta.tif", "A 24048-2025")</f>
+        <v/>
+      </c>
+      <c r="AA52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24048-2025 FSC-klagomål.docx", "A 24048-2025")</f>
+        <v/>
+      </c>
+      <c r="AB52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24048-2025 FSC-klagomål mail.docx", "A 24048-2025")</f>
+        <v/>
+      </c>
+      <c r="AC52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24048-2025 tillsynsbegäran.docx", "A 24048-2025")</f>
+        <v/>
+      </c>
+      <c r="AD52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24048-2025 tillsynsbegäran mail.docx", "A 24048-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>A 38860-2025</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>45887</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="n">
         <v>3</v>
       </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsknipprot
 Revlummer</t>
         </is>
       </c>
-      <c r="W52">
+      <c r="W53">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 38860-2025 artfynd.xlsx", "A 38860-2025")</f>
         <v/>
       </c>
-      <c r="X52">
+      <c r="X53">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 38860-2025 karta.png", "A 38860-2025")</f>
         <v/>
       </c>
-      <c r="Y52">
+      <c r="Y53">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 38860-2025 georefererad karta.tif", "A 38860-2025")</f>
         <v/>
       </c>
-      <c r="AA52">
+      <c r="AA53">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 38860-2025 FSC-klagomål.docx", "A 38860-2025")</f>
         <v/>
       </c>
-      <c r="AB52">
+      <c r="AB53">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 38860-2025 FSC-klagomål mail.docx", "A 38860-2025")</f>
         <v/>
       </c>
-      <c r="AC52">
+      <c r="AC53">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 38860-2025 tillsynsbegäran.docx", "A 38860-2025")</f>
         <v/>
       </c>
-      <c r="AD52">
+      <c r="AD53">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 38860-2025 tillsynsbegäran mail.docx", "A 38860-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>A 24048-2025</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="n">
-        <v>45796</v>
-      </c>
-      <c r="E53" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>2</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>2</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>2</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>3</v>
-      </c>
-      <c r="T53" t="n">
-        <v>5</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" s="2" t="inlineStr">
-        <is>
-          <t>Loppstarr
-Ängsstarr
-Kärrknipprot</t>
-        </is>
-      </c>
-      <c r="W53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24048-2025 artfynd.xlsx", "A 24048-2025")</f>
-        <v/>
-      </c>
-      <c r="X53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24048-2025 karta.png", "A 24048-2025")</f>
-        <v/>
-      </c>
-      <c r="Y53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24048-2025 georefererad karta.tif", "A 24048-2025")</f>
-        <v/>
-      </c>
-      <c r="AA53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24048-2025 FSC-klagomål.docx", "A 24048-2025")</f>
-        <v/>
-      </c>
-      <c r="AB53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24048-2025 FSC-klagomål mail.docx", "A 24048-2025")</f>
-        <v/>
-      </c>
-      <c r="AC53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24048-2025 tillsynsbegäran.docx", "A 24048-2025")</f>
-        <v/>
-      </c>
-      <c r="AD53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24048-2025 tillsynsbegäran mail.docx", "A 24048-2025")</f>
         <v/>
       </c>
     </row>
@@ -6705,7 +6705,7 @@
         <v>45911</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 15285-2026</t>
+          <t>A 32174-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46105</v>
+        <v>44781</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6830,13 +6830,13 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" t="n">
         <v>1</v>
@@ -6866,381 +6866,381 @@
         <v>3</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>Backklöver
+Tvåblad
+Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="W55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 32174-2022 artfynd.xlsx", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="X55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 32174-2022 karta.png", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="Y55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 32174-2022 georefererad karta.tif", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="AA55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 32174-2022 FSC-klagomål.docx", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="AB55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 32174-2022 FSC-klagomål mail.docx", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="AC55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 32174-2022 tillsynsbegäran.docx", "A 32174-2022")</f>
+        <v/>
+      </c>
+      <c r="AD55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 32174-2022 tillsynsbegäran mail.docx", "A 32174-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>A 15285-2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>3</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Havsörn
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W55">
+      <c r="W56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 15285-2026 artfynd.xlsx", "A 15285-2026")</f>
         <v/>
       </c>
-      <c r="X55">
+      <c r="X56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 15285-2026 karta.png", "A 15285-2026")</f>
         <v/>
       </c>
-      <c r="Y55">
+      <c r="Y56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 15285-2026 georefererad karta.tif", "A 15285-2026")</f>
         <v/>
       </c>
-      <c r="AA55">
+      <c r="AA56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 15285-2026 FSC-klagomål.docx", "A 15285-2026")</f>
         <v/>
       </c>
-      <c r="AB55">
+      <c r="AB56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 15285-2026 FSC-klagomål mail.docx", "A 15285-2026")</f>
         <v/>
       </c>
-      <c r="AC55">
+      <c r="AC56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 15285-2026 tillsynsbegäran.docx", "A 15285-2026")</f>
         <v/>
       </c>
-      <c r="AD55">
+      <c r="AD56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 15285-2026 tillsynsbegäran mail.docx", "A 15285-2026")</f>
         <v/>
       </c>
-      <c r="AE55">
+      <c r="AE56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 15285-2026 prioriterade fågelarter.docx", "A 15285-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>A 26849-2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>Myskmadra
+Purpurknipprot
+Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="W57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26849-2026 artfynd.xlsx", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="X57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26849-2026 karta.png", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="Y57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26849-2026 georefererad karta.tif", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="AA57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26849-2026 FSC-klagomål.docx", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="AB57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26849-2026 FSC-klagomål mail.docx", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="AC57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26849-2026 tillsynsbegäran.docx", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="AD57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26849-2026 tillsynsbegäran mail.docx", "A 26849-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>A 27283-2026</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D56" s="1" t="n">
+      <c r="D58" s="1" t="n">
         <v>46188</v>
       </c>
-      <c r="E56" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F56" t="inlineStr">
+      <c r="E58" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I56" t="n">
+      <c r="I58" t="n">
         <v>2</v>
       </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" t="n">
-        <v>1</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
         <v>2</v>
       </c>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
-      <c r="S56" t="n">
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
+      <c r="S58" t="n">
         <v>3</v>
       </c>
-      <c r="T56" t="n">
+      <c r="T58" t="n">
         <v>3</v>
       </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" s="2" t="inlineStr">
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
         <is>
           <t>Ask
 Mindre poppelglasvinge
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W56">
+      <c r="W58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27283-2026 artfynd.xlsx", "A 27283-2026")</f>
         <v/>
       </c>
-      <c r="X56">
+      <c r="X58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27283-2026 karta.png", "A 27283-2026")</f>
         <v/>
       </c>
-      <c r="Y56">
+      <c r="Y58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27283-2026 georefererad karta.tif", "A 27283-2026")</f>
         <v/>
       </c>
-      <c r="AA56">
+      <c r="AA58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27283-2026 FSC-klagomål.docx", "A 27283-2026")</f>
         <v/>
       </c>
-      <c r="AB56">
+      <c r="AB58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27283-2026 FSC-klagomål mail.docx", "A 27283-2026")</f>
         <v/>
       </c>
-      <c r="AC56">
+      <c r="AC58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27283-2026 tillsynsbegäran.docx", "A 27283-2026")</f>
         <v/>
       </c>
-      <c r="AD56">
+      <c r="AD58">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27283-2026 tillsynsbegäran mail.docx", "A 27283-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>A 26849-2026</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="n">
-        <v>46185</v>
-      </c>
-      <c r="E57" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I57" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J57" t="n">
-        <v>2</v>
-      </c>
-      <c r="K57" t="n">
-        <v>3</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>3</v>
-      </c>
-      <c r="T57" t="n">
-        <v>3</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" s="2" t="inlineStr">
-        <is>
-          <t>Myskmadra
-Purpurknipprot
-Vit skogslilja</t>
-        </is>
-      </c>
-      <c r="W57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26849-2026 artfynd.xlsx", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="X57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26849-2026 karta.png", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="Y57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26849-2026 georefererad karta.tif", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="AA57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26849-2026 FSC-klagomål.docx", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="AB57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26849-2026 FSC-klagomål mail.docx", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="AC57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26849-2026 tillsynsbegäran.docx", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="AD57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26849-2026 tillsynsbegäran mail.docx", "A 26849-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>A 32174-2022</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="n">
-        <v>44781</v>
-      </c>
-      <c r="E58" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I58" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2</v>
-      </c>
-      <c r="K58" t="n">
-        <v>2</v>
-      </c>
-      <c r="L58" t="n">
-        <v>1</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>3</v>
-      </c>
-      <c r="T58" t="n">
-        <v>3</v>
-      </c>
-      <c r="U58" t="n">
-        <v>3</v>
-      </c>
-      <c r="V58" s="2" t="inlineStr">
-        <is>
-          <t>Backklöver
-Tvåblad
-Vit skogslilja</t>
-        </is>
-      </c>
-      <c r="W58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 32174-2022 artfynd.xlsx", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="X58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 32174-2022 karta.png", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="Y58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 32174-2022 georefererad karta.tif", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="AA58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 32174-2022 FSC-klagomål.docx", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="AB58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 32174-2022 FSC-klagomål mail.docx", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="AC58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 32174-2022 tillsynsbegäran.docx", "A 32174-2022")</f>
-        <v/>
-      </c>
-      <c r="AD58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 32174-2022 tillsynsbegäran mail.docx", "A 32174-2022")</f>
         <v/>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
         <v>44837</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>46223</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>46105</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>46188</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>46223</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44623</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>44725</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 21908-2022</t>
+          <t>A 60141-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44711</v>
+        <v>45994</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8056,13 +8056,13 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>1</v>
       </c>
       <c r="K66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -8089,50 +8089,50 @@
         <v>2</v>
       </c>
       <c r="T66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra
-Skogsknipprot</t>
+          <t>Strävlosta
+Långbensgroda</t>
         </is>
       </c>
       <c r="W66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21908-2022 artfynd.xlsx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 60141-2025 artfynd.xlsx", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="X66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21908-2022 karta.png", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 60141-2025 karta.png", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="Y66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21908-2022 georefererad karta.tif", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 60141-2025 georefererad karta.tif", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="AA66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21908-2022 FSC-klagomål.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 60141-2025 FSC-klagomål.docx", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="AB66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21908-2022 FSC-klagomål mail.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 60141-2025 FSC-klagomål mail.docx", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="AC66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21908-2022 tillsynsbegäran.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 60141-2025 tillsynsbegäran.docx", "A 60141-2025")</f>
         <v/>
       </c>
       <c r="AD66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21908-2022 tillsynsbegäran mail.docx", "A 21908-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 60141-2025 tillsynsbegäran mail.docx", "A 60141-2025")</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 9253-2026</t>
+          <t>A 60140-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8146,10 +8146,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46070</v>
+        <v>45994</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8162,13 +8162,13 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -8195,50 +8195,50 @@
         <v>2</v>
       </c>
       <c r="T67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>Murgröna
-Gullviva</t>
+          <t>Skogsknipprot
+Strävlosta</t>
         </is>
       </c>
       <c r="W67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9253-2026 artfynd.xlsx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 60140-2025 artfynd.xlsx", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="X67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9253-2026 karta.png", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 60140-2025 karta.png", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="Y67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9253-2026 georefererad karta.tif", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 60140-2025 georefererad karta.tif", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="AA67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9253-2026 FSC-klagomål.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 60140-2025 FSC-klagomål.docx", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="AB67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9253-2026 FSC-klagomål mail.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 60140-2025 FSC-klagomål mail.docx", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="AC67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9253-2026 tillsynsbegäran.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 60140-2025 tillsynsbegäran.docx", "A 60140-2025")</f>
         <v/>
       </c>
       <c r="AD67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9253-2026 tillsynsbegäran mail.docx", "A 9253-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 60140-2025 tillsynsbegäran mail.docx", "A 60140-2025")</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60141-2025</t>
+          <t>A 9253-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -8252,10 +8252,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45994</v>
+        <v>46070</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>1</v>
@@ -8301,50 +8301,50 @@
         <v>2</v>
       </c>
       <c r="T68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>Strävlosta
-Långbensgroda</t>
+          <t>Murgröna
+Gullviva</t>
         </is>
       </c>
       <c r="W68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 60141-2025 artfynd.xlsx", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9253-2026 artfynd.xlsx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="X68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 60141-2025 karta.png", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9253-2026 karta.png", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="Y68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 60141-2025 georefererad karta.tif", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9253-2026 georefererad karta.tif", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AA68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 60141-2025 FSC-klagomål.docx", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9253-2026 FSC-klagomål.docx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AB68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 60141-2025 FSC-klagomål mail.docx", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9253-2026 FSC-klagomål mail.docx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AC68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 60141-2025 tillsynsbegäran.docx", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9253-2026 tillsynsbegäran.docx", "A 9253-2026")</f>
         <v/>
       </c>
       <c r="AD68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 60141-2025 tillsynsbegäran mail.docx", "A 60141-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9253-2026 tillsynsbegäran mail.docx", "A 9253-2026")</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 60140-2025</t>
+          <t>A 44678-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -8358,10 +8358,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45994</v>
+        <v>44840</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8374,13 +8374,13 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>1</v>
       </c>
       <c r="K69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -8389,7 +8389,7 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8398,59 +8398,59 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S69" t="n">
         <v>2</v>
       </c>
       <c r="T69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot
-Strävlosta</t>
+          <t>Ask
+Skogsknipprot</t>
         </is>
       </c>
       <c r="W69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 60140-2025 artfynd.xlsx", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 44678-2022 artfynd.xlsx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="X69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 60140-2025 karta.png", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 44678-2022 karta.png", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="Y69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 60140-2025 georefererad karta.tif", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 44678-2022 georefererad karta.tif", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AA69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 60140-2025 FSC-klagomål.docx", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 44678-2022 FSC-klagomål.docx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AB69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 60140-2025 FSC-klagomål mail.docx", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 44678-2022 FSC-klagomål mail.docx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AC69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 60140-2025 tillsynsbegäran.docx", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 44678-2022 tillsynsbegäran.docx", "A 44678-2022")</f>
         <v/>
       </c>
       <c r="AD69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 60140-2025 tillsynsbegäran mail.docx", "A 60140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 44678-2022 tillsynsbegäran mail.docx", "A 44678-2022")</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24322-2026</t>
+          <t>A 17699-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -8464,10 +8464,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46169</v>
+        <v>45758</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8479,37 +8479,32 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>5.5</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
         <v>2</v>
       </c>
-      <c r="K70" t="n">
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
         <v>2</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
@@ -8521,47 +8516,47 @@
         <v>2</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>Purpurknipprot
-Skogsknipprot</t>
+          <t>Backtimjan
+Klibbveronika</t>
         </is>
       </c>
       <c r="W70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24322-2026 artfynd.xlsx", "A 24322-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 17699-2025 artfynd.xlsx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="X70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24322-2026 karta.png", "A 24322-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 17699-2025 karta.png", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="Y70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24322-2026 georefererad karta.tif", "A 24322-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 17699-2025 georefererad karta.tif", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AA70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24322-2026 FSC-klagomål.docx", "A 24322-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 17699-2025 FSC-klagomål.docx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AB70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24322-2026 FSC-klagomål mail.docx", "A 24322-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 17699-2025 FSC-klagomål mail.docx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AC70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24322-2026 tillsynsbegäran.docx", "A 24322-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 17699-2025 tillsynsbegäran.docx", "A 17699-2025")</f>
         <v/>
       </c>
       <c r="AD70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24322-2026 tillsynsbegäran mail.docx", "A 24322-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 17699-2025 tillsynsbegäran mail.docx", "A 17699-2025")</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29411-2026</t>
+          <t>A 24322-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8571,14 +8566,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46203</v>
+        <v>46169</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8596,19 +8591,19 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>5.5</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
@@ -8620,10 +8615,10 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>2</v>
@@ -8632,47 +8627,47 @@
         <v>2</v>
       </c>
       <c r="U71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare
-Ekoxe</t>
+          <t>Purpurknipprot
+Skogsknipprot</t>
         </is>
       </c>
       <c r="W71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 29411-2026 artfynd.xlsx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24322-2026 artfynd.xlsx", "A 24322-2026")</f>
         <v/>
       </c>
       <c r="X71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 29411-2026 karta.png", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24322-2026 karta.png", "A 24322-2026")</f>
         <v/>
       </c>
       <c r="Y71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 29411-2026 georefererad karta.tif", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24322-2026 georefererad karta.tif", "A 24322-2026")</f>
         <v/>
       </c>
       <c r="AA71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 29411-2026 FSC-klagomål.docx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24322-2026 FSC-klagomål.docx", "A 24322-2026")</f>
         <v/>
       </c>
       <c r="AB71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 29411-2026 FSC-klagomål mail.docx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24322-2026 FSC-klagomål mail.docx", "A 24322-2026")</f>
         <v/>
       </c>
       <c r="AC71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 29411-2026 tillsynsbegäran.docx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24322-2026 tillsynsbegäran.docx", "A 24322-2026")</f>
         <v/>
       </c>
       <c r="AD71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 29411-2026 tillsynsbegäran mail.docx", "A 29411-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24322-2026 tillsynsbegäran mail.docx", "A 24322-2026")</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 44678-2022</t>
+          <t>A 21908-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8686,10 +8681,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44840</v>
+        <v>44711</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8702,13 +8697,13 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J72" t="n">
         <v>1</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -8717,7 +8712,7 @@
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -8726,10 +8721,10 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>2</v>
@@ -8738,47 +8733,47 @@
         <v>2</v>
       </c>
       <c r="U72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>Ask
+          <t>Myskmadra
 Skogsknipprot</t>
         </is>
       </c>
       <c r="W72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 44678-2022 artfynd.xlsx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21908-2022 artfynd.xlsx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="X72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 44678-2022 karta.png", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21908-2022 karta.png", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="Y72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 44678-2022 georefererad karta.tif", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21908-2022 georefererad karta.tif", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AA72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 44678-2022 FSC-klagomål.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21908-2022 FSC-klagomål.docx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AB72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 44678-2022 FSC-klagomål mail.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21908-2022 FSC-klagomål mail.docx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AC72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 44678-2022 tillsynsbegäran.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21908-2022 tillsynsbegäran.docx", "A 21908-2022")</f>
         <v/>
       </c>
       <c r="AD72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 44678-2022 tillsynsbegäran mail.docx", "A 44678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21908-2022 tillsynsbegäran mail.docx", "A 21908-2022")</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 29434-2026</t>
+          <t>A 29411-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8795,7 +8790,7 @@
         <v>46203</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8813,19 +8808,19 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
@@ -8837,10 +8832,10 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S73" t="n">
         <v>2</v>
@@ -8849,47 +8844,47 @@
         <v>2</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
           <t>Bredbrämad bastardsvärmare
-Purpurmusseron</t>
+Ekoxe</t>
         </is>
       </c>
       <c r="W73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 29434-2026 artfynd.xlsx", "A 29434-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 29411-2026 artfynd.xlsx", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="X73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 29434-2026 karta.png", "A 29434-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 29411-2026 karta.png", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="Y73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 29434-2026 georefererad karta.tif", "A 29434-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 29411-2026 georefererad karta.tif", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="AA73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 29434-2026 FSC-klagomål.docx", "A 29434-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 29411-2026 FSC-klagomål.docx", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="AB73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 29434-2026 FSC-klagomål mail.docx", "A 29434-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 29411-2026 FSC-klagomål mail.docx", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="AC73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 29434-2026 tillsynsbegäran.docx", "A 29434-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 29411-2026 tillsynsbegäran.docx", "A 29411-2026")</f>
         <v/>
       </c>
       <c r="AD73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 29434-2026 tillsynsbegäran mail.docx", "A 29434-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 29411-2026 tillsynsbegäran mail.docx", "A 29411-2026")</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17699-2025</t>
+          <t>A 29434-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8899,14 +8894,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45758</v>
+        <v>46203</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8918,8 +8913,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8928,10 +8928,10 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
         <v>2</v>
-      </c>
-      <c r="M74" t="n">
-        <v>0</v>
       </c>
       <c r="N74" t="n">
         <v>0</v>
@@ -8946,7 +8946,7 @@
         <v>2</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S74" t="n">
         <v>2</v>
@@ -8955,47 +8955,47 @@
         <v>2</v>
       </c>
       <c r="U74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan
-Klibbveronika</t>
+          <t>Bredbrämad bastardsvärmare
+Purpurmusseron</t>
         </is>
       </c>
       <c r="W74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 17699-2025 artfynd.xlsx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 29434-2026 artfynd.xlsx", "A 29434-2026")</f>
         <v/>
       </c>
       <c r="X74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 17699-2025 karta.png", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 29434-2026 karta.png", "A 29434-2026")</f>
         <v/>
       </c>
       <c r="Y74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 17699-2025 georefererad karta.tif", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 29434-2026 georefererad karta.tif", "A 29434-2026")</f>
         <v/>
       </c>
       <c r="AA74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 17699-2025 FSC-klagomål.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 29434-2026 FSC-klagomål.docx", "A 29434-2026")</f>
         <v/>
       </c>
       <c r="AB74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 17699-2025 FSC-klagomål mail.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 29434-2026 FSC-klagomål mail.docx", "A 29434-2026")</f>
         <v/>
       </c>
       <c r="AC74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 17699-2025 tillsynsbegäran.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 29434-2026 tillsynsbegäran.docx", "A 29434-2026")</f>
         <v/>
       </c>
       <c r="AD74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 17699-2025 tillsynsbegäran mail.docx", "A 17699-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 29434-2026 tillsynsbegäran mail.docx", "A 29434-2026")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S 6144-2022</t>
+          <t>S 1650-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9005,14 +9005,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44865</v>
+        <v>44649</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9025,16 +9025,16 @@
         </is>
       </c>
       <c r="I75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
         <v>2</v>
       </c>
-      <c r="J75" t="n">
-        <v>1</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -9049,7 +9049,7 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -9058,50 +9058,50 @@
         <v>2</v>
       </c>
       <c r="T75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>Oxtungssvamp
-Fläcknycklar</t>
+          <t>Guldlockmossa
+Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="W75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 6144-2022 artfynd.xlsx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1650-2022 artfynd.xlsx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="X75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 6144-2022 karta.png", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1650-2022 karta.png", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="Y75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 6144-2022 georefererad karta.tif", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1650-2022 georefererad karta.tif", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AA75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 6144-2022 FSC-klagomål.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1650-2022 FSC-klagomål.docx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AB75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 6144-2022 FSC-klagomål mail.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1650-2022 FSC-klagomål mail.docx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AC75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 6144-2022 tillsynsbegäran.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1650-2022 tillsynsbegäran.docx", "S 1650-2022")</f>
         <v/>
       </c>
       <c r="AD75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 6144-2022 tillsynsbegäran mail.docx", "S 6144-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1650-2022 tillsynsbegäran mail.docx", "S 1650-2022")</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S 1650-2022</t>
+          <t>S 6144-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9111,14 +9111,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44649</v>
+        <v>44865</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9131,16 +9131,16 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -9155,7 +9155,7 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
@@ -9164,43 +9164,43 @@
         <v>2</v>
       </c>
       <c r="T76" t="n">
+        <v>3</v>
+      </c>
+      <c r="U76" t="n">
         <v>2</v>
       </c>
-      <c r="U76" t="n">
-        <v>0</v>
-      </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa
-Gulpudrad spiklav</t>
+          <t>Oxtungssvamp
+Fläcknycklar</t>
         </is>
       </c>
       <c r="W76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1650-2022 artfynd.xlsx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 6144-2022 artfynd.xlsx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="X76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1650-2022 karta.png", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 6144-2022 karta.png", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="Y76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1650-2022 georefererad karta.tif", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 6144-2022 georefererad karta.tif", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AA76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1650-2022 FSC-klagomål.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 6144-2022 FSC-klagomål.docx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AB76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1650-2022 FSC-klagomål mail.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 6144-2022 FSC-klagomål mail.docx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AC76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1650-2022 tillsynsbegäran.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 6144-2022 tillsynsbegäran.docx", "S 6144-2022")</f>
         <v/>
       </c>
       <c r="AD76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1650-2022 tillsynsbegäran mail.docx", "S 1650-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 6144-2022 tillsynsbegäran mail.docx", "S 6144-2022")</f>
         <v/>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
         <v>46203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>46203</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>44772</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44781</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 24701-2023</t>
+          <t>A 40339-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9663,10 +9663,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45084</v>
+        <v>45169</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9679,13 +9679,13 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -9694,7 +9694,7 @@
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -9703,58 +9703,58 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
       </c>
       <c r="T81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24701-2023 artfynd.xlsx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 40339-2023 artfynd.xlsx", "A 40339-2023")</f>
         <v/>
       </c>
       <c r="X81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24701-2023 karta.png", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 40339-2023 karta.png", "A 40339-2023")</f>
         <v/>
       </c>
       <c r="Y81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24701-2023 georefererad karta.tif", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 40339-2023 georefererad karta.tif", "A 40339-2023")</f>
         <v/>
       </c>
       <c r="AA81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24701-2023 FSC-klagomål.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 40339-2023 FSC-klagomål.docx", "A 40339-2023")</f>
         <v/>
       </c>
       <c r="AB81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24701-2023 FSC-klagomål mail.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 40339-2023 FSC-klagomål mail.docx", "A 40339-2023")</f>
         <v/>
       </c>
       <c r="AC81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24701-2023 tillsynsbegäran.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 40339-2023 tillsynsbegäran.docx", "A 40339-2023")</f>
         <v/>
       </c>
       <c r="AD81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24701-2023 tillsynsbegäran mail.docx", "A 24701-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 40339-2023 tillsynsbegäran mail.docx", "A 40339-2023")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 40339-2023</t>
+          <t>A 41831-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9768,10 +9768,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45169</v>
+        <v>45902</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
         <v>1</v>
@@ -9820,46 +9820,46 @@
         <v>1</v>
       </c>
       <c r="U82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 40339-2023 artfynd.xlsx", "A 40339-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 41831-2025 artfynd.xlsx", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="X82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 40339-2023 karta.png", "A 40339-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 41831-2025 karta.png", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="Y82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 40339-2023 georefererad karta.tif", "A 40339-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 41831-2025 georefererad karta.tif", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="AA82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 40339-2023 FSC-klagomål.docx", "A 40339-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 41831-2025 FSC-klagomål.docx", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="AB82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 40339-2023 FSC-klagomål mail.docx", "A 40339-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 41831-2025 FSC-klagomål mail.docx", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="AC82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 40339-2023 tillsynsbegäran.docx", "A 40339-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 41831-2025 tillsynsbegäran.docx", "A 41831-2025")</f>
         <v/>
       </c>
       <c r="AD82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 40339-2023 tillsynsbegäran mail.docx", "A 40339-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 41831-2025 tillsynsbegäran mail.docx", "A 41831-2025")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 41831-2025</t>
+          <t>A 9745-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9873,10 +9873,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45902</v>
+        <v>44984</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>1</v>
@@ -9922,10 +9922,10 @@
         <v>1</v>
       </c>
       <c r="T83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
@@ -9933,38 +9933,38 @@
         </is>
       </c>
       <c r="W83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 41831-2025 artfynd.xlsx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9745-2023 artfynd.xlsx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="X83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 41831-2025 karta.png", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9745-2023 karta.png", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="Y83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 41831-2025 georefererad karta.tif", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9745-2023 georefererad karta.tif", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AA83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 41831-2025 FSC-klagomål.docx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9745-2023 FSC-klagomål.docx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AB83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 41831-2025 FSC-klagomål mail.docx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9745-2023 FSC-klagomål mail.docx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AC83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 41831-2025 tillsynsbegäran.docx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9745-2023 tillsynsbegäran.docx", "A 9745-2023")</f>
         <v/>
       </c>
       <c r="AD83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 41831-2025 tillsynsbegäran mail.docx", "A 41831-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9745-2023 tillsynsbegäran mail.docx", "A 9745-2023")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 28785-2025</t>
+          <t>A 20878-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9974,14 +9974,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45820</v>
+        <v>45439</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9993,13 +9993,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>1</v>
@@ -10032,46 +10027,42 @@
         <v>1</v>
       </c>
       <c r="T84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28785-2025 artfynd.xlsx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 20878-2024 artfynd.xlsx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="X84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28785-2025 karta.png", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 20878-2024 karta.png", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="Y84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28785-2025 georefererad karta.tif", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 20878-2024 georefererad karta.tif", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AA84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28785-2025 FSC-klagomål.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 20878-2024 FSC-klagomål.docx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AB84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28785-2025 FSC-klagomål mail.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 20878-2024 FSC-klagomål mail.docx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AC84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28785-2025 tillsynsbegäran.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 20878-2024 tillsynsbegäran.docx", "A 20878-2024")</f>
         <v/>
       </c>
       <c r="AD84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28785-2025 tillsynsbegäran mail.docx", "A 28785-2025")</f>
-        <v/>
-      </c>
-      <c r="AE84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 28785-2025 prioriterade fågelarter.docx", "A 28785-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 20878-2024 tillsynsbegäran mail.docx", "A 20878-2024")</f>
         <v/>
       </c>
     </row>
@@ -10095,7 +10086,7 @@
         <v>45820</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10192,7 +10183,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3302-2026</t>
+          <t>A 28785-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10202,14 +10193,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46041</v>
+        <v>45820</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10221,8 +10212,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J86" t="n">
         <v>1</v>
@@ -10262,42 +10258,46 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 3302-2026 artfynd.xlsx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28785-2025 artfynd.xlsx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="X86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 3302-2026 karta.png", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28785-2025 karta.png", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="Y86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 3302-2026 georefererad karta.tif", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28785-2025 georefererad karta.tif", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AA86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 3302-2026 FSC-klagomål.docx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28785-2025 FSC-klagomål.docx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AB86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 3302-2026 FSC-klagomål mail.docx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28785-2025 FSC-klagomål mail.docx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AC86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 3302-2026 tillsynsbegäran.docx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28785-2025 tillsynsbegäran.docx", "A 28785-2025")</f>
         <v/>
       </c>
       <c r="AD86">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 3302-2026 tillsynsbegäran mail.docx", "A 3302-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28785-2025 tillsynsbegäran mail.docx", "A 28785-2025")</f>
+        <v/>
+      </c>
+      <c r="AE86">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 28785-2025 prioriterade fågelarter.docx", "A 28785-2025")</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 7481-2026</t>
+          <t>A 31720-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10311,10 +10311,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46059</v>
+        <v>44776</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10326,14 +10326,19 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="J87" t="n">
         <v>1</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -10360,49 +10365,49 @@
         <v>1</v>
       </c>
       <c r="T87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 7481-2026 artfynd.xlsx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31720-2022 artfynd.xlsx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="X87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 7481-2026 karta.png", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31720-2022 karta.png", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="Y87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 7481-2026 georefererad karta.tif", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31720-2022 georefererad karta.tif", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AA87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 7481-2026 FSC-klagomål.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31720-2022 FSC-klagomål.docx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AB87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 7481-2026 FSC-klagomål mail.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31720-2022 FSC-klagomål mail.docx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AC87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 7481-2026 tillsynsbegäran.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31720-2022 tillsynsbegäran.docx", "A 31720-2022")</f>
         <v/>
       </c>
       <c r="AD87">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 7481-2026 tillsynsbegäran mail.docx", "A 7481-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31720-2022 tillsynsbegäran mail.docx", "A 31720-2022")</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 9104-2026</t>
+          <t>A 3302-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10416,10 +10421,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46069</v>
+        <v>46041</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10432,10 +10437,10 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -10468,46 +10473,46 @@
         <v>1</v>
       </c>
       <c r="U88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9104-2026 artfynd.xlsx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 3302-2026 artfynd.xlsx", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="X88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9104-2026 karta.png", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 3302-2026 karta.png", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="Y88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9104-2026 georefererad karta.tif", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 3302-2026 georefererad karta.tif", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="AA88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9104-2026 FSC-klagomål.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 3302-2026 FSC-klagomål.docx", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="AB88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9104-2026 FSC-klagomål mail.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 3302-2026 FSC-klagomål mail.docx", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="AC88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9104-2026 tillsynsbegäran.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 3302-2026 tillsynsbegäran.docx", "A 3302-2026")</f>
         <v/>
       </c>
       <c r="AD88">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9104-2026 tillsynsbegäran mail.docx", "A 9104-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 3302-2026 tillsynsbegäran mail.docx", "A 3302-2026")</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 9905-2026</t>
+          <t>A 7481-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10521,10 +10526,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46073</v>
+        <v>46059</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10537,10 +10542,10 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -10552,7 +10557,7 @@
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -10561,58 +10566,58 @@
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>1</v>
       </c>
       <c r="T89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U89" t="n">
         <v>0</v>
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9905-2026 artfynd.xlsx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 7481-2026 artfynd.xlsx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="X89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9905-2026 karta.png", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 7481-2026 karta.png", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="Y89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9905-2026 georefererad karta.tif", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 7481-2026 georefererad karta.tif", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AA89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9905-2026 FSC-klagomål.docx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 7481-2026 FSC-klagomål.docx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AB89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9905-2026 FSC-klagomål mail.docx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 7481-2026 FSC-klagomål mail.docx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AC89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9905-2026 tillsynsbegäran.docx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 7481-2026 tillsynsbegäran.docx", "A 7481-2026")</f>
         <v/>
       </c>
       <c r="AD89">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9905-2026 tillsynsbegäran mail.docx", "A 9905-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 7481-2026 tillsynsbegäran mail.docx", "A 7481-2026")</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 63276-2023</t>
+          <t>A 9104-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10622,14 +10627,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45273</v>
+        <v>46069</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10642,7 +10647,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -10654,7 +10659,7 @@
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
         <v>0</v>
@@ -10666,10 +10671,10 @@
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>1</v>
@@ -10678,46 +10683,46 @@
         <v>1</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>Elaphomyces barrioi</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="W90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 63276-2023 artfynd.xlsx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9104-2026 artfynd.xlsx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="X90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 63276-2023 karta.png", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9104-2026 karta.png", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="Y90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 63276-2023 georefererad karta.tif", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9104-2026 georefererad karta.tif", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AA90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 63276-2023 FSC-klagomål.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9104-2026 FSC-klagomål.docx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AB90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 63276-2023 FSC-klagomål mail.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9104-2026 FSC-klagomål mail.docx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AC90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 63276-2023 tillsynsbegäran.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9104-2026 tillsynsbegäran.docx", "A 9104-2026")</f>
         <v/>
       </c>
       <c r="AD90">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 63276-2023 tillsynsbegäran mail.docx", "A 63276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9104-2026 tillsynsbegäran mail.docx", "A 9104-2026")</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 24704-2023</t>
+          <t>A 9905-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10731,10 +10736,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45084</v>
+        <v>46073</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10747,7 +10752,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -10780,7 +10785,7 @@
         <v>1</v>
       </c>
       <c r="T91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
@@ -10791,38 +10796,38 @@
         </is>
       </c>
       <c r="W91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24704-2023 artfynd.xlsx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9905-2026 artfynd.xlsx", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="X91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24704-2023 karta.png", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9905-2026 karta.png", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="Y91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24704-2023 georefererad karta.tif", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9905-2026 georefererad karta.tif", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="AA91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24704-2023 FSC-klagomål.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9905-2026 FSC-klagomål.docx", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="AB91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24704-2023 FSC-klagomål mail.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9905-2026 FSC-klagomål mail.docx", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="AC91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24704-2023 tillsynsbegäran.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9905-2026 tillsynsbegäran.docx", "A 9905-2026")</f>
         <v/>
       </c>
       <c r="AD91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24704-2023 tillsynsbegäran mail.docx", "A 24704-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9905-2026 tillsynsbegäran mail.docx", "A 9905-2026")</f>
         <v/>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 9745-2023</t>
+          <t>A 24701-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10836,10 +10841,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44984</v>
+        <v>45084</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10852,13 +10857,13 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -10867,7 +10872,7 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -10876,58 +10881,58 @@
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S92" t="n">
         <v>1</v>
       </c>
       <c r="T92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 9745-2023 artfynd.xlsx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24701-2023 artfynd.xlsx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="X92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 9745-2023 karta.png", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24701-2023 karta.png", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="Y92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 9745-2023 georefererad karta.tif", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24701-2023 georefererad karta.tif", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AA92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 9745-2023 FSC-klagomål.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24701-2023 FSC-klagomål.docx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AB92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 9745-2023 FSC-klagomål mail.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24701-2023 FSC-klagomål mail.docx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AC92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 9745-2023 tillsynsbegäran.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24701-2023 tillsynsbegäran.docx", "A 24701-2023")</f>
         <v/>
       </c>
       <c r="AD92">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 9745-2023 tillsynsbegäran mail.docx", "A 9745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24701-2023 tillsynsbegäran mail.docx", "A 24701-2023")</f>
         <v/>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 26840-2026</t>
+          <t>A 24704-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10937,14 +10942,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46185</v>
+        <v>45084</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10956,13 +10961,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -10995,7 +10995,7 @@
         <v>1</v>
       </c>
       <c r="T93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
@@ -11006,38 +11006,38 @@
         </is>
       </c>
       <c r="W93">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26840-2026 artfynd.xlsx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24704-2023 artfynd.xlsx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="X93">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26840-2026 karta.png", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24704-2023 karta.png", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="Y93">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26840-2026 georefererad karta.tif", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24704-2023 georefererad karta.tif", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AA93">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26840-2026 FSC-klagomål.docx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24704-2023 FSC-klagomål.docx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AB93">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26840-2026 FSC-klagomål mail.docx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24704-2023 FSC-klagomål mail.docx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AC93">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26840-2026 tillsynsbegäran.docx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24704-2023 tillsynsbegäran.docx", "A 24704-2023")</f>
         <v/>
       </c>
       <c r="AD93">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26840-2026 tillsynsbegäran mail.docx", "A 26840-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24704-2023 tillsynsbegäran mail.docx", "A 24704-2023")</f>
         <v/>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 28374-2026</t>
+          <t>A 26840-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -11051,10 +11051,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46196</v>
+        <v>46185</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -11084,10 +11084,10 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11105,42 +11105,42 @@
         <v>1</v>
       </c>
       <c r="T94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>Purpurmusseron</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28374-2026 artfynd.xlsx", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26840-2026 artfynd.xlsx", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="X94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28374-2026 karta.png", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26840-2026 karta.png", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="Y94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28374-2026 georefererad karta.tif", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26840-2026 georefererad karta.tif", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="AA94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28374-2026 FSC-klagomål.docx", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26840-2026 FSC-klagomål.docx", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="AB94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28374-2026 FSC-klagomål mail.docx", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26840-2026 FSC-klagomål mail.docx", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="AC94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28374-2026 tillsynsbegäran.docx", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26840-2026 tillsynsbegäran.docx", "A 26840-2026")</f>
         <v/>
       </c>
       <c r="AD94">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28374-2026 tillsynsbegäran mail.docx", "A 28374-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26840-2026 tillsynsbegäran mail.docx", "A 26840-2026")</f>
         <v/>
       </c>
     </row>
@@ -11164,7 +11164,7 @@
         <v>46197</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 31720-2022</t>
+          <t>A 28374-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -11267,14 +11267,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44776</v>
+        <v>46196</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11292,19 +11292,19 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N96" t="n">
         <v>0</v>
@@ -11316,10 +11316,10 @@
         <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S96" t="n">
         <v>1</v>
@@ -11328,39 +11328,39 @@
         <v>1</v>
       </c>
       <c r="U96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Purpurmusseron</t>
         </is>
       </c>
       <c r="W96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31720-2022 artfynd.xlsx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 28374-2026 artfynd.xlsx", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="X96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31720-2022 karta.png", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 28374-2026 karta.png", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="Y96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31720-2022 georefererad karta.tif", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 28374-2026 georefererad karta.tif", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="AA96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31720-2022 FSC-klagomål.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 28374-2026 FSC-klagomål.docx", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="AB96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31720-2022 FSC-klagomål mail.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 28374-2026 FSC-klagomål mail.docx", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="AC96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31720-2022 tillsynsbegäran.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 28374-2026 tillsynsbegäran.docx", "A 28374-2026")</f>
         <v/>
       </c>
       <c r="AD96">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31720-2022 tillsynsbegäran mail.docx", "A 31720-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 28374-2026 tillsynsbegäran mail.docx", "A 28374-2026")</f>
         <v/>
       </c>
     </row>
@@ -11384,7 +11384,7 @@
         <v>45433</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 33293-2026</t>
+          <t>A 63276-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -11482,14 +11482,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46246</v>
+        <v>45273</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11501,25 +11501,20 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="J98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N98" t="n">
         <v>0</v>
@@ -11531,58 +11526,58 @@
         <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S98" t="n">
         <v>1</v>
       </c>
       <c r="T98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Elaphomyces barrioi</t>
         </is>
       </c>
       <c r="W98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 33293-2026 artfynd.xlsx", "A 33293-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 63276-2023 artfynd.xlsx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="X98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 33293-2026 karta.png", "A 33293-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 63276-2023 karta.png", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="Y98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 33293-2026 georefererad karta.tif", "A 33293-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 63276-2023 georefererad karta.tif", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AA98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 33293-2026 FSC-klagomål.docx", "A 33293-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 63276-2023 FSC-klagomål.docx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AB98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 33293-2026 FSC-klagomål mail.docx", "A 33293-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 63276-2023 FSC-klagomål mail.docx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AC98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 33293-2026 tillsynsbegäran.docx", "A 33293-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 63276-2023 tillsynsbegäran.docx", "A 63276-2023")</f>
         <v/>
       </c>
       <c r="AD98">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 33293-2026 tillsynsbegäran mail.docx", "A 33293-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 63276-2023 tillsynsbegäran mail.docx", "A 63276-2023")</f>
         <v/>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 13043-2024</t>
+          <t>A 33293-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -11592,14 +11587,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45385</v>
+        <v>46246</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11611,8 +11606,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="J99" t="n">
         <v>1</v>
@@ -11645,49 +11645,49 @@
         <v>1</v>
       </c>
       <c r="T99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
       </c>
       <c r="V99" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W99">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 13043-2024 artfynd.xlsx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 33293-2026 artfynd.xlsx", "A 33293-2026")</f>
         <v/>
       </c>
       <c r="X99">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 13043-2024 karta.png", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 33293-2026 karta.png", "A 33293-2026")</f>
         <v/>
       </c>
       <c r="Y99">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 13043-2024 georefererad karta.tif", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 33293-2026 georefererad karta.tif", "A 33293-2026")</f>
         <v/>
       </c>
       <c r="AA99">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 13043-2024 FSC-klagomål.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 33293-2026 FSC-klagomål.docx", "A 33293-2026")</f>
         <v/>
       </c>
       <c r="AB99">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 13043-2024 FSC-klagomål mail.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 33293-2026 FSC-klagomål mail.docx", "A 33293-2026")</f>
         <v/>
       </c>
       <c r="AC99">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 13043-2024 tillsynsbegäran.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 33293-2026 tillsynsbegäran.docx", "A 33293-2026")</f>
         <v/>
       </c>
       <c r="AD99">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 13043-2024 tillsynsbegäran mail.docx", "A 13043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 33293-2026 tillsynsbegäran mail.docx", "A 33293-2026")</f>
         <v/>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20878-2024</t>
+          <t>A 13043-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11701,10 +11701,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45439</v>
+        <v>45385</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11717,13 +11717,13 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J100" t="n">
         <v>1</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -11750,42 +11750,42 @@
         <v>1</v>
       </c>
       <c r="T100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
       </c>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W100">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 20878-2024 artfynd.xlsx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 13043-2024 artfynd.xlsx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="X100">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 20878-2024 karta.png", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 13043-2024 karta.png", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="Y100">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 20878-2024 georefererad karta.tif", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 13043-2024 georefererad karta.tif", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AA100">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 20878-2024 FSC-klagomål.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 13043-2024 FSC-klagomål.docx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AB100">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 20878-2024 FSC-klagomål mail.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 13043-2024 FSC-klagomål mail.docx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AC100">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 20878-2024 tillsynsbegäran.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 13043-2024 tillsynsbegäran.docx", "A 13043-2024")</f>
         <v/>
       </c>
       <c r="AD100">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 20878-2024 tillsynsbegäran mail.docx", "A 20878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 13043-2024 tillsynsbegäran mail.docx", "A 13043-2024")</f>
         <v/>
       </c>
     </row>
@@ -11809,7 +11809,7 @@
         <v>45111</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>45903</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>46185</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S 1803-2026</t>
+          <t>S 1813-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -12130,10 +12130,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12151,82 +12151,82 @@
         </is>
       </c>
       <c r="I104" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>1</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>1</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
+        <v>1</v>
+      </c>
+      <c r="T104" t="n">
         <v>2</v>
       </c>
-      <c r="J104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" t="n">
-        <v>1</v>
-      </c>
-      <c r="N104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>1</v>
-      </c>
-      <c r="R104" t="n">
-        <v>1</v>
-      </c>
-      <c r="S104" t="n">
-        <v>1</v>
-      </c>
-      <c r="T104" t="n">
-        <v>1</v>
-      </c>
       <c r="U104" t="n">
         <v>0</v>
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>Purpurmusseron</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="W104">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1803-2026 artfynd.xlsx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1813-2026 artfynd.xlsx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="X104">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1803-2026 karta.png", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1813-2026 karta.png", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="Y104">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1803-2026 georefererad karta.tif", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1813-2026 georefererad karta.tif", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AA104">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1803-2026 FSC-klagomål.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1813-2026 FSC-klagomål.docx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AB104">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1803-2026 FSC-klagomål mail.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1813-2026 FSC-klagomål mail.docx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AC104">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1803-2026 tillsynsbegäran.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1813-2026 tillsynsbegäran.docx", "S 1813-2026")</f>
         <v/>
       </c>
       <c r="AD104">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1803-2026 tillsynsbegäran mail.docx", "S 1803-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1813-2026 tillsynsbegäran mail.docx", "S 1813-2026")</f>
         <v/>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S 1813-2026</t>
+          <t>S 1803-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -12240,10 +12240,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -12270,10 +12270,10 @@
         <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N105" t="n">
         <v>0</v>
@@ -12288,48 +12288,48 @@
         <v>1</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S105" t="n">
         <v>1</v>
       </c>
       <c r="T105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
       </c>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Purpurmusseron</t>
         </is>
       </c>
       <c r="W105">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1813-2026 artfynd.xlsx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 1803-2026 artfynd.xlsx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="X105">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1813-2026 karta.png", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 1803-2026 karta.png", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="Y105">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1813-2026 georefererad karta.tif", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 1803-2026 georefererad karta.tif", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AA105">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1813-2026 FSC-klagomål.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 1803-2026 FSC-klagomål.docx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AB105">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1813-2026 FSC-klagomål mail.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 1803-2026 FSC-klagomål mail.docx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AC105">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1813-2026 tillsynsbegäran.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 1803-2026 tillsynsbegäran.docx", "S 1803-2026")</f>
         <v/>
       </c>
       <c r="AD105">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1813-2026 tillsynsbegäran mail.docx", "S 1813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 1803-2026 tillsynsbegäran mail.docx", "S 1803-2026")</f>
         <v/>
       </c>
     </row>
@@ -12353,7 +12353,7 @@
         <v>46246</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v>44783</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>44747</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>44840</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>44783</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>44501</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>44742</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>44503</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 3878-2023</t>
+          <t>A 31699-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12981,10 +12981,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44951</v>
+        <v>44776</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12996,8 +12996,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -13040,7 +13045,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 12937-2022</t>
+          <t>A 22785-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -13054,10 +13059,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44642</v>
+        <v>45789</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13069,13 +13074,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 26190-2025</t>
+          <t>A 26160-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -13128,14 +13128,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45805</v>
+        <v>45468</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -13187,11 +13187,35 @@
         <v>0</v>
       </c>
       <c r="V116" s="2" t="inlineStr"/>
+      <c r="X116">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26160-2024 karta.png", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="Y116">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26160-2024 georefererad karta.tif", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AA116">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26160-2024 FSC-klagomål.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AB116">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26160-2024 FSC-klagomål mail.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AC116">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26160-2024 tillsynsbegäran.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
+      <c r="AD116">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26160-2024 tillsynsbegäran mail.docx", "A 26160-2024")</f>
+        <v/>
+      </c>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 41950-2025</t>
+          <t>A 26190-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -13205,10 +13229,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45903</v>
+        <v>45805</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13221,7 +13245,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -13264,7 +13288,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 55367-2024</t>
+          <t>A 41950-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13278,10 +13302,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45621</v>
+        <v>45903</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13294,7 +13318,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -13354,7 +13378,7 @@
         <v>45923</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13427,7 +13451,7 @@
         <v>45928</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13483,7 +13507,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 9259-2026</t>
+          <t>A 4159-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -13497,10 +13521,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46070</v>
+        <v>45323</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13513,7 +13537,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -13556,7 +13580,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 4159-2024</t>
+          <t>A 36269-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -13570,10 +13594,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45323</v>
+        <v>45867</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13585,8 +13609,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -13629,7 +13658,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 15272-2026</t>
+          <t>A 4165-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -13639,14 +13668,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46105</v>
+        <v>44953</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13658,13 +13687,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -13707,7 +13731,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 15264-2026</t>
+          <t>A 32921-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -13717,14 +13741,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46105</v>
+        <v>45125</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13736,13 +13760,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -13785,7 +13804,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 32921-2023</t>
+          <t>A 9259-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -13799,10 +13818,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45125</v>
+        <v>46070</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13815,7 +13834,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -13858,7 +13877,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 31699-2022</t>
+          <t>A 15272-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -13868,14 +13887,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44776</v>
+        <v>46105</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13893,7 +13912,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -13936,7 +13955,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 1614-2025</t>
+          <t>A 15264-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -13946,14 +13965,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45670</v>
+        <v>46105</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13965,8 +13984,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -14009,7 +14033,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 36269-2025</t>
+          <t>A 43603-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -14023,10 +14047,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45867</v>
+        <v>45569</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14038,13 +14062,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -14087,7 +14106,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 9076-2025</t>
+          <t>A 63075-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -14097,14 +14116,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45713</v>
+        <v>45273</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14116,13 +14135,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -14182,7 +14196,7 @@
         <v>45671</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14238,7 +14252,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 27357-2025</t>
+          <t>A 34780-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -14248,14 +14262,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45812</v>
+        <v>44795</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14273,7 +14287,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -14316,7 +14330,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 9050-2025</t>
+          <t>A 55367-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -14326,14 +14340,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45713</v>
+        <v>45621</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14345,13 +14359,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -14394,7 +14403,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 7669-2024</t>
+          <t>A 20287-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -14404,14 +14413,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45348</v>
+        <v>45774</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14424,7 +14433,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -14467,7 +14476,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 24323-2026</t>
+          <t>A 9076-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -14481,10 +14490,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46169</v>
+        <v>45713</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14502,7 +14511,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -14545,7 +14554,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 43603-2024</t>
+          <t>A 27357-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -14555,14 +14564,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45569</v>
+        <v>45812</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14574,8 +14583,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -14618,7 +14632,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 28381-2026</t>
+          <t>A 7669-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -14628,14 +14642,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46196</v>
+        <v>45348</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14647,13 +14661,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -14696,7 +14705,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 28380-2026</t>
+          <t>A 32919-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -14706,14 +14715,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46196</v>
+        <v>45125</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14725,13 +14734,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -14774,7 +14778,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 28411-2026</t>
+          <t>A 24323-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -14784,14 +14788,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46197</v>
+        <v>46169</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14809,7 +14813,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -14852,7 +14856,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 29413-2026</t>
+          <t>A 34951-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -14866,10 +14870,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46203</v>
+        <v>44796</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14887,7 +14891,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -14930,7 +14934,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 29414-2026</t>
+          <t>A 5175-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -14940,14 +14944,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46203</v>
+        <v>45330</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14959,13 +14963,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -15008,7 +15007,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 29431-2026</t>
+          <t>A 28380-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -15022,10 +15021,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46203</v>
+        <v>46196</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15043,7 +15042,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -15086,7 +15085,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 29410-2026</t>
+          <t>A 3878-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -15096,14 +15095,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46203</v>
+        <v>44951</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15115,13 +15114,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -15164,7 +15158,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 32919-2023</t>
+          <t>A 28381-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -15174,14 +15168,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45125</v>
+        <v>46196</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15193,8 +15187,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -15237,7 +15236,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 5175-2024</t>
+          <t>A 28411-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -15247,14 +15246,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45330</v>
+        <v>46197</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15266,8 +15265,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -15310,7 +15314,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 34951-2022</t>
+          <t>A 29413-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -15324,10 +15328,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44796</v>
+        <v>46203</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15345,7 +15349,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -15388,7 +15392,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 13383-2023</t>
+          <t>A 29414-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -15398,14 +15402,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45005</v>
+        <v>46203</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15417,8 +15421,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -15461,7 +15470,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 61438-2023</t>
+          <t>A 29431-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -15471,14 +15480,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45264</v>
+        <v>46203</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15490,8 +15499,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -15534,7 +15548,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 13041-2024</t>
+          <t>A 29410-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -15544,14 +15558,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45385</v>
+        <v>46203</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15563,8 +15577,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -15607,7 +15626,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 4165-2023</t>
+          <t>A 13383-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -15621,10 +15640,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44953</v>
+        <v>45005</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15637,7 +15656,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -15680,7 +15699,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 24338-2026</t>
+          <t>A 12937-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -15690,14 +15709,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46169</v>
+        <v>44642</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15715,7 +15734,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -15758,7 +15777,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 34780-2022</t>
+          <t>A 61438-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -15768,14 +15787,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44795</v>
+        <v>45264</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15787,13 +15806,8 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>6.7</v>
+        <v>1.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -15836,7 +15850,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 20287-2025</t>
+          <t>A 13041-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -15846,14 +15860,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45774</v>
+        <v>45385</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15866,7 +15880,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -15909,7 +15923,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 26160-2024</t>
+          <t>A 1614-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -15919,14 +15933,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45468</v>
+        <v>45670</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15939,7 +15953,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -15978,35 +15992,11 @@
         <v>0</v>
       </c>
       <c r="V153" s="2" t="inlineStr"/>
-      <c r="X153">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26160-2024 karta.png", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="Y153">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26160-2024 georefererad karta.tif", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AA153">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26160-2024 FSC-klagomål.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AB153">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26160-2024 FSC-klagomål mail.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AC153">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26160-2024 tillsynsbegäran.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
-      <c r="AD153">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26160-2024 tillsynsbegäran mail.docx", "A 26160-2024")</f>
-        <v/>
-      </c>
     </row>
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 63075-2023</t>
+          <t>A 24338-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -16016,14 +16006,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45273</v>
+        <v>46169</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16033,6 +16023,11 @@
       <c r="G154" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I154" t="n">
@@ -16079,7 +16074,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 22785-2025</t>
+          <t>A 9050-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -16089,14 +16084,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45789</v>
+        <v>45713</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16108,8 +16103,13 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
         <v>44756</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>45713</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>45812</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45812</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>45754</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>46105</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>46105</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>46169</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>S 1806-2026</t>
+          <t>S 1812-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -16780,10 +16780,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S 1807-2026</t>
+          <t>S 1806-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -16861,7 +16861,7 @@
         <v>46196</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -16922,7 +16922,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S 1812-2026</t>
+          <t>S 1807-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -16936,10 +16936,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>46203</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>46203</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>46203</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>46203</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>

--- a/Översikt BORGHOLM.xlsx
+++ b/Översikt BORGHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45029</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>44704</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>45433</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>45029</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>44903</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45903</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>46254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>45918</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44809</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>46307</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45918</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>44523</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 29656-2023</t>
+          <t>A 32178-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2643,14 +2643,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45107</v>
+        <v>44781</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2662,11 +2662,16 @@
           <t>BORGHOLM</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
         <v>4</v>
@@ -2675,33 +2680,151 @@
         <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
       </c>
       <c r="T18" t="n">
+        <v>22</v>
+      </c>
+      <c r="U18" t="n">
+        <v>12</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Järnek
+Skogsalm
+Fyrflikig jordstjärna
+Grantaggsvamp
+Grönsångare
+Kalktallört
+Kamjordstjärna
+Skogsknipprot
+Tvåblad
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 32178-2022 artfynd.xlsx", "A 32178-2022")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 32178-2022 karta.png", "A 32178-2022")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 32178-2022 georefererad karta.tif", "A 32178-2022")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 32178-2022 FSC-klagomål.docx", "A 32178-2022")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 32178-2022 FSC-klagomål mail.docx", "A 32178-2022")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 32178-2022 tillsynsbegäran.docx", "A 32178-2022")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 32178-2022 tillsynsbegäran mail.docx", "A 32178-2022")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 32178-2022 prioriterade fågelarter.docx", "A 32178-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 29656-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45107</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="n">
         <v>15</v>
       </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Blå halmlav
 Klosterlav
@@ -2715,155 +2838,32 @@
 Tvåfläckig praktbagge</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 29656-2023 artfynd.xlsx", "A 29656-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 29656-2023 karta.png", "A 29656-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 29656-2023 georefererad karta.tif", "A 29656-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 29656-2023 FSC-klagomål.docx", "A 29656-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 29656-2023 FSC-klagomål mail.docx", "A 29656-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 29656-2023 tillsynsbegäran.docx", "A 29656-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 29656-2023 tillsynsbegäran mail.docx", "A 29656-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 32178-2022</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44781</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L19" t="n">
-        <v>3</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="n">
-        <v>22</v>
-      </c>
-      <c r="U19" t="n">
-        <v>12</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Järnek
-Skogsalm
-Fyrflikig jordstjärna
-Grantaggsvamp
-Grönsångare
-Kalktallört
-Kamjordstjärna
-Skogsknipprot
-Tvåblad
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 32178-2022 artfynd.xlsx", "A 32178-2022")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 32178-2022 karta.png", "A 32178-2022")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 32178-2022 georefererad karta.tif", "A 32178-2022")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 32178-2022 FSC-klagomål.docx", "A 32178-2022")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 32178-2022 FSC-klagomål mail.docx", "A 32178-2022")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 32178-2022 tillsynsbegäran.docx", "A 32178-2022")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 32178-2022 tillsynsbegäran mail.docx", "A 32178-2022")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 32178-2022 prioriterade fågelarter.docx", "A 32178-2022")</f>
         <v/>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
         <v>45161</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>45146</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>45930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 12534-2022</t>
+          <t>A 13558-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44638</v>
+        <v>45736</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3364,19 +3364,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>8.6</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3391,18 +3391,130 @@
         <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
       </c>
       <c r="T24" t="n">
+        <v>8</v>
+      </c>
+      <c r="U24" t="n">
+        <v>8</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Honungsblomster
+Backruta
+Jordtistel
+Stallört
+Ängsstarr
+Tvåblad
+Kärrknipprot
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 13558-2025 artfynd.xlsx", "A 13558-2025")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 13558-2025 karta.png", "A 13558-2025")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 13558-2025 georefererad karta.tif", "A 13558-2025")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 13558-2025 FSC-klagomål.docx", "A 13558-2025")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 13558-2025 FSC-klagomål mail.docx", "A 13558-2025")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 13558-2025 tillsynsbegäran.docx", "A 13558-2025")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 13558-2025 tillsynsbegäran mail.docx", "A 13558-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 12534-2022</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>44638</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>5</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>8</v>
+      </c>
+      <c r="T25" t="n">
         <v>9</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>9</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Backklöver
 Backtimjan
@@ -3414,151 +3526,39 @@
 Sankt pers nycklar</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 12534-2022 artfynd.xlsx", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 12534-2022 karta.png", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 12534-2022 georefererad karta.tif", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 12534-2022 FSC-klagomål.docx", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 12534-2022 FSC-klagomål mail.docx", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 12534-2022 tillsynsbegäran.docx", "A 12534-2022")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 12534-2022 tillsynsbegäran mail.docx", "A 12534-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 13558-2025</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45736</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J25" t="n">
-        <v>4</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>4</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>8</v>
-      </c>
-      <c r="T25" t="n">
-        <v>8</v>
-      </c>
-      <c r="U25" t="n">
-        <v>8</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Honungsblomster
-Backruta
-Jordtistel
-Stallört
-Ängsstarr
-Tvåblad
-Kärrknipprot
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 13558-2025 artfynd.xlsx", "A 13558-2025")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 13558-2025 karta.png", "A 13558-2025")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 13558-2025 georefererad karta.tif", "A 13558-2025")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 13558-2025 FSC-klagomål.docx", "A 13558-2025")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 13558-2025 FSC-klagomål mail.docx", "A 13558-2025")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 13558-2025 tillsynsbegäran.docx", "A 13558-2025")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 13558-2025 tillsynsbegäran mail.docx", "A 13558-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 31515-2026</t>
+          <t>A 31399-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3568,14 +3568,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46223</v>
+        <v>46220</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3587,19 +3587,14 @@
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
         <v>3</v>
@@ -3626,12 +3621,129 @@
         <v>8</v>
       </c>
       <c r="T26" t="n">
+        <v>8</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Backklöver
+Jordtistel
+Stallört
+Flugblomster
+Tvåblad
+Grönvit nattviol
+Krutbrännare
+Vanliga ängsnycklar</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31399-2026 artfynd.xlsx", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31399-2026 karta.png", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31399-2026 georefererad karta.tif", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31399-2026 FSC-klagomål.docx", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31399-2026 FSC-klagomål mail.docx", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31399-2026 tillsynsbegäran.docx", "A 31399-2026")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31399-2026 tillsynsbegäran mail.docx", "A 31399-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 31515-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>8</v>
+      </c>
+      <c r="T27" t="n">
         <v>11</v>
       </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Blå slemspindling
 Sårläka
@@ -3643,112 +3755,112 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31515-2026 artfynd.xlsx", "A 31515-2026")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31515-2026 karta.png", "A 31515-2026")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31515-2026 georefererad karta.tif", "A 31515-2026")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31515-2026 FSC-klagomål.docx", "A 31515-2026")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31515-2026 FSC-klagomål mail.docx", "A 31515-2026")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31515-2026 tillsynsbegäran.docx", "A 31515-2026")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31515-2026 tillsynsbegäran mail.docx", "A 31515-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>A 31516-2026</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D27" s="1" t="n">
+      <c r="D28" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="E27" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="E28" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I27" t="n">
+      <c r="I28" t="n">
         <v>0.8</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J28" t="n">
         <v>3</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K28" t="n">
         <v>3</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L28" t="n">
         <v>3</v>
       </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
         <v>3</v>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>8</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T28" t="n">
         <v>11</v>
       </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Blå slemspindling
 Sårläka
@@ -3760,144 +3872,32 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31516-2026 artfynd.xlsx", "A 31516-2026")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31516-2026 karta.png", "A 31516-2026")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31516-2026 georefererad karta.tif", "A 31516-2026")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31516-2026 FSC-klagomål.docx", "A 31516-2026")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31516-2026 FSC-klagomål mail.docx", "A 31516-2026")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31516-2026 tillsynsbegäran.docx", "A 31516-2026")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31516-2026 tillsynsbegäran mail.docx", "A 31516-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 31399-2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J28" t="n">
-        <v>5</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" t="n">
-        <v>3</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>8</v>
-      </c>
-      <c r="T28" t="n">
-        <v>8</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Backklöver
-Jordtistel
-Stallört
-Flugblomster
-Tvåblad
-Grönvit nattviol
-Krutbrännare
-Vanliga ängsnycklar</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31399-2026 artfynd.xlsx", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31399-2026 karta.png", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31399-2026 georefererad karta.tif", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31399-2026 FSC-klagomål.docx", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31399-2026 FSC-klagomål mail.docx", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31399-2026 tillsynsbegäran.docx", "A 31399-2026")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31399-2026 tillsynsbegäran mail.docx", "A 31399-2026")</f>
         <v/>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
         <v>44704</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>45175</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 16171-2023</t>
+          <t>A 46794-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4371,14 +4371,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45027</v>
+        <v>45926</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4391,13 +4391,13 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>12.2</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L33" t="n">
         <v>2</v>
@@ -4424,12 +4424,122 @@
         <v>6</v>
       </c>
       <c r="T33" t="n">
+        <v>10</v>
+      </c>
+      <c r="U33" t="n">
+        <v>9</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Mindre ekbock
+Sårläka
+Murgröna
+Myskmadra
+Vit skogslilja
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 46794-2025 artfynd.xlsx", "A 46794-2025")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 46794-2025 karta.png", "A 46794-2025")</f>
+        <v/>
+      </c>
+      <c r="Y33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 46794-2025 georefererad karta.tif", "A 46794-2025")</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 46794-2025 FSC-klagomål.docx", "A 46794-2025")</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 46794-2025 FSC-klagomål mail.docx", "A 46794-2025")</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 46794-2025 tillsynsbegäran.docx", "A 46794-2025")</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 46794-2025 tillsynsbegäran mail.docx", "A 46794-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A 16171-2023</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>45027</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>2</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>6</v>
+      </c>
+      <c r="T34" t="n">
         <v>7</v>
       </c>
-      <c r="U33" t="n">
+      <c r="U34" t="n">
         <v>6</v>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Sårläka
 Älg
@@ -4439,142 +4549,32 @@
 Bredarun</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 16171-2023 artfynd.xlsx", "A 16171-2023")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 16171-2023 karta.png", "A 16171-2023")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 16171-2023 georefererad karta.tif", "A 16171-2023")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 16171-2023 FSC-klagomål.docx", "A 16171-2023")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 16171-2023 FSC-klagomål mail.docx", "A 16171-2023")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 16171-2023 tillsynsbegäran.docx", "A 16171-2023")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 16171-2023 tillsynsbegäran mail.docx", "A 16171-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 46794-2025</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>45926</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" t="n">
-        <v>3</v>
-      </c>
-      <c r="L34" t="n">
-        <v>2</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>6</v>
-      </c>
-      <c r="T34" t="n">
-        <v>10</v>
-      </c>
-      <c r="U34" t="n">
-        <v>9</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Mindre ekbock
-Sårläka
-Murgröna
-Myskmadra
-Vit skogslilja
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 46794-2025 artfynd.xlsx", "A 46794-2025")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 46794-2025 karta.png", "A 46794-2025")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 46794-2025 georefererad karta.tif", "A 46794-2025")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 46794-2025 FSC-klagomål.docx", "A 46794-2025")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 46794-2025 FSC-klagomål mail.docx", "A 46794-2025")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 46794-2025 tillsynsbegäran.docx", "A 46794-2025")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 46794-2025 tillsynsbegäran mail.docx", "A 46794-2025")</f>
         <v/>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
         <v>46188</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>46224</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>44704</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45478</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>46188</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>46224</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>46169</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>46169</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>45736</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45280</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 21797-2024</t>
+          <t>A 4164-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45442</v>
+        <v>44953</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5735,31 +5735,31 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
         <v>2</v>
       </c>
-      <c r="K45" t="n">
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
         <v>2</v>
-      </c>
-      <c r="L45" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5768,12 +5768,120 @@
         <v>4</v>
       </c>
       <c r="T45" t="n">
+        <v>5</v>
+      </c>
+      <c r="U45" t="n">
+        <v>4</v>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>Crepis tectorum subsp. tectorum
+Kösa
+Murgröna
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 4164-2023 artfynd.xlsx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="X45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 4164-2023 karta.png", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="Y45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 4164-2023 georefererad karta.tif", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AA45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 4164-2023 FSC-klagomål.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AB45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 4164-2023 FSC-klagomål mail.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AC45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 4164-2023 tillsynsbegäran.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+      <c r="AD45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 4164-2023 tillsynsbegäran mail.docx", "A 4164-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A 21797-2024</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>45442</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>4</v>
+      </c>
+      <c r="T46" t="n">
         <v>11</v>
       </c>
-      <c r="U45" t="n">
+      <c r="U46" t="n">
         <v>6</v>
       </c>
-      <c r="V45" s="2" t="inlineStr">
+      <c r="V46" s="2" t="inlineStr">
         <is>
           <t>Sydlig kantmusseron
 Murgröna
@@ -5781,112 +5889,112 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W45">
+      <c r="W46">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 21797-2024 artfynd.xlsx", "A 21797-2024")</f>
         <v/>
       </c>
-      <c r="X45">
+      <c r="X46">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 21797-2024 karta.png", "A 21797-2024")</f>
         <v/>
       </c>
-      <c r="Y45">
+      <c r="Y46">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 21797-2024 georefererad karta.tif", "A 21797-2024")</f>
         <v/>
       </c>
-      <c r="AA45">
+      <c r="AA46">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 21797-2024 FSC-klagomål.docx", "A 21797-2024")</f>
         <v/>
       </c>
-      <c r="AB45">
+      <c r="AB46">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 21797-2024 FSC-klagomål mail.docx", "A 21797-2024")</f>
         <v/>
       </c>
-      <c r="AC45">
+      <c r="AC46">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 21797-2024 tillsynsbegäran.docx", "A 21797-2024")</f>
         <v/>
       </c>
-      <c r="AD45">
+      <c r="AD46">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 21797-2024 tillsynsbegäran mail.docx", "A 21797-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>A 27290-2026</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D46" s="1" t="n">
+      <c r="D47" s="1" t="n">
         <v>46188</v>
       </c>
-      <c r="E46" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F46" t="inlineStr">
+      <c r="E47" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I46" t="n">
+      <c r="I47" t="n">
         <v>4.1</v>
       </c>
-      <c r="J46" t="n">
+      <c r="J47" t="n">
         <v>2</v>
       </c>
-      <c r="K46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>1</v>
-      </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
         <v>2</v>
       </c>
-      <c r="R46" t="n">
+      <c r="R47" t="n">
         <v>2</v>
       </c>
-      <c r="S46" t="n">
+      <c r="S47" t="n">
         <v>4</v>
       </c>
-      <c r="T46" t="n">
+      <c r="T47" t="n">
         <v>4</v>
       </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
         <is>
           <t>Ask
 Gotlandsmåra
@@ -5894,144 +6002,36 @@
 Havsörn</t>
         </is>
       </c>
-      <c r="W46">
+      <c r="W47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27290-2026 artfynd.xlsx", "A 27290-2026")</f>
         <v/>
       </c>
-      <c r="X46">
+      <c r="X47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27290-2026 karta.png", "A 27290-2026")</f>
         <v/>
       </c>
-      <c r="Y46">
+      <c r="Y47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27290-2026 georefererad karta.tif", "A 27290-2026")</f>
         <v/>
       </c>
-      <c r="AA46">
+      <c r="AA47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27290-2026 FSC-klagomål.docx", "A 27290-2026")</f>
         <v/>
       </c>
-      <c r="AB46">
+      <c r="AB47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27290-2026 FSC-klagomål mail.docx", "A 27290-2026")</f>
         <v/>
       </c>
-      <c r="AC46">
+      <c r="AC47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27290-2026 tillsynsbegäran.docx", "A 27290-2026")</f>
         <v/>
       </c>
-      <c r="AD46">
+      <c r="AD47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27290-2026 tillsynsbegäran mail.docx", "A 27290-2026")</f>
         <v/>
       </c>
-      <c r="AE46">
+      <c r="AE47">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 27290-2026 prioriterade fågelarter.docx", "A 27290-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>A 4164-2023</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>44953</v>
-      </c>
-      <c r="E47" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J47" t="n">
-        <v>1</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" t="n">
-        <v>2</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>2</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>4</v>
-      </c>
-      <c r="T47" t="n">
-        <v>5</v>
-      </c>
-      <c r="U47" t="n">
-        <v>4</v>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>Crepis tectorum subsp. tectorum
-Kösa
-Murgröna
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 4164-2023 artfynd.xlsx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 4164-2023 karta.png", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 4164-2023 georefererad karta.tif", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 4164-2023 FSC-klagomål.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 4164-2023 FSC-klagomål mail.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 4164-2023 tillsynsbegäran.docx", "A 4164-2023")</f>
-        <v/>
-      </c>
-      <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 4164-2023 tillsynsbegäran mail.docx", "A 4164-2023")</f>
         <v/>
       </c>
     </row>
@@ -6055,7 +6055,7 @@
         <v>44973</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>44704</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>44704</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>44783</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 24048-2025</t>
+          <t>A 38860-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45796</v>
+        <v>45887</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6504,22 +6504,22 @@
         </is>
       </c>
       <c r="I52" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J52" t="n">
         <v>2</v>
       </c>
-      <c r="J52" t="n">
-        <v>1</v>
-      </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6528,1256 +6528,1256 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
       </c>
       <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsknipprot
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 38860-2025 artfynd.xlsx", "A 38860-2025")</f>
+        <v/>
+      </c>
+      <c r="X52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 38860-2025 karta.png", "A 38860-2025")</f>
+        <v/>
+      </c>
+      <c r="Y52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 38860-2025 georefererad karta.tif", "A 38860-2025")</f>
+        <v/>
+      </c>
+      <c r="AA52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 38860-2025 FSC-klagomål.docx", "A 38860-2025")</f>
+        <v/>
+      </c>
+      <c r="AB52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 38860-2025 FSC-klagomål mail.docx", "A 38860-2025")</f>
+        <v/>
+      </c>
+      <c r="AC52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 38860-2025 tillsynsbegäran.docx", "A 38860-2025")</f>
+        <v/>
+      </c>
+      <c r="AD52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 38860-2025 tillsynsbegäran mail.docx", "A 38860-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>A 43542-2025</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>45911</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>2</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>3</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>Vårärt
+Ängsskära
+Underviol</t>
+        </is>
+      </c>
+      <c r="W53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 43542-2025 artfynd.xlsx", "A 43542-2025")</f>
+        <v/>
+      </c>
+      <c r="X53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 43542-2025 karta.png", "A 43542-2025")</f>
+        <v/>
+      </c>
+      <c r="Y53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 43542-2025 georefererad karta.tif", "A 43542-2025")</f>
+        <v/>
+      </c>
+      <c r="AA53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 43542-2025 FSC-klagomål.docx", "A 43542-2025")</f>
+        <v/>
+      </c>
+      <c r="AB53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 43542-2025 FSC-klagomål mail.docx", "A 43542-2025")</f>
+        <v/>
+      </c>
+      <c r="AC53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 43542-2025 tillsynsbegäran.docx", "A 43542-2025")</f>
+        <v/>
+      </c>
+      <c r="AD53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 43542-2025 tillsynsbegäran mail.docx", "A 43542-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>A 27283-2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>2</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" t="n">
+        <v>3</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Mindre poppelglasvinge
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 27283-2026 artfynd.xlsx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="X54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 27283-2026 karta.png", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="Y54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 27283-2026 georefererad karta.tif", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AA54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 27283-2026 FSC-klagomål.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AB54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 27283-2026 FSC-klagomål mail.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AC54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 27283-2026 tillsynsbegäran.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+      <c r="AD54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 27283-2026 tillsynsbegäran mail.docx", "A 27283-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>A 26849-2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>3</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>Myskmadra
+Purpurknipprot
+Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="W55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26849-2026 artfynd.xlsx", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="X55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26849-2026 karta.png", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="Y55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26849-2026 georefererad karta.tif", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="AA55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26849-2026 FSC-klagomål.docx", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="AB55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26849-2026 FSC-klagomål mail.docx", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="AC55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26849-2026 tillsynsbegäran.docx", "A 26849-2026")</f>
+        <v/>
+      </c>
+      <c r="AD55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26849-2026 tillsynsbegäran mail.docx", "A 26849-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>A 24048-2025</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>45796</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>2</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>2</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>3</v>
+      </c>
+      <c r="T56" t="n">
         <v>5</v>
       </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
         <is>
           <t>Loppstarr
 Ängsstarr
 Kärrknipprot</t>
         </is>
       </c>
-      <c r="W52">
+      <c r="W56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 24048-2025 artfynd.xlsx", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="X52">
+      <c r="X56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 24048-2025 karta.png", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="Y52">
+      <c r="Y56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 24048-2025 georefererad karta.tif", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="AA52">
+      <c r="AA56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 24048-2025 FSC-klagomål.docx", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="AB52">
+      <c r="AB56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 24048-2025 FSC-klagomål mail.docx", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="AC52">
+      <c r="AC56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 24048-2025 tillsynsbegäran.docx", "A 24048-2025")</f>
         <v/>
       </c>
-      <c r="AD52">
+      <c r="AD56">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 24048-2025 tillsynsbegäran mail.docx", "A 24048-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>A 38860-2025</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>A 15285-2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="n">
-        <v>45887</v>
-      </c>
-      <c r="E53" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F53" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J53" t="n">
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Havsörn
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 15285-2026 artfynd.xlsx", "A 15285-2026")</f>
+        <v/>
+      </c>
+      <c r="X57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 15285-2026 karta.png", "A 15285-2026")</f>
+        <v/>
+      </c>
+      <c r="Y57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 15285-2026 georefererad karta.tif", "A 15285-2026")</f>
+        <v/>
+      </c>
+      <c r="AA57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 15285-2026 FSC-klagomål.docx", "A 15285-2026")</f>
+        <v/>
+      </c>
+      <c r="AB57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 15285-2026 FSC-klagomål mail.docx", "A 15285-2026")</f>
+        <v/>
+      </c>
+      <c r="AC57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 15285-2026 tillsynsbegäran.docx", "A 15285-2026")</f>
+        <v/>
+      </c>
+      <c r="AD57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 15285-2026 tillsynsbegäran mail.docx", "A 15285-2026")</f>
+        <v/>
+      </c>
+      <c r="AE57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 15285-2026 prioriterade fågelarter.docx", "A 15285-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>A 31520-2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Grönsiska
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 31520-2026 artfynd.xlsx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="X58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 31520-2026 karta.png", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 31520-2026 georefererad karta.tif", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 31520-2026 FSC-klagomål.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 31520-2026 FSC-klagomål mail.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 31520-2026 tillsynsbegäran.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 31520-2026 tillsynsbegäran mail.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+      <c r="AE58">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 31520-2026 prioriterade fågelarter.docx", "A 31520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>A 32174-2022</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>44781</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J59" t="n">
         <v>2</v>
       </c>
-      <c r="K53" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>1</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>1</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1</v>
-      </c>
-      <c r="S53" t="n">
+      <c r="K59" t="n">
+        <v>2</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
         <v>3</v>
       </c>
-      <c r="T53" t="n">
+      <c r="T59" t="n">
         <v>3</v>
       </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsknipprot
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 38860-2025 artfynd.xlsx", "A 38860-2025")</f>
-        <v/>
-      </c>
-      <c r="X53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 38860-2025 karta.png", "A 38860-2025")</f>
-        <v/>
-      </c>
-      <c r="Y53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 38860-2025 georefererad karta.tif", "A 38860-2025")</f>
-        <v/>
-      </c>
-      <c r="AA53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 38860-2025 FSC-klagomål.docx", "A 38860-2025")</f>
-        <v/>
-      </c>
-      <c r="AB53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 38860-2025 FSC-klagomål mail.docx", "A 38860-2025")</f>
-        <v/>
-      </c>
-      <c r="AC53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 38860-2025 tillsynsbegäran.docx", "A 38860-2025")</f>
-        <v/>
-      </c>
-      <c r="AD53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 38860-2025 tillsynsbegäran mail.docx", "A 38860-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>A 43542-2025</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="n">
-        <v>45911</v>
-      </c>
-      <c r="E54" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1</v>
-      </c>
-      <c r="L54" t="n">
-        <v>2</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>2</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
+      <c r="U59" t="n">
         <v>3</v>
       </c>
-      <c r="T54" t="n">
-        <v>3</v>
-      </c>
-      <c r="U54" t="n">
-        <v>3</v>
-      </c>
-      <c r="V54" s="2" t="inlineStr">
-        <is>
-          <t>Vårärt
-Ängsskära
-Underviol</t>
-        </is>
-      </c>
-      <c r="W54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 43542-2025 artfynd.xlsx", "A 43542-2025")</f>
-        <v/>
-      </c>
-      <c r="X54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 43542-2025 karta.png", "A 43542-2025")</f>
-        <v/>
-      </c>
-      <c r="Y54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 43542-2025 georefererad karta.tif", "A 43542-2025")</f>
-        <v/>
-      </c>
-      <c r="AA54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 43542-2025 FSC-klagomål.docx", "A 43542-2025")</f>
-        <v/>
-      </c>
-      <c r="AB54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 43542-2025 FSC-klagomål mail.docx", "A 43542-2025")</f>
-        <v/>
-      </c>
-      <c r="AC54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 43542-2025 tillsynsbegäran.docx", "A 43542-2025")</f>
-        <v/>
-      </c>
-      <c r="AD54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 43542-2025 tillsynsbegäran mail.docx", "A 43542-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>A 32174-2022</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D55" s="1" t="n">
-        <v>44781</v>
-      </c>
-      <c r="E55" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>BORGHOLM</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J55" t="n">
-        <v>2</v>
-      </c>
-      <c r="K55" t="n">
-        <v>2</v>
-      </c>
-      <c r="L55" t="n">
-        <v>1</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>1</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>3</v>
-      </c>
-      <c r="T55" t="n">
-        <v>3</v>
-      </c>
-      <c r="U55" t="n">
-        <v>3</v>
-      </c>
-      <c r="V55" s="2" t="inlineStr">
+      <c r="V59" s="2" t="inlineStr">
         <is>
           <t>Backklöver
 Tvåblad
 Vit skogslilja</t>
         </is>
       </c>
-      <c r="W55">
+      <c r="W59">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 32174-2022 artfynd.xlsx", "A 32174-2022")</f>
         <v/>
       </c>
-      <c r="X55">
+      <c r="X59">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 32174-2022 karta.png", "A 32174-2022")</f>
         <v/>
       </c>
-      <c r="Y55">
+      <c r="Y59">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 32174-2022 georefererad karta.tif", "A 32174-2022")</f>
         <v/>
       </c>
-      <c r="AA55">
+      <c r="AA59">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 32174-2022 FSC-klagomål.docx", "A 32174-2022")</f>
         <v/>
       </c>
-      <c r="AB55">
+      <c r="AB59">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 32174-2022 FSC-klagomål mail.docx", "A 32174-2022")</f>
         <v/>
       </c>
-      <c r="AC55">
+      <c r="AC59">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 32174-2022 tillsynsbegäran.docx", "A 32174-2022")</f>
         <v/>
       </c>
-      <c r="AD55">
+      <c r="AD59">
         <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 32174-2022 tillsynsbegäran mail.docx", "A 32174-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>A 15285-2026</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>A 43756-2022</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="n">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>44837</v>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>BORGHOLM</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>3</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>5</v>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>Murgröna
+Blåsippa
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 43756-2022 artfynd.xlsx", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="X60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 43756-2022 karta.png", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="Y60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 43756-2022 georefererad karta.tif", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="AA60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 43756-2022 FSC-klagomål.docx", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="AB60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 43756-2022 FSC-klagomål mail.docx", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="AC60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 43756-2022 tillsynsbegäran.docx", "A 43756-2022")</f>
+        <v/>
+      </c>
+      <c r="AD60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 43756-2022 tillsynsbegäran mail.docx", "A 43756-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>S 846-2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="n">
         <v>46105</v>
       </c>
-      <c r="E56" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F56" t="inlineStr">
+      <c r="E61" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I56" t="n">
+      <c r="I61" t="n">
         <v>1.7</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J61" t="n">
         <v>3</v>
       </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>1</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>1</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
         <v>3</v>
       </c>
-      <c r="T56" t="n">
+      <c r="T61" t="n">
         <v>3</v>
       </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" s="2" t="inlineStr">
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Havsörn
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 15285-2026 artfynd.xlsx", "A 15285-2026")</f>
-        <v/>
-      </c>
-      <c r="X56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 15285-2026 karta.png", "A 15285-2026")</f>
-        <v/>
-      </c>
-      <c r="Y56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 15285-2026 georefererad karta.tif", "A 15285-2026")</f>
-        <v/>
-      </c>
-      <c r="AA56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 15285-2026 FSC-klagomål.docx", "A 15285-2026")</f>
-        <v/>
-      </c>
-      <c r="AB56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 15285-2026 FSC-klagomål mail.docx", "A 15285-2026")</f>
-        <v/>
-      </c>
-      <c r="AC56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 15285-2026 tillsynsbegäran.docx", "A 15285-2026")</f>
-        <v/>
-      </c>
-      <c r="AD56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 15285-2026 tillsynsbegäran mail.docx", "A 15285-2026")</f>
-        <v/>
-      </c>
-      <c r="AE56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/A 15285-2026 prioriterade fågelarter.docx", "A 15285-2026")</f>
+      <c r="W61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/S 846-2026 artfynd.xlsx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="X61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/S 846-2026 karta.png", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="Y61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/S 846-2026 georefererad karta.tif", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AA61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/S 846-2026 FSC-klagomål.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AB61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/S 846-2026 FSC-klagomål mail.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AC61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/S 846-2026 tillsynsbegäran.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AD61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/S 846-2026 tillsynsbegäran mail.docx", "S 846-2026")</f>
+        <v/>
+      </c>
+      <c r="AE61">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0885/fåglar/S 846-2026 prioriterade fågelarter.docx", "S 846-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>A 26849-2026</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="n">
-        <v>46185</v>
-      </c>
-      <c r="E57" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F57" t="inlineStr">
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>S 1726-2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E62" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>BORGHOLM</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I57" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J57" t="n">
+      <c r="I62" t="n">
         <v>2</v>
       </c>
-      <c r="K57" t="n">
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>2</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1</v>
+      </c>
+      <c r="S62" t="n">
         <v>3</v>
       </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
+      <c r="T62" t="n">
         <v>3</v>
       </c>
-      <c r="T57" t="n">
-        <v>3</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" s="2" t="inlineStr">
-        <is>
-          <t>Myskmadra
-Purpurknipprot
-Vit skogslilja</t>
-        </is>
-      </c>
-      <c r="W57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/artfynd/A 26849-2026 artfynd.xlsx", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="X57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor/A 26849-2026 karta.png", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="Y57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/kartor_geotiff/A 26849-2026 georefererad karta.tif", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="AA57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomål/A 26849-2026 FSC-klagomål.docx", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="AB57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/klagomålsmail/A 26849-2026 FSC-klagomål mail.docx", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="AC57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsyn/A 26849-2026 tillsynsbegäran.docx", "A 26849-2026")</f>
-        <v/>
-      </c>
-      <c r="AD57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0885/tillsynsmail/A 26849-2026 tillsynsbegäran mail.docx", "A 26849-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>A 27283-2026</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c 